--- a/planilhas/equipment_processado.xlsx
+++ b/planilhas/equipment_processado.xlsx
@@ -528,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>71.61840000007436</v>
+        <v>71.2610995689099</v>
       </c>
       <c r="K2" t="n">
-        <v>-101.7373978435884</v>
+        <v>-101.7379132139436</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -576,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>90.14039999930736</v>
+        <v>89.69069428422497</v>
       </c>
       <c r="K3" t="n">
-        <v>-101.4286348733132</v>
+        <v>-101.4291486795703</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>98.4752999993373</v>
+        <v>97.98401190648997</v>
       </c>
       <c r="K4" t="n">
-        <v>-128.2910130495196</v>
+        <v>-128.2916629323196</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -672,10 +672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J5" t="n">
-        <v>75.63149999992793</v>
+        <v>75.25417842391448</v>
       </c>
       <c r="K5" t="n">
-        <v>-48.01264146748147</v>
+        <v>-48.01288468475079</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J6" t="n">
-        <v>80.26199999919329</v>
+        <v>79.86157710220309</v>
       </c>
       <c r="K6" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J7" t="n">
-        <v>84.89249999954443</v>
+        <v>84.46897578157201</v>
       </c>
       <c r="K7" t="n">
-        <v>-48.01264146748147</v>
+        <v>-48.01288468475079</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J8" t="n">
-        <v>75.01409999943036</v>
+        <v>74.63985859955012</v>
       </c>
       <c r="K8" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J9" t="n">
-        <v>84.27510000018196</v>
+        <v>83.8546559583371</v>
       </c>
       <c r="K9" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J10" t="n">
-        <v>62.04870000018441</v>
+        <v>61.73914229904563</v>
       </c>
       <c r="K10" t="n">
-        <v>-112.85286466687</v>
+        <v>-112.8534363447602</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J11" t="n">
-        <v>73.47059999929687</v>
+        <v>73.1040590397441</v>
       </c>
       <c r="K11" t="n">
-        <v>-113.1616276371451</v>
+        <v>-113.1622008791336</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J12" t="n">
-        <v>85.20119999981789</v>
+        <v>84.77613569377876</v>
       </c>
       <c r="K12" t="n">
-        <v>-113.1616276371451</v>
+        <v>-113.1622008791336</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J13" t="n">
-        <v>97.24049999942791</v>
+        <v>96.75537225884159</v>
       </c>
       <c r="K13" t="n">
-        <v>-112.85286466687</v>
+        <v>-112.8534363447602</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J14" t="n">
-        <v>66.67919999944978</v>
+        <v>66.34654097733423</v>
       </c>
       <c r="K14" t="n">
-        <v>-101.4286348733132</v>
+        <v>-101.4291486795703</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J15" t="n">
-        <v>73.47059999929687</v>
+        <v>73.1040590397441</v>
       </c>
       <c r="K15" t="n">
-        <v>-103.28121267127</v>
+        <v>-103.2817358621162</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J16" t="n">
-        <v>85.81859999918035</v>
+        <v>85.39045551701368</v>
       </c>
       <c r="K16" t="n">
-        <v>-103.28121267127</v>
+        <v>-103.2817358621162</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J17" t="n">
-        <v>96.93180000028956</v>
+        <v>96.4482123477643</v>
       </c>
       <c r="K17" t="n">
-        <v>-103.28121267127</v>
+        <v>-103.2817358621162</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J18" t="n">
-        <v>66.37049999917632</v>
+        <v>66.0393810651275</v>
       </c>
       <c r="K18" t="n">
-        <v>-89.38687912814896</v>
+        <v>-89.38733193457641</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J19" t="n">
-        <v>77.79239999942388</v>
+        <v>77.40429780695541</v>
       </c>
       <c r="K19" t="n">
-        <v>-91.85698287771322</v>
+        <v>-91.85744819692626</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J20" t="n">
-        <v>89.5229999999449</v>
+        <v>89.07637446099007</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.85698287771322</v>
+        <v>-91.85744819692626</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J21" t="n">
-        <v>97.24049999942791</v>
+        <v>96.75537225884159</v>
       </c>
       <c r="K21" t="n">
-        <v>-91.85698287771322</v>
+        <v>-91.85744819692626</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J22" t="n">
-        <v>81.49680000018843</v>
+        <v>81.0902167509318</v>
       </c>
       <c r="K22" t="n">
-        <v>-81.35904197207762</v>
+        <v>-81.35945411195199</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J23" t="n">
-        <v>89.5229999999449</v>
+        <v>89.07637446099007</v>
       </c>
       <c r="K23" t="n">
-        <v>-81.35904197207762</v>
+        <v>-81.35945411195199</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J24" t="n">
-        <v>97.24049999942791</v>
+        <v>96.75537225884159</v>
       </c>
       <c r="K24" t="n">
-        <v>-81.35904197207762</v>
+        <v>-81.35945411195199</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J25" t="n">
-        <v>81.80549999932678</v>
+        <v>81.39737666200909</v>
       </c>
       <c r="K25" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J26" t="n">
-        <v>89.21429999967144</v>
+        <v>88.76921454878332</v>
       </c>
       <c r="K26" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J27" t="n">
-        <v>96.93180000028956</v>
+        <v>96.4482123477643</v>
       </c>
       <c r="K27" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J28" t="n">
-        <v>75.32279999970382</v>
+        <v>74.94701851175685</v>
       </c>
       <c r="K28" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J29" t="n">
-        <v>79.95330000005494</v>
+        <v>79.55441719112579</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J30" t="n">
-        <v>84.89249999954443</v>
+        <v>84.46897578157201</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.60233024090317</v>
+        <v>-40.60253591981579</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J31" t="n">
-        <v>89.83170000016901</v>
+        <v>89.3835343731477</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J32" t="n">
-        <v>96.62310000006545</v>
+        <v>96.14105243560667</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.60233024090317</v>
+        <v>-40.60253591981579</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J33" t="n">
-        <v>75.01409999943036</v>
+        <v>74.63985859955012</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J34" t="n">
-        <v>79.64459999983083</v>
+        <v>79.24725727896816</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J35" t="n">
-        <v>84.58379999932032</v>
+        <v>84.1618158694144</v>
       </c>
       <c r="K35" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J36" t="n">
-        <v>89.5229999999449</v>
+        <v>89.07637446099007</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J37" t="n">
-        <v>93.84480000007191</v>
+        <v>93.37661322820138</v>
       </c>
       <c r="K37" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J38" t="n">
-        <v>98.4752999993373</v>
+        <v>97.98401190648997</v>
       </c>
       <c r="K38" t="n">
-        <v>-30.72191528687506</v>
+        <v>-30.7220709146455</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J39" t="n">
-        <v>103.1057999996884</v>
+        <v>102.5914105858589</v>
       </c>
       <c r="K39" t="n">
-        <v>-30.72191528687506</v>
+        <v>-30.7220709146455</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J40" t="n">
-        <v>74.705400000292</v>
+        <v>74.33269868847283</v>
       </c>
       <c r="K40" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J41" t="n">
-        <v>84.27510000018196</v>
+        <v>83.8546559583371</v>
       </c>
       <c r="K41" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J42" t="n">
-        <v>93.53609999979845</v>
+        <v>93.06945331599464</v>
       </c>
       <c r="K42" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J43" t="n">
-        <v>74.705400000292</v>
+        <v>74.33269868847283</v>
       </c>
       <c r="K43" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J44" t="n">
-        <v>84.27510000018196</v>
+        <v>83.8546559583371</v>
       </c>
       <c r="K44" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J45" t="n">
-        <v>93.22739999957435</v>
+        <v>92.76229340383701</v>
       </c>
       <c r="K45" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J46" t="n">
-        <v>102.797099999415</v>
+        <v>102.2842506736522</v>
       </c>
       <c r="K46" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>106.5015000001795</v>
+        <v>105.9701696176286</v>
       </c>
       <c r="K47" t="n">
-        <v>-126.747198221838</v>
+        <v>-126.7478402841471</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>106.5015000001795</v>
+        <v>105.9701696176286</v>
       </c>
       <c r="K48" t="n">
-        <v>-94.32708661622024</v>
+        <v>-94.32756444821884</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>95.38830000015606</v>
+        <v>94.91241278795827</v>
       </c>
       <c r="K49" t="n">
-        <v>-67.15594545868147</v>
+        <v>-67.15628565003887</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>95.38830000015606</v>
+        <v>94.91241278795827</v>
       </c>
       <c r="K50" t="n">
-        <v>-26.09047076828911</v>
+        <v>-26.09060293458661</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>95.07959999993196</v>
+        <v>94.60525287580066</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.96108535591459</v>
+        <v>-10.96114088140054</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>86.43599999967792</v>
+        <v>86.00477534137804</v>
       </c>
       <c r="K52" t="n">
-        <v>7.255929735517227</v>
+        <v>7.255966491824789</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>95.38830000015606</v>
+        <v>94.91241278795827</v>
       </c>
       <c r="K53" t="n">
-        <v>10.65232238484966</v>
+        <v>10.65237634623739</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>86.74469999995138</v>
+        <v>86.31193525358476</v>
       </c>
       <c r="K54" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>86.74469999995138</v>
+        <v>86.31193525358476</v>
       </c>
       <c r="K55" t="n">
-        <v>24.85541888718858</v>
+        <v>24.85554479709324</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>95.07959999993196</v>
+        <v>94.60525287580066</v>
       </c>
       <c r="K56" t="n">
-        <v>51.10027113469175</v>
+        <v>51.10052999294297</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>94.77089999970784</v>
+        <v>94.29809296364303</v>
       </c>
       <c r="K57" t="n">
-        <v>104.8250275100088</v>
+        <v>104.825558521346</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>102.797099999415</v>
+        <v>102.2842506736522</v>
       </c>
       <c r="K58" t="n">
-        <v>104.5162645397337</v>
+        <v>104.5167939869727</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J59" t="n">
-        <v>81.80549999932678</v>
+        <v>81.39737666200909</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.15026328021784</v>
+        <v>-21.15037042094418</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J60" t="n">
-        <v>88.90559999944733</v>
+        <v>88.46205463662569</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.15026328021784</v>
+        <v>-21.15037042094418</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J61" t="n">
-        <v>96.62310000006545</v>
+        <v>96.14105243560667</v>
       </c>
       <c r="K61" t="n">
-        <v>-20.84150032099992</v>
+        <v>-20.84160589762811</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J62" t="n">
-        <v>81.18809999991497</v>
+        <v>80.78305683872507</v>
       </c>
       <c r="K62" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J63" t="n">
-        <v>88.90559999944733</v>
+        <v>88.46205463662569</v>
       </c>
       <c r="K63" t="n">
-        <v>13.43118909363182</v>
+        <v>13.43125713190331</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J64" t="n">
-        <v>96.62310000006545</v>
+        <v>96.14105243560667</v>
       </c>
       <c r="K64" t="n">
-        <v>13.43118909363182</v>
+        <v>13.43125713190331</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         <v>2.6</v>
       </c>
       <c r="J65" t="n">
-        <v>75.32279999970382</v>
+        <v>74.94701851175685</v>
       </c>
       <c r="K65" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>2.6</v>
       </c>
       <c r="J66" t="n">
-        <v>104.0318999993243</v>
+        <v>103.5128903213006</v>
       </c>
       <c r="K66" t="n">
-        <v>-59.74563424316039</v>
+        <v>-59.74593689616115</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>2.6</v>
       </c>
       <c r="J67" t="n">
-        <v>75.32279999970382</v>
+        <v>74.94701851175685</v>
       </c>
       <c r="K67" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>103.4144999999125</v>
+        <v>102.8985704980165</v>
       </c>
       <c r="K68" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         <v>2.6</v>
       </c>
       <c r="J69" t="n">
-        <v>75.01409999943036</v>
+        <v>74.63985859955012</v>
       </c>
       <c r="K69" t="n">
-        <v>94.01832364515531</v>
+        <v>94.01879991305569</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>2.6</v>
       </c>
       <c r="J70" t="n">
-        <v>103.4144999999125</v>
+        <v>102.8985704980165</v>
       </c>
       <c r="K70" t="n">
-        <v>94.32708660437322</v>
+        <v>94.32756443637174</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J71" t="n">
-        <v>81.18809999991497</v>
+        <v>80.78305683872507</v>
       </c>
       <c r="K71" t="n">
-        <v>-65.61213061915282</v>
+        <v>-65.61246299001924</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J72" t="n">
-        <v>89.21429999967144</v>
+        <v>88.76921454878332</v>
       </c>
       <c r="K72" t="n">
-        <v>-65.30336765993491</v>
+        <v>-65.30369846670318</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J73" t="n">
-        <v>96.93180000028956</v>
+        <v>96.4482123477643</v>
       </c>
       <c r="K73" t="n">
-        <v>-65.61213061915282</v>
+        <v>-65.61246299001924</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J74" t="n">
-        <v>81.49680000018843</v>
+        <v>81.0902167509318</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J75" t="n">
-        <v>89.21429999967144</v>
+        <v>88.76921454878332</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J76" t="n">
-        <v>97.24049999942791</v>
+        <v>96.75537225884159</v>
       </c>
       <c r="K76" t="n">
-        <v>-6.638403807603781</v>
+        <v>-6.638437435714992</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J77" t="n">
-        <v>81.18809999991497</v>
+        <v>80.78305683872507</v>
       </c>
       <c r="K77" t="n">
-        <v>28.86933747628147</v>
+        <v>28.86948371946272</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J78" t="n">
-        <v>89.5229999999449</v>
+        <v>89.07637446099007</v>
       </c>
       <c r="K78" t="n">
-        <v>28.86933747628147</v>
+        <v>28.86948371946272</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J79" t="n">
-        <v>98.4752999993373</v>
+        <v>97.98401190648997</v>
       </c>
       <c r="K79" t="n">
-        <v>29.17810043549939</v>
+        <v>29.17824824277879</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>1.09964</v>
       </c>
       <c r="J80" t="n">
-        <v>81.49680000018843</v>
+        <v>81.0902167509318</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         <v>1.09964</v>
       </c>
       <c r="J81" t="n">
-        <v>89.83170000016901</v>
+        <v>89.3835343731477</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.28944908189924</v>
+        <v>-61.28975955539097</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>1.09964</v>
       </c>
       <c r="J82" t="n">
-        <v>98.7839999995614</v>
+        <v>98.2911718186476</v>
       </c>
       <c r="K82" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
         <v>1.09964</v>
       </c>
       <c r="J83" t="n">
-        <v>80.87939999969086</v>
+        <v>80.47589692656744</v>
       </c>
       <c r="K83" t="n">
-        <v>6.020877866263713</v>
+        <v>6.020908366178501</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>1.09964</v>
       </c>
       <c r="J84" t="n">
-        <v>88.90559999944733</v>
+        <v>88.46205463662569</v>
       </c>
       <c r="K84" t="n">
-        <v>6.020877866263713</v>
+        <v>6.020908366178501</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         <v>1.09964</v>
       </c>
       <c r="J85" t="n">
-        <v>96.31439999979199</v>
+        <v>95.83389252339994</v>
       </c>
       <c r="K85" t="n">
-        <v>6.329640836538847</v>
+        <v>6.329672900551844</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J86" t="n">
-        <v>81.49680000018843</v>
+        <v>81.0902167509318</v>
       </c>
       <c r="K86" t="n">
-        <v>-13.43118909442162</v>
+        <v>-13.43125713269311</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J87" t="n">
-        <v>89.21429999967144</v>
+        <v>88.76921454878332</v>
       </c>
       <c r="K87" t="n">
-        <v>-13.43118909442162</v>
+        <v>-13.43125713269311</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J88" t="n">
-        <v>96.62310000006545</v>
+        <v>96.14105243560667</v>
       </c>
       <c r="K88" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4704,10 +4704,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J89" t="n">
-        <v>81.49680000018843</v>
+        <v>81.0902167509318</v>
       </c>
       <c r="K89" t="n">
-        <v>21.7677892191885</v>
+        <v>21.76789948811125</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J90" t="n">
-        <v>89.21429999967144</v>
+        <v>88.76921454878332</v>
       </c>
       <c r="K90" t="n">
-        <v>21.7677892191885</v>
+        <v>21.76789948811125</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4800,10 +4800,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J91" t="n">
-        <v>97.24049999942791</v>
+        <v>96.75537225884159</v>
       </c>
       <c r="K91" t="n">
-        <v>22.07655217840642</v>
+        <v>22.07666401142732</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>2.6</v>
       </c>
       <c r="J92" t="n">
-        <v>103.4144999999125</v>
+        <v>102.8985704980165</v>
       </c>
       <c r="K92" t="n">
-        <v>-120.8807018339985</v>
+        <v>-120.8813141784419</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
         <v>2.6</v>
       </c>
       <c r="J93" t="n">
-        <v>17.5959000001893</v>
+        <v>17.5081149804627</v>
       </c>
       <c r="K93" t="n">
-        <v>-175.5317470972368</v>
+        <v>-175.5326362870606</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>2.6</v>
       </c>
       <c r="J94" t="n">
-        <v>60.81389999918927</v>
+        <v>60.51050265031691</v>
       </c>
       <c r="K94" t="n">
-        <v>-176.1492730377871</v>
+        <v>-176.1501653558073</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         <v>2.6</v>
       </c>
       <c r="J95" t="n">
-        <v>104.0318999993243</v>
+        <v>103.5128903213006</v>
       </c>
       <c r="K95" t="n">
-        <v>-175.5317470972368</v>
+        <v>-175.5326362870606</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>6.109054</v>
       </c>
       <c r="J96" t="n">
-        <v>56.80079999933571</v>
+        <v>56.51742379531233</v>
       </c>
       <c r="K96" t="n">
-        <v>-119.0281240241948</v>
+        <v>-119.0287269840489</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>6.109054</v>
       </c>
       <c r="J97" t="n">
-        <v>68.22269999958327</v>
+        <v>67.88234053714025</v>
       </c>
       <c r="K97" t="n">
-        <v>-119.0281240241948</v>
+        <v>-119.0287269840489</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>6.109054</v>
       </c>
       <c r="J98" t="n">
-        <v>80.5706999994174</v>
+        <v>80.16873701436072</v>
       </c>
       <c r="K98" t="n">
-        <v>-118.7193610547094</v>
+        <v>-118.7199624504654</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         <v>6.109054</v>
       </c>
       <c r="J99" t="n">
-        <v>91.06650000007839</v>
+        <v>90.61217402079608</v>
       </c>
       <c r="K99" t="n">
-        <v>-118.7193610547094</v>
+        <v>-118.7199624504654</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.34800000042636</v>
+        <v>-12.28639647780974</v>
       </c>
       <c r="K100" t="n">
-        <v>-110.3827609283629</v>
+        <v>-110.3833200934676</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>26.23949999930823</v>
+        <v>26.10859251375587</v>
       </c>
       <c r="K101" t="n">
-        <v>-115.3229684164342</v>
+        <v>-115.3235526071101</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>44.14409999917876</v>
+        <v>43.92386740583603</v>
       </c>
       <c r="K102" t="n">
-        <v>-115.3229684164342</v>
+        <v>-115.3235526071101</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>1.09964</v>
       </c>
       <c r="J103" t="n">
-        <v>-33.03090000029042</v>
+        <v>-32.86611057729519</v>
       </c>
       <c r="K103" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>1.09964</v>
       </c>
       <c r="J104" t="n">
-        <v>-21.91770000031632</v>
+        <v>-21.80835374767401</v>
       </c>
       <c r="K104" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5472,10 +5472,10 @@
         <v>1.09964</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.11320000056633</v>
+        <v>-11.05775683021046</v>
       </c>
       <c r="K105" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>1.09964</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.173999999941742</v>
+        <v>-6.143198238634784</v>
       </c>
       <c r="K106" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>1.09964</v>
       </c>
       <c r="J107" t="n">
-        <v>-1.543500000676371</v>
+        <v>-1.535799560346184</v>
       </c>
       <c r="K107" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>1.09964</v>
       </c>
       <c r="J108" t="n">
-        <v>6.173999999941742</v>
+        <v>6.143198238634784</v>
       </c>
       <c r="K108" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         <v>1.09964</v>
       </c>
       <c r="J109" t="n">
-        <v>16.97849999969173</v>
+        <v>16.89379515609834</v>
       </c>
       <c r="K109" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>1.09964</v>
       </c>
       <c r="J110" t="n">
-        <v>21.60900000004286</v>
+        <v>21.50119383546727</v>
       </c>
       <c r="K110" t="n">
-        <v>-48.01264146748147</v>
+        <v>-48.01288468475079</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
         <v>1.09964</v>
       </c>
       <c r="J111" t="n">
-        <v>26.54819999958169</v>
+        <v>26.41575242596261</v>
       </c>
       <c r="K111" t="n">
-        <v>-48.01264146748147</v>
+        <v>-48.01288468475079</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>1.09964</v>
       </c>
       <c r="J112" t="n">
-        <v>35.80919999919819</v>
+        <v>35.63054978362015</v>
       </c>
       <c r="K112" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5856,10 +5856,10 @@
         <v>1.09964</v>
       </c>
       <c r="J113" t="n">
-        <v>45.07019999994979</v>
+        <v>44.84534714240713</v>
       </c>
       <c r="K113" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>1.09964</v>
       </c>
       <c r="J114" t="n">
-        <v>55.25730000028797</v>
+        <v>54.98162423658665</v>
       </c>
       <c r="K114" t="n">
-        <v>-48.32140443775661</v>
+        <v>-48.32164921912414</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5952,10 +5952,10 @@
         <v>1.09964</v>
       </c>
       <c r="J115" t="n">
-        <v>65.44439999954039</v>
+        <v>65.11790132968585</v>
       </c>
       <c r="K115" t="n">
-        <v>-48.01264146748147</v>
+        <v>-48.01288468475079</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>1.09964</v>
       </c>
       <c r="J116" t="n">
-        <v>-33.64829999970223</v>
+        <v>-33.48043040057922</v>
       </c>
       <c r="K116" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         <v>1.09964</v>
       </c>
       <c r="J117" t="n">
-        <v>-22.53510000081389</v>
+        <v>-22.42267357203837</v>
       </c>
       <c r="K117" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>1.09964</v>
       </c>
       <c r="J118" t="n">
-        <v>-11.42189999970468</v>
+        <v>-11.36491674128774</v>
       </c>
       <c r="K118" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6144,10 +6144,10 @@
         <v>1.09964</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.865300000803389</v>
+        <v>-5.836038327557494</v>
       </c>
       <c r="K119" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>1.09964</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.852199999814724</v>
+        <v>-1.842959471423474</v>
       </c>
       <c r="K120" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
         <v>1.09964</v>
       </c>
       <c r="J121" t="n">
-        <v>2.469599999177186</v>
+        <v>2.457279294658391</v>
       </c>
       <c r="K121" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>1.09964</v>
       </c>
       <c r="J122" t="n">
-        <v>7.100099999577665</v>
+        <v>7.064677974076436</v>
       </c>
       <c r="K122" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         <v>1.09964</v>
       </c>
       <c r="J123" t="n">
-        <v>12.03929999906715</v>
+        <v>11.97923656452266</v>
       </c>
       <c r="K123" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>1.09964</v>
       </c>
       <c r="J124" t="n">
-        <v>16.66979999941827</v>
+        <v>16.5866352438916</v>
       </c>
       <c r="K124" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
         <v>1.09964</v>
       </c>
       <c r="J125" t="n">
-        <v>22.22639999945467</v>
+        <v>22.1155136587513</v>
       </c>
       <c r="K125" t="n">
-        <v>65.61213061836303</v>
+        <v>65.61246298922944</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>1.09964</v>
       </c>
       <c r="J126" t="n">
-        <v>26.23949999930823</v>
+        <v>26.10859251375587</v>
       </c>
       <c r="K126" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6528,10 +6528,10 @@
         <v>1.09964</v>
       </c>
       <c r="J127" t="n">
-        <v>30.56129999943525</v>
+        <v>30.40883128096718</v>
       </c>
       <c r="K127" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>1.09964</v>
       </c>
       <c r="J128" t="n">
-        <v>35.19179999978638</v>
+        <v>35.01622996033612</v>
       </c>
       <c r="K128" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
         <v>1.09964</v>
       </c>
       <c r="J129" t="n">
-        <v>40.13099999932521</v>
+        <v>39.93078855083146</v>
       </c>
       <c r="K129" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J130" t="n">
-        <v>44.76149999967633</v>
+        <v>44.53818723020039</v>
       </c>
       <c r="K130" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6720,10 +6720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J131" t="n">
-        <v>54.6398999997904</v>
+        <v>54.3673044122223</v>
       </c>
       <c r="K131" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J132" t="n">
-        <v>64.82700000017793</v>
+        <v>64.50358150645093</v>
       </c>
       <c r="K132" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J133" t="n">
-        <v>-33.03090000029042</v>
+        <v>-32.86611057729519</v>
       </c>
       <c r="K133" t="n">
-        <v>-39.98480431219993</v>
+        <v>-39.98500686291619</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J134" t="n">
-        <v>-21.91770000031632</v>
+        <v>-21.80835374767401</v>
       </c>
       <c r="K134" t="n">
-        <v>-39.98480431219993</v>
+        <v>-39.98500686291619</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.66980000055338</v>
+        <v>-16.58663524502105</v>
       </c>
       <c r="K135" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.11320000056633</v>
+        <v>-11.05775683021046</v>
       </c>
       <c r="K136" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7008,10 +7008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J137" t="n">
-        <v>-6.173999999941742</v>
+        <v>-6.143198238634784</v>
       </c>
       <c r="K137" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.543500000676371</v>
+        <v>-1.535799560346184</v>
       </c>
       <c r="K138" t="n">
-        <v>-39.98480431219993</v>
+        <v>-39.98500686291619</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7104,10 +7104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J139" t="n">
-        <v>2.469599999177186</v>
+        <v>2.457279294658391</v>
       </c>
       <c r="K139" t="n">
-        <v>-39.36727837164965</v>
+        <v>-39.36747779416951</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J140" t="n">
-        <v>7.408799999801774</v>
+        <v>7.371837886234064</v>
       </c>
       <c r="K140" t="n">
-        <v>-39.98480431219993</v>
+        <v>-39.98500686291619</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J141" t="n">
-        <v>16.97849999969173</v>
+        <v>16.89379515609834</v>
       </c>
       <c r="K141" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J142" t="n">
-        <v>21.60900000004286</v>
+        <v>21.50119383546727</v>
       </c>
       <c r="K142" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7296,10 +7296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J143" t="n">
-        <v>26.54819999958169</v>
+        <v>26.41575242596261</v>
       </c>
       <c r="K143" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J144" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K144" t="n">
-        <v>-39.36727837164965</v>
+        <v>-39.36747779416951</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J145" t="n">
-        <v>35.50050000005984</v>
+        <v>35.32338987254285</v>
       </c>
       <c r="K145" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J146" t="n">
-        <v>45.07019999994979</v>
+        <v>44.84534714240713</v>
       </c>
       <c r="K146" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J147" t="n">
-        <v>55.25730000028797</v>
+        <v>54.98162423658665</v>
       </c>
       <c r="K147" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J148" t="n">
-        <v>65.13569999931629</v>
+        <v>64.81074141752822</v>
       </c>
       <c r="K148" t="n">
-        <v>-39.67604134192479</v>
+        <v>-39.67624232854285</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -7584,10 +7584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J149" t="n">
-        <v>-33.03090000029042</v>
+        <v>-32.86611057729519</v>
       </c>
       <c r="K149" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J150" t="n">
-        <v>-22.22640000054043</v>
+        <v>-22.11551365983164</v>
       </c>
       <c r="K150" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.11320000056633</v>
+        <v>-11.05775683021046</v>
       </c>
       <c r="K151" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.173999999941742</v>
+        <v>-6.143198238634784</v>
       </c>
       <c r="K152" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7776,10 +7776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.543500000676371</v>
+        <v>-1.535799560346184</v>
       </c>
       <c r="K153" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J154" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K154" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J155" t="n">
-        <v>7.408799999801774</v>
+        <v>7.371837886234064</v>
       </c>
       <c r="K155" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J156" t="n">
-        <v>12.03929999906715</v>
+        <v>11.97923656452266</v>
       </c>
       <c r="K156" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J157" t="n">
-        <v>16.97849999969173</v>
+        <v>16.89379515609834</v>
       </c>
       <c r="K157" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J158" t="n">
-        <v>21.60900000004286</v>
+        <v>21.50119383546727</v>
       </c>
       <c r="K158" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J159" t="n">
-        <v>26.54819999958169</v>
+        <v>26.41575242596261</v>
       </c>
       <c r="K159" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J160" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K160" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8160,10 +8160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J161" t="n">
-        <v>35.50050000005984</v>
+        <v>35.32338987254285</v>
       </c>
       <c r="K161" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J162" t="n">
-        <v>40.13099999932521</v>
+        <v>39.93078855083146</v>
       </c>
       <c r="K162" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J163" t="n">
-        <v>45.07019999994979</v>
+        <v>44.84534714240713</v>
       </c>
       <c r="K163" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J164" t="n">
-        <v>54.94860000006386</v>
+        <v>54.67446432442903</v>
       </c>
       <c r="K164" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8352,10 +8352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J165" t="n">
-        <v>65.13569999931629</v>
+        <v>64.81074141752822</v>
       </c>
       <c r="K165" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J166" t="n">
-        <v>-33.64829999970223</v>
+        <v>-33.48043040057922</v>
       </c>
       <c r="K166" t="n">
-        <v>73.02244184494133</v>
+        <v>73.02281175416444</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -8448,10 +8448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J167" t="n">
-        <v>-22.53510000081389</v>
+        <v>-22.42267357203837</v>
       </c>
       <c r="K167" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J168" t="n">
-        <v>-16.97850000082684</v>
+        <v>-16.89379515722778</v>
       </c>
       <c r="K168" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -8544,10 +8544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.42189999970468</v>
+        <v>-11.36491674128774</v>
       </c>
       <c r="K169" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.852199999814724</v>
+        <v>-1.842959471423474</v>
       </c>
       <c r="K170" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J171" t="n">
-        <v>3.086999999674756</v>
+        <v>3.071599119022754</v>
       </c>
       <c r="K171" t="n">
-        <v>73.94873074470951</v>
+        <v>73.94910534622719</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>1.09964</v>
       </c>
       <c r="J172" t="n">
-        <v>7.100099999577665</v>
+        <v>7.064677974076436</v>
       </c>
       <c r="K172" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>1.09964</v>
       </c>
       <c r="J173" t="n">
-        <v>12.03929999906715</v>
+        <v>11.97923656452266</v>
       </c>
       <c r="K173" t="n">
-        <v>73.94873074470951</v>
+        <v>73.94910534622719</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>1.09964</v>
       </c>
       <c r="J174" t="n">
-        <v>16.66979999941827</v>
+        <v>16.5866352438916</v>
       </c>
       <c r="K174" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
         <v>1.09964</v>
       </c>
       <c r="J175" t="n">
-        <v>25.93080000016988</v>
+        <v>25.80143260267858</v>
       </c>
       <c r="K175" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>1.09964</v>
       </c>
       <c r="J176" t="n">
-        <v>31.48740000015693</v>
+        <v>31.33031101748917</v>
       </c>
       <c r="K176" t="n">
-        <v>73.94873074470951</v>
+        <v>73.94910534622719</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         <v>1.09964</v>
       </c>
       <c r="J177" t="n">
-        <v>35.50050000005984</v>
+        <v>35.32338987254285</v>
       </c>
       <c r="K177" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>1.09964</v>
       </c>
       <c r="J178" t="n">
-        <v>40.13099999932521</v>
+        <v>39.93078855083146</v>
       </c>
       <c r="K178" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9024,10 +9024,10 @@
         <v>1.09964</v>
       </c>
       <c r="J179" t="n">
-        <v>44.76149999967633</v>
+        <v>44.53818723020039</v>
       </c>
       <c r="K179" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>1.09964</v>
       </c>
       <c r="J180" t="n">
-        <v>54.94860000006386</v>
+        <v>54.67446432442903</v>
       </c>
       <c r="K180" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9120,10 +9120,10 @@
         <v>1.09964</v>
       </c>
       <c r="J181" t="n">
-        <v>64.82700000017793</v>
+        <v>64.50358150645093</v>
       </c>
       <c r="K181" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>1.09964</v>
       </c>
       <c r="J182" t="n">
-        <v>-33.64829999970223</v>
+        <v>-33.48043040057922</v>
       </c>
       <c r="K182" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9216,10 +9216,10 @@
         <v>1.09964</v>
       </c>
       <c r="J183" t="n">
-        <v>-22.53510000081389</v>
+        <v>-22.42267357203837</v>
       </c>
       <c r="K183" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>1.09964</v>
       </c>
       <c r="J184" t="n">
-        <v>-11.42189999970468</v>
+        <v>-11.36491674128774</v>
       </c>
       <c r="K184" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -9312,10 +9312,10 @@
         <v>1.09964</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.852199999814724</v>
+        <v>-1.842959471423474</v>
       </c>
       <c r="K185" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>1.09964</v>
       </c>
       <c r="J186" t="n">
-        <v>7.100099999577665</v>
+        <v>7.064677974076436</v>
       </c>
       <c r="K186" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -9408,10 +9408,10 @@
         <v>1.09964</v>
       </c>
       <c r="J187" t="n">
-        <v>12.34799999929125</v>
+        <v>12.28639647668029</v>
       </c>
       <c r="K187" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>1.09964</v>
       </c>
       <c r="J188" t="n">
-        <v>16.66979999941827</v>
+        <v>16.5866352438916</v>
       </c>
       <c r="K188" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -9504,10 +9504,10 @@
         <v>1.09964</v>
       </c>
       <c r="J189" t="n">
-        <v>25.93080000016988</v>
+        <v>25.80143260267858</v>
       </c>
       <c r="K189" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>1.09964</v>
       </c>
       <c r="J190" t="n">
-        <v>35.19179999978638</v>
+        <v>35.01622996033612</v>
       </c>
       <c r="K190" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -9600,10 +9600,10 @@
         <v>1.09964</v>
       </c>
       <c r="J191" t="n">
-        <v>40.74839999982278</v>
+        <v>40.54510837519582</v>
       </c>
       <c r="K191" t="n">
-        <v>82.59409384054133</v>
+        <v>82.59451223680848</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>1.09964</v>
       </c>
       <c r="J192" t="n">
-        <v>44.45279999945222</v>
+        <v>44.23102731804276</v>
       </c>
       <c r="K192" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -9696,10 +9696,10 @@
         <v>1.09964</v>
       </c>
       <c r="J193" t="n">
-        <v>54.6398999997904</v>
+        <v>54.3673044122223</v>
       </c>
       <c r="K193" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>1.09964</v>
       </c>
       <c r="J194" t="n">
-        <v>64.82700000017793</v>
+        <v>64.50358150645093</v>
       </c>
       <c r="K194" t="n">
-        <v>82.28533087026619</v>
+        <v>82.28574770243513</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -9792,10 +9792,10 @@
         <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.261000000208728</v>
+        <v>-9.214797358246813</v>
       </c>
       <c r="K195" t="n">
-        <v>-94.9446125457133</v>
+        <v>-94.94509350590825</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>12.96539999978882</v>
+        <v>12.90071630104466</v>
       </c>
       <c r="K196" t="n">
-        <v>-94.63584958649538</v>
+        <v>-94.63632898259218</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -9888,10 +9888,10 @@
         <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>40.13099999932521</v>
+        <v>39.93078855083146</v>
       </c>
       <c r="K197" t="n">
-        <v>-94.63584958649538</v>
+        <v>-94.63632898259218</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>41.36579999918524</v>
+        <v>41.15942819843074</v>
       </c>
       <c r="K198" t="n">
-        <v>-93.70956067645977</v>
+        <v>-93.71003538026196</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -9984,10 +9984,10 @@
         <v>1</v>
       </c>
       <c r="J199" t="n">
-        <v>49.39200000007681</v>
+        <v>49.14558590961844</v>
       </c>
       <c r="K199" t="n">
-        <v>-91.54821990743808</v>
+        <v>-91.54868366255292</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>1</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.66980000055338</v>
+        <v>-16.58663524502105</v>
       </c>
       <c r="K200" t="n">
-        <v>-71.47862700699228</v>
+        <v>-71.47898909572442</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10080,10 +10080,10 @@
         <v>1</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.90460000041341</v>
+        <v>-17.81527489262033</v>
       </c>
       <c r="K201" t="n">
-        <v>-69.31728623797059</v>
+        <v>-69.31763737801538</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>1</v>
       </c>
       <c r="J202" t="n">
-        <v>13.89149999942475</v>
+        <v>13.82219603648631</v>
       </c>
       <c r="K202" t="n">
-        <v>-71.16986403671714</v>
+        <v>-71.17022456135108</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="J203" t="n">
-        <v>46.30499999980983</v>
+        <v>46.07398679000641</v>
       </c>
       <c r="K203" t="n">
-        <v>-71.16986403671714</v>
+        <v>-71.17022456135108</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>1</v>
       </c>
       <c r="J204" t="n">
-        <v>-19.75680000082037</v>
+        <v>-19.65823436463308</v>
       </c>
       <c r="K204" t="n">
-        <v>-56.34924159382796</v>
+        <v>-56.34952704174854</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -10272,10 +10272,10 @@
         <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>0.308699999681231</v>
+        <v>0.3071599116174588</v>
       </c>
       <c r="K205" t="n">
-        <v>-62.21573798166742</v>
+        <v>-62.21605314745372</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K206" t="n">
-        <v>-62.21573798166742</v>
+        <v>-62.21605314745372</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -10368,10 +10368,10 @@
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>13.58280000028639</v>
+        <v>13.51503612540902</v>
       </c>
       <c r="K207" t="n">
-        <v>-56.34924159382796</v>
+        <v>-56.34952704174854</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>1</v>
       </c>
       <c r="J208" t="n">
-        <v>37.35269999933168</v>
+        <v>37.16634934342616</v>
       </c>
       <c r="K208" t="n">
-        <v>-56.34924159382796</v>
+        <v>-56.34952704174854</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -10464,10 +10464,10 @@
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>-18.21330000068687</v>
+        <v>-18.12243480482706</v>
       </c>
       <c r="K209" t="n">
-        <v>-39.36727837164965</v>
+        <v>-39.36747779416951</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>-20.06549999995872</v>
+        <v>-19.96539427571037</v>
       </c>
       <c r="K210" t="n">
-        <v>-36.58841166286749</v>
+        <v>-36.58859700850359</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.20020000078396</v>
+        <v>-14.12935594977338</v>
       </c>
       <c r="K211" t="n">
-        <v>-39.36727837164965</v>
+        <v>-39.36747779416951</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>1</v>
       </c>
       <c r="J212" t="n">
-        <v>0.6173999999546922</v>
+        <v>0.6143198238241934</v>
       </c>
       <c r="K212" t="n">
-        <v>-37.82346353212101</v>
+        <v>-37.82365513414988</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -10656,10 +10656,10 @@
         <v>1</v>
       </c>
       <c r="J213" t="n">
-        <v>28.7091000001634</v>
+        <v>28.56587181008388</v>
       </c>
       <c r="K213" t="n">
-        <v>-38.13222650239614</v>
+        <v>-38.13241966852322</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>1</v>
       </c>
       <c r="J214" t="n">
-        <v>-20.06549999995872</v>
+        <v>-19.96539427571037</v>
       </c>
       <c r="K214" t="n">
-        <v>-11.57861128461784</v>
+        <v>-11.57866993830014</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -10752,10 +10752,10 @@
         <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>-18.21330000068687</v>
+        <v>-18.12243480482706</v>
       </c>
       <c r="K215" t="n">
-        <v>-9.417270516385944</v>
+        <v>-9.417318221380908</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.83070000004933</v>
+        <v>-18.73675462806198</v>
       </c>
       <c r="K216" t="n">
-        <v>-5.712114908625401</v>
+        <v>-5.712143844442046</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -10848,10 +10848,10 @@
         <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>-18.83070000004933</v>
+        <v>-18.73675462806198</v>
       </c>
       <c r="K217" t="n">
-        <v>9.417270515596142</v>
+        <v>9.417318220591103</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>1</v>
       </c>
       <c r="J218" t="n">
-        <v>-23.76990000067392</v>
+        <v>-23.65131321963765</v>
       </c>
       <c r="K218" t="n">
-        <v>17.44510767166749</v>
+        <v>17.44519604321551</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -10944,10 +10944,10 @@
         <v>1</v>
       </c>
       <c r="J219" t="n">
-        <v>-16.05240000005581</v>
+        <v>-15.97231542065668</v>
       </c>
       <c r="K219" t="n">
-        <v>17.44510767166749</v>
+        <v>17.44519604321551</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>1</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6173999999546922</v>
+        <v>0.6143198238241934</v>
       </c>
       <c r="K220" t="n">
-        <v>-14.66624096367513</v>
+        <v>-14.6663152583394</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -11040,10 +11040,10 @@
         <v>1</v>
       </c>
       <c r="J221" t="n">
-        <v>0.6173999999546922</v>
+        <v>0.6143198238241934</v>
       </c>
       <c r="K221" t="n">
-        <v>-11.26984832539992</v>
+        <v>-11.26990541498408</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>1</v>
       </c>
       <c r="J222" t="n">
-        <v>28.7091000001634</v>
+        <v>28.56587181008388</v>
       </c>
       <c r="K222" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>1</v>
       </c>
       <c r="J223" t="n">
-        <v>28.7091000001634</v>
+        <v>28.56587181008388</v>
       </c>
       <c r="K223" t="n">
-        <v>-11.26984832539992</v>
+        <v>-11.26990541498408</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>1</v>
       </c>
       <c r="J224" t="n">
-        <v>37.35269999933168</v>
+        <v>37.16634934342616</v>
       </c>
       <c r="K224" t="n">
-        <v>-26.39923373856425</v>
+        <v>-26.39936746895995</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -11232,10 +11232,10 @@
         <v>1</v>
       </c>
       <c r="J225" t="n">
-        <v>13.27410000006229</v>
+        <v>13.20787621325139</v>
       </c>
       <c r="K225" t="n">
-        <v>-26.39923373856425</v>
+        <v>-26.39936746895995</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="J226" t="n">
-        <v>13.58280000028639</v>
+        <v>13.51503612540902</v>
       </c>
       <c r="K226" t="n">
-        <v>0.7719074189745225</v>
+        <v>0.7719113292200094</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -11328,10 +11328,10 @@
         <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>37.35269999933168</v>
+        <v>37.16634934342616</v>
       </c>
       <c r="K227" t="n">
-        <v>1.080670389249656</v>
+        <v>1.080675863593352</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>0.308699999681231</v>
+        <v>0.3071599116174588</v>
       </c>
       <c r="K228" t="n">
-        <v>7.564692705792361</v>
+        <v>7.564731026198131</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -11424,10 +11424,10 @@
         <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K229" t="n">
-        <v>7.564692705792361</v>
+        <v>7.564731026198131</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>0.6173999999546922</v>
+        <v>0.6143198238241934</v>
       </c>
       <c r="K230" t="n">
-        <v>20.8415003091529</v>
+        <v>20.84160588578103</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>0.308699999681231</v>
+        <v>0.3071599116174588</v>
       </c>
       <c r="K231" t="n">
-        <v>24.23789295848533</v>
+        <v>24.23801574019364</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>12.96539999978882</v>
+        <v>12.90071630104466</v>
       </c>
       <c r="K232" t="n">
-        <v>17.44510767166749</v>
+        <v>17.44519604321551</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -11616,10 +11616,10 @@
         <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K233" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>1</v>
       </c>
       <c r="J234" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K234" t="n">
-        <v>24.23789295848533</v>
+        <v>24.23801574019364</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -11712,10 +11712,10 @@
         <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>37.04400000019333</v>
+        <v>36.85918943234887</v>
       </c>
       <c r="K235" t="n">
-        <v>17.44510767166749</v>
+        <v>17.44519604321551</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.778300000536403</v>
+        <v>-2.764439207945464</v>
       </c>
       <c r="K236" t="n">
-        <v>37.20593759157074</v>
+        <v>37.2061260654032</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -11808,10 +11808,10 @@
         <v>1</v>
       </c>
       <c r="J237" t="n">
-        <v>4.939200000032358</v>
+        <v>4.914558590986397</v>
       </c>
       <c r="K237" t="n">
-        <v>37.20593759157074</v>
+        <v>37.2061260654032</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>7.717500000075235</v>
+        <v>7.678997798440799</v>
       </c>
       <c r="K238" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -11904,10 +11904,10 @@
         <v>1</v>
       </c>
       <c r="J239" t="n">
-        <v>25.31339999967231</v>
+        <v>25.18711277831422</v>
       </c>
       <c r="K239" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>1</v>
       </c>
       <c r="J240" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K240" t="n">
-        <v>37.82346353133121</v>
+        <v>37.82365513336007</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>1</v>
       </c>
       <c r="J241" t="n">
-        <v>33.03090000029042</v>
+        <v>32.86611057729519</v>
       </c>
       <c r="K241" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>1</v>
       </c>
       <c r="J242" t="n">
-        <v>40.43969999954932</v>
+        <v>40.23794846298908</v>
       </c>
       <c r="K242" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -12096,10 +12096,10 @@
         <v>1</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.428777427596287e-10</v>
+        <v>-5.401693542511253e-10</v>
       </c>
       <c r="K243" t="n">
-        <v>50.4827452059885</v>
+        <v>50.48300093604337</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>1</v>
       </c>
       <c r="J244" t="n">
-        <v>7.717500000075235</v>
+        <v>7.678997798440799</v>
       </c>
       <c r="K244" t="n">
-        <v>47.39511552693121</v>
+        <v>47.39535561600411</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
         <v>1</v>
       </c>
       <c r="J245" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K245" t="n">
-        <v>47.70387849720634</v>
+        <v>47.70412015037746</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="J246" t="n">
-        <v>37.04400000019333</v>
+        <v>36.85918943234887</v>
       </c>
       <c r="K246" t="n">
-        <v>50.4827452059885</v>
+        <v>50.48300093604337</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -12288,10 +12288,10 @@
         <v>1</v>
       </c>
       <c r="J247" t="n">
-        <v>-14.50889999992232</v>
+        <v>-14.43651586085067</v>
       </c>
       <c r="K247" t="n">
-        <v>72.713678875456</v>
+        <v>72.71404722058091</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>1</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.428777427596287e-10</v>
+        <v>-5.401693542511253e-10</v>
       </c>
       <c r="K248" t="n">
-        <v>75.49254558344836</v>
+        <v>75.49292800545702</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -12384,10 +12384,10 @@
         <v>1</v>
       </c>
       <c r="J249" t="n">
-        <v>4.32179999958414</v>
+        <v>4.300238766671141</v>
       </c>
       <c r="K249" t="n">
-        <v>73.94873074470951</v>
+        <v>73.94910534622719</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>1</v>
       </c>
       <c r="J250" t="n">
-        <v>7.717500000075235</v>
+        <v>7.678997798440799</v>
       </c>
       <c r="K250" t="n">
-        <v>72.09615293490573</v>
+        <v>72.09651815183422</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -12480,10 +12480,10 @@
         <v>1</v>
       </c>
       <c r="J251" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K251" t="n">
-        <v>72.40491590518086</v>
+        <v>72.40528268620756</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>1</v>
       </c>
       <c r="J252" t="n">
-        <v>13.89149999942475</v>
+        <v>13.82219603648631</v>
       </c>
       <c r="K252" t="n">
-        <v>82.59409384054133</v>
+        <v>82.59451223680848</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -12576,10 +12576,10 @@
         <v>1</v>
       </c>
       <c r="J253" t="n">
-        <v>41.98319999968281</v>
+        <v>41.7737480227951</v>
       </c>
       <c r="K253" t="n">
-        <v>82.59409384054133</v>
+        <v>82.59451223680848</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>1</v>
       </c>
       <c r="J254" t="n">
-        <v>-13.58280000033575</v>
+        <v>-13.51503612545812</v>
       </c>
       <c r="K254" t="n">
-        <v>89.07811615708404</v>
+        <v>89.07856739941326</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -12672,10 +12672,10 @@
         <v>1</v>
       </c>
       <c r="J255" t="n">
-        <v>7.408799999801774</v>
+        <v>7.371837886234064</v>
       </c>
       <c r="K255" t="n">
-        <v>91.23945693716294</v>
+        <v>91.23991912817957</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>1</v>
       </c>
       <c r="J256" t="n">
-        <v>18.21329999955177</v>
+        <v>18.12243480369762</v>
       </c>
       <c r="K256" t="n">
-        <v>90.62193099661268</v>
+        <v>90.62239005943289</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -12768,10 +12768,10 @@
         <v>1</v>
       </c>
       <c r="J257" t="n">
-        <v>28.4003999999393</v>
+        <v>28.25871189792625</v>
       </c>
       <c r="K257" t="n">
-        <v>91.54821989559106</v>
+        <v>91.54868365070584</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>1</v>
       </c>
       <c r="J258" t="n">
-        <v>46.30499999980983</v>
+        <v>46.07398679000641</v>
       </c>
       <c r="K258" t="n">
-        <v>90.93069396688782</v>
+        <v>90.93115459380623</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -12864,10 +12864,10 @@
         <v>1</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.791400000439312</v>
+        <v>-6.757518062999146</v>
       </c>
       <c r="K259" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>1</v>
       </c>
       <c r="J260" t="n">
-        <v>0.9261000001788009</v>
+        <v>0.9214797359818215</v>
       </c>
       <c r="K260" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -12960,10 +12960,10 @@
         <v>1</v>
       </c>
       <c r="J261" t="n">
-        <v>8.026200000299344</v>
+        <v>7.986157710598427</v>
       </c>
       <c r="K261" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>1</v>
       </c>
       <c r="J262" t="n">
-        <v>21.30029999981875</v>
+        <v>21.19403392330965</v>
       </c>
       <c r="K262" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -13056,10 +13056,10 @@
         <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>36.42659999969576</v>
+        <v>36.2448696079845</v>
       </c>
       <c r="K263" t="n">
-        <v>93.70956067566998</v>
+        <v>93.71003537947215</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>59.57909999932924</v>
+        <v>59.28186300271763</v>
       </c>
       <c r="K264" t="n">
-        <v>109.1477090583196</v>
+        <v>109.1482619670316</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -13152,10 +13152,10 @@
         <v>1</v>
       </c>
       <c r="J265" t="n">
-        <v>69.14879999916984</v>
+        <v>68.80382027253279</v>
       </c>
       <c r="K265" t="n">
-        <v>104.5162645397337</v>
+        <v>104.5167939869727</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>1</v>
       </c>
       <c r="J266" t="n">
-        <v>69.14879999916984</v>
+        <v>68.80382027253279</v>
       </c>
       <c r="K266" t="n">
-        <v>112.544101695805</v>
+        <v>112.5446718095971</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -13248,10 +13248,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K267" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J268" t="n">
-        <v>1.852199999814724</v>
+        <v>1.842959471423474</v>
       </c>
       <c r="K268" t="n">
-        <v>-21.15026328021784</v>
+        <v>-21.15037042094418</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -13344,10 +13344,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J269" t="n">
-        <v>10.49580000006876</v>
+        <v>10.44343700584609</v>
       </c>
       <c r="K269" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J270" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K270" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -13440,10 +13440,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J271" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K271" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J272" t="n">
-        <v>38.58749999919171</v>
+        <v>38.39498899102544</v>
       </c>
       <c r="K272" t="n">
-        <v>-21.15026328021784</v>
+        <v>-21.15037042094418</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J273" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K273" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J274" t="n">
-        <v>1.852199999814724</v>
+        <v>1.842959471423474</v>
       </c>
       <c r="K274" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -13632,10 +13632,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J275" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K275" t="n">
-        <v>13.43118909363182</v>
+        <v>13.43125713190331</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J276" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K276" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -13728,10 +13728,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J277" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K277" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J278" t="n">
-        <v>38.27880000005337</v>
+        <v>38.08782907994815</v>
       </c>
       <c r="K278" t="n">
-        <v>13.12242612335668</v>
+        <v>13.12249259752997</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         <v>2.6</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.49580000006876</v>
+        <v>-10.44343700584609</v>
       </c>
       <c r="K279" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>2.6</v>
       </c>
       <c r="J280" t="n">
-        <v>17.5959000001893</v>
+        <v>17.5081149804627</v>
       </c>
       <c r="K280" t="n">
-        <v>-60.67192314213877</v>
+        <v>-60.67223048743409</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -13920,10 +13920,10 @@
         <v>2.6</v>
       </c>
       <c r="J281" t="n">
-        <v>45.68759999931225</v>
+        <v>45.45966696564204</v>
       </c>
       <c r="K281" t="n">
-        <v>-60.0543972015885</v>
+        <v>-60.05470141868741</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>2.6</v>
       </c>
       <c r="J282" t="n">
-        <v>-10.49580000006876</v>
+        <v>-10.44343700584609</v>
       </c>
       <c r="K282" t="n">
-        <v>5.403351926503246</v>
+        <v>5.403379298221623</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -14016,10 +14016,10 @@
         <v>2.6</v>
       </c>
       <c r="J283" t="n">
-        <v>17.5959000001893</v>
+        <v>17.5081149804627</v>
       </c>
       <c r="K283" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>2.6</v>
       </c>
       <c r="J284" t="n">
-        <v>45.37890000017391</v>
+        <v>45.15250705456476</v>
       </c>
       <c r="K284" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -14112,10 +14112,10 @@
         <v>2.6</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.11320000056633</v>
+        <v>-11.05775683021046</v>
       </c>
       <c r="K285" t="n">
-        <v>93.70956067566998</v>
+        <v>93.71003537947215</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>2.6</v>
       </c>
       <c r="J286" t="n">
-        <v>17.28719999991584</v>
+        <v>17.20095506825596</v>
       </c>
       <c r="K286" t="n">
-        <v>94.01832364515531</v>
+        <v>94.01879991305569</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -14208,10 +14208,10 @@
         <v>2.6</v>
       </c>
       <c r="J287" t="n">
-        <v>45.07019999994979</v>
+        <v>44.84534714240713</v>
       </c>
       <c r="K287" t="n">
-        <v>94.01832364515531</v>
+        <v>94.01879991305569</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.93920000008171</v>
+        <v>-4.914558591035504</v>
       </c>
       <c r="K288" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -14304,10 +14304,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J289" t="n">
-        <v>4.939200000032358</v>
+        <v>4.914558590986397</v>
       </c>
       <c r="K289" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J290" t="n">
-        <v>15.12629999933413</v>
+        <v>15.05083568413469</v>
       </c>
       <c r="K290" t="n">
-        <v>-73.6399677862814</v>
+        <v>-73.64034082370092</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J291" t="n">
-        <v>23.76989999953881</v>
+        <v>23.65131321850821</v>
       </c>
       <c r="K291" t="n">
-        <v>-73.6399677862814</v>
+        <v>-73.64034082370092</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J292" t="n">
-        <v>33.03090000029042</v>
+        <v>32.86611057729519</v>
       </c>
       <c r="K292" t="n">
-        <v>-72.40491591702788</v>
+        <v>-72.40528269805465</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -14496,10 +14496,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J293" t="n">
-        <v>46.30499999980983</v>
+        <v>46.07398679000641</v>
       </c>
       <c r="K293" t="n">
-        <v>-73.94873075655653</v>
+        <v>-73.94910535807428</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.321800000669896</v>
+        <v>-4.30023876775148</v>
       </c>
       <c r="K294" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -14592,10 +14592,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J295" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K295" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J296" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K296" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -14688,10 +14688,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J297" t="n">
-        <v>23.76989999953881</v>
+        <v>23.65131321850821</v>
       </c>
       <c r="K297" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J298" t="n">
-        <v>31.48740000015693</v>
+        <v>31.33031101748917</v>
       </c>
       <c r="K298" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -14784,10 +14784,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J299" t="n">
-        <v>38.89619999941583</v>
+        <v>38.70214890318307</v>
       </c>
       <c r="K299" t="n">
-        <v>-66.22965655970309</v>
+        <v>-66.22999205876593</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>1</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.308700000816339</v>
+        <v>-0.3071599127469039</v>
       </c>
       <c r="K300" t="n">
-        <v>-81.35904197207762</v>
+        <v>-81.35945411195199</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -14880,10 +14880,10 @@
         <v>1</v>
       </c>
       <c r="J301" t="n">
-        <v>30.25260000029689</v>
+        <v>30.10167136988989</v>
       </c>
       <c r="K301" t="n">
-        <v>-81.35904197207762</v>
+        <v>-81.35945411195199</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>1</v>
       </c>
       <c r="J302" t="n">
-        <v>50.00939999943927</v>
+        <v>49.75990573285335</v>
       </c>
       <c r="K302" t="n">
-        <v>-80.1239901028241</v>
+        <v>-80.12439598630571</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -14976,10 +14976,10 @@
         <v>1</v>
       </c>
       <c r="J303" t="n">
-        <v>52.17030000007034</v>
+        <v>51.91002511702374</v>
       </c>
       <c r="K303" t="n">
-        <v>-84.44667165113491</v>
+        <v>-84.44709943199126</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>1</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.93920000008171</v>
+        <v>-4.914558591035504</v>
       </c>
       <c r="K304" t="n">
-        <v>46.46882662795283</v>
+        <v>46.46906202473117</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -15072,10 +15072,10 @@
         <v>1</v>
       </c>
       <c r="J305" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K305" t="n">
-        <v>46.46882662795283</v>
+        <v>46.46906202473117</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K306" t="n">
-        <v>46.77758959743816</v>
+        <v>46.7778265583147</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -15168,10 +15168,10 @@
         <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>23.15250000017635</v>
+        <v>23.03699339527329</v>
       </c>
       <c r="K307" t="n">
-        <v>46.46882662795283</v>
+        <v>46.46906202473117</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>1</v>
       </c>
       <c r="J308" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K308" t="n">
-        <v>46.77758959743816</v>
+        <v>46.7778265583147</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -15264,10 +15264,10 @@
         <v>1</v>
       </c>
       <c r="J309" t="n">
-        <v>38.58749999919171</v>
+        <v>38.39498899102544</v>
       </c>
       <c r="K309" t="n">
-        <v>46.46882662795283</v>
+        <v>46.46906202473117</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.93920000008171</v>
+        <v>-4.914558591035504</v>
       </c>
       <c r="K310" t="n">
-        <v>54.80542675350951</v>
+        <v>54.80570438093911</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -15360,10 +15360,10 @@
         <v>1</v>
       </c>
       <c r="J311" t="n">
-        <v>1.852199999814724</v>
+        <v>1.842959471423474</v>
       </c>
       <c r="K311" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>1</v>
       </c>
       <c r="J312" t="n">
-        <v>10.49580000006876</v>
+        <v>10.44343700584609</v>
       </c>
       <c r="K312" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -15456,10 +15456,10 @@
         <v>1</v>
       </c>
       <c r="J313" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K313" t="n">
-        <v>55.11418972378465</v>
+        <v>55.11446891531246</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>1</v>
       </c>
       <c r="J314" t="n">
-        <v>38.27880000005337</v>
+        <v>38.08782907994815</v>
       </c>
       <c r="K314" t="n">
-        <v>55.11418972378465</v>
+        <v>55.11446891531246</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -15552,10 +15552,10 @@
         <v>1</v>
       </c>
       <c r="J315" t="n">
-        <v>30.56129999943525</v>
+        <v>30.40883128096718</v>
       </c>
       <c r="K315" t="n">
-        <v>54.80542675350951</v>
+        <v>54.80570438093911</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.321800000669896</v>
+        <v>-4.30023876775148</v>
       </c>
       <c r="K316" t="n">
-        <v>39.67604134113499</v>
+        <v>39.67624232775304</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -15648,10 +15648,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J317" t="n">
-        <v>4.32179999958414</v>
+        <v>4.300238766671141</v>
       </c>
       <c r="K317" t="n">
-        <v>39.67604134113499</v>
+        <v>39.67624232775304</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J318" t="n">
-        <v>11.73059999992879</v>
+        <v>11.67207665344537</v>
       </c>
       <c r="K318" t="n">
-        <v>39.98480431141012</v>
+        <v>39.98500686212638</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -15744,10 +15744,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J319" t="n">
-        <v>23.76989999953881</v>
+        <v>23.65131321850821</v>
       </c>
       <c r="K319" t="n">
-        <v>39.98480431141012</v>
+        <v>39.98500686212638</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J320" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K320" t="n">
-        <v>39.67604134113499</v>
+        <v>39.67624232775304</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -15840,10 +15840,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J321" t="n">
-        <v>39.20489999968929</v>
+        <v>39.0093088153898</v>
       </c>
       <c r="K321" t="n">
-        <v>39.67604134113499</v>
+        <v>39.67624232775304</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J322" t="n">
-        <v>-14.81760000019578</v>
+        <v>-14.7436757730574</v>
       </c>
       <c r="K322" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.93920000008171</v>
+        <v>-4.914558591035504</v>
       </c>
       <c r="K323" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J324" t="n">
-        <v>5.247899999170711</v>
+        <v>5.221718502063687</v>
       </c>
       <c r="K324" t="n">
-        <v>-78.58017526329546</v>
+        <v>-78.58057332628609</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -16032,10 +16032,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J325" t="n">
-        <v>15.43499999955824</v>
+        <v>15.35799559629232</v>
       </c>
       <c r="K325" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J326" t="n">
-        <v>25.0046999994482</v>
+        <v>24.87995286615659</v>
       </c>
       <c r="K326" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -16128,10 +16128,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J327" t="n">
-        <v>35.50050000005984</v>
+        <v>35.32338987254285</v>
       </c>
       <c r="K327" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J328" t="n">
-        <v>45.68759999931225</v>
+        <v>45.45966696564204</v>
       </c>
       <c r="K328" t="n">
-        <v>-78.27141229302032</v>
+        <v>-78.27180879191273</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -16224,10 +16224,10 @@
         <v>6.109054</v>
       </c>
       <c r="J329" t="n">
-        <v>-14.20020000078396</v>
+        <v>-14.12935594977338</v>
       </c>
       <c r="K329" t="n">
-        <v>-88.46059022917059</v>
+        <v>-88.46103834330346</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>6.109054</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.321800000669896</v>
+        <v>-4.30023876775148</v>
       </c>
       <c r="K330" t="n">
-        <v>-89.07811616893106</v>
+        <v>-89.07856741126034</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -16320,10 +16320,10 @@
         <v>6.109054</v>
       </c>
       <c r="J331" t="n">
-        <v>5.865299999668281</v>
+        <v>5.836038326428049</v>
       </c>
       <c r="K331" t="n">
-        <v>-88.76935319865592</v>
+        <v>-88.769802876887</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>6.109054</v>
       </c>
       <c r="J332" t="n">
-        <v>16.05240000005581</v>
+        <v>15.97231542065668</v>
       </c>
       <c r="K332" t="n">
-        <v>-89.07811616893106</v>
+        <v>-89.07856741126034</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -16416,10 +16416,10 @@
         <v>6.109054</v>
       </c>
       <c r="J333" t="n">
-        <v>25.62209999994577</v>
+        <v>25.49427269052095</v>
       </c>
       <c r="K333" t="n">
-        <v>-88.76935319865592</v>
+        <v>-88.769802876887</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>6.109054</v>
       </c>
       <c r="J334" t="n">
-        <v>35.19179999978638</v>
+        <v>35.01622996033612</v>
       </c>
       <c r="K334" t="n">
-        <v>-88.76935319865592</v>
+        <v>-88.769802876887</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -16512,10 +16512,10 @@
         <v>6.109054</v>
       </c>
       <c r="J335" t="n">
-        <v>45.68759999931225</v>
+        <v>45.45966696564204</v>
       </c>
       <c r="K335" t="n">
-        <v>-88.46059022917059</v>
+        <v>-88.46103834330346</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J336" t="n">
-        <v>-4.013100000445787</v>
+        <v>-3.993078855593851</v>
       </c>
       <c r="K336" t="n">
-        <v>-7.255929748154049</v>
+        <v>-7.255966504461676</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -16608,10 +16608,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J337" t="n">
-        <v>3.086999999674756</v>
+        <v>3.071599119022754</v>
       </c>
       <c r="K337" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -16656,10 +16656,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J338" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K338" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -16704,10 +16704,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J339" t="n">
-        <v>23.76989999953881</v>
+        <v>23.65131321850821</v>
       </c>
       <c r="K339" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J340" t="n">
-        <v>31.17869999993282</v>
+        <v>31.02315110533155</v>
       </c>
       <c r="K340" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -16800,10 +16800,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J341" t="n">
-        <v>38.89619999941583</v>
+        <v>38.70214890318307</v>
       </c>
       <c r="K341" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J342" t="n">
-        <v>-4.321800000669896</v>
+        <v>-4.30023876775148</v>
       </c>
       <c r="K342" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -16896,10 +16896,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J343" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K343" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J344" t="n">
-        <v>10.49580000006876</v>
+        <v>10.44343700584609</v>
       </c>
       <c r="K344" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J345" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K345" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J346" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K346" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -17088,10 +17088,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J347" t="n">
-        <v>38.89619999941583</v>
+        <v>38.70214890318307</v>
       </c>
       <c r="K347" t="n">
-        <v>28.56057450600634</v>
+        <v>28.56071918508938</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>1.09964</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K348" t="n">
-        <v>-60.67192314213877</v>
+        <v>-60.67223048743409</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -17184,10 +17184,10 @@
         <v>1.09964</v>
       </c>
       <c r="J349" t="n">
-        <v>2.469599999177186</v>
+        <v>2.457279294658391</v>
       </c>
       <c r="K349" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>1.09964</v>
       </c>
       <c r="J350" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K350" t="n">
-        <v>-60.67192314213877</v>
+        <v>-60.67223048743409</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -17280,10 +17280,10 @@
         <v>1.09964</v>
       </c>
       <c r="J351" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K351" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>1.09964</v>
       </c>
       <c r="J352" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K352" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -17376,10 +17376,10 @@
         <v>1.09964</v>
       </c>
       <c r="J353" t="n">
-        <v>38.58749999919171</v>
+        <v>38.39498899102544</v>
       </c>
       <c r="K353" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>1.09964</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K354" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
         <v>1.09964</v>
       </c>
       <c r="J355" t="n">
-        <v>2.469599999177186</v>
+        <v>2.457279294658391</v>
       </c>
       <c r="K355" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>1.09964</v>
       </c>
       <c r="J356" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K356" t="n">
-        <v>5.403351926503246</v>
+        <v>5.403379298221623</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -17568,10 +17568,10 @@
         <v>1.09964</v>
       </c>
       <c r="J357" t="n">
-        <v>24.69599999917474</v>
+        <v>24.57279295394986</v>
       </c>
       <c r="K357" t="n">
-        <v>5.71211489677838</v>
+        <v>5.712143832594965</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>1.09964</v>
       </c>
       <c r="J358" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K358" t="n">
-        <v>6.329640836538847</v>
+        <v>6.329672900551844</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -17664,10 +17664,10 @@
         <v>1.09964</v>
       </c>
       <c r="J359" t="n">
-        <v>38.58749999919171</v>
+        <v>38.39498899102544</v>
       </c>
       <c r="K359" t="n">
-        <v>6.020877866263713</v>
+        <v>6.020908366178501</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K360" t="n">
-        <v>-14.04871503418209</v>
+        <v>-14.04878620064999</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -17760,10 +17760,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J361" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K361" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J362" t="n">
-        <v>10.49580000006876</v>
+        <v>10.44343700584609</v>
       </c>
       <c r="K362" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -17856,10 +17856,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J363" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K363" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J364" t="n">
-        <v>31.17869999993282</v>
+        <v>31.02315110533155</v>
       </c>
       <c r="K364" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -17952,10 +17952,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J365" t="n">
-        <v>38.89619999941583</v>
+        <v>38.70214890318307</v>
       </c>
       <c r="K365" t="n">
-        <v>-13.73995206469675</v>
+        <v>-13.74002166706646</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J366" t="n">
-        <v>-4.630499999808249</v>
+        <v>-4.607398678828769</v>
       </c>
       <c r="K366" t="n">
-        <v>21.45902624970317</v>
+        <v>21.45913495452772</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J367" t="n">
-        <v>2.778299999450647</v>
+        <v>2.764439206865126</v>
       </c>
       <c r="K367" t="n">
-        <v>21.45902624970317</v>
+        <v>21.45913495452772</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J368" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K368" t="n">
-        <v>21.45902624970317</v>
+        <v>21.45913495452772</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -18144,10 +18144,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J369" t="n">
-        <v>23.46119999931471</v>
+        <v>23.34415330635058</v>
       </c>
       <c r="K369" t="n">
-        <v>21.45902624970317</v>
+        <v>21.45913495452772</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J370" t="n">
-        <v>30.86999999970871</v>
+        <v>30.71599119317392</v>
       </c>
       <c r="K370" t="n">
-        <v>21.7677892191885</v>
+        <v>21.76789948811125</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -18240,10 +18240,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J371" t="n">
-        <v>38.27880000005337</v>
+        <v>38.08782907994815</v>
       </c>
       <c r="K371" t="n">
-        <v>21.45902624970317</v>
+        <v>21.45913495452772</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>2.6</v>
       </c>
       <c r="J372" t="n">
-        <v>-10.80450000029287</v>
+        <v>-10.75059691800372</v>
       </c>
       <c r="K372" t="n">
-        <v>-120.5719388637234</v>
+        <v>-120.5725496440686</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>2.6</v>
       </c>
       <c r="J373" t="n">
-        <v>17.5959000001893</v>
+        <v>17.5081149804627</v>
       </c>
       <c r="K373" t="n">
-        <v>-120.8807018339985</v>
+        <v>-120.8813141784419</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>1</v>
       </c>
       <c r="J374" t="n">
-        <v>-102.1797000000525</v>
+        <v>-101.6699308504173</v>
       </c>
       <c r="K374" t="n">
-        <v>-115.6317313756521</v>
+        <v>-115.6323171304261</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -18432,10 +18432,10 @@
         <v>1</v>
       </c>
       <c r="J375" t="n">
-        <v>-77.48370000033488</v>
+        <v>-77.09713789592723</v>
       </c>
       <c r="K375" t="n">
-        <v>-115.6317313756521</v>
+        <v>-115.6323171304261</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>1</v>
       </c>
       <c r="J376" t="n">
-        <v>-51.86160000093199</v>
+        <v>-51.60286520594644</v>
       </c>
       <c r="K376" t="n">
-        <v>-115.6317313756521</v>
+        <v>-115.6323171304261</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -18528,10 +18528,10 @@
         <v>1</v>
       </c>
       <c r="J377" t="n">
-        <v>-62.66610000068198</v>
+        <v>-62.35346212341</v>
       </c>
       <c r="K377" t="n">
-        <v>154.8446282665081</v>
+        <v>154.8454126617529</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>1</v>
       </c>
       <c r="J378" t="n">
-        <v>-44.76150000081144</v>
+        <v>-44.53818723132984</v>
       </c>
       <c r="K378" t="n">
-        <v>154.8446282665081</v>
+        <v>154.8454126617529</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -18624,10 +18624,10 @@
         <v>1.09964</v>
       </c>
       <c r="J379" t="n">
-        <v>-100.0188000005565</v>
+        <v>-99.51981146737633</v>
       </c>
       <c r="K379" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J380" t="n">
-        <v>-95.38830000020542</v>
+        <v>-94.91241278800739</v>
       </c>
       <c r="K380" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -18720,10 +18720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J381" t="n">
-        <v>-90.75779999980493</v>
+        <v>-90.30501410858935</v>
       </c>
       <c r="K381" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J382" t="n">
-        <v>-81.80550000041254</v>
+        <v>-81.39737666308943</v>
       </c>
       <c r="K382" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -18816,10 +18816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J383" t="n">
-        <v>-71.92710000029848</v>
+        <v>-71.56825948106753</v>
       </c>
       <c r="K383" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J384" t="n">
-        <v>-67.29659999994735</v>
+        <v>-66.9608608016986</v>
       </c>
       <c r="K384" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J385" t="n">
-        <v>-62.35740000045787</v>
+        <v>-62.04630221125237</v>
       </c>
       <c r="K385" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J386" t="n">
-        <v>-53.40509999993037</v>
+        <v>-53.13866476462302</v>
       </c>
       <c r="K386" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -19008,10 +19008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J387" t="n">
-        <v>-43.83540000008976</v>
+        <v>-43.61670749480785</v>
       </c>
       <c r="K387" t="n">
-        <v>-48.63016740803174</v>
+        <v>-48.63041375349748</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J388" t="n">
-        <v>-95.07959999993196</v>
+        <v>-94.60525287580066</v>
       </c>
       <c r="K388" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -19104,10 +19104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J389" t="n">
-        <v>-90.75779999980493</v>
+        <v>-90.30501410858935</v>
       </c>
       <c r="K389" t="n">
-        <v>64.37707874910951</v>
+        <v>64.37740486358315</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J390" t="n">
-        <v>-86.74469999995138</v>
+        <v>-86.31193525358476</v>
       </c>
       <c r="K390" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -19200,10 +19200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J391" t="n">
-        <v>-82.114200000686</v>
+        <v>-81.70453657529617</v>
       </c>
       <c r="K391" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J392" t="n">
-        <v>-77.17500000006142</v>
+        <v>-76.78997798372049</v>
       </c>
       <c r="K392" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -19296,10 +19296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J393" t="n">
-        <v>-72.5444999997103</v>
+        <v>-72.18257930435156</v>
       </c>
       <c r="K393" t="n">
-        <v>64.37707874910951</v>
+        <v>64.37740486358315</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J394" t="n">
-        <v>-67.91400000044491</v>
+        <v>-67.57518062606296</v>
       </c>
       <c r="K394" t="n">
-        <v>64.06831577883437</v>
+        <v>64.06864032920981</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J395" t="n">
-        <v>-62.97479999982033</v>
+        <v>-62.66062203448728</v>
       </c>
       <c r="K395" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J396" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K396" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -19488,10 +19488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J397" t="n">
-        <v>-53.71380000020383</v>
+        <v>-53.44582467682975</v>
       </c>
       <c r="K397" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J398" t="n">
-        <v>-49.08329999980335</v>
+        <v>-48.8384259974117</v>
       </c>
       <c r="K398" t="n">
-        <v>65.30336764808789</v>
+        <v>65.30369845485609</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -19584,10 +19584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J399" t="n">
-        <v>-44.45280000053798</v>
+        <v>-44.23102731912311</v>
       </c>
       <c r="K399" t="n">
-        <v>64.68584171938464</v>
+        <v>64.68616939795649</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J400" t="n">
-        <v>-95.69700000042953</v>
+        <v>-95.21957270016502</v>
       </c>
       <c r="K400" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -19680,10 +19680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J401" t="n">
-        <v>-90.44910000066658</v>
+        <v>-89.99785419751205</v>
       </c>
       <c r="K401" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J402" t="n">
-        <v>-86.43600000081302</v>
+        <v>-86.00477534250747</v>
       </c>
       <c r="K402" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J403" t="n">
-        <v>-81.80550000041254</v>
+        <v>-81.39737666308943</v>
       </c>
       <c r="K403" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J404" t="n">
-        <v>-71.92710000029848</v>
+        <v>-71.56825948106753</v>
       </c>
       <c r="K404" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -19872,10 +19872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J405" t="n">
-        <v>-67.29659999994735</v>
+        <v>-66.9608608016986</v>
       </c>
       <c r="K405" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J406" t="n">
-        <v>-62.35740000045787</v>
+        <v>-62.04630221125237</v>
       </c>
       <c r="K406" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -19968,10 +19968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J407" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K407" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J408" t="n">
-        <v>-53.71380000020383</v>
+        <v>-53.44582467682975</v>
       </c>
       <c r="K408" t="n">
-        <v>-39.98480431219993</v>
+        <v>-39.98500686291619</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -20064,10 +20064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J409" t="n">
-        <v>-43.83540000008976</v>
+        <v>-43.61670749480785</v>
       </c>
       <c r="K409" t="n">
-        <v>-40.29356728168526</v>
+        <v>-40.29377139649973</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J410" t="n">
-        <v>-95.38830000020542</v>
+        <v>-94.91241278800739</v>
       </c>
       <c r="K410" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -20160,10 +20160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J411" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K411" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J412" t="n">
-        <v>-81.80550000041254</v>
+        <v>-81.39737666308943</v>
       </c>
       <c r="K412" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -20256,10 +20256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J413" t="n">
-        <v>-76.86629999983731</v>
+        <v>-76.48281807156286</v>
       </c>
       <c r="K413" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J414" t="n">
-        <v>-71.92710000029848</v>
+        <v>-71.56825948106753</v>
       </c>
       <c r="K414" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J415" t="n">
-        <v>-67.29659999994735</v>
+        <v>-66.9608608016986</v>
       </c>
       <c r="K415" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J416" t="n">
-        <v>-62.35740000045787</v>
+        <v>-62.04630221125237</v>
       </c>
       <c r="K416" t="n">
-        <v>-31.3394412155783</v>
+        <v>-31.3395999715451</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -20448,10 +20448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J417" t="n">
-        <v>-58.03560000033085</v>
+        <v>-57.74606344404106</v>
       </c>
       <c r="K417" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J418" t="n">
-        <v>-53.40509999993037</v>
+        <v>-53.13866476462302</v>
       </c>
       <c r="K418" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -20544,10 +20544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J419" t="n">
-        <v>-48.774600000665</v>
+        <v>-48.53126608633441</v>
       </c>
       <c r="K419" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J420" t="n">
-        <v>-44.14410000031387</v>
+        <v>-43.92386740696548</v>
       </c>
       <c r="K420" t="n">
-        <v>-31.64820418585344</v>
+        <v>-31.64836450591844</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -20640,10 +20640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J421" t="n">
-        <v>-91.06650000007839</v>
+        <v>-90.61217402079608</v>
       </c>
       <c r="K421" t="n">
-        <v>73.02244184494133</v>
+        <v>73.02281175416444</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>1.09964</v>
       </c>
       <c r="J422" t="n">
-        <v>-86.74469999995138</v>
+        <v>-86.31193525358476</v>
       </c>
       <c r="K422" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>1.09964</v>
       </c>
       <c r="J423" t="n">
-        <v>-82.114200000686</v>
+        <v>-81.70453657529617</v>
       </c>
       <c r="K423" t="n">
-        <v>73.02244184494133</v>
+        <v>73.02281175416444</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -20784,10 +20784,10 @@
         <v>1.09964</v>
       </c>
       <c r="J424" t="n">
-        <v>-77.48370000033488</v>
+        <v>-77.09713789592723</v>
       </c>
       <c r="K424" t="n">
-        <v>73.02244184494133</v>
+        <v>73.02281175416444</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -20832,10 +20832,10 @@
         <v>1.09964</v>
       </c>
       <c r="J425" t="n">
-        <v>-72.5444999997103</v>
+        <v>-72.18257930435156</v>
       </c>
       <c r="K425" t="n">
-        <v>73.02244184494133</v>
+        <v>73.02281175416444</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>1.09964</v>
       </c>
       <c r="J426" t="n">
-        <v>-62.66610000068198</v>
+        <v>-62.35346212341</v>
       </c>
       <c r="K426" t="n">
-        <v>72.713678875456</v>
+        <v>72.71404722058091</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -20928,10 +20928,10 @@
         <v>1.09964</v>
       </c>
       <c r="J427" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K427" t="n">
-        <v>72.40491590518086</v>
+        <v>72.40528268620756</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>1.09964</v>
       </c>
       <c r="J428" t="n">
-        <v>-54.02250000042794</v>
+        <v>-53.75298458898737</v>
       </c>
       <c r="K428" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -21024,10 +21024,10 @@
         <v>1.09964</v>
       </c>
       <c r="J429" t="n">
-        <v>-49.39200000007681</v>
+        <v>-49.14558590961844</v>
       </c>
       <c r="K429" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>1.09964</v>
       </c>
       <c r="J430" t="n">
-        <v>-44.45280000053798</v>
+        <v>-44.23102731912311</v>
       </c>
       <c r="K430" t="n">
-        <v>73.33120481521647</v>
+        <v>73.33157628853778</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -21120,10 +21120,10 @@
         <v>1.09964</v>
       </c>
       <c r="J431" t="n">
-        <v>-82.114200000686</v>
+        <v>-81.70453657529617</v>
       </c>
       <c r="K431" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>1.09964</v>
       </c>
       <c r="J432" t="n">
-        <v>-77.48370000033488</v>
+        <v>-77.09713789592723</v>
       </c>
       <c r="K432" t="n">
-        <v>81.97656790078086</v>
+        <v>81.9769831688516</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -21216,10 +21216,10 @@
         <v>1.09964</v>
       </c>
       <c r="J433" t="n">
-        <v>-72.5444999997103</v>
+        <v>-72.18257930435156</v>
       </c>
       <c r="K433" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>1.09964</v>
       </c>
       <c r="J434" t="n">
-        <v>-63.28350000004444</v>
+        <v>-62.96778194664491</v>
       </c>
       <c r="K434" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
@@ -21312,10 +21312,10 @@
         <v>1.09964</v>
       </c>
       <c r="J435" t="n">
-        <v>-53.40509999993037</v>
+        <v>-53.13866476462302</v>
       </c>
       <c r="K435" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>1.09964</v>
       </c>
       <c r="J436" t="n">
-        <v>-49.70070000030093</v>
+        <v>-49.45274582177607</v>
       </c>
       <c r="K436" t="n">
-        <v>81.05027900101268</v>
+        <v>81.05068957678886</v>
       </c>
       <c r="L436" t="inlineStr">
         <is>
@@ -21408,10 +21408,10 @@
         <v>1.09964</v>
       </c>
       <c r="J437" t="n">
-        <v>-44.45280000053798</v>
+        <v>-44.23102731912311</v>
       </c>
       <c r="K437" t="n">
-        <v>81.66780494156295</v>
+        <v>81.66821864553553</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>1</v>
       </c>
       <c r="J438" t="n">
-        <v>-42.60060000018038</v>
+        <v>-42.38806784715946</v>
       </c>
       <c r="K438" t="n">
-        <v>-105.751316409777</v>
+        <v>-105.7518521134088</v>
       </c>
       <c r="L438" t="inlineStr">
         <is>
@@ -21504,10 +21504,10 @@
         <v>1</v>
       </c>
       <c r="J439" t="n">
-        <v>-103.723200000186</v>
+        <v>-103.2057304102233</v>
       </c>
       <c r="K439" t="n">
-        <v>-94.63584958649538</v>
+        <v>-94.63632898259218</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>1</v>
       </c>
       <c r="J440" t="n">
-        <v>-68.84010000008084</v>
+        <v>-68.49666036150461</v>
       </c>
       <c r="K440" t="n">
-        <v>-94.32708661622024</v>
+        <v>-94.32756444821884</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
         <v>1</v>
       </c>
       <c r="J441" t="n">
-        <v>-43.5266999998163</v>
+        <v>-43.30954758260111</v>
       </c>
       <c r="K441" t="n">
-        <v>-97.41471629527754</v>
+        <v>-97.41520976825809</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>1</v>
       </c>
       <c r="J442" t="n">
-        <v>-55.25730000033732</v>
+        <v>-54.98162423663576</v>
       </c>
       <c r="K442" t="n">
-        <v>-83.2116197818814</v>
+        <v>-83.21204130634497</v>
       </c>
       <c r="L442" t="inlineStr">
         <is>
@@ -21696,10 +21696,10 @@
         <v>1</v>
       </c>
       <c r="J443" t="n">
-        <v>-68.84010000008084</v>
+        <v>-68.49666036150461</v>
       </c>
       <c r="K443" t="n">
-        <v>-72.71367887624579</v>
+        <v>-72.71404722137071</v>
       </c>
       <c r="L443" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>1</v>
       </c>
       <c r="J444" t="n">
-        <v>-68.84010000008084</v>
+        <v>-68.49666036150461</v>
       </c>
       <c r="K444" t="n">
-        <v>-64.68584172017445</v>
+        <v>-64.6861693987463</v>
       </c>
       <c r="L444" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>1</v>
       </c>
       <c r="J445" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K445" t="n">
-        <v>-62.52450095115275</v>
+        <v>-62.52481768103726</v>
       </c>
       <c r="L445" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>1</v>
       </c>
       <c r="J446" t="n">
-        <v>-55.56600000056143</v>
+        <v>-55.28878414879339</v>
       </c>
       <c r="K446" t="n">
-        <v>-62.21573798166742</v>
+        <v>-62.21605314745372</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -21888,10 +21888,10 @@
         <v>1</v>
       </c>
       <c r="J447" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K447" t="n">
-        <v>-58.81934533233499</v>
+        <v>-58.81964329304112</v>
       </c>
       <c r="L447" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>1</v>
       </c>
       <c r="J448" t="n">
-        <v>-83.96639999995784</v>
+        <v>-83.54749604617948</v>
       </c>
       <c r="K448" t="n">
-        <v>-37.82346353212101</v>
+        <v>-37.82365513414988</v>
       </c>
       <c r="L448" t="inlineStr">
         <is>
@@ -21984,10 +21984,10 @@
         <v>1</v>
       </c>
       <c r="J449" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K449" t="n">
-        <v>-37.82346353212101</v>
+        <v>-37.82365513414988</v>
       </c>
       <c r="L449" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>1</v>
       </c>
       <c r="J450" t="n">
-        <v>-69.14880000030495</v>
+        <v>-68.80382027366224</v>
       </c>
       <c r="K450" t="n">
-        <v>-23.929129989</v>
+        <v>-23.9292512066101</v>
       </c>
       <c r="L450" t="inlineStr">
         <is>
@@ -22080,10 +22080,10 @@
         <v>1</v>
       </c>
       <c r="J451" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K451" t="n">
-        <v>-14.66624096367513</v>
+        <v>-14.6663152583394</v>
       </c>
       <c r="L451" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>1</v>
       </c>
       <c r="J452" t="n">
-        <v>-55.56600000056143</v>
+        <v>-55.28878414879339</v>
       </c>
       <c r="K452" t="n">
-        <v>-14.66624096367513</v>
+        <v>-14.6663152583394</v>
       </c>
       <c r="L452" t="inlineStr">
         <is>
@@ -22176,10 +22176,10 @@
         <v>1</v>
       </c>
       <c r="J453" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K453" t="n">
-        <v>-10.96108535591459</v>
+        <v>-10.96114088140054</v>
       </c>
       <c r="L453" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>1</v>
       </c>
       <c r="J454" t="n">
-        <v>-69.14880000030495</v>
+        <v>-68.80382027366224</v>
       </c>
       <c r="K454" t="n">
-        <v>-11.57861128461784</v>
+        <v>-11.57866993830014</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -22272,10 +22272,10 @@
         <v>1</v>
       </c>
       <c r="J455" t="n">
-        <v>-55.56600000056143</v>
+        <v>-55.28878414879339</v>
       </c>
       <c r="K455" t="n">
-        <v>-10.65232238563946</v>
+        <v>-10.6523763470272</v>
       </c>
       <c r="L455" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>1</v>
       </c>
       <c r="J456" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K456" t="n">
-        <v>7.255929735517227</v>
+        <v>7.255966491824789</v>
       </c>
       <c r="L456" t="inlineStr">
         <is>
@@ -22368,10 +22368,10 @@
         <v>1</v>
       </c>
       <c r="J457" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K457" t="n">
-        <v>7.564692705792361</v>
+        <v>7.564731026198131</v>
       </c>
       <c r="L457" t="inlineStr">
         <is>
@@ -22416,10 +22416,10 @@
         <v>1</v>
       </c>
       <c r="J458" t="n">
-        <v>-69.14880000030495</v>
+        <v>-68.80382027366224</v>
       </c>
       <c r="K458" t="n">
-        <v>10.03479644429939</v>
+        <v>10.03484727749071</v>
       </c>
       <c r="L458" t="inlineStr">
         <is>
@@ -22464,10 +22464,10 @@
         <v>1</v>
       </c>
       <c r="J459" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K459" t="n">
-        <v>20.53273733887777</v>
+        <v>20.53284135140769</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>1</v>
       </c>
       <c r="J460" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K460" t="n">
-        <v>20.8415003091529</v>
+        <v>20.84160588578103</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -22560,10 +22560,10 @@
         <v>1</v>
       </c>
       <c r="J461" t="n">
-        <v>-83.6577000008195</v>
+        <v>-83.24033613510218</v>
       </c>
       <c r="K461" t="n">
-        <v>24.23789295848533</v>
+        <v>24.23801574019364</v>
       </c>
       <c r="L461" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>1</v>
       </c>
       <c r="J462" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K462" t="n">
-        <v>24.23789295848533</v>
+        <v>24.23801574019364</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -22656,10 +22656,10 @@
         <v>1</v>
       </c>
       <c r="J463" t="n">
-        <v>-91.99259999971432</v>
+        <v>-91.53365375623773</v>
       </c>
       <c r="K463" t="n">
-        <v>37.20593759157074</v>
+        <v>37.2061260654032</v>
       </c>
       <c r="L463" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>1</v>
       </c>
       <c r="J464" t="n">
-        <v>-84.58380000045543</v>
+        <v>-84.16181587054383</v>
       </c>
       <c r="K464" t="n">
-        <v>37.20593759157074</v>
+        <v>37.2061260654032</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -22752,10 +22752,10 @@
         <v>1</v>
       </c>
       <c r="J465" t="n">
-        <v>-83.34900000054604</v>
+        <v>-82.93317622289545</v>
       </c>
       <c r="K465" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>1</v>
       </c>
       <c r="J466" t="n">
-        <v>-76.86629999983731</v>
+        <v>-76.48281807156286</v>
       </c>
       <c r="K466" t="n">
-        <v>37.20593759157074</v>
+        <v>37.2061260654032</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>
@@ -22848,10 +22848,10 @@
         <v>1</v>
       </c>
       <c r="J467" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K467" t="n">
-        <v>43.38119694889553</v>
+        <v>43.38141670469191</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>1</v>
       </c>
       <c r="J468" t="n">
-        <v>-77.48370000033488</v>
+        <v>-77.09713789592723</v>
       </c>
       <c r="K468" t="n">
-        <v>48.01264146669168</v>
+        <v>48.01288468396099</v>
       </c>
       <c r="L468" t="inlineStr">
         <is>
@@ -22944,10 +22944,10 @@
         <v>1</v>
       </c>
       <c r="J469" t="n">
-        <v>-69.45750000057841</v>
+        <v>-69.11098018586897</v>
       </c>
       <c r="K469" t="n">
-        <v>50.17398223571337</v>
+        <v>50.17423640167003</v>
       </c>
       <c r="L469" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>1</v>
       </c>
       <c r="J470" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K470" t="n">
-        <v>46.77758959743816</v>
+        <v>46.7778265583147</v>
       </c>
       <c r="L470" t="inlineStr">
         <is>
@@ -23040,10 +23040,10 @@
         <v>1</v>
       </c>
       <c r="J471" t="n">
-        <v>-93.84480000007191</v>
+        <v>-93.37661322820138</v>
       </c>
       <c r="K471" t="n">
-        <v>64.99460467781276</v>
+        <v>64.99493392048275</v>
       </c>
       <c r="L471" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>1</v>
       </c>
       <c r="J472" t="n">
-        <v>-56.49210000019735</v>
+        <v>-56.21026388423504</v>
       </c>
       <c r="K472" t="n">
-        <v>71.47862700620249</v>
+        <v>71.47898909493462</v>
       </c>
       <c r="L472" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>1</v>
       </c>
       <c r="J473" t="n">
-        <v>-84.58380000045543</v>
+        <v>-84.16181587054383</v>
       </c>
       <c r="K473" t="n">
-        <v>73.63996777443438</v>
+        <v>73.64034081185385</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>1</v>
       </c>
       <c r="J474" t="n">
-        <v>-83.96639999995784</v>
+        <v>-83.54749604617948</v>
       </c>
       <c r="K474" t="n">
-        <v>72.40491590518086</v>
+        <v>72.40528268620756</v>
       </c>
       <c r="L474" t="inlineStr">
         <is>
@@ -23232,10 +23232,10 @@
         <v>1</v>
       </c>
       <c r="J475" t="n">
-        <v>-69.45750000057841</v>
+        <v>-69.11098018586897</v>
       </c>
       <c r="K475" t="n">
-        <v>75.18378261396302</v>
+        <v>75.18416347187348</v>
       </c>
       <c r="L475" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>1</v>
       </c>
       <c r="J476" t="n">
-        <v>-100.636199999919</v>
+        <v>-100.1341312906112</v>
       </c>
       <c r="K476" t="n">
-        <v>89.07811615708404</v>
+        <v>89.07856739941326</v>
       </c>
       <c r="L476" t="inlineStr">
         <is>
@@ -23328,10 +23328,10 @@
         <v>1</v>
       </c>
       <c r="J477" t="n">
-        <v>-76.55760000069895</v>
+        <v>-76.17565816048558</v>
       </c>
       <c r="K477" t="n">
-        <v>89.07811615708404</v>
+        <v>89.07856739941326</v>
       </c>
       <c r="L477" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>1</v>
       </c>
       <c r="J478" t="n">
-        <v>-83.96639999995784</v>
+        <v>-83.54749604617948</v>
       </c>
       <c r="K478" t="n">
-        <v>92.78327176484457</v>
+        <v>92.78374177635212</v>
       </c>
       <c r="L478" t="inlineStr">
         <is>
@@ -23424,10 +23424,10 @@
         <v>1</v>
       </c>
       <c r="J479" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K479" t="n">
-        <v>91.8569828658662</v>
+        <v>91.85744818507918</v>
       </c>
       <c r="L479" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>1</v>
       </c>
       <c r="J480" t="n">
-        <v>-83.96639999995784</v>
+        <v>-83.54749604617948</v>
       </c>
       <c r="K480" t="n">
-        <v>94.32708660437322</v>
+        <v>94.32756443637174</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -23520,10 +23520,10 @@
         <v>1</v>
       </c>
       <c r="J481" t="n">
-        <v>-56.18339999992389</v>
+        <v>-55.90310397202831</v>
       </c>
       <c r="K481" t="n">
-        <v>95.56213848468396</v>
+        <v>95.56262257307532</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>1</v>
       </c>
       <c r="J482" t="n">
-        <v>-69.76620000080251</v>
+        <v>-69.4181400980266</v>
       </c>
       <c r="K482" t="n">
-        <v>105.4425534505591</v>
+        <v>105.4430875900927</v>
       </c>
       <c r="L482" t="inlineStr">
         <is>
@@ -23616,10 +23616,10 @@
         <v>1</v>
       </c>
       <c r="J483" t="n">
-        <v>-49.39200000007681</v>
+        <v>-49.14558590961844</v>
       </c>
       <c r="K483" t="n">
-        <v>104.2075015702484</v>
+        <v>104.2080294533891</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>1</v>
       </c>
       <c r="J484" t="n">
-        <v>-44.45280000053798</v>
+        <v>-44.23102731912311</v>
       </c>
       <c r="K484" t="n">
-        <v>100.8111089319732</v>
+        <v>100.8116196100338</v>
       </c>
       <c r="L484" t="inlineStr">
         <is>
@@ -23712,10 +23712,10 @@
         <v>1</v>
       </c>
       <c r="J485" t="n">
-        <v>-42.60060000018038</v>
+        <v>-42.38806784715946</v>
       </c>
       <c r="K485" t="n">
-        <v>100.8111089319732</v>
+        <v>100.8116196100338</v>
       </c>
       <c r="L485" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>1</v>
       </c>
       <c r="J486" t="n">
-        <v>-34.88310000069738</v>
+        <v>-34.70907004930794</v>
       </c>
       <c r="K486" t="n">
-        <v>104.5162645397337</v>
+        <v>104.5167939869727</v>
       </c>
       <c r="L486" t="inlineStr">
         <is>
@@ -23808,10 +23808,10 @@
         <v>1</v>
       </c>
       <c r="J487" t="n">
-        <v>-56.18339999992389</v>
+        <v>-55.90310397202831</v>
       </c>
       <c r="K487" t="n">
-        <v>116.2492573146228</v>
+        <v>116.2498461975932</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>1</v>
       </c>
       <c r="J488" t="n">
-        <v>-69.76620000080251</v>
+        <v>-69.4181400980266</v>
       </c>
       <c r="K488" t="n">
-        <v>128.9085389892801</v>
+        <v>128.9091920002765</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -23904,10 +23904,10 @@
         <v>1</v>
       </c>
       <c r="J489" t="n">
-        <v>-74.3967000000679</v>
+        <v>-74.0255387763152</v>
       </c>
       <c r="K489" t="n">
-        <v>143.7291614321693</v>
+        <v>143.729889519879</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>1</v>
       </c>
       <c r="J490" t="n">
-        <v>-74.3967000000679</v>
+        <v>-74.0255387763152</v>
       </c>
       <c r="K490" t="n">
-        <v>151.1394726587476</v>
+        <v>151.140238284814</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
@@ -24000,10 +24000,10 @@
         <v>1</v>
       </c>
       <c r="J491" t="n">
-        <v>-69.76620000080251</v>
+        <v>-69.4181400980266</v>
       </c>
       <c r="K491" t="n">
-        <v>152.6832874982762</v>
+        <v>152.6840609448337</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>1</v>
       </c>
       <c r="J492" t="n">
-        <v>-61.43130000082195</v>
+        <v>-61.12482247581072</v>
       </c>
       <c r="K492" t="n">
-        <v>168.1214358698687</v>
+        <v>168.1222875213358</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -24096,10 +24096,10 @@
         <v>1</v>
       </c>
       <c r="J493" t="n">
-        <v>-69.76620000080251</v>
+        <v>-69.4181400980266</v>
       </c>
       <c r="K493" t="n">
-        <v>177.3843249062508</v>
+        <v>177.3852234806638</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>1</v>
       </c>
       <c r="J494" t="n">
-        <v>-35.8092000003333</v>
+        <v>-35.63054978474959</v>
       </c>
       <c r="K494" t="n">
-        <v>-124.277094471484</v>
+        <v>-124.2777240210074</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -24192,10 +24192,10 @@
         <v>1</v>
       </c>
       <c r="J495" t="n">
-        <v>-31.48740000020628</v>
+        <v>-31.33031101753828</v>
       </c>
       <c r="K495" t="n">
-        <v>-125.2033833823094</v>
+        <v>-125.2040176241275</v>
       </c>
       <c r="L495" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>1</v>
       </c>
       <c r="J496" t="n">
-        <v>-35.8092000003333</v>
+        <v>-35.63054978474959</v>
       </c>
       <c r="K496" t="n">
-        <v>-112.2353387381667</v>
+        <v>-112.2359072878606</v>
       </c>
       <c r="L496" t="inlineStr">
         <is>
@@ -24288,10 +24288,10 @@
         <v>1</v>
       </c>
       <c r="J497" t="n">
-        <v>-31.17869999993282</v>
+        <v>-31.02315110533155</v>
       </c>
       <c r="K497" t="n">
-        <v>-97.72347925449546</v>
+        <v>-97.72397429157415</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -24336,10 +24336,10 @@
         <v>1</v>
       </c>
       <c r="J498" t="n">
-        <v>-30.86999999970871</v>
+        <v>-30.71599119317392</v>
       </c>
       <c r="K498" t="n">
-        <v>-94.63584958649538</v>
+        <v>-94.63632898259218</v>
       </c>
       <c r="L498" t="inlineStr">
         <is>
@@ -24384,10 +24384,10 @@
         <v>1</v>
       </c>
       <c r="J499" t="n">
-        <v>-36.11790000055741</v>
+        <v>-35.93770969690722</v>
       </c>
       <c r="K499" t="n">
-        <v>-88.15182725889545</v>
+        <v>-88.15227380893012</v>
       </c>
       <c r="L499" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>1</v>
       </c>
       <c r="J500" t="n">
-        <v>-32.72220000006631</v>
+        <v>-32.55895066513756</v>
       </c>
       <c r="K500" t="n">
-        <v>-79.81522713254897</v>
+        <v>-79.81563145193236</v>
       </c>
       <c r="L500" t="inlineStr">
         <is>
@@ -24480,10 +24480,10 @@
         <v>1</v>
       </c>
       <c r="J501" t="n">
-        <v>-35.8092000003333</v>
+        <v>-35.63054978474959</v>
       </c>
       <c r="K501" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>1</v>
       </c>
       <c r="J502" t="n">
-        <v>-36.11790000055741</v>
+        <v>-35.93770969690722</v>
       </c>
       <c r="K502" t="n">
-        <v>-31.03067824530317</v>
+        <v>-31.03083543717176</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -24576,10 +24576,10 @@
         <v>1</v>
       </c>
       <c r="J503" t="n">
-        <v>-41.67450000054446</v>
+        <v>-41.46658811171781</v>
       </c>
       <c r="K503" t="n">
-        <v>-9.417270516385944</v>
+        <v>-9.417318221380908</v>
       </c>
       <c r="L503" t="inlineStr">
         <is>
@@ -24624,10 +24624,10 @@
         <v>1</v>
       </c>
       <c r="J504" t="n">
-        <v>-36.11790000055741</v>
+        <v>-35.93770969690722</v>
       </c>
       <c r="K504" t="n">
-        <v>-0.771907419764324</v>
+        <v>-0.7719113300098148</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -24672,10 +24672,10 @@
         <v>1</v>
       </c>
       <c r="J505" t="n">
-        <v>-41.36580000032035</v>
+        <v>-41.15942819956018</v>
       </c>
       <c r="K505" t="n">
-        <v>12.19613721332108</v>
+        <v>12.19619899519974</v>
       </c>
       <c r="L505" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>1</v>
       </c>
       <c r="J506" t="n">
-        <v>-36.42660000083087</v>
+        <v>-36.24486960911396</v>
       </c>
       <c r="K506" t="n">
-        <v>29.17810043549939</v>
+        <v>29.17824824277879</v>
       </c>
       <c r="L506" t="inlineStr">
         <is>
@@ -24768,10 +24768,10 @@
         <v>1</v>
       </c>
       <c r="J507" t="n">
-        <v>-42.29189999995627</v>
+        <v>-42.08090793500183</v>
       </c>
       <c r="K507" t="n">
-        <v>39.36727837085986</v>
+        <v>39.3674777933797</v>
       </c>
       <c r="L507" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>1</v>
       </c>
       <c r="J508" t="n">
-        <v>-36.42660000083087</v>
+        <v>-36.24486960911396</v>
       </c>
       <c r="K508" t="n">
-        <v>59.12810830182032</v>
+        <v>59.12840782662466</v>
       </c>
       <c r="L508" t="inlineStr">
         <is>
@@ -24864,10 +24864,10 @@
         <v>1</v>
       </c>
       <c r="J509" t="n">
-        <v>-41.98320000081792</v>
+        <v>-41.77374802392454</v>
       </c>
       <c r="K509" t="n">
-        <v>70.24357513615917</v>
+        <v>70.24393096849852</v>
       </c>
       <c r="L509" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>1</v>
       </c>
       <c r="J510" t="n">
-        <v>-36.73529999991987</v>
+        <v>-36.55202952014213</v>
       </c>
       <c r="K510" t="n">
-        <v>89.07811615708404</v>
+        <v>89.07856739941326</v>
       </c>
       <c r="L510" t="inlineStr">
         <is>
@@ -24960,10 +24960,10 @@
         <v>6.8</v>
       </c>
       <c r="J511" t="n">
-        <v>-100.0188000005565</v>
+        <v>-99.51981146737633</v>
       </c>
       <c r="K511" t="n">
-        <v>-84.44667165113491</v>
+        <v>-84.44709943199126</v>
       </c>
       <c r="L511" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>6.8</v>
       </c>
       <c r="J512" t="n">
-        <v>-43.83540000008976</v>
+        <v>-43.61670749480785</v>
       </c>
       <c r="K512" t="n">
-        <v>-84.75543462062025</v>
+        <v>-84.75586396557479</v>
       </c>
       <c r="L512" t="inlineStr">
         <is>
@@ -25056,10 +25056,10 @@
         <v>6.8</v>
       </c>
       <c r="J513" t="n">
-        <v>-40.43970000068443</v>
+        <v>-40.23794846411853</v>
       </c>
       <c r="K513" t="n">
-        <v>117.7930721541514</v>
+        <v>117.7936688576128</v>
       </c>
       <c r="L513" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J514" t="n">
-        <v>-93.53610000093357</v>
+        <v>-93.06945331712409</v>
       </c>
       <c r="K514" t="n">
-        <v>-21.7677892199783</v>
+        <v>-21.76789948890106</v>
       </c>
       <c r="L514" t="inlineStr">
         <is>
@@ -25152,10 +25152,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J515" t="n">
-        <v>-86.43600000081302</v>
+        <v>-86.00477534250747</v>
       </c>
       <c r="K515" t="n">
-        <v>-21.7677892199783</v>
+        <v>-21.76789948890106</v>
       </c>
       <c r="L515" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J516" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K516" t="n">
-        <v>-21.7677892199783</v>
+        <v>-21.76789948890106</v>
       </c>
       <c r="L516" t="inlineStr">
         <is>
@@ -25248,10 +25248,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J517" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K517" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L517" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J518" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K518" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L518" t="inlineStr">
         <is>
@@ -25344,10 +25344,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J519" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K519" t="n">
-        <v>-21.45902625049297</v>
+        <v>-21.45913495531752</v>
       </c>
       <c r="L519" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J520" t="n">
-        <v>-94.77089999970784</v>
+        <v>-94.29809296364303</v>
       </c>
       <c r="K520" t="n">
-        <v>11.88737425410317</v>
+        <v>11.88743447188368</v>
       </c>
       <c r="L520" t="inlineStr">
         <is>
@@ -25440,10 +25440,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J521" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K521" t="n">
-        <v>11.88737425410317</v>
+        <v>11.88743447188368</v>
       </c>
       <c r="L521" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J522" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K522" t="n">
-        <v>12.50490018280642</v>
+        <v>12.50496352878328</v>
       </c>
       <c r="L522" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J523" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K523" t="n">
-        <v>12.81366315308155</v>
+        <v>12.81372806315662</v>
       </c>
       <c r="L523" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J524" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K524" t="n">
-        <v>12.19613721332108</v>
+        <v>12.19619899519974</v>
       </c>
       <c r="L524" t="inlineStr">
         <is>
@@ -25632,10 +25632,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J525" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K525" t="n">
-        <v>12.81366315308155</v>
+        <v>12.81372806315662</v>
       </c>
       <c r="L525" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J526" t="n">
-        <v>-66.06180000008732</v>
+        <v>-65.73222115409932</v>
       </c>
       <c r="K526" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L526" t="inlineStr">
         <is>
@@ -25728,10 +25728,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J527" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K527" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L527" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J528" t="n">
-        <v>-50.93550000021031</v>
+        <v>-50.68138546942446</v>
       </c>
       <c r="K528" t="n">
-        <v>54.80542675350951</v>
+        <v>54.80570438093911</v>
       </c>
       <c r="L528" t="inlineStr">
         <is>
@@ -25824,10 +25824,10 @@
         <v>2.6</v>
       </c>
       <c r="J529" t="n">
-        <v>-72.8531999999344</v>
+        <v>-72.48973921650918</v>
       </c>
       <c r="K529" t="n">
-        <v>160.4023616840724</v>
+        <v>160.4031742330847</v>
       </c>
       <c r="L529" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>2.6</v>
       </c>
       <c r="J530" t="n">
-        <v>-44.76150000081144</v>
+        <v>-44.53818723132984</v>
       </c>
       <c r="K530" t="n">
-        <v>160.4023616840724</v>
+        <v>160.4031742330847</v>
       </c>
       <c r="L530" t="inlineStr">
         <is>
@@ -25920,10 +25920,10 @@
         <v>2.6</v>
       </c>
       <c r="J531" t="n">
-        <v>-100.0188000005565</v>
+        <v>-99.51981146737633</v>
       </c>
       <c r="K531" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L531" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>2.6</v>
       </c>
       <c r="J532" t="n">
-        <v>-71.92710000029848</v>
+        <v>-71.56825948106753</v>
       </c>
       <c r="K532" t="n">
-        <v>-60.67192314213877</v>
+        <v>-60.67223048743409</v>
       </c>
       <c r="L532" t="inlineStr">
         <is>
@@ -26016,10 +26016,10 @@
         <v>2.6</v>
       </c>
       <c r="J533" t="n">
-        <v>-43.83540000008976</v>
+        <v>-43.61670749480785</v>
       </c>
       <c r="K533" t="n">
-        <v>-60.36316017186363</v>
+        <v>-60.36346595306075</v>
       </c>
       <c r="L533" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>2.6</v>
       </c>
       <c r="J534" t="n">
-        <v>-100.32750000083</v>
+        <v>-99.82697137958306</v>
       </c>
       <c r="K534" t="n">
-        <v>4.785825997010199</v>
+        <v>4.785850240532214</v>
       </c>
       <c r="L534" t="inlineStr">
         <is>
@@ -26112,10 +26112,10 @@
         <v>2.6</v>
       </c>
       <c r="J535" t="n">
-        <v>-72.5444999997103</v>
+        <v>-72.18257930435156</v>
       </c>
       <c r="K535" t="n">
-        <v>5.403351926503246</v>
+        <v>5.403379298221623</v>
       </c>
       <c r="L535" t="inlineStr">
         <is>
@@ -26160,10 +26160,10 @@
         <v>2.6</v>
       </c>
       <c r="J536" t="n">
-        <v>-44.14410000031387</v>
+        <v>-43.92386740696548</v>
       </c>
       <c r="K536" t="n">
-        <v>5.403351926503246</v>
+        <v>5.403379298221623</v>
       </c>
       <c r="L536" t="inlineStr">
         <is>
@@ -26208,10 +26208,10 @@
         <v>2.6</v>
       </c>
       <c r="J537" t="n">
-        <v>-100.636199999919</v>
+        <v>-100.1341312906112</v>
       </c>
       <c r="K537" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L537" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>2.6</v>
       </c>
       <c r="J538" t="n">
-        <v>-72.5444999997103</v>
+        <v>-72.18257930435156</v>
       </c>
       <c r="K538" t="n">
-        <v>93.70956067566998</v>
+        <v>93.71003537947215</v>
       </c>
       <c r="L538" t="inlineStr">
         <is>
@@ -26304,10 +26304,10 @@
         <v>2.6</v>
       </c>
       <c r="J539" t="n">
-        <v>-44.76150000081144</v>
+        <v>-44.53818723132984</v>
       </c>
       <c r="K539" t="n">
-        <v>94.01832364515531</v>
+        <v>94.01879991305569</v>
       </c>
       <c r="L539" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J540" t="n">
-        <v>-93.53610000093357</v>
+        <v>-93.06945331712409</v>
       </c>
       <c r="K540" t="n">
-        <v>-85.68172352038843</v>
+        <v>-85.68215755763754</v>
       </c>
       <c r="L540" t="inlineStr">
         <is>
@@ -26400,10 +26400,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J541" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K541" t="n">
-        <v>-85.68172352038843</v>
+        <v>-85.68215755763754</v>
       </c>
       <c r="L541" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J542" t="n">
-        <v>-78.40979999992145</v>
+        <v>-78.01861763131977</v>
       </c>
       <c r="K542" t="n">
-        <v>-85.68172352038843</v>
+        <v>-85.68215755763754</v>
       </c>
       <c r="L542" t="inlineStr">
         <is>
@@ -26496,10 +26496,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J543" t="n">
-        <v>-65.4444000006755</v>
+        <v>-65.11790133081529</v>
       </c>
       <c r="K543" t="n">
-        <v>-85.68172352038843</v>
+        <v>-85.68215755763754</v>
       </c>
       <c r="L543" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J544" t="n">
-        <v>-57.72690000005739</v>
+        <v>-57.43890353183432</v>
       </c>
       <c r="K544" t="n">
-        <v>-85.68172352038843</v>
+        <v>-85.68215755763754</v>
       </c>
       <c r="L544" t="inlineStr">
         <is>
@@ -26592,10 +26592,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J545" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K545" t="n">
-        <v>-85.37296055011329</v>
+        <v>-85.3733930232642</v>
       </c>
       <c r="L545" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J546" t="n">
-        <v>-94.46220000056948</v>
+        <v>-93.99093305256574</v>
       </c>
       <c r="K546" t="n">
-        <v>-66.53841952918843</v>
+        <v>-66.53875659234947</v>
       </c>
       <c r="L546" t="inlineStr">
         <is>
@@ -26688,10 +26688,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J547" t="n">
-        <v>-85.50990000009135</v>
+        <v>-85.08329560598548</v>
       </c>
       <c r="K547" t="n">
-        <v>-66.84718249946356</v>
+        <v>-66.84752112672281</v>
       </c>
       <c r="L547" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J548" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K548" t="n">
-        <v>-66.53841952918843</v>
+        <v>-66.53875659234947</v>
       </c>
       <c r="L548" t="inlineStr">
         <is>
@@ -26784,10 +26784,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J549" t="n">
-        <v>-65.4444000006755</v>
+        <v>-65.11790133081529</v>
       </c>
       <c r="K549" t="n">
-        <v>-66.53841952918843</v>
+        <v>-66.53875659234947</v>
       </c>
       <c r="L549" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J550" t="n">
-        <v>-58.03560000033085</v>
+        <v>-57.74606344404106</v>
       </c>
       <c r="K550" t="n">
-        <v>-66.53841952918843</v>
+        <v>-66.53875659234947</v>
       </c>
       <c r="L550" t="inlineStr">
         <is>
@@ -26880,10 +26880,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J551" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K551" t="n">
-        <v>-66.53841952918843</v>
+        <v>-66.53875659234947</v>
       </c>
       <c r="L551" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J552" t="n">
-        <v>-66.06180000008732</v>
+        <v>-65.73222115409932</v>
       </c>
       <c r="K552" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L552" t="inlineStr">
         <is>
@@ -26976,10 +26976,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J553" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K553" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L553" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J554" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K554" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L554" t="inlineStr">
         <is>
@@ -27072,10 +27072,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J555" t="n">
-        <v>-66.37050000031142</v>
+        <v>-66.03938106625694</v>
       </c>
       <c r="K555" t="n">
-        <v>118.7193610539196</v>
+        <v>118.7199624496756</v>
       </c>
       <c r="L555" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J556" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K556" t="n">
-        <v>118.7193610539196</v>
+        <v>118.7199624496756</v>
       </c>
       <c r="L556" t="inlineStr">
         <is>
@@ -27168,10 +27168,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J557" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K557" t="n">
-        <v>118.7193610539196</v>
+        <v>118.7199624496756</v>
       </c>
       <c r="L557" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>1</v>
       </c>
       <c r="J558" t="n">
-        <v>-112.0581000001666</v>
+        <v>-111.4990480324392</v>
       </c>
       <c r="K558" t="n">
-        <v>-104.5162645515807</v>
+        <v>-104.5167939988198</v>
       </c>
       <c r="L558" t="inlineStr">
         <is>
@@ -27264,10 +27264,10 @@
         <v>1</v>
       </c>
       <c r="J559" t="n">
-        <v>-112.36680000044</v>
+        <v>-111.8062079446459</v>
       </c>
       <c r="K559" t="n">
-        <v>-100.8111089327629</v>
+        <v>-100.8116196108236</v>
       </c>
       <c r="L559" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>1</v>
       </c>
       <c r="J560" t="n">
-        <v>-114.2189999997119</v>
+        <v>-113.6491674155292</v>
       </c>
       <c r="K560" t="n">
-        <v>-98.95853113480619</v>
+        <v>-98.95903242827772</v>
       </c>
       <c r="L560" t="inlineStr">
         <is>
@@ -27360,10 +27360,10 @@
         <v>1</v>
       </c>
       <c r="J561" t="n">
-        <v>-91.68390000057596</v>
+        <v>-91.22649384516043</v>
       </c>
       <c r="K561" t="n">
-        <v>-95.25337551519863</v>
+        <v>-95.25385803949177</v>
       </c>
       <c r="L561" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>1</v>
       </c>
       <c r="J562" t="n">
-        <v>-71.92710000029848</v>
+        <v>-71.56825948106753</v>
       </c>
       <c r="K562" t="n">
-        <v>-95.56213848547375</v>
+        <v>-95.56262257386511</v>
       </c>
       <c r="L562" t="inlineStr">
         <is>
@@ -27456,10 +27456,10 @@
         <v>1</v>
       </c>
       <c r="J563" t="n">
-        <v>-62.04870000018441</v>
+        <v>-61.73914229904563</v>
       </c>
       <c r="K563" t="n">
-        <v>-95.25337551519863</v>
+        <v>-95.25385803949177</v>
       </c>
       <c r="L563" t="inlineStr">
         <is>
@@ -27504,10 +27504,10 @@
         <v>1</v>
       </c>
       <c r="J564" t="n">
-        <v>-40.74839999982278</v>
+        <v>-40.54510837519582</v>
       </c>
       <c r="K564" t="n">
-        <v>-97.72347925449546</v>
+        <v>-97.72397429157415</v>
       </c>
       <c r="L564" t="inlineStr">
         <is>
@@ -27552,10 +27552,10 @@
         <v>1</v>
       </c>
       <c r="J565" t="n">
-        <v>-43.5266999998163</v>
+        <v>-43.30954758260111</v>
       </c>
       <c r="K565" t="n">
-        <v>-92.47450880720626</v>
+        <v>-92.47497725461567</v>
       </c>
       <c r="L565" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>1</v>
       </c>
       <c r="J566" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K566" t="n">
-        <v>46.16006365767769</v>
+        <v>46.16029749035783</v>
       </c>
       <c r="L566" t="inlineStr">
         <is>
@@ -27648,10 +27648,10 @@
         <v>1</v>
       </c>
       <c r="J567" t="n">
-        <v>-85.50990000009135</v>
+        <v>-85.08329560598548</v>
       </c>
       <c r="K567" t="n">
-        <v>45.85130068740256</v>
+        <v>45.85153295598448</v>
       </c>
       <c r="L567" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>1</v>
       </c>
       <c r="J568" t="n">
-        <v>-79.64459999983083</v>
+        <v>-79.24725727896816</v>
       </c>
       <c r="K568" t="n">
-        <v>46.16006365767769</v>
+        <v>46.16029749035783</v>
       </c>
       <c r="L568" t="inlineStr">
         <is>
@@ -27744,10 +27744,10 @@
         <v>1</v>
       </c>
       <c r="J569" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K569" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L569" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>1</v>
       </c>
       <c r="J570" t="n">
-        <v>-86.74469999995138</v>
+        <v>-86.31193525358476</v>
       </c>
       <c r="K570" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L570" t="inlineStr">
         <is>
@@ -27840,10 +27840,10 @@
         <v>1</v>
       </c>
       <c r="J571" t="n">
-        <v>-79.02720000041901</v>
+        <v>-78.63293745568414</v>
       </c>
       <c r="K571" t="n">
-        <v>54.80542675350951</v>
+        <v>54.80570438093911</v>
       </c>
       <c r="L571" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>1</v>
       </c>
       <c r="J572" t="n">
-        <v>-100.32750000083</v>
+        <v>-99.82697137958306</v>
       </c>
       <c r="K572" t="n">
-        <v>54.49666378323437</v>
+        <v>54.49693984656577</v>
       </c>
       <c r="L572" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>1</v>
       </c>
       <c r="J573" t="n">
-        <v>-100.9449000001925</v>
+        <v>-100.441291202818</v>
       </c>
       <c r="K573" t="n">
-        <v>64.37707874910951</v>
+        <v>64.37740486358315</v>
       </c>
       <c r="L573" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>1</v>
       </c>
       <c r="J574" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K574" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L574" t="inlineStr">
         <is>
@@ -28032,10 +28032,10 @@
         <v>1</v>
       </c>
       <c r="J575" t="n">
-        <v>-87.05340000017549</v>
+        <v>-86.61909516574239</v>
       </c>
       <c r="K575" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L575" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>1</v>
       </c>
       <c r="J576" t="n">
-        <v>-79.33590000069248</v>
+        <v>-78.94009736789087</v>
       </c>
       <c r="K576" t="n">
-        <v>99.57605706271963</v>
+        <v>99.57656148438751</v>
       </c>
       <c r="L576" t="inlineStr">
         <is>
@@ -28128,10 +28128,10 @@
         <v>1</v>
       </c>
       <c r="J577" t="n">
-        <v>-94.46220000056948</v>
+        <v>-93.99093305256574</v>
       </c>
       <c r="K577" t="n">
-        <v>106.3688423495375</v>
+        <v>106.3693811813656</v>
       </c>
       <c r="L577" t="inlineStr">
         <is>
@@ -28176,10 +28176,10 @@
         <v>1</v>
       </c>
       <c r="J578" t="n">
-        <v>-86.74469999995138</v>
+        <v>-86.31193525358476</v>
       </c>
       <c r="K578" t="n">
-        <v>106.3688423495375</v>
+        <v>106.3693811813656</v>
       </c>
       <c r="L578" t="inlineStr">
         <is>
@@ -28224,10 +28224,10 @@
         <v>1</v>
       </c>
       <c r="J579" t="n">
-        <v>-79.33590000069248</v>
+        <v>-78.94009736789087</v>
       </c>
       <c r="K579" t="n">
-        <v>106.3688423495375</v>
+        <v>106.3693811813656</v>
       </c>
       <c r="L579" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>1</v>
       </c>
       <c r="J580" t="n">
-        <v>-94.46220000056948</v>
+        <v>-93.99093305256574</v>
       </c>
       <c r="K580" t="n">
-        <v>112.2353387255299</v>
+        <v>112.2359072752237</v>
       </c>
       <c r="L580" t="inlineStr">
         <is>
@@ -28320,10 +28320,10 @@
         <v>1</v>
       </c>
       <c r="J581" t="n">
-        <v>-86.74469999995138</v>
+        <v>-86.31193525358476</v>
       </c>
       <c r="K581" t="n">
-        <v>112.544101695805</v>
+        <v>112.5446718095971</v>
       </c>
       <c r="L581" t="inlineStr">
         <is>
@@ -28368,10 +28368,10 @@
         <v>1</v>
       </c>
       <c r="J582" t="n">
-        <v>-79.33590000069248</v>
+        <v>-78.94009736789087</v>
       </c>
       <c r="K582" t="n">
-        <v>112.2353387255299</v>
+        <v>112.2359072752237</v>
       </c>
       <c r="L582" t="inlineStr">
         <is>
@@ -28416,10 +28416,10 @@
         <v>1</v>
       </c>
       <c r="J583" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K583" t="n">
-        <v>127.6734871089694</v>
+        <v>127.6741338635729</v>
       </c>
       <c r="L583" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J584" t="n">
-        <v>-92.91870000043599</v>
+        <v>-92.45513349275971</v>
       </c>
       <c r="K584" t="n">
-        <v>39.36727837085986</v>
+        <v>39.3674777933797</v>
       </c>
       <c r="L584" t="inlineStr">
         <is>
@@ -28512,10 +28512,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J585" t="n">
-        <v>-85.50990000009135</v>
+        <v>-85.08329560598548</v>
       </c>
       <c r="K585" t="n">
-        <v>39.36727837085986</v>
+        <v>39.3674777933797</v>
       </c>
       <c r="L585" t="inlineStr">
         <is>
@@ -28560,10 +28560,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J586" t="n">
-        <v>-79.33590000069248</v>
+        <v>-78.94009736789087</v>
       </c>
       <c r="K586" t="n">
-        <v>39.05851540058472</v>
+        <v>39.05871325900636</v>
       </c>
       <c r="L586" t="inlineStr">
         <is>
@@ -28608,10 +28608,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J587" t="n">
-        <v>-107.1189000006771</v>
+        <v>-106.5844894419929</v>
       </c>
       <c r="K587" t="n">
-        <v>-92.78327177669159</v>
+        <v>-92.78374178819921</v>
       </c>
       <c r="L587" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J588" t="n">
-        <v>-96.93180000028956</v>
+        <v>-96.4482123477643</v>
       </c>
       <c r="K588" t="n">
-        <v>-92.78327177669159</v>
+        <v>-92.78374178819921</v>
       </c>
       <c r="L588" t="inlineStr">
         <is>
@@ -28704,10 +28704,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J589" t="n">
-        <v>-87.05340000017549</v>
+        <v>-86.61909516574239</v>
       </c>
       <c r="K589" t="n">
-        <v>-92.78327177669159</v>
+        <v>-92.78374178819921</v>
       </c>
       <c r="L589" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J590" t="n">
-        <v>-76.86629999983731</v>
+        <v>-76.48281807156286</v>
       </c>
       <c r="K590" t="n">
-        <v>-92.78327177669159</v>
+        <v>-92.78374178819921</v>
       </c>
       <c r="L590" t="inlineStr">
         <is>
@@ -28800,10 +28800,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J591" t="n">
-        <v>-66.98790000080899</v>
+        <v>-66.65370089062131</v>
       </c>
       <c r="K591" t="n">
-        <v>-92.78327177669159</v>
+        <v>-92.78374178819921</v>
       </c>
       <c r="L591" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J592" t="n">
-        <v>-56.80080000042147</v>
+        <v>-56.51742379639267</v>
       </c>
       <c r="K592" t="n">
-        <v>-92.47450880720626</v>
+        <v>-92.47497725461567</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -28896,10 +28896,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J593" t="n">
-        <v>-46.9224000003074</v>
+        <v>-46.68830661437077</v>
       </c>
       <c r="K593" t="n">
-        <v>-92.47450880720626</v>
+        <v>-92.47497725461567</v>
       </c>
       <c r="L593" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J594" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K594" t="n">
-        <v>126.7471982092012</v>
+        <v>126.7478402715102</v>
       </c>
       <c r="L594" t="inlineStr">
         <is>
@@ -28992,10 +28992,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J595" t="n">
-        <v>-55.87470000078554</v>
+        <v>-55.59594406095102</v>
       </c>
       <c r="K595" t="n">
-        <v>126.7471982092012</v>
+        <v>126.7478402715102</v>
       </c>
       <c r="L595" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J596" t="n">
-        <v>-41.05710000004689</v>
+        <v>-40.85226828735345</v>
       </c>
       <c r="K596" t="n">
-        <v>126.7471982092012</v>
+        <v>126.7478402715102</v>
       </c>
       <c r="L596" t="inlineStr">
         <is>
@@ -29088,10 +29088,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J597" t="n">
-        <v>-35.8092000003333</v>
+        <v>-35.63054978474959</v>
       </c>
       <c r="K597" t="n">
-        <v>126.7471982092012</v>
+        <v>126.7478402715102</v>
       </c>
       <c r="L597" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J598" t="n">
-        <v>-66.67920000058488</v>
+        <v>-66.34654097846368</v>
       </c>
       <c r="K598" t="n">
-        <v>174.6054581974686</v>
+        <v>174.6063426949979</v>
       </c>
       <c r="L598" t="inlineStr">
         <is>
@@ -29184,10 +29184,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J599" t="n">
-        <v>-58.96169999996678</v>
+        <v>-58.66754317948271</v>
       </c>
       <c r="K599" t="n">
-        <v>174.6054581974686</v>
+        <v>174.6063426949979</v>
       </c>
       <c r="L599" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J600" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K600" t="n">
-        <v>174.6054581974686</v>
+        <v>174.6063426949979</v>
       </c>
       <c r="L600" t="inlineStr">
         <is>
@@ -29280,10 +29280,10 @@
         <v>6.109054</v>
       </c>
       <c r="J601" t="n">
-        <v>-106.1927999999554</v>
+        <v>-105.6630097054709</v>
       </c>
       <c r="K601" t="n">
-        <v>-102.9724497128419</v>
+        <v>-102.9729713395899</v>
       </c>
       <c r="L601" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6.109054</v>
       </c>
       <c r="J602" t="n">
-        <v>-96.31439999984133</v>
+        <v>-95.83389252344904</v>
       </c>
       <c r="K602" t="n">
-        <v>-103.28121267127</v>
+        <v>-103.2817358621162</v>
       </c>
       <c r="L602" t="inlineStr">
         <is>
@@ -29376,10 +29376,10 @@
         <v>6.109054</v>
       </c>
       <c r="J603" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K603" t="n">
-        <v>-102.9724497128419</v>
+        <v>-102.9729713395899</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6.109054</v>
       </c>
       <c r="J604" t="n">
-        <v>-76.24890000042549</v>
+        <v>-75.86849824827884</v>
       </c>
       <c r="K604" t="n">
-        <v>-102.9724497128419</v>
+        <v>-102.9729713395899</v>
       </c>
       <c r="L604" t="inlineStr">
         <is>
@@ -29472,10 +29472,10 @@
         <v>6.109054</v>
       </c>
       <c r="J605" t="n">
-        <v>-66.06180000008732</v>
+        <v>-65.73222115409932</v>
       </c>
       <c r="K605" t="n">
-        <v>-102.9724497128419</v>
+        <v>-102.9729713395899</v>
       </c>
       <c r="L605" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>6.109054</v>
       </c>
       <c r="J606" t="n">
-        <v>-56.18339999992389</v>
+        <v>-55.90310397202831</v>
       </c>
       <c r="K606" t="n">
-        <v>-103.28121267127</v>
+        <v>-103.2817358621162</v>
       </c>
       <c r="L606" t="inlineStr">
         <is>
@@ -29568,10 +29568,10 @@
         <v>6.109054</v>
       </c>
       <c r="J607" t="n">
-        <v>-45.99630000067148</v>
+        <v>-45.76682687892912</v>
       </c>
       <c r="K607" t="n">
-        <v>-102.9724497128419</v>
+        <v>-102.9729713395899</v>
       </c>
       <c r="L607" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6.109054</v>
       </c>
       <c r="J608" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K608" t="n">
-        <v>136.3188502048012</v>
+        <v>136.3195407541542</v>
       </c>
       <c r="L608" t="inlineStr">
         <is>
@@ -29664,10 +29664,10 @@
         <v>6.109054</v>
       </c>
       <c r="J609" t="n">
-        <v>-55.56600000056143</v>
+        <v>-55.28878414879339</v>
       </c>
       <c r="K609" t="n">
-        <v>136.6276131750763</v>
+        <v>136.6283052885276</v>
       </c>
       <c r="L609" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6.109054</v>
       </c>
       <c r="J610" t="n">
-        <v>-45.37890000017391</v>
+        <v>-45.15250705456476</v>
       </c>
       <c r="K610" t="n">
-        <v>136.6276131750763</v>
+        <v>136.6283052885276</v>
       </c>
       <c r="L610" t="inlineStr">
         <is>
@@ -29760,10 +29760,10 @@
         <v>6.109054</v>
       </c>
       <c r="J611" t="n">
-        <v>-35.50050000005984</v>
+        <v>-35.32338987254285</v>
       </c>
       <c r="K611" t="n">
-        <v>136.6276131750763</v>
+        <v>136.6283052885276</v>
       </c>
       <c r="L611" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J612" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K612" t="n">
-        <v>-78.88893823357058</v>
+        <v>-78.88933786065942</v>
       </c>
       <c r="L612" t="inlineStr">
         <is>
@@ -29856,10 +29856,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J613" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K613" t="n">
-        <v>-78.88893823357058</v>
+        <v>-78.88933786065942</v>
       </c>
       <c r="L613" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J614" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K614" t="n">
-        <v>-78.58017526329546</v>
+        <v>-78.58057332628609</v>
       </c>
       <c r="L614" t="inlineStr">
         <is>
@@ -29952,10 +29952,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J615" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K615" t="n">
-        <v>-78.58017526329546</v>
+        <v>-78.58057332628609</v>
       </c>
       <c r="L615" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J616" t="n">
-        <v>-58.96169999996678</v>
+        <v>-58.66754317948271</v>
       </c>
       <c r="K616" t="n">
-        <v>-78.58017526329546</v>
+        <v>-78.58057332628609</v>
       </c>
       <c r="L616" t="inlineStr">
         <is>
@@ -30048,10 +30048,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J617" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K617" t="n">
-        <v>-78.58017526329546</v>
+        <v>-78.58057332628609</v>
       </c>
       <c r="L617" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J618" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K618" t="n">
-        <v>-7.255929748154049</v>
+        <v>-7.255966504461676</v>
       </c>
       <c r="L618" t="inlineStr">
         <is>
@@ -30144,10 +30144,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J619" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K619" t="n">
-        <v>-7.255929748154049</v>
+        <v>-7.255966504461676</v>
       </c>
       <c r="L619" t="inlineStr">
         <is>
@@ -30192,10 +30192,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J620" t="n">
-        <v>-79.02720000041901</v>
+        <v>-78.63293745568414</v>
       </c>
       <c r="K620" t="n">
-        <v>-7.564692706582162</v>
+        <v>-7.564731026987936</v>
       </c>
       <c r="L620" t="inlineStr">
         <is>
@@ -30240,10 +30240,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J621" t="n">
-        <v>-66.06180000008732</v>
+        <v>-65.73222115409932</v>
       </c>
       <c r="K621" t="n">
-        <v>-7.255929748154049</v>
+        <v>-7.255966504461676</v>
       </c>
       <c r="L621" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J622" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K622" t="n">
-        <v>-6.947166777878915</v>
+        <v>-6.947201970088334</v>
       </c>
       <c r="L622" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J623" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K623" t="n">
-        <v>-7.255929748154049</v>
+        <v>-7.255966504461676</v>
       </c>
       <c r="L623" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J624" t="n">
-        <v>-94.15350000029602</v>
+        <v>-93.68377314035899</v>
       </c>
       <c r="K624" t="n">
-        <v>27.63428559597074</v>
+        <v>27.63442558275915</v>
       </c>
       <c r="L624" t="inlineStr">
         <is>
@@ -30432,10 +30432,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J625" t="n">
-        <v>-86.43600000081302</v>
+        <v>-86.00477534250747</v>
       </c>
       <c r="K625" t="n">
-        <v>27.94304856624587</v>
+        <v>27.9431901171325</v>
       </c>
       <c r="L625" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J626" t="n">
-        <v>-79.33590000069248</v>
+        <v>-78.94009736789087</v>
       </c>
       <c r="K626" t="n">
-        <v>28.25181153573121</v>
+        <v>28.25195465071603</v>
       </c>
       <c r="L626" t="inlineStr">
         <is>
@@ -30528,10 +30528,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J627" t="n">
-        <v>-66.06180000008732</v>
+        <v>-65.73222115409932</v>
       </c>
       <c r="K627" t="n">
-        <v>27.94304856624587</v>
+        <v>27.9431901171325</v>
       </c>
       <c r="L627" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J628" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K628" t="n">
-        <v>27.94304856624587</v>
+        <v>27.9431901171325</v>
       </c>
       <c r="L628" t="inlineStr">
         <is>
@@ -30624,10 +30624,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J629" t="n">
-        <v>-50.93550000021031</v>
+        <v>-50.68138546942446</v>
       </c>
       <c r="K629" t="n">
-        <v>27.94304856624587</v>
+        <v>27.9431901171325</v>
       </c>
       <c r="L629" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J630" t="n">
-        <v>-66.37050000031142</v>
+        <v>-66.03938106625694</v>
       </c>
       <c r="K630" t="n">
-        <v>39.36727837085986</v>
+        <v>39.3674777933797</v>
       </c>
       <c r="L630" t="inlineStr">
         <is>
@@ -30720,10 +30720,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J631" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K631" t="n">
-        <v>39.67604134113499</v>
+        <v>39.67624232775304</v>
       </c>
       <c r="L631" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J632" t="n">
-        <v>-50.93550000021031</v>
+        <v>-50.68138546942446</v>
       </c>
       <c r="K632" t="n">
-        <v>39.36727837085986</v>
+        <v>39.3674777933797</v>
       </c>
       <c r="L632" t="inlineStr">
         <is>
@@ -30816,10 +30816,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J633" t="n">
-        <v>-66.37050000031142</v>
+        <v>-66.03938106625694</v>
       </c>
       <c r="K633" t="n">
-        <v>112.2353387255299</v>
+        <v>112.2359072752237</v>
       </c>
       <c r="L633" t="inlineStr">
         <is>
@@ -30864,10 +30864,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J634" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K634" t="n">
-        <v>112.2353387255299</v>
+        <v>112.2359072752237</v>
       </c>
       <c r="L634" t="inlineStr">
         <is>
@@ -30912,10 +30912,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J635" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K635" t="n">
-        <v>111.9265757671018</v>
+        <v>111.9271427526975</v>
       </c>
       <c r="L635" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J636" t="n">
-        <v>-93.84480000007191</v>
+        <v>-93.37661322820138</v>
       </c>
       <c r="K636" t="n">
-        <v>-61.28944908189924</v>
+        <v>-61.28975955539097</v>
       </c>
       <c r="L636" t="inlineStr">
         <is>
@@ -31008,10 +31008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J637" t="n">
-        <v>-85.81860000031546</v>
+        <v>-85.39045551814311</v>
       </c>
       <c r="K637" t="n">
-        <v>-61.28944908189924</v>
+        <v>-61.28975955539097</v>
       </c>
       <c r="L637" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J638" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K638" t="n">
-        <v>-61.28944908189924</v>
+        <v>-61.28975955539097</v>
       </c>
       <c r="L638" t="inlineStr">
         <is>
@@ -31104,10 +31104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J639" t="n">
-        <v>-65.4444000006755</v>
+        <v>-65.11790133081529</v>
       </c>
       <c r="K639" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L639" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J640" t="n">
-        <v>-58.03560000033085</v>
+        <v>-57.74606344404106</v>
       </c>
       <c r="K640" t="n">
-        <v>-60.98068611241391</v>
+        <v>-60.98099502180744</v>
       </c>
       <c r="L640" t="inlineStr">
         <is>
@@ -31200,10 +31200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J641" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K641" t="n">
-        <v>-60.67192314213877</v>
+        <v>-60.67223048743409</v>
       </c>
       <c r="L641" t="inlineStr">
         <is>
@@ -31248,10 +31248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J642" t="n">
-        <v>-93.84480000007191</v>
+        <v>-93.37661322820138</v>
       </c>
       <c r="K642" t="n">
-        <v>4.785825997010199</v>
+        <v>4.785850240532214</v>
       </c>
       <c r="L642" t="inlineStr">
         <is>
@@ -31296,10 +31296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J643" t="n">
-        <v>-86.43600000081302</v>
+        <v>-86.00477534250747</v>
       </c>
       <c r="K643" t="n">
-        <v>5.094588967285333</v>
+        <v>5.094614774905557</v>
       </c>
       <c r="L643" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J644" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K644" t="n">
-        <v>5.094588967285333</v>
+        <v>5.094614774905557</v>
       </c>
       <c r="L644" t="inlineStr">
         <is>
@@ -31392,10 +31392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J645" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K645" t="n">
-        <v>5.094588967285333</v>
+        <v>5.094614774905557</v>
       </c>
       <c r="L645" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J646" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K646" t="n">
-        <v>5.094588967285333</v>
+        <v>5.094614774905557</v>
       </c>
       <c r="L646" t="inlineStr">
         <is>
@@ -31488,10 +31488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J647" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K647" t="n">
-        <v>5.094588967285333</v>
+        <v>5.094614774905557</v>
       </c>
       <c r="L647" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J648" t="n">
-        <v>-95.38830000020542</v>
+        <v>-94.91241278800739</v>
       </c>
       <c r="K648" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L648" t="inlineStr">
         <is>
@@ -31584,10 +31584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J649" t="n">
-        <v>-87.67080000067305</v>
+        <v>-87.23341499010675</v>
       </c>
       <c r="K649" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L649" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J650" t="n">
-        <v>-80.2620000003284</v>
+        <v>-79.86157710333252</v>
       </c>
       <c r="K650" t="n">
-        <v>93.09203473511971</v>
+        <v>93.09250631072547</v>
       </c>
       <c r="L650" t="inlineStr">
         <is>
@@ -31680,10 +31680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J651" t="n">
-        <v>-66.37050000031142</v>
+        <v>-66.03938106625694</v>
       </c>
       <c r="K651" t="n">
-        <v>93.70956067566998</v>
+        <v>93.71003537947215</v>
       </c>
       <c r="L651" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J652" t="n">
-        <v>-58.65300000082842</v>
+        <v>-58.36038326840542</v>
       </c>
       <c r="K652" t="n">
-        <v>93.40079770539484</v>
+        <v>93.40127084509881</v>
       </c>
       <c r="L652" t="inlineStr">
         <is>
@@ -31776,10 +31776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J653" t="n">
-        <v>-51.24420000043442</v>
+        <v>-50.98854538158208</v>
       </c>
       <c r="K653" t="n">
-        <v>93.70956067566998</v>
+        <v>93.71003537947215</v>
       </c>
       <c r="L653" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J654" t="n">
-        <v>-93.84480000007191</v>
+        <v>-93.37661322820138</v>
       </c>
       <c r="K654" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L654" t="inlineStr">
         <is>
@@ -31872,10 +31872,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J655" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K655" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L655" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J656" t="n">
-        <v>-78.71850000019491</v>
+        <v>-78.32577754352651</v>
       </c>
       <c r="K656" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L656" t="inlineStr">
         <is>
@@ -31968,10 +31968,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J657" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K657" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L657" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J658" t="n">
-        <v>-58.03560000033085</v>
+        <v>-57.74606344404106</v>
       </c>
       <c r="K658" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L658" t="inlineStr">
         <is>
@@ -32064,10 +32064,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J659" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K659" t="n">
-        <v>-14.3574779934</v>
+        <v>-14.35755072396606</v>
       </c>
       <c r="L659" t="inlineStr">
         <is>
@@ -32112,10 +32112,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J660" t="n">
-        <v>-93.84480000007191</v>
+        <v>-93.37661322820138</v>
       </c>
       <c r="K660" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L660" t="inlineStr">
         <is>
@@ -32160,10 +32160,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J661" t="n">
-        <v>-86.12730000053956</v>
+        <v>-85.69761543030074</v>
       </c>
       <c r="K661" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L661" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J662" t="n">
-        <v>-79.02720000041901</v>
+        <v>-78.63293745568414</v>
       </c>
       <c r="K662" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L662" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J663" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K663" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L663" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J664" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K664" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L664" t="inlineStr">
         <is>
@@ -32352,10 +32352,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J665" t="n">
-        <v>-50.93550000021031</v>
+        <v>-50.68138546942446</v>
       </c>
       <c r="K665" t="n">
-        <v>21.15026327942804</v>
+        <v>21.15037042015437</v>
       </c>
       <c r="L665" t="inlineStr">
         <is>
@@ -32400,10 +32400,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J666" t="n">
-        <v>-65.75309999981386</v>
+        <v>-65.42506124189258</v>
       </c>
       <c r="K666" t="n">
-        <v>46.16006365767769</v>
+        <v>46.16029749035783</v>
       </c>
       <c r="L666" t="inlineStr">
         <is>
@@ -32448,10 +32448,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J667" t="n">
-        <v>-58.34430000055496</v>
+        <v>-58.05322335619869</v>
       </c>
       <c r="K667" t="n">
-        <v>46.16006365767769</v>
+        <v>46.16029749035783</v>
       </c>
       <c r="L667" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J668" t="n">
-        <v>-50.62679999993685</v>
+        <v>-50.37422555721772</v>
       </c>
       <c r="K668" t="n">
-        <v>46.16006365767769</v>
+        <v>46.16029749035783</v>
       </c>
       <c r="L668" t="inlineStr">
         <is>
@@ -32544,10 +32544,10 @@
         <v>2.6</v>
       </c>
       <c r="J669" t="n">
-        <v>-116.0712000000695</v>
+        <v>-115.4921268874928</v>
       </c>
       <c r="K669" t="n">
-        <v>-109.7652349988699</v>
+        <v>-109.7657910357782</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J670" t="n">
-        <v>-66.37050000031142</v>
+        <v>-66.03938106625694</v>
       </c>
       <c r="K670" t="n">
-        <v>168.4301988401438</v>
+        <v>168.4310520557092</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -32640,10 +32640,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J671" t="n">
-        <v>-58.96169999996678</v>
+        <v>-58.66754317948271</v>
       </c>
       <c r="K671" t="n">
-        <v>168.4301988401438</v>
+        <v>168.4310520557092</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -32688,10 +32688,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J672" t="n">
-        <v>-50.93550000021031</v>
+        <v>-50.68138546942446</v>
       </c>
       <c r="K672" t="n">
-        <v>168.7389618096291</v>
+        <v>168.7398165892927</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J673" t="n">
-        <v>-46.30499999980983</v>
+        <v>-46.07398679000641</v>
       </c>
       <c r="K673" t="n">
-        <v>126.7471982092012</v>
+        <v>126.7478402715102</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>1</v>
       </c>
       <c r="J674" t="n">
-        <v>-83.34900000054604</v>
+        <v>-82.93317622289545</v>
       </c>
       <c r="K674" t="n">
-        <v>-127.0559611802661</v>
+        <v>-127.0566048066733</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -32832,10 +32832,10 @@
         <v>1</v>
       </c>
       <c r="J675" t="n">
-        <v>-68.53139999980738</v>
+        <v>-68.18950044929788</v>
       </c>
       <c r="K675" t="n">
-        <v>-125.5121463407375</v>
+        <v>-125.5127821466537</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -32880,10 +32880,10 @@
         <v>1</v>
       </c>
       <c r="J676" t="n">
-        <v>-55.25730000033732</v>
+        <v>-54.98162423663576</v>
       </c>
       <c r="K676" t="n">
-        <v>-127.0559611802661</v>
+        <v>-127.0566048066733</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -32928,10 +32928,10 @@
         <v>2.6</v>
       </c>
       <c r="J677" t="n">
-        <v>-99.71010000033243</v>
+        <v>-99.2126515552187</v>
       </c>
       <c r="K677" t="n">
-        <v>-134.1575094373591</v>
+        <v>-134.1581890380248</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>2.6</v>
       </c>
       <c r="J678" t="n">
-        <v>-71.61840000007436</v>
+        <v>-71.2610995689099</v>
       </c>
       <c r="K678" t="n">
-        <v>-134.1575094373591</v>
+        <v>-134.1581890380248</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -33024,10 +33024,10 @@
         <v>2.6</v>
       </c>
       <c r="J679" t="n">
-        <v>-43.5266999998163</v>
+        <v>-43.30954758260111</v>
       </c>
       <c r="K679" t="n">
-        <v>-134.1575094373591</v>
+        <v>-134.1581890380248</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J680" t="n">
-        <v>-93.22740000066011</v>
+        <v>-92.76229340491734</v>
       </c>
       <c r="K680" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -33120,10 +33120,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J681" t="n">
-        <v>-85.81860000031546</v>
+        <v>-85.39045551814311</v>
       </c>
       <c r="K681" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -33168,10 +33168,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J682" t="n">
-        <v>-78.10110000078309</v>
+        <v>-77.71145772024249</v>
       </c>
       <c r="K682" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -33216,10 +33216,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J683" t="n">
-        <v>-65.13570000045139</v>
+        <v>-64.81074141865766</v>
       </c>
       <c r="K683" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J684" t="n">
-        <v>-57.72690000005739</v>
+        <v>-57.43890353183432</v>
       </c>
       <c r="K684" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -33312,10 +33312,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J685" t="n">
-        <v>-50.00940000057439</v>
+        <v>-49.7599057339828</v>
       </c>
       <c r="K685" t="n">
-        <v>-148.3606059507552</v>
+        <v>-148.3613574999379</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J686" t="n">
-        <v>-93.22740000066011</v>
+        <v>-92.76229340491734</v>
       </c>
       <c r="K686" t="n">
-        <v>-142.4941095629158</v>
+        <v>-142.4948313942328</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -33408,10 +33408,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J687" t="n">
-        <v>-85.81860000031546</v>
+        <v>-85.39045551814311</v>
       </c>
       <c r="K687" t="n">
-        <v>-142.4941095629158</v>
+        <v>-142.4948313942328</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J688" t="n">
-        <v>-78.10110000078309</v>
+        <v>-77.71145772024249</v>
       </c>
       <c r="K688" t="n">
-        <v>-142.1853465934304</v>
+        <v>-142.1860668606492</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -33504,10 +33504,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J689" t="n">
-        <v>-65.13570000045139</v>
+        <v>-64.81074141865766</v>
       </c>
       <c r="K689" t="n">
-        <v>-142.1853465934304</v>
+        <v>-142.1860668606492</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J690" t="n">
-        <v>-57.72690000005739</v>
+        <v>-57.43890353183432</v>
       </c>
       <c r="K690" t="n">
-        <v>-142.1853465934304</v>
+        <v>-142.1860668606492</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -33600,10 +33600,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J691" t="n">
-        <v>-50.00940000057439</v>
+        <v>-49.7599057339828</v>
       </c>
       <c r="K691" t="n">
-        <v>-142.1853465934304</v>
+        <v>-142.1860668606492</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>1</v>
       </c>
       <c r="J692" t="n">
-        <v>78.25544999983407</v>
+        <v>77.86503767526551</v>
       </c>
       <c r="K692" t="n">
-        <v>-17.4451076724573</v>
+        <v>-17.44519604400532</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -33696,10 +33696,10 @@
         <v>16.0614894048131</v>
       </c>
       <c r="J693" t="n">
-        <v>70.38360000016499</v>
+        <v>70.03245992126152</v>
       </c>
       <c r="K693" t="n">
-        <v>-54.4966637958712</v>
+        <v>-54.49693985920266</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>17.6058633850347</v>
       </c>
       <c r="J694" t="n">
-        <v>87.20775000031222</v>
+        <v>86.77267512184577</v>
       </c>
       <c r="K694" t="n">
-        <v>-21.7677892199783</v>
+        <v>-21.76789948890106</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -33792,10 +33792,10 @@
         <v>17.6085645678712</v>
       </c>
       <c r="J695" t="n">
-        <v>87.20775000031222</v>
+        <v>86.77267512184577</v>
       </c>
       <c r="K695" t="n">
-        <v>12.65928166833888</v>
+        <v>12.65934579636486</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>1</v>
       </c>
       <c r="J696" t="n">
-        <v>71.00099999957679</v>
+        <v>70.64677974454554</v>
       </c>
       <c r="K696" t="n">
-        <v>17.59948914535294</v>
+        <v>17.59957829895</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -33888,10 +33888,10 @@
         <v>39.2380095193426</v>
       </c>
       <c r="J697" t="n">
-        <v>90.91214999994166</v>
+        <v>90.4585940646927</v>
       </c>
       <c r="K697" t="n">
-        <v>-70.08919366326352</v>
+        <v>-70.08954871355384</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>1</v>
       </c>
       <c r="J698" t="n">
-        <v>110.9776499993082</v>
+        <v>110.4239883398138</v>
       </c>
       <c r="K698" t="n">
-        <v>-70.86110106644202</v>
+        <v>-70.86146002697774</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -33984,10 +33984,10 @@
         <v>8.345320482737019</v>
       </c>
       <c r="J699" t="n">
-        <v>75.47714999979119</v>
+        <v>75.10059846781111</v>
       </c>
       <c r="K699" t="n">
-        <v>105.5969349242445</v>
+        <v>105.5974698458272</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>1</v>
       </c>
       <c r="J700" t="n">
-        <v>116.0712000000695</v>
+        <v>115.4921268874928</v>
       </c>
       <c r="K700" t="n">
-        <v>-70.86110106644202</v>
+        <v>-70.86146002697774</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -34080,10 +34080,10 @@
         <v>1</v>
       </c>
       <c r="J701" t="n">
-        <v>-23.61555000053719</v>
+        <v>-23.49773326353428</v>
       </c>
       <c r="K701" t="n">
-        <v>-117.4843091854559</v>
+        <v>-117.4849043248191</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>26.5650228690678</v>
       </c>
       <c r="J702" t="n">
-        <v>-10.1870999997953</v>
+        <v>-10.13627709363936</v>
       </c>
       <c r="K702" t="n">
-        <v>-122.5788981472126</v>
+        <v>-122.579519094196</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -34176,10 +34176,10 @@
         <v>1</v>
       </c>
       <c r="J703" t="n">
-        <v>-23.61555000053719</v>
+        <v>-23.49773326353428</v>
       </c>
       <c r="K703" t="n">
-        <v>-73.02244184573114</v>
+        <v>-73.02281175495425</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>75.36545028155891</v>
       </c>
       <c r="J704" t="n">
-        <v>13.89149999942475</v>
+        <v>13.82219603648631</v>
       </c>
       <c r="K704" t="n">
-        <v>-82.28533087105599</v>
+        <v>-82.28574770322494</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -34272,10 +34272,10 @@
         <v>1</v>
       </c>
       <c r="J705" t="n">
-        <v>-7.717500000075235</v>
+        <v>-7.678997798440799</v>
       </c>
       <c r="K705" t="n">
-        <v>-41.99176360674637</v>
+        <v>-41.99197632410093</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>85.2500016533164</v>
       </c>
       <c r="J706" t="n">
-        <v>15.7436999998317</v>
+        <v>15.66515550849905</v>
       </c>
       <c r="K706" t="n">
-        <v>-54.95980823983178</v>
+        <v>-54.96008664931049</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -34368,10 +34368,10 @@
         <v>1</v>
       </c>
       <c r="J707" t="n">
-        <v>-8.026200000299344</v>
+        <v>-7.986157710598427</v>
       </c>
       <c r="K707" t="n">
-        <v>-4.631444513057334</v>
+        <v>-4.631467974530251</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>17.9147381814938</v>
       </c>
       <c r="J708" t="n">
-        <v>0.9261000001788009</v>
+        <v>0.9214797359818215</v>
       </c>
       <c r="K708" t="n">
-        <v>-22.07655219025344</v>
+        <v>-22.0766640232744</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -34464,10 +34464,10 @@
         <v>1</v>
       </c>
       <c r="J709" t="n">
-        <v>-8.026200000299344</v>
+        <v>-7.986157710598427</v>
       </c>
       <c r="K709" t="n">
-        <v>25.62732630142429</v>
+        <v>25.62745612157441</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>17.9173927965757</v>
       </c>
       <c r="J710" t="n">
-        <v>29.01780000043686</v>
+        <v>28.87303172229061</v>
       </c>
       <c r="K710" t="n">
-        <v>-21.92217070551077</v>
+        <v>-21.92228175648263</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -34560,10 +34560,10 @@
         <v>1</v>
       </c>
       <c r="J711" t="n">
-        <v>19.91114999982199</v>
+        <v>19.811814319607</v>
       </c>
       <c r="K711" t="n">
-        <v>-3.550774128546486</v>
+        <v>-3.550792115675732</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>18.2236129780023</v>
       </c>
       <c r="J712" t="n">
-        <v>0.7717500000420703</v>
+        <v>0.7678997798784543</v>
       </c>
       <c r="K712" t="n">
-        <v>12.19613721332108</v>
+        <v>12.19619899519974</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -34656,10 +34656,10 @@
         <v>1</v>
       </c>
       <c r="J713" t="n">
-        <v>19.75679999968526</v>
+        <v>19.65823436350363</v>
       </c>
       <c r="K713" t="n">
-        <v>78.7345567361911</v>
+        <v>78.73495558123076</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>17.6058633850347</v>
       </c>
       <c r="J714" t="n">
-        <v>28.86345000030013</v>
+        <v>28.71945176618724</v>
       </c>
       <c r="K714" t="n">
-        <v>12.50490018280642</v>
+        <v>12.50496352878328</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -34752,10 +34752,10 @@
         <v>1</v>
       </c>
       <c r="J715" t="n">
-        <v>12.19364999920388</v>
+        <v>12.13281652062603</v>
       </c>
       <c r="K715" t="n">
-        <v>-156.6972060771017</v>
+        <v>-156.6979998569357</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>44.7868454542777</v>
       </c>
       <c r="J716" t="n">
-        <v>16.51544999933089</v>
+        <v>16.43305528783734</v>
       </c>
       <c r="K716" t="n">
-        <v>55.73171565327769</v>
+        <v>55.73199797300186</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -34848,10 +34848,10 @@
         <v>1</v>
       </c>
       <c r="J717" t="n">
-        <v>58.80734999983004</v>
+        <v>58.51396322337934</v>
       </c>
       <c r="K717" t="n">
-        <v>-174.7598396830011</v>
+        <v>-174.7607249625794</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -34896,10 +34896,10 @@
         <v>46.6400942320942</v>
       </c>
       <c r="J718" t="n">
-        <v>35.65484999906146</v>
+        <v>35.47696982751678</v>
       </c>
       <c r="K718" t="n">
-        <v>-177.3843249070406</v>
+        <v>-177.3852234814536</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -34944,10 +34944,10 @@
         <v>1</v>
       </c>
       <c r="J719" t="n">
-        <v>11.88495000006552</v>
+        <v>11.82565660954874</v>
       </c>
       <c r="K719" t="n">
-        <v>-126.2840537660304</v>
+        <v>-126.2846934821922</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>74.13059267213769</v>
       </c>
       <c r="J720" t="n">
-        <v>10.1870999997953</v>
+        <v>10.13627709363936</v>
       </c>
       <c r="K720" t="n">
-        <v>98.18662370872346</v>
+        <v>98.18712109194946</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -35040,10 +35040,10 @@
         <v>78.1459320571828</v>
       </c>
       <c r="J721" t="n">
-        <v>-69.92054999980414</v>
+        <v>-69.57172005300052</v>
       </c>
       <c r="K721" t="n">
-        <v>-96.02528292943434</v>
+        <v>-96.02576936397296</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -35088,10 +35088,10 @@
         <v>1</v>
       </c>
       <c r="J722" t="n">
-        <v>-47.23110000058086</v>
+        <v>-46.9954665265775</v>
       </c>
       <c r="K722" t="n">
-        <v>37.51470056105607</v>
+        <v>37.51489059898673</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>44.1701726245875</v>
       </c>
       <c r="J723" t="n">
-        <v>-52.94204999956953</v>
+        <v>-52.67792489636201</v>
       </c>
       <c r="K723" t="n">
-        <v>-55.26857120931711</v>
+        <v>-55.26885118289402</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>1</v>
       </c>
       <c r="J724" t="n">
-        <v>-75.01410000056546</v>
+        <v>-74.63985860067956</v>
       </c>
       <c r="K724" t="n">
-        <v>-42.45490806176417</v>
+        <v>-42.45512312526604</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -35232,10 +35232,10 @@
         <v>19.1502373674291</v>
       </c>
       <c r="J725" t="n">
-        <v>-84.89249999959378</v>
+        <v>-84.46897578162113</v>
       </c>
       <c r="K725" t="n">
-        <v>-22.38531516052857</v>
+        <v>-22.38542855764774</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>1</v>
       </c>
       <c r="J726" t="n">
-        <v>-75.16844999956709</v>
+        <v>-74.79343855565348</v>
       </c>
       <c r="K726" t="n">
-        <v>-5.403351927293047</v>
+        <v>-5.403379299011428</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -35328,10 +35328,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J727" t="n">
-        <v>-56.80080000042147</v>
+        <v>-56.51742379639267</v>
       </c>
       <c r="K727" t="n">
-        <v>-22.38531516052857</v>
+        <v>-22.38542855764774</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>1</v>
       </c>
       <c r="J728" t="n">
-        <v>-75.32279999970382</v>
+        <v>-74.94701851175685</v>
       </c>
       <c r="K728" t="n">
-        <v>34.11830792357066</v>
+        <v>34.11848075642121</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         <v>18.8438866439532</v>
       </c>
       <c r="J729" t="n">
-        <v>-84.73814999945705</v>
+        <v>-84.31539582551775</v>
       </c>
       <c r="K729" t="n">
-        <v>12.04175573884584</v>
+        <v>12.04181673867545</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>1</v>
       </c>
       <c r="J730" t="n">
-        <v>-75.47714999984055</v>
+        <v>-75.10059846786022</v>
       </c>
       <c r="K730" t="n">
-        <v>79.04331971752346</v>
+        <v>79.04372012666138</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -35520,10 +35520,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J731" t="n">
-        <v>-56.80080000042147</v>
+        <v>-56.51742379639267</v>
       </c>
       <c r="K731" t="n">
-        <v>12.19613721332108</v>
+        <v>12.19619899519974</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>18.2236129780023</v>
       </c>
       <c r="J732" t="n">
-        <v>-84.73814999945705</v>
+        <v>-84.31539582551775</v>
       </c>
       <c r="K732" t="n">
-        <v>55.42295268300256</v>
+        <v>55.42323343862852</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -35616,10 +35616,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J733" t="n">
-        <v>-56.80080000042147</v>
+        <v>-56.51742379639267</v>
       </c>
       <c r="K733" t="n">
-        <v>54.18790081374905</v>
+        <v>54.18817531298223</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>37.0662586828766</v>
       </c>
       <c r="J734" t="n">
-        <v>-50.31809999971274</v>
+        <v>-50.06706564506009</v>
       </c>
       <c r="K734" t="n">
-        <v>130.2979723432763</v>
+        <v>130.2986323927146</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -35712,10 +35712,10 @@
         <v>1</v>
       </c>
       <c r="J735" t="n">
-        <v>-39.2049000008244</v>
+        <v>-39.00930881651925</v>
       </c>
       <c r="K735" t="n">
-        <v>-9.417270516385944</v>
+        <v>-9.417318221380908</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>65.79105449957601</v>
       </c>
       <c r="J736" t="n">
-        <v>-73.00755000007113</v>
+        <v>-72.64331917261255</v>
       </c>
       <c r="K736" t="n">
-        <v>-69.78043068193116</v>
+        <v>-69.78078416812322</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>1</v>
       </c>
       <c r="J737" t="n">
-        <v>-31.95045000056712</v>
+        <v>-31.79105088579928</v>
       </c>
       <c r="K737" t="n">
-        <v>109.9196164725553</v>
+        <v>109.9201732915127</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -35856,10 +35856,10 @@
         <v>7.13084897104345</v>
       </c>
       <c r="J738" t="n">
-        <v>-35.65485000019657</v>
+        <v>-35.47696982864623</v>
       </c>
       <c r="K738" t="n">
-        <v>99.57605705166242</v>
+        <v>99.57656147333024</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -35904,10 +35904,10 @@
         <v>1</v>
       </c>
       <c r="J739" t="n">
-        <v>-27.01124999994253</v>
+        <v>-26.8764922942236</v>
       </c>
       <c r="K739" t="n">
-        <v>109.1477090472624</v>
+        <v>109.1482619559743</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -35952,10 +35952,10 @@
         <v>1</v>
       </c>
       <c r="J740" t="n">
-        <v>-106.1927999999554</v>
+        <v>-105.6630097054709</v>
       </c>
       <c r="K740" t="n">
-        <v>-71.63300849173496</v>
+        <v>-71.63337136251619</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>

--- a/planilhas/equipment_processado.xlsx
+++ b/planilhas/equipment_processado.xlsx
@@ -528,10 +528,10 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>71.2610995689099</v>
+        <v>71.61840000007436</v>
       </c>
       <c r="K2" t="n">
-        <v>-101.7379132139436</v>
+        <v>-101.7373978435884</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -576,10 +576,10 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>89.69069428422497</v>
+        <v>90.14039999930736</v>
       </c>
       <c r="K3" t="n">
-        <v>-101.4291486795703</v>
+        <v>-101.4286348733132</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -624,10 +624,10 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>97.98401190648997</v>
+        <v>98.4752999993373</v>
       </c>
       <c r="K4" t="n">
-        <v>-128.2916629323196</v>
+        <v>-128.2910130495196</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -672,10 +672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J5" t="n">
-        <v>75.25417842391448</v>
+        <v>75.63149999992793</v>
       </c>
       <c r="K5" t="n">
-        <v>-48.01288468475079</v>
+        <v>-48.01264146748147</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J6" t="n">
-        <v>79.86157710220309</v>
+        <v>80.26199999919329</v>
       </c>
       <c r="K6" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -768,10 +768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J7" t="n">
-        <v>84.46897578157201</v>
+        <v>84.89249999954443</v>
       </c>
       <c r="K7" t="n">
-        <v>-48.01288468475079</v>
+        <v>-48.01264146748147</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -816,10 +816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J8" t="n">
-        <v>74.63985859955012</v>
+        <v>75.01409999943036</v>
       </c>
       <c r="K8" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J9" t="n">
-        <v>83.8546559583371</v>
+        <v>84.27510000018196</v>
       </c>
       <c r="K9" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J10" t="n">
-        <v>61.73914229904563</v>
+        <v>62.04870000018441</v>
       </c>
       <c r="K10" t="n">
-        <v>-112.8534363447602</v>
+        <v>-112.85286466687</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J11" t="n">
-        <v>73.1040590397441</v>
+        <v>73.47059999929687</v>
       </c>
       <c r="K11" t="n">
-        <v>-113.1622008791336</v>
+        <v>-113.1616276371451</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1008,10 +1008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J12" t="n">
-        <v>84.77613569377876</v>
+        <v>85.20119999981789</v>
       </c>
       <c r="K12" t="n">
-        <v>-113.1622008791336</v>
+        <v>-113.1616276371451</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J13" t="n">
-        <v>96.75537225884159</v>
+        <v>97.24049999942791</v>
       </c>
       <c r="K13" t="n">
-        <v>-112.8534363447602</v>
+        <v>-112.85286466687</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1104,10 +1104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J14" t="n">
-        <v>66.34654097733423</v>
+        <v>66.67919999944978</v>
       </c>
       <c r="K14" t="n">
-        <v>-101.4291486795703</v>
+        <v>-101.4286348733132</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1152,10 +1152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J15" t="n">
-        <v>73.1040590397441</v>
+        <v>73.47059999929687</v>
       </c>
       <c r="K15" t="n">
-        <v>-103.2817358621162</v>
+        <v>-103.28121267127</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J16" t="n">
-        <v>85.39045551701368</v>
+        <v>85.81859999918035</v>
       </c>
       <c r="K16" t="n">
-        <v>-103.2817358621162</v>
+        <v>-103.28121267127</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J17" t="n">
-        <v>96.4482123477643</v>
+        <v>96.93180000028956</v>
       </c>
       <c r="K17" t="n">
-        <v>-103.2817358621162</v>
+        <v>-103.28121267127</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J18" t="n">
-        <v>66.0393810651275</v>
+        <v>66.37049999917632</v>
       </c>
       <c r="K18" t="n">
-        <v>-89.38733193457641</v>
+        <v>-89.38687912814896</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J19" t="n">
-        <v>77.40429780695541</v>
+        <v>77.79239999942388</v>
       </c>
       <c r="K19" t="n">
-        <v>-91.85744819692626</v>
+        <v>-91.85698287771322</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J20" t="n">
-        <v>89.07637446099007</v>
+        <v>89.5229999999449</v>
       </c>
       <c r="K20" t="n">
-        <v>-91.85744819692626</v>
+        <v>-91.85698287771322</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J21" t="n">
-        <v>96.75537225884159</v>
+        <v>97.24049999942791</v>
       </c>
       <c r="K21" t="n">
-        <v>-91.85744819692626</v>
+        <v>-91.85698287771322</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J22" t="n">
-        <v>81.0902167509318</v>
+        <v>81.49680000018843</v>
       </c>
       <c r="K22" t="n">
-        <v>-81.35945411195199</v>
+        <v>-81.35904197207762</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J23" t="n">
-        <v>89.07637446099007</v>
+        <v>89.5229999999449</v>
       </c>
       <c r="K23" t="n">
-        <v>-81.35945411195199</v>
+        <v>-81.35904197207762</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J24" t="n">
-        <v>96.75537225884159</v>
+        <v>97.24049999942791</v>
       </c>
       <c r="K24" t="n">
-        <v>-81.35945411195199</v>
+        <v>-81.35904197207762</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J25" t="n">
-        <v>81.39737666200909</v>
+        <v>81.80549999932678</v>
       </c>
       <c r="K25" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J26" t="n">
-        <v>88.76921454878332</v>
+        <v>89.21429999967144</v>
       </c>
       <c r="K26" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1728,10 +1728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J27" t="n">
-        <v>96.4482123477643</v>
+        <v>96.93180000028956</v>
       </c>
       <c r="K27" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1776,10 +1776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J28" t="n">
-        <v>74.94701851175685</v>
+        <v>75.32279999970382</v>
       </c>
       <c r="K28" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J29" t="n">
-        <v>79.55441719112579</v>
+        <v>79.95330000005494</v>
       </c>
       <c r="K29" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J30" t="n">
-        <v>84.46897578157201</v>
+        <v>84.89249999954443</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.60253591981579</v>
+        <v>-40.60233024090317</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J31" t="n">
-        <v>89.3835343731477</v>
+        <v>89.83170000016901</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J32" t="n">
-        <v>96.14105243560667</v>
+        <v>96.62310000006545</v>
       </c>
       <c r="K32" t="n">
-        <v>-40.60253591981579</v>
+        <v>-40.60233024090317</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J33" t="n">
-        <v>74.63985859955012</v>
+        <v>75.01409999943036</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J34" t="n">
-        <v>79.24725727896816</v>
+        <v>79.64459999983083</v>
       </c>
       <c r="K34" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J35" t="n">
-        <v>84.1618158694144</v>
+        <v>84.58379999932032</v>
       </c>
       <c r="K35" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2160,10 +2160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J36" t="n">
-        <v>89.07637446099007</v>
+        <v>89.5229999999449</v>
       </c>
       <c r="K36" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2208,10 +2208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J37" t="n">
-        <v>93.37661322820138</v>
+        <v>93.84480000007191</v>
       </c>
       <c r="K37" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J38" t="n">
-        <v>97.98401190648997</v>
+        <v>98.4752999993373</v>
       </c>
       <c r="K38" t="n">
-        <v>-30.7220709146455</v>
+        <v>-30.72191528687506</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J39" t="n">
-        <v>102.5914105858589</v>
+        <v>103.1057999996884</v>
       </c>
       <c r="K39" t="n">
-        <v>-30.7220709146455</v>
+        <v>-30.72191528687506</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2352,10 +2352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J40" t="n">
-        <v>74.33269868847283</v>
+        <v>74.705400000292</v>
       </c>
       <c r="K40" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J41" t="n">
-        <v>83.8546559583371</v>
+        <v>84.27510000018196</v>
       </c>
       <c r="K41" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J42" t="n">
-        <v>93.06945331599464</v>
+        <v>93.53609999979845</v>
       </c>
       <c r="K42" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2496,10 +2496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J43" t="n">
-        <v>74.33269868847283</v>
+        <v>74.705400000292</v>
       </c>
       <c r="K43" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J44" t="n">
-        <v>83.8546559583371</v>
+        <v>84.27510000018196</v>
       </c>
       <c r="K44" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J45" t="n">
-        <v>92.76229340383701</v>
+        <v>93.22739999957435</v>
       </c>
       <c r="K45" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2640,10 +2640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J46" t="n">
-        <v>102.2842506736522</v>
+        <v>102.797099999415</v>
       </c>
       <c r="K46" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2688,10 +2688,10 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>105.9701696176286</v>
+        <v>106.5015000001795</v>
       </c>
       <c r="K47" t="n">
-        <v>-126.7478402841471</v>
+        <v>-126.747198221838</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2736,10 +2736,10 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>105.9701696176286</v>
+        <v>106.5015000001795</v>
       </c>
       <c r="K48" t="n">
-        <v>-94.32756444821884</v>
+        <v>-94.32708661622024</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2784,10 +2784,10 @@
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>94.91241278795827</v>
+        <v>95.38830000015606</v>
       </c>
       <c r="K49" t="n">
-        <v>-67.15628565003887</v>
+        <v>-67.15594545868147</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2832,10 +2832,10 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>94.91241278795827</v>
+        <v>95.38830000015606</v>
       </c>
       <c r="K50" t="n">
-        <v>-26.09060293458661</v>
+        <v>-26.09047076828911</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2880,10 +2880,10 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>94.60525287580066</v>
+        <v>95.07959999993196</v>
       </c>
       <c r="K51" t="n">
-        <v>-10.96114088140054</v>
+        <v>-10.96108535591459</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>86.00477534137804</v>
+        <v>86.43599999967792</v>
       </c>
       <c r="K52" t="n">
-        <v>7.255966491824789</v>
+        <v>7.255929735517227</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2976,10 +2976,10 @@
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>94.91241278795827</v>
+        <v>95.38830000015606</v>
       </c>
       <c r="K53" t="n">
-        <v>10.65237634623739</v>
+        <v>10.65232238484966</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>86.31193525358476</v>
+        <v>86.74469999995138</v>
       </c>
       <c r="K54" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>86.31193525358476</v>
+        <v>86.74469999995138</v>
       </c>
       <c r="K55" t="n">
-        <v>24.85554479709324</v>
+        <v>24.85541888718858</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>94.60525287580066</v>
+        <v>95.07959999993196</v>
       </c>
       <c r="K56" t="n">
-        <v>51.10052999294297</v>
+        <v>51.10027113469175</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3168,10 +3168,10 @@
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>94.29809296364303</v>
+        <v>94.77089999970784</v>
       </c>
       <c r="K57" t="n">
-        <v>104.825558521346</v>
+        <v>104.8250275100088</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3216,10 +3216,10 @@
         <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>102.2842506736522</v>
+        <v>102.797099999415</v>
       </c>
       <c r="K58" t="n">
-        <v>104.5167939869727</v>
+        <v>104.5162645397337</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3264,10 +3264,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J59" t="n">
-        <v>81.39737666200909</v>
+        <v>81.80549999932678</v>
       </c>
       <c r="K59" t="n">
-        <v>-21.15037042094418</v>
+        <v>-21.15026328021784</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J60" t="n">
-        <v>88.46205463662569</v>
+        <v>88.90559999944733</v>
       </c>
       <c r="K60" t="n">
-        <v>-21.15037042094418</v>
+        <v>-21.15026328021784</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J61" t="n">
-        <v>96.14105243560667</v>
+        <v>96.62310000006545</v>
       </c>
       <c r="K61" t="n">
-        <v>-20.84160589762811</v>
+        <v>-20.84150032099992</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3408,10 +3408,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J62" t="n">
-        <v>80.78305683872507</v>
+        <v>81.18809999991497</v>
       </c>
       <c r="K62" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J63" t="n">
-        <v>88.46205463662569</v>
+        <v>88.90559999944733</v>
       </c>
       <c r="K63" t="n">
-        <v>13.43125713190331</v>
+        <v>13.43118909363182</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J64" t="n">
-        <v>96.14105243560667</v>
+        <v>96.62310000006545</v>
       </c>
       <c r="K64" t="n">
-        <v>13.43125713190331</v>
+        <v>13.43118909363182</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         <v>2.6</v>
       </c>
       <c r="J65" t="n">
-        <v>74.94701851175685</v>
+        <v>75.32279999970382</v>
       </c>
       <c r="K65" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3600,10 +3600,10 @@
         <v>2.6</v>
       </c>
       <c r="J66" t="n">
-        <v>103.5128903213006</v>
+        <v>104.0318999993243</v>
       </c>
       <c r="K66" t="n">
-        <v>-59.74593689616115</v>
+        <v>-59.74563424316039</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3648,10 +3648,10 @@
         <v>2.6</v>
       </c>
       <c r="J67" t="n">
-        <v>74.94701851175685</v>
+        <v>75.32279999970382</v>
       </c>
       <c r="K67" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>102.8985704980165</v>
+        <v>103.4144999999125</v>
       </c>
       <c r="K68" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         <v>2.6</v>
       </c>
       <c r="J69" t="n">
-        <v>74.63985859955012</v>
+        <v>75.01409999943036</v>
       </c>
       <c r="K69" t="n">
-        <v>94.01879991305569</v>
+        <v>94.01832364515531</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3792,10 +3792,10 @@
         <v>2.6</v>
       </c>
       <c r="J70" t="n">
-        <v>102.8985704980165</v>
+        <v>103.4144999999125</v>
       </c>
       <c r="K70" t="n">
-        <v>94.32756443637174</v>
+        <v>94.32708660437322</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3840,10 +3840,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J71" t="n">
-        <v>80.78305683872507</v>
+        <v>81.18809999991497</v>
       </c>
       <c r="K71" t="n">
-        <v>-65.61246299001924</v>
+        <v>-65.61213061915282</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3888,10 +3888,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J72" t="n">
-        <v>88.76921454878332</v>
+        <v>89.21429999967144</v>
       </c>
       <c r="K72" t="n">
-        <v>-65.30369846670318</v>
+        <v>-65.30336765993491</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3936,10 +3936,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J73" t="n">
-        <v>96.4482123477643</v>
+        <v>96.93180000028956</v>
       </c>
       <c r="K73" t="n">
-        <v>-65.61246299001924</v>
+        <v>-65.61213061915282</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J74" t="n">
-        <v>81.0902167509318</v>
+        <v>81.49680000018843</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J75" t="n">
-        <v>88.76921454878332</v>
+        <v>89.21429999967144</v>
       </c>
       <c r="K75" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J76" t="n">
-        <v>96.75537225884159</v>
+        <v>97.24049999942791</v>
       </c>
       <c r="K76" t="n">
-        <v>-6.638437435714992</v>
+        <v>-6.638403807603781</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J77" t="n">
-        <v>80.78305683872507</v>
+        <v>81.18809999991497</v>
       </c>
       <c r="K77" t="n">
-        <v>28.86948371946272</v>
+        <v>28.86933747628147</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4176,10 +4176,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J78" t="n">
-        <v>89.07637446099007</v>
+        <v>89.5229999999449</v>
       </c>
       <c r="K78" t="n">
-        <v>28.86948371946272</v>
+        <v>28.86933747628147</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4224,10 +4224,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J79" t="n">
-        <v>97.98401190648997</v>
+        <v>98.4752999993373</v>
       </c>
       <c r="K79" t="n">
-        <v>29.17824824277879</v>
+        <v>29.17810043549939</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         <v>1.09964</v>
       </c>
       <c r="J80" t="n">
-        <v>81.0902167509318</v>
+        <v>81.49680000018843</v>
       </c>
       <c r="K80" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4320,10 +4320,10 @@
         <v>1.09964</v>
       </c>
       <c r="J81" t="n">
-        <v>89.3835343731477</v>
+        <v>89.83170000016901</v>
       </c>
       <c r="K81" t="n">
-        <v>-61.28975955539097</v>
+        <v>-61.28944908189924</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>1.09964</v>
       </c>
       <c r="J82" t="n">
-        <v>98.2911718186476</v>
+        <v>98.7839999995614</v>
       </c>
       <c r="K82" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4416,10 +4416,10 @@
         <v>1.09964</v>
       </c>
       <c r="J83" t="n">
-        <v>80.47589692656744</v>
+        <v>80.87939999969086</v>
       </c>
       <c r="K83" t="n">
-        <v>6.020908366178501</v>
+        <v>6.020877866263713</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         <v>1.09964</v>
       </c>
       <c r="J84" t="n">
-        <v>88.46205463662569</v>
+        <v>88.90559999944733</v>
       </c>
       <c r="K84" t="n">
-        <v>6.020908366178501</v>
+        <v>6.020877866263713</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         <v>1.09964</v>
       </c>
       <c r="J85" t="n">
-        <v>95.83389252339994</v>
+        <v>96.31439999979199</v>
       </c>
       <c r="K85" t="n">
-        <v>6.329672900551844</v>
+        <v>6.329640836538847</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4560,10 +4560,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J86" t="n">
-        <v>81.0902167509318</v>
+        <v>81.49680000018843</v>
       </c>
       <c r="K86" t="n">
-        <v>-13.43125713269311</v>
+        <v>-13.43118909442162</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J87" t="n">
-        <v>88.76921454878332</v>
+        <v>89.21429999967144</v>
       </c>
       <c r="K87" t="n">
-        <v>-13.43125713269311</v>
+        <v>-13.43118909442162</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4656,10 +4656,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J88" t="n">
-        <v>96.14105243560667</v>
+        <v>96.62310000006545</v>
       </c>
       <c r="K88" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4704,10 +4704,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J89" t="n">
-        <v>81.0902167509318</v>
+        <v>81.49680000018843</v>
       </c>
       <c r="K89" t="n">
-        <v>21.76789948811125</v>
+        <v>21.7677892191885</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4752,10 +4752,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J90" t="n">
-        <v>88.76921454878332</v>
+        <v>89.21429999967144</v>
       </c>
       <c r="K90" t="n">
-        <v>21.76789948811125</v>
+        <v>21.7677892191885</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4800,10 +4800,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J91" t="n">
-        <v>96.75537225884159</v>
+        <v>97.24049999942791</v>
       </c>
       <c r="K91" t="n">
-        <v>22.07666401142732</v>
+        <v>22.07655217840642</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4848,10 +4848,10 @@
         <v>2.6</v>
       </c>
       <c r="J92" t="n">
-        <v>102.8985704980165</v>
+        <v>103.4144999999125</v>
       </c>
       <c r="K92" t="n">
-        <v>-120.8813141784419</v>
+        <v>-120.8807018339985</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4896,10 +4896,10 @@
         <v>2.6</v>
       </c>
       <c r="J93" t="n">
-        <v>17.5081149804627</v>
+        <v>17.5959000001893</v>
       </c>
       <c r="K93" t="n">
-        <v>-175.5326362870606</v>
+        <v>-175.5317470972368</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         <v>2.6</v>
       </c>
       <c r="J94" t="n">
-        <v>60.51050265031691</v>
+        <v>60.81389999918927</v>
       </c>
       <c r="K94" t="n">
-        <v>-176.1501653558073</v>
+        <v>-176.1492730377871</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4992,10 +4992,10 @@
         <v>2.6</v>
       </c>
       <c r="J95" t="n">
-        <v>103.5128903213006</v>
+        <v>104.0318999993243</v>
       </c>
       <c r="K95" t="n">
-        <v>-175.5326362870606</v>
+        <v>-175.5317470972368</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5040,10 +5040,10 @@
         <v>6.109054</v>
       </c>
       <c r="J96" t="n">
-        <v>56.51742379531233</v>
+        <v>56.80079999933571</v>
       </c>
       <c r="K96" t="n">
-        <v>-119.0287269840489</v>
+        <v>-119.0281240241948</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         <v>6.109054</v>
       </c>
       <c r="J97" t="n">
-        <v>67.88234053714025</v>
+        <v>68.22269999958327</v>
       </c>
       <c r="K97" t="n">
-        <v>-119.0287269840489</v>
+        <v>-119.0281240241948</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5136,10 +5136,10 @@
         <v>6.109054</v>
       </c>
       <c r="J98" t="n">
-        <v>80.16873701436072</v>
+        <v>80.5706999994174</v>
       </c>
       <c r="K98" t="n">
-        <v>-118.7199624504654</v>
+        <v>-118.7193610547094</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         <v>6.109054</v>
       </c>
       <c r="J99" t="n">
-        <v>90.61217402079608</v>
+        <v>91.06650000007839</v>
       </c>
       <c r="K99" t="n">
-        <v>-118.7199624504654</v>
+        <v>-118.7193610547094</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5232,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.28639647780974</v>
+        <v>-12.34800000042636</v>
       </c>
       <c r="K100" t="n">
-        <v>-110.3833200934676</v>
+        <v>-110.3827609283629</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5280,10 +5280,10 @@
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>26.10859251375587</v>
+        <v>26.23949999930823</v>
       </c>
       <c r="K101" t="n">
-        <v>-115.3235526071101</v>
+        <v>-115.3229684164342</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
         <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>43.92386740583603</v>
+        <v>44.14409999917876</v>
       </c>
       <c r="K102" t="n">
-        <v>-115.3235526071101</v>
+        <v>-115.3229684164342</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5376,10 +5376,10 @@
         <v>1.09964</v>
       </c>
       <c r="J103" t="n">
-        <v>-32.86611057729519</v>
+        <v>-33.03090000029042</v>
       </c>
       <c r="K103" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5424,10 +5424,10 @@
         <v>1.09964</v>
       </c>
       <c r="J104" t="n">
-        <v>-21.80835374767401</v>
+        <v>-21.91770000031632</v>
       </c>
       <c r="K104" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5472,10 +5472,10 @@
         <v>1.09964</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.05775683021046</v>
+        <v>-11.11320000056633</v>
       </c>
       <c r="K105" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5520,10 +5520,10 @@
         <v>1.09964</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.143198238634784</v>
+        <v>-6.173999999941742</v>
       </c>
       <c r="K106" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5568,10 +5568,10 @@
         <v>1.09964</v>
       </c>
       <c r="J107" t="n">
-        <v>-1.535799560346184</v>
+        <v>-1.543500000676371</v>
       </c>
       <c r="K107" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         <v>1.09964</v>
       </c>
       <c r="J108" t="n">
-        <v>6.143198238634784</v>
+        <v>6.173999999941742</v>
       </c>
       <c r="K108" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5664,10 +5664,10 @@
         <v>1.09964</v>
       </c>
       <c r="J109" t="n">
-        <v>16.89379515609834</v>
+        <v>16.97849999969173</v>
       </c>
       <c r="K109" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         <v>1.09964</v>
       </c>
       <c r="J110" t="n">
-        <v>21.50119383546727</v>
+        <v>21.60900000004286</v>
       </c>
       <c r="K110" t="n">
-        <v>-48.01288468475079</v>
+        <v>-48.01264146748147</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5760,10 +5760,10 @@
         <v>1.09964</v>
       </c>
       <c r="J111" t="n">
-        <v>26.41575242596261</v>
+        <v>26.54819999958169</v>
       </c>
       <c r="K111" t="n">
-        <v>-48.01288468475079</v>
+        <v>-48.01264146748147</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5808,10 +5808,10 @@
         <v>1.09964</v>
       </c>
       <c r="J112" t="n">
-        <v>35.63054978362015</v>
+        <v>35.80919999919819</v>
       </c>
       <c r="K112" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5856,10 +5856,10 @@
         <v>1.09964</v>
       </c>
       <c r="J113" t="n">
-        <v>44.84534714240713</v>
+        <v>45.07019999994979</v>
       </c>
       <c r="K113" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
         <v>1.09964</v>
       </c>
       <c r="J114" t="n">
-        <v>54.98162423658665</v>
+        <v>55.25730000028797</v>
       </c>
       <c r="K114" t="n">
-        <v>-48.32164921912414</v>
+        <v>-48.32140443775661</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5952,10 +5952,10 @@
         <v>1.09964</v>
       </c>
       <c r="J115" t="n">
-        <v>65.11790132968585</v>
+        <v>65.44439999954039</v>
       </c>
       <c r="K115" t="n">
-        <v>-48.01288468475079</v>
+        <v>-48.01264146748147</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>1.09964</v>
       </c>
       <c r="J116" t="n">
-        <v>-33.48043040057922</v>
+        <v>-33.64829999970223</v>
       </c>
       <c r="K116" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6048,10 +6048,10 @@
         <v>1.09964</v>
       </c>
       <c r="J117" t="n">
-        <v>-22.42267357203837</v>
+        <v>-22.53510000081389</v>
       </c>
       <c r="K117" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6096,10 +6096,10 @@
         <v>1.09964</v>
       </c>
       <c r="J118" t="n">
-        <v>-11.36491674128774</v>
+        <v>-11.42189999970468</v>
       </c>
       <c r="K118" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6144,10 +6144,10 @@
         <v>1.09964</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.836038327557494</v>
+        <v>-5.865300000803389</v>
       </c>
       <c r="K119" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>1.09964</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.842959471423474</v>
+        <v>-1.852199999814724</v>
       </c>
       <c r="K120" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6240,10 +6240,10 @@
         <v>1.09964</v>
       </c>
       <c r="J121" t="n">
-        <v>2.457279294658391</v>
+        <v>2.469599999177186</v>
       </c>
       <c r="K121" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6288,10 +6288,10 @@
         <v>1.09964</v>
       </c>
       <c r="J122" t="n">
-        <v>7.064677974076436</v>
+        <v>7.100099999577665</v>
       </c>
       <c r="K122" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         <v>1.09964</v>
       </c>
       <c r="J123" t="n">
-        <v>11.97923656452266</v>
+        <v>12.03929999906715</v>
       </c>
       <c r="K123" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -6384,10 +6384,10 @@
         <v>1.09964</v>
       </c>
       <c r="J124" t="n">
-        <v>16.5866352438916</v>
+        <v>16.66979999941827</v>
       </c>
       <c r="K124" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
         <v>1.09964</v>
       </c>
       <c r="J125" t="n">
-        <v>22.1155136587513</v>
+        <v>22.22639999945467</v>
       </c>
       <c r="K125" t="n">
-        <v>65.61246298922944</v>
+        <v>65.61213061836303</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -6480,10 +6480,10 @@
         <v>1.09964</v>
       </c>
       <c r="J126" t="n">
-        <v>26.10859251375587</v>
+        <v>26.23949999930823</v>
       </c>
       <c r="K126" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -6528,10 +6528,10 @@
         <v>1.09964</v>
       </c>
       <c r="J127" t="n">
-        <v>30.40883128096718</v>
+        <v>30.56129999943525</v>
       </c>
       <c r="K127" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -6576,10 +6576,10 @@
         <v>1.09964</v>
       </c>
       <c r="J128" t="n">
-        <v>35.01622996033612</v>
+        <v>35.19179999978638</v>
       </c>
       <c r="K128" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
         <v>1.09964</v>
       </c>
       <c r="J129" t="n">
-        <v>39.93078855083146</v>
+        <v>40.13099999932521</v>
       </c>
       <c r="K129" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6672,10 +6672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J130" t="n">
-        <v>44.53818723020039</v>
+        <v>44.76149999967633</v>
       </c>
       <c r="K130" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6720,10 +6720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J131" t="n">
-        <v>54.3673044122223</v>
+        <v>54.6398999997904</v>
       </c>
       <c r="K131" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6768,10 +6768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J132" t="n">
-        <v>64.50358150645093</v>
+        <v>64.82700000017793</v>
       </c>
       <c r="K132" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6816,10 +6816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J133" t="n">
-        <v>-32.86611057729519</v>
+        <v>-33.03090000029042</v>
       </c>
       <c r="K133" t="n">
-        <v>-39.98500686291619</v>
+        <v>-39.98480431219993</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6864,10 +6864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J134" t="n">
-        <v>-21.80835374767401</v>
+        <v>-21.91770000031632</v>
       </c>
       <c r="K134" t="n">
-        <v>-39.98500686291619</v>
+        <v>-39.98480431219993</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J135" t="n">
-        <v>-16.58663524502105</v>
+        <v>-16.66980000055338</v>
       </c>
       <c r="K135" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6960,10 +6960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.05775683021046</v>
+        <v>-11.11320000056633</v>
       </c>
       <c r="K136" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -7008,10 +7008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J137" t="n">
-        <v>-6.143198238634784</v>
+        <v>-6.173999999941742</v>
       </c>
       <c r="K137" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -7056,10 +7056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.535799560346184</v>
+        <v>-1.543500000676371</v>
       </c>
       <c r="K138" t="n">
-        <v>-39.98500686291619</v>
+        <v>-39.98480431219993</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -7104,10 +7104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J139" t="n">
-        <v>2.457279294658391</v>
+        <v>2.469599999177186</v>
       </c>
       <c r="K139" t="n">
-        <v>-39.36747779416951</v>
+        <v>-39.36727837164965</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -7152,10 +7152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J140" t="n">
-        <v>7.371837886234064</v>
+        <v>7.408799999801774</v>
       </c>
       <c r="K140" t="n">
-        <v>-39.98500686291619</v>
+        <v>-39.98480431219993</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -7200,10 +7200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J141" t="n">
-        <v>16.89379515609834</v>
+        <v>16.97849999969173</v>
       </c>
       <c r="K141" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -7248,10 +7248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J142" t="n">
-        <v>21.50119383546727</v>
+        <v>21.60900000004286</v>
       </c>
       <c r="K142" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -7296,10 +7296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J143" t="n">
-        <v>26.41575242596261</v>
+        <v>26.54819999958169</v>
       </c>
       <c r="K143" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J144" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K144" t="n">
-        <v>-39.36747779416951</v>
+        <v>-39.36727837164965</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -7392,10 +7392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J145" t="n">
-        <v>35.32338987254285</v>
+        <v>35.50050000005984</v>
       </c>
       <c r="K145" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J146" t="n">
-        <v>44.84534714240713</v>
+        <v>45.07019999994979</v>
       </c>
       <c r="K146" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -7488,10 +7488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J147" t="n">
-        <v>54.98162423658665</v>
+        <v>55.25730000028797</v>
       </c>
       <c r="K147" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -7536,10 +7536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J148" t="n">
-        <v>64.81074141752822</v>
+        <v>65.13569999931629</v>
       </c>
       <c r="K148" t="n">
-        <v>-39.67624232854285</v>
+        <v>-39.67604134192479</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -7584,10 +7584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J149" t="n">
-        <v>-32.86611057729519</v>
+        <v>-33.03090000029042</v>
       </c>
       <c r="K149" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J150" t="n">
-        <v>-22.11551365983164</v>
+        <v>-22.22640000054043</v>
       </c>
       <c r="K150" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -7680,10 +7680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.05775683021046</v>
+        <v>-11.11320000056633</v>
       </c>
       <c r="K151" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -7728,10 +7728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J152" t="n">
-        <v>-6.143198238634784</v>
+        <v>-6.173999999941742</v>
       </c>
       <c r="K152" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7776,10 +7776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.535799560346184</v>
+        <v>-1.543500000676371</v>
       </c>
       <c r="K153" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7824,10 +7824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J154" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K154" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7872,10 +7872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J155" t="n">
-        <v>7.371837886234064</v>
+        <v>7.408799999801774</v>
       </c>
       <c r="K155" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7920,10 +7920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J156" t="n">
-        <v>11.97923656452266</v>
+        <v>12.03929999906715</v>
       </c>
       <c r="K156" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -7968,10 +7968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J157" t="n">
-        <v>16.89379515609834</v>
+        <v>16.97849999969173</v>
       </c>
       <c r="K157" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -8016,10 +8016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J158" t="n">
-        <v>21.50119383546727</v>
+        <v>21.60900000004286</v>
       </c>
       <c r="K158" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J159" t="n">
-        <v>26.41575242596261</v>
+        <v>26.54819999958169</v>
       </c>
       <c r="K159" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -8112,10 +8112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J160" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K160" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -8160,10 +8160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J161" t="n">
-        <v>35.32338987254285</v>
+        <v>35.50050000005984</v>
       </c>
       <c r="K161" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -8208,10 +8208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J162" t="n">
-        <v>39.93078855083146</v>
+        <v>40.13099999932521</v>
       </c>
       <c r="K162" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J163" t="n">
-        <v>44.84534714240713</v>
+        <v>45.07019999994979</v>
       </c>
       <c r="K163" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -8304,10 +8304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J164" t="n">
-        <v>54.67446432442903</v>
+        <v>54.94860000006386</v>
       </c>
       <c r="K164" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -8352,10 +8352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J165" t="n">
-        <v>64.81074141752822</v>
+        <v>65.13569999931629</v>
       </c>
       <c r="K165" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -8400,10 +8400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J166" t="n">
-        <v>-33.48043040057922</v>
+        <v>-33.64829999970223</v>
       </c>
       <c r="K166" t="n">
-        <v>73.02281175416444</v>
+        <v>73.02244184494133</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -8448,10 +8448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J167" t="n">
-        <v>-22.42267357203837</v>
+        <v>-22.53510000081389</v>
       </c>
       <c r="K167" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -8496,10 +8496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J168" t="n">
-        <v>-16.89379515722778</v>
+        <v>-16.97850000082684</v>
       </c>
       <c r="K168" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -8544,10 +8544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.36491674128774</v>
+        <v>-11.42189999970468</v>
       </c>
       <c r="K169" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J170" t="n">
-        <v>-1.842959471423474</v>
+        <v>-1.852199999814724</v>
       </c>
       <c r="K170" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J171" t="n">
-        <v>3.071599119022754</v>
+        <v>3.086999999674756</v>
       </c>
       <c r="K171" t="n">
-        <v>73.94910534622719</v>
+        <v>73.94873074470951</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
         <v>1.09964</v>
       </c>
       <c r="J172" t="n">
-        <v>7.064677974076436</v>
+        <v>7.100099999577665</v>
       </c>
       <c r="K172" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         <v>1.09964</v>
       </c>
       <c r="J173" t="n">
-        <v>11.97923656452266</v>
+        <v>12.03929999906715</v>
       </c>
       <c r="K173" t="n">
-        <v>73.94910534622719</v>
+        <v>73.94873074470951</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -8784,10 +8784,10 @@
         <v>1.09964</v>
       </c>
       <c r="J174" t="n">
-        <v>16.5866352438916</v>
+        <v>16.66979999941827</v>
       </c>
       <c r="K174" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -8832,10 +8832,10 @@
         <v>1.09964</v>
       </c>
       <c r="J175" t="n">
-        <v>25.80143260267858</v>
+        <v>25.93080000016988</v>
       </c>
       <c r="K175" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -8880,10 +8880,10 @@
         <v>1.09964</v>
       </c>
       <c r="J176" t="n">
-        <v>31.33031101748917</v>
+        <v>31.48740000015693</v>
       </c>
       <c r="K176" t="n">
-        <v>73.94910534622719</v>
+        <v>73.94873074470951</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8928,10 +8928,10 @@
         <v>1.09964</v>
       </c>
       <c r="J177" t="n">
-        <v>35.32338987254285</v>
+        <v>35.50050000005984</v>
       </c>
       <c r="K177" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         <v>1.09964</v>
       </c>
       <c r="J178" t="n">
-        <v>39.93078855083146</v>
+        <v>40.13099999932521</v>
       </c>
       <c r="K178" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -9024,10 +9024,10 @@
         <v>1.09964</v>
       </c>
       <c r="J179" t="n">
-        <v>44.53818723020039</v>
+        <v>44.76149999967633</v>
       </c>
       <c r="K179" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -9072,10 +9072,10 @@
         <v>1.09964</v>
       </c>
       <c r="J180" t="n">
-        <v>54.67446432442903</v>
+        <v>54.94860000006386</v>
       </c>
       <c r="K180" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -9120,10 +9120,10 @@
         <v>1.09964</v>
       </c>
       <c r="J181" t="n">
-        <v>64.50358150645093</v>
+        <v>64.82700000017793</v>
       </c>
       <c r="K181" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -9168,10 +9168,10 @@
         <v>1.09964</v>
       </c>
       <c r="J182" t="n">
-        <v>-33.48043040057922</v>
+        <v>-33.64829999970223</v>
       </c>
       <c r="K182" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -9216,10 +9216,10 @@
         <v>1.09964</v>
       </c>
       <c r="J183" t="n">
-        <v>-22.42267357203837</v>
+        <v>-22.53510000081389</v>
       </c>
       <c r="K183" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -9264,10 +9264,10 @@
         <v>1.09964</v>
       </c>
       <c r="J184" t="n">
-        <v>-11.36491674128774</v>
+        <v>-11.42189999970468</v>
       </c>
       <c r="K184" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -9312,10 +9312,10 @@
         <v>1.09964</v>
       </c>
       <c r="J185" t="n">
-        <v>-1.842959471423474</v>
+        <v>-1.852199999814724</v>
       </c>
       <c r="K185" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -9360,10 +9360,10 @@
         <v>1.09964</v>
       </c>
       <c r="J186" t="n">
-        <v>7.064677974076436</v>
+        <v>7.100099999577665</v>
       </c>
       <c r="K186" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -9408,10 +9408,10 @@
         <v>1.09964</v>
       </c>
       <c r="J187" t="n">
-        <v>12.28639647668029</v>
+        <v>12.34799999929125</v>
       </c>
       <c r="K187" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>1.09964</v>
       </c>
       <c r="J188" t="n">
-        <v>16.5866352438916</v>
+        <v>16.66979999941827</v>
       </c>
       <c r="K188" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -9504,10 +9504,10 @@
         <v>1.09964</v>
       </c>
       <c r="J189" t="n">
-        <v>25.80143260267858</v>
+        <v>25.93080000016988</v>
       </c>
       <c r="K189" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
         <v>1.09964</v>
       </c>
       <c r="J190" t="n">
-        <v>35.01622996033612</v>
+        <v>35.19179999978638</v>
       </c>
       <c r="K190" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -9600,10 +9600,10 @@
         <v>1.09964</v>
       </c>
       <c r="J191" t="n">
-        <v>40.54510837519582</v>
+        <v>40.74839999982278</v>
       </c>
       <c r="K191" t="n">
-        <v>82.59451223680848</v>
+        <v>82.59409384054133</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -9648,10 +9648,10 @@
         <v>1.09964</v>
       </c>
       <c r="J192" t="n">
-        <v>44.23102731804276</v>
+        <v>44.45279999945222</v>
       </c>
       <c r="K192" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -9696,10 +9696,10 @@
         <v>1.09964</v>
       </c>
       <c r="J193" t="n">
-        <v>54.3673044122223</v>
+        <v>54.6398999997904</v>
       </c>
       <c r="K193" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -9744,10 +9744,10 @@
         <v>1.09964</v>
       </c>
       <c r="J194" t="n">
-        <v>64.50358150645093</v>
+        <v>64.82700000017793</v>
       </c>
       <c r="K194" t="n">
-        <v>82.28574770243513</v>
+        <v>82.28533087026619</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -9792,10 +9792,10 @@
         <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>-9.214797358246813</v>
+        <v>-9.261000000208728</v>
       </c>
       <c r="K195" t="n">
-        <v>-94.94509350590825</v>
+        <v>-94.9446125457133</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -9840,10 +9840,10 @@
         <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>12.90071630104466</v>
+        <v>12.96539999978882</v>
       </c>
       <c r="K196" t="n">
-        <v>-94.63632898259218</v>
+        <v>-94.63584958649538</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -9888,10 +9888,10 @@
         <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>39.93078855083146</v>
+        <v>40.13099999932521</v>
       </c>
       <c r="K197" t="n">
-        <v>-94.63632898259218</v>
+        <v>-94.63584958649538</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -9936,10 +9936,10 @@
         <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>41.15942819843074</v>
+        <v>41.36579999918524</v>
       </c>
       <c r="K198" t="n">
-        <v>-93.71003538026196</v>
+        <v>-93.70956067645977</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -9984,10 +9984,10 @@
         <v>1</v>
       </c>
       <c r="J199" t="n">
-        <v>49.14558590961844</v>
+        <v>49.39200000007681</v>
       </c>
       <c r="K199" t="n">
-        <v>-91.54868366255292</v>
+        <v>-91.54821990743808</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         <v>1</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.58663524502105</v>
+        <v>-16.66980000055338</v>
       </c>
       <c r="K200" t="n">
-        <v>-71.47898909572442</v>
+        <v>-71.47862700699228</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -10080,10 +10080,10 @@
         <v>1</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.81527489262033</v>
+        <v>-17.90460000041341</v>
       </c>
       <c r="K201" t="n">
-        <v>-69.31763737801538</v>
+        <v>-69.31728623797059</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -10128,10 +10128,10 @@
         <v>1</v>
       </c>
       <c r="J202" t="n">
-        <v>13.82219603648631</v>
+        <v>13.89149999942475</v>
       </c>
       <c r="K202" t="n">
-        <v>-71.17022456135108</v>
+        <v>-71.16986403671714</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -10176,10 +10176,10 @@
         <v>1</v>
       </c>
       <c r="J203" t="n">
-        <v>46.07398679000641</v>
+        <v>46.30499999980983</v>
       </c>
       <c r="K203" t="n">
-        <v>-71.17022456135108</v>
+        <v>-71.16986403671714</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -10224,10 +10224,10 @@
         <v>1</v>
       </c>
       <c r="J204" t="n">
-        <v>-19.65823436463308</v>
+        <v>-19.75680000082037</v>
       </c>
       <c r="K204" t="n">
-        <v>-56.34952704174854</v>
+        <v>-56.34924159382796</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -10272,10 +10272,10 @@
         <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>0.3071599116174588</v>
+        <v>0.308699999681231</v>
       </c>
       <c r="K205" t="n">
-        <v>-62.21605314745372</v>
+        <v>-62.21573798166742</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -10320,10 +10320,10 @@
         <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K206" t="n">
-        <v>-62.21605314745372</v>
+        <v>-62.21573798166742</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -10368,10 +10368,10 @@
         <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>13.51503612540902</v>
+        <v>13.58280000028639</v>
       </c>
       <c r="K207" t="n">
-        <v>-56.34952704174854</v>
+        <v>-56.34924159382796</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -10416,10 +10416,10 @@
         <v>1</v>
       </c>
       <c r="J208" t="n">
-        <v>37.16634934342616</v>
+        <v>37.35269999933168</v>
       </c>
       <c r="K208" t="n">
-        <v>-56.34952704174854</v>
+        <v>-56.34924159382796</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -10464,10 +10464,10 @@
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>-18.12243480482706</v>
+        <v>-18.21330000068687</v>
       </c>
       <c r="K209" t="n">
-        <v>-39.36747779416951</v>
+        <v>-39.36727837164965</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -10512,10 +10512,10 @@
         <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>-19.96539427571037</v>
+        <v>-20.06549999995872</v>
       </c>
       <c r="K210" t="n">
-        <v>-36.58859700850359</v>
+        <v>-36.58841166286749</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -10560,10 +10560,10 @@
         <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>-14.12935594977338</v>
+        <v>-14.20020000078396</v>
       </c>
       <c r="K211" t="n">
-        <v>-39.36747779416951</v>
+        <v>-39.36727837164965</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -10608,10 +10608,10 @@
         <v>1</v>
       </c>
       <c r="J212" t="n">
-        <v>0.6143198238241934</v>
+        <v>0.6173999999546922</v>
       </c>
       <c r="K212" t="n">
-        <v>-37.82365513414988</v>
+        <v>-37.82346353212101</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -10656,10 +10656,10 @@
         <v>1</v>
       </c>
       <c r="J213" t="n">
-        <v>28.56587181008388</v>
+        <v>28.7091000001634</v>
       </c>
       <c r="K213" t="n">
-        <v>-38.13241966852322</v>
+        <v>-38.13222650239614</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -10704,10 +10704,10 @@
         <v>1</v>
       </c>
       <c r="J214" t="n">
-        <v>-19.96539427571037</v>
+        <v>-20.06549999995872</v>
       </c>
       <c r="K214" t="n">
-        <v>-11.57866993830014</v>
+        <v>-11.57861128461784</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -10752,10 +10752,10 @@
         <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>-18.12243480482706</v>
+        <v>-18.21330000068687</v>
       </c>
       <c r="K215" t="n">
-        <v>-9.417318221380908</v>
+        <v>-9.417270516385944</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -10800,10 +10800,10 @@
         <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>-18.73675462806198</v>
+        <v>-18.83070000004933</v>
       </c>
       <c r="K216" t="n">
-        <v>-5.712143844442046</v>
+        <v>-5.712114908625401</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -10848,10 +10848,10 @@
         <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>-18.73675462806198</v>
+        <v>-18.83070000004933</v>
       </c>
       <c r="K217" t="n">
-        <v>9.417318220591103</v>
+        <v>9.417270515596142</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -10896,10 +10896,10 @@
         <v>1</v>
       </c>
       <c r="J218" t="n">
-        <v>-23.65131321963765</v>
+        <v>-23.76990000067392</v>
       </c>
       <c r="K218" t="n">
-        <v>17.44519604321551</v>
+        <v>17.44510767166749</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -10944,10 +10944,10 @@
         <v>1</v>
       </c>
       <c r="J219" t="n">
-        <v>-15.97231542065668</v>
+        <v>-16.05240000005581</v>
       </c>
       <c r="K219" t="n">
-        <v>17.44519604321551</v>
+        <v>17.44510767166749</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -10992,10 +10992,10 @@
         <v>1</v>
       </c>
       <c r="J220" t="n">
-        <v>0.6143198238241934</v>
+        <v>0.6173999999546922</v>
       </c>
       <c r="K220" t="n">
-        <v>-14.6663152583394</v>
+        <v>-14.66624096367513</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -11040,10 +11040,10 @@
         <v>1</v>
       </c>
       <c r="J221" t="n">
-        <v>0.6143198238241934</v>
+        <v>0.6173999999546922</v>
       </c>
       <c r="K221" t="n">
-        <v>-11.26990541498408</v>
+        <v>-11.26984832539992</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -11088,10 +11088,10 @@
         <v>1</v>
       </c>
       <c r="J222" t="n">
-        <v>28.56587181008388</v>
+        <v>28.7091000001634</v>
       </c>
       <c r="K222" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -11136,10 +11136,10 @@
         <v>1</v>
       </c>
       <c r="J223" t="n">
-        <v>28.56587181008388</v>
+        <v>28.7091000001634</v>
       </c>
       <c r="K223" t="n">
-        <v>-11.26990541498408</v>
+        <v>-11.26984832539992</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -11184,10 +11184,10 @@
         <v>1</v>
       </c>
       <c r="J224" t="n">
-        <v>37.16634934342616</v>
+        <v>37.35269999933168</v>
       </c>
       <c r="K224" t="n">
-        <v>-26.39936746895995</v>
+        <v>-26.39923373856425</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -11232,10 +11232,10 @@
         <v>1</v>
       </c>
       <c r="J225" t="n">
-        <v>13.20787621325139</v>
+        <v>13.27410000006229</v>
       </c>
       <c r="K225" t="n">
-        <v>-26.39936746895995</v>
+        <v>-26.39923373856425</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -11280,10 +11280,10 @@
         <v>1</v>
       </c>
       <c r="J226" t="n">
-        <v>13.51503612540902</v>
+        <v>13.58280000028639</v>
       </c>
       <c r="K226" t="n">
-        <v>0.7719113292200094</v>
+        <v>0.7719074189745225</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -11328,10 +11328,10 @@
         <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>37.16634934342616</v>
+        <v>37.35269999933168</v>
       </c>
       <c r="K227" t="n">
-        <v>1.080675863593352</v>
+        <v>1.080670389249656</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
         <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>0.3071599116174588</v>
+        <v>0.308699999681231</v>
       </c>
       <c r="K228" t="n">
-        <v>7.564731026198131</v>
+        <v>7.564692705792361</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -11424,10 +11424,10 @@
         <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K229" t="n">
-        <v>7.564731026198131</v>
+        <v>7.564692705792361</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
         <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>0.6143198238241934</v>
+        <v>0.6173999999546922</v>
       </c>
       <c r="K230" t="n">
-        <v>20.84160588578103</v>
+        <v>20.8415003091529</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -11520,10 +11520,10 @@
         <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>0.3071599116174588</v>
+        <v>0.308699999681231</v>
       </c>
       <c r="K231" t="n">
-        <v>24.23801574019364</v>
+        <v>24.23789295848533</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -11568,10 +11568,10 @@
         <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>12.90071630104466</v>
+        <v>12.96539999978882</v>
       </c>
       <c r="K232" t="n">
-        <v>17.44519604321551</v>
+        <v>17.44510767166749</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -11616,10 +11616,10 @@
         <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K233" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -11664,10 +11664,10 @@
         <v>1</v>
       </c>
       <c r="J234" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K234" t="n">
-        <v>24.23801574019364</v>
+        <v>24.23789295848533</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -11712,10 +11712,10 @@
         <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>36.85918943234887</v>
+        <v>37.04400000019333</v>
       </c>
       <c r="K235" t="n">
-        <v>17.44519604321551</v>
+        <v>17.44510767166749</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -11760,10 +11760,10 @@
         <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>-2.764439207945464</v>
+        <v>-2.778300000536403</v>
       </c>
       <c r="K236" t="n">
-        <v>37.2061260654032</v>
+        <v>37.20593759157074</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -11808,10 +11808,10 @@
         <v>1</v>
       </c>
       <c r="J237" t="n">
-        <v>4.914558590986397</v>
+        <v>4.939200000032358</v>
       </c>
       <c r="K237" t="n">
-        <v>37.2061260654032</v>
+        <v>37.20593759157074</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -11856,10 +11856,10 @@
         <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>7.678997798440799</v>
+        <v>7.717500000075235</v>
       </c>
       <c r="K238" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -11904,10 +11904,10 @@
         <v>1</v>
       </c>
       <c r="J239" t="n">
-        <v>25.18711277831422</v>
+        <v>25.31339999967231</v>
       </c>
       <c r="K239" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         <v>1</v>
       </c>
       <c r="J240" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K240" t="n">
-        <v>37.82365513336007</v>
+        <v>37.82346353133121</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>1</v>
       </c>
       <c r="J241" t="n">
-        <v>32.86611057729519</v>
+        <v>33.03090000029042</v>
       </c>
       <c r="K241" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -12048,10 +12048,10 @@
         <v>1</v>
       </c>
       <c r="J242" t="n">
-        <v>40.23794846298908</v>
+        <v>40.43969999954932</v>
       </c>
       <c r="K242" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -12096,10 +12096,10 @@
         <v>1</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.401693542511253e-10</v>
+        <v>-5.428777427596287e-10</v>
       </c>
       <c r="K243" t="n">
-        <v>50.48300093604337</v>
+        <v>50.4827452059885</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -12144,10 +12144,10 @@
         <v>1</v>
       </c>
       <c r="J244" t="n">
-        <v>7.678997798440799</v>
+        <v>7.717500000075235</v>
       </c>
       <c r="K244" t="n">
-        <v>47.39535561600411</v>
+        <v>47.39511552693121</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -12192,10 +12192,10 @@
         <v>1</v>
       </c>
       <c r="J245" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K245" t="n">
-        <v>47.70412015037746</v>
+        <v>47.70387849720634</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -12240,10 +12240,10 @@
         <v>1</v>
       </c>
       <c r="J246" t="n">
-        <v>36.85918943234887</v>
+        <v>37.04400000019333</v>
       </c>
       <c r="K246" t="n">
-        <v>50.48300093604337</v>
+        <v>50.4827452059885</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -12288,10 +12288,10 @@
         <v>1</v>
       </c>
       <c r="J247" t="n">
-        <v>-14.43651586085067</v>
+        <v>-14.50889999992232</v>
       </c>
       <c r="K247" t="n">
-        <v>72.71404722058091</v>
+        <v>72.713678875456</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -12336,10 +12336,10 @@
         <v>1</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.401693542511253e-10</v>
+        <v>-5.428777427596287e-10</v>
       </c>
       <c r="K248" t="n">
-        <v>75.49292800545702</v>
+        <v>75.49254558344836</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -12384,10 +12384,10 @@
         <v>1</v>
       </c>
       <c r="J249" t="n">
-        <v>4.300238766671141</v>
+        <v>4.32179999958414</v>
       </c>
       <c r="K249" t="n">
-        <v>73.94910534622719</v>
+        <v>73.94873074470951</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -12432,10 +12432,10 @@
         <v>1</v>
       </c>
       <c r="J250" t="n">
-        <v>7.678997798440799</v>
+        <v>7.717500000075235</v>
       </c>
       <c r="K250" t="n">
-        <v>72.09651815183422</v>
+        <v>72.09615293490573</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -12480,10 +12480,10 @@
         <v>1</v>
       </c>
       <c r="J251" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K251" t="n">
-        <v>72.40528268620756</v>
+        <v>72.40491590518086</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -12528,10 +12528,10 @@
         <v>1</v>
       </c>
       <c r="J252" t="n">
-        <v>13.82219603648631</v>
+        <v>13.89149999942475</v>
       </c>
       <c r="K252" t="n">
-        <v>82.59451223680848</v>
+        <v>82.59409384054133</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -12576,10 +12576,10 @@
         <v>1</v>
       </c>
       <c r="J253" t="n">
-        <v>41.7737480227951</v>
+        <v>41.98319999968281</v>
       </c>
       <c r="K253" t="n">
-        <v>82.59451223680848</v>
+        <v>82.59409384054133</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -12624,10 +12624,10 @@
         <v>1</v>
       </c>
       <c r="J254" t="n">
-        <v>-13.51503612545812</v>
+        <v>-13.58280000033575</v>
       </c>
       <c r="K254" t="n">
-        <v>89.07856739941326</v>
+        <v>89.07811615708404</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -12672,10 +12672,10 @@
         <v>1</v>
       </c>
       <c r="J255" t="n">
-        <v>7.371837886234064</v>
+        <v>7.408799999801774</v>
       </c>
       <c r="K255" t="n">
-        <v>91.23991912817957</v>
+        <v>91.23945693716294</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         <v>1</v>
       </c>
       <c r="J256" t="n">
-        <v>18.12243480369762</v>
+        <v>18.21329999955177</v>
       </c>
       <c r="K256" t="n">
-        <v>90.62239005943289</v>
+        <v>90.62193099661268</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -12768,10 +12768,10 @@
         <v>1</v>
       </c>
       <c r="J257" t="n">
-        <v>28.25871189792625</v>
+        <v>28.4003999999393</v>
       </c>
       <c r="K257" t="n">
-        <v>91.54868365070584</v>
+        <v>91.54821989559106</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>1</v>
       </c>
       <c r="J258" t="n">
-        <v>46.07398679000641</v>
+        <v>46.30499999980983</v>
       </c>
       <c r="K258" t="n">
-        <v>90.93115459380623</v>
+        <v>90.93069396688782</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -12864,10 +12864,10 @@
         <v>1</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.757518062999146</v>
+        <v>-6.791400000439312</v>
       </c>
       <c r="K259" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -12912,10 +12912,10 @@
         <v>1</v>
       </c>
       <c r="J260" t="n">
-        <v>0.9214797359818215</v>
+        <v>0.9261000001788009</v>
       </c>
       <c r="K260" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -12960,10 +12960,10 @@
         <v>1</v>
       </c>
       <c r="J261" t="n">
-        <v>7.986157710598427</v>
+        <v>8.026200000299344</v>
       </c>
       <c r="K261" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -13008,10 +13008,10 @@
         <v>1</v>
       </c>
       <c r="J262" t="n">
-        <v>21.19403392330965</v>
+        <v>21.30029999981875</v>
       </c>
       <c r="K262" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -13056,10 +13056,10 @@
         <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>36.2448696079845</v>
+        <v>36.42659999969576</v>
       </c>
       <c r="K263" t="n">
-        <v>93.71003537947215</v>
+        <v>93.70956067566998</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -13104,10 +13104,10 @@
         <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>59.28186300271763</v>
+        <v>59.57909999932924</v>
       </c>
       <c r="K264" t="n">
-        <v>109.1482619670316</v>
+        <v>109.1477090583196</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -13152,10 +13152,10 @@
         <v>1</v>
       </c>
       <c r="J265" t="n">
-        <v>68.80382027253279</v>
+        <v>69.14879999916984</v>
       </c>
       <c r="K265" t="n">
-        <v>104.5167939869727</v>
+        <v>104.5162645397337</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -13200,10 +13200,10 @@
         <v>1</v>
       </c>
       <c r="J266" t="n">
-        <v>68.80382027253279</v>
+        <v>69.14879999916984</v>
       </c>
       <c r="K266" t="n">
-        <v>112.5446718095971</v>
+        <v>112.544101695805</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -13248,10 +13248,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J267" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K267" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -13296,10 +13296,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J268" t="n">
-        <v>1.842959471423474</v>
+        <v>1.852199999814724</v>
       </c>
       <c r="K268" t="n">
-        <v>-21.15037042094418</v>
+        <v>-21.15026328021784</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -13344,10 +13344,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J269" t="n">
-        <v>10.44343700584609</v>
+        <v>10.49580000006876</v>
       </c>
       <c r="K269" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -13392,10 +13392,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J270" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K270" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -13440,10 +13440,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J271" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K271" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -13488,10 +13488,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J272" t="n">
-        <v>38.39498899102544</v>
+        <v>38.58749999919171</v>
       </c>
       <c r="K272" t="n">
-        <v>-21.15037042094418</v>
+        <v>-21.15026328021784</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J273" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K273" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J274" t="n">
-        <v>1.842959471423474</v>
+        <v>1.852199999814724</v>
       </c>
       <c r="K274" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -13632,10 +13632,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J275" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K275" t="n">
-        <v>13.43125713190331</v>
+        <v>13.43118909363182</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -13680,10 +13680,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J276" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K276" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -13728,10 +13728,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J277" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K277" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -13776,10 +13776,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J278" t="n">
-        <v>38.08782907994815</v>
+        <v>38.27880000005337</v>
       </c>
       <c r="K278" t="n">
-        <v>13.12249259752997</v>
+        <v>13.12242612335668</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         <v>2.6</v>
       </c>
       <c r="J279" t="n">
-        <v>-10.44343700584609</v>
+        <v>-10.49580000006876</v>
       </c>
       <c r="K279" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -13872,10 +13872,10 @@
         <v>2.6</v>
       </c>
       <c r="J280" t="n">
-        <v>17.5081149804627</v>
+        <v>17.5959000001893</v>
       </c>
       <c r="K280" t="n">
-        <v>-60.67223048743409</v>
+        <v>-60.67192314213877</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -13920,10 +13920,10 @@
         <v>2.6</v>
       </c>
       <c r="J281" t="n">
-        <v>45.45966696564204</v>
+        <v>45.68759999931225</v>
       </c>
       <c r="K281" t="n">
-        <v>-60.05470141868741</v>
+        <v>-60.0543972015885</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -13968,10 +13968,10 @@
         <v>2.6</v>
       </c>
       <c r="J282" t="n">
-        <v>-10.44343700584609</v>
+        <v>-10.49580000006876</v>
       </c>
       <c r="K282" t="n">
-        <v>5.403379298221623</v>
+        <v>5.403351926503246</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -14016,10 +14016,10 @@
         <v>2.6</v>
       </c>
       <c r="J283" t="n">
-        <v>17.5081149804627</v>
+        <v>17.5959000001893</v>
       </c>
       <c r="K283" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -14064,10 +14064,10 @@
         <v>2.6</v>
       </c>
       <c r="J284" t="n">
-        <v>45.15250705456476</v>
+        <v>45.37890000017391</v>
       </c>
       <c r="K284" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -14112,10 +14112,10 @@
         <v>2.6</v>
       </c>
       <c r="J285" t="n">
-        <v>-11.05775683021046</v>
+        <v>-11.11320000056633</v>
       </c>
       <c r="K285" t="n">
-        <v>93.71003537947215</v>
+        <v>93.70956067566998</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -14160,10 +14160,10 @@
         <v>2.6</v>
       </c>
       <c r="J286" t="n">
-        <v>17.20095506825596</v>
+        <v>17.28719999991584</v>
       </c>
       <c r="K286" t="n">
-        <v>94.01879991305569</v>
+        <v>94.01832364515531</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -14208,10 +14208,10 @@
         <v>2.6</v>
       </c>
       <c r="J287" t="n">
-        <v>44.84534714240713</v>
+        <v>45.07019999994979</v>
       </c>
       <c r="K287" t="n">
-        <v>94.01879991305569</v>
+        <v>94.01832364515531</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -14256,10 +14256,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J288" t="n">
-        <v>-4.914558591035504</v>
+        <v>-4.93920000008171</v>
       </c>
       <c r="K288" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -14304,10 +14304,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J289" t="n">
-        <v>4.914558590986397</v>
+        <v>4.939200000032358</v>
       </c>
       <c r="K289" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -14352,10 +14352,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J290" t="n">
-        <v>15.05083568413469</v>
+        <v>15.12629999933413</v>
       </c>
       <c r="K290" t="n">
-        <v>-73.64034082370092</v>
+        <v>-73.6399677862814</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -14400,10 +14400,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J291" t="n">
-        <v>23.65131321850821</v>
+        <v>23.76989999953881</v>
       </c>
       <c r="K291" t="n">
-        <v>-73.64034082370092</v>
+        <v>-73.6399677862814</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -14448,10 +14448,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J292" t="n">
-        <v>32.86611057729519</v>
+        <v>33.03090000029042</v>
       </c>
       <c r="K292" t="n">
-        <v>-72.40528269805465</v>
+        <v>-72.40491591702788</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -14496,10 +14496,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J293" t="n">
-        <v>46.07398679000641</v>
+        <v>46.30499999980983</v>
       </c>
       <c r="K293" t="n">
-        <v>-73.94910535807428</v>
+        <v>-73.94873075655653</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -14544,10 +14544,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.30023876775148</v>
+        <v>-4.321800000669896</v>
       </c>
       <c r="K294" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -14592,10 +14592,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J295" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K295" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -14640,10 +14640,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J296" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K296" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -14688,10 +14688,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J297" t="n">
-        <v>23.65131321850821</v>
+        <v>23.76989999953881</v>
       </c>
       <c r="K297" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -14736,10 +14736,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J298" t="n">
-        <v>31.33031101748917</v>
+        <v>31.48740000015693</v>
       </c>
       <c r="K298" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -14784,10 +14784,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J299" t="n">
-        <v>38.70214890318307</v>
+        <v>38.89619999941583</v>
       </c>
       <c r="K299" t="n">
-        <v>-66.22999205876593</v>
+        <v>-66.22965655970309</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -14832,10 +14832,10 @@
         <v>1</v>
       </c>
       <c r="J300" t="n">
-        <v>-0.3071599127469039</v>
+        <v>-0.308700000816339</v>
       </c>
       <c r="K300" t="n">
-        <v>-81.35945411195199</v>
+        <v>-81.35904197207762</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -14880,10 +14880,10 @@
         <v>1</v>
       </c>
       <c r="J301" t="n">
-        <v>30.10167136988989</v>
+        <v>30.25260000029689</v>
       </c>
       <c r="K301" t="n">
-        <v>-81.35945411195199</v>
+        <v>-81.35904197207762</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -14928,10 +14928,10 @@
         <v>1</v>
       </c>
       <c r="J302" t="n">
-        <v>49.75990573285335</v>
+        <v>50.00939999943927</v>
       </c>
       <c r="K302" t="n">
-        <v>-80.12439598630571</v>
+        <v>-80.1239901028241</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -14976,10 +14976,10 @@
         <v>1</v>
       </c>
       <c r="J303" t="n">
-        <v>51.91002511702374</v>
+        <v>52.17030000007034</v>
       </c>
       <c r="K303" t="n">
-        <v>-84.44709943199126</v>
+        <v>-84.44667165113491</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -15024,10 +15024,10 @@
         <v>1</v>
       </c>
       <c r="J304" t="n">
-        <v>-4.914558591035504</v>
+        <v>-4.93920000008171</v>
       </c>
       <c r="K304" t="n">
-        <v>46.46906202473117</v>
+        <v>46.46882662795283</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -15072,10 +15072,10 @@
         <v>1</v>
       </c>
       <c r="J305" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K305" t="n">
-        <v>46.46906202473117</v>
+        <v>46.46882662795283</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -15120,10 +15120,10 @@
         <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K306" t="n">
-        <v>46.7778265583147</v>
+        <v>46.77758959743816</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -15168,10 +15168,10 @@
         <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>23.03699339527329</v>
+        <v>23.15250000017635</v>
       </c>
       <c r="K307" t="n">
-        <v>46.46906202473117</v>
+        <v>46.46882662795283</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -15216,10 +15216,10 @@
         <v>1</v>
       </c>
       <c r="J308" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K308" t="n">
-        <v>46.7778265583147</v>
+        <v>46.77758959743816</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -15264,10 +15264,10 @@
         <v>1</v>
       </c>
       <c r="J309" t="n">
-        <v>38.39498899102544</v>
+        <v>38.58749999919171</v>
       </c>
       <c r="K309" t="n">
-        <v>46.46906202473117</v>
+        <v>46.46882662795283</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -15312,10 +15312,10 @@
         <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.914558591035504</v>
+        <v>-4.93920000008171</v>
       </c>
       <c r="K310" t="n">
-        <v>54.80570438093911</v>
+        <v>54.80542675350951</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -15360,10 +15360,10 @@
         <v>1</v>
       </c>
       <c r="J311" t="n">
-        <v>1.842959471423474</v>
+        <v>1.852199999814724</v>
       </c>
       <c r="K311" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -15408,10 +15408,10 @@
         <v>1</v>
       </c>
       <c r="J312" t="n">
-        <v>10.44343700584609</v>
+        <v>10.49580000006876</v>
       </c>
       <c r="K312" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -15456,10 +15456,10 @@
         <v>1</v>
       </c>
       <c r="J313" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K313" t="n">
-        <v>55.11446891531246</v>
+        <v>55.11418972378465</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -15504,10 +15504,10 @@
         <v>1</v>
       </c>
       <c r="J314" t="n">
-        <v>38.08782907994815</v>
+        <v>38.27880000005337</v>
       </c>
       <c r="K314" t="n">
-        <v>55.11446891531246</v>
+        <v>55.11418972378465</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -15552,10 +15552,10 @@
         <v>1</v>
       </c>
       <c r="J315" t="n">
-        <v>30.40883128096718</v>
+        <v>30.56129999943525</v>
       </c>
       <c r="K315" t="n">
-        <v>54.80570438093911</v>
+        <v>54.80542675350951</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -15600,10 +15600,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J316" t="n">
-        <v>-4.30023876775148</v>
+        <v>-4.321800000669896</v>
       </c>
       <c r="K316" t="n">
-        <v>39.67624232775304</v>
+        <v>39.67604134113499</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -15648,10 +15648,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J317" t="n">
-        <v>4.300238766671141</v>
+        <v>4.32179999958414</v>
       </c>
       <c r="K317" t="n">
-        <v>39.67624232775304</v>
+        <v>39.67604134113499</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -15696,10 +15696,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J318" t="n">
-        <v>11.67207665344537</v>
+        <v>11.73059999992879</v>
       </c>
       <c r="K318" t="n">
-        <v>39.98500686212638</v>
+        <v>39.98480431141012</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -15744,10 +15744,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J319" t="n">
-        <v>23.65131321850821</v>
+        <v>23.76989999953881</v>
       </c>
       <c r="K319" t="n">
-        <v>39.98500686212638</v>
+        <v>39.98480431141012</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -15792,10 +15792,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J320" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K320" t="n">
-        <v>39.67624232775304</v>
+        <v>39.67604134113499</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -15840,10 +15840,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J321" t="n">
-        <v>39.0093088153898</v>
+        <v>39.20489999968929</v>
       </c>
       <c r="K321" t="n">
-        <v>39.67624232775304</v>
+        <v>39.67604134113499</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J322" t="n">
-        <v>-14.7436757730574</v>
+        <v>-14.81760000019578</v>
       </c>
       <c r="K322" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -15936,10 +15936,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J323" t="n">
-        <v>-4.914558591035504</v>
+        <v>-4.93920000008171</v>
       </c>
       <c r="K323" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -15984,10 +15984,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J324" t="n">
-        <v>5.221718502063687</v>
+        <v>5.247899999170711</v>
       </c>
       <c r="K324" t="n">
-        <v>-78.58057332628609</v>
+        <v>-78.58017526329546</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -16032,10 +16032,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J325" t="n">
-        <v>15.35799559629232</v>
+        <v>15.43499999955824</v>
       </c>
       <c r="K325" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -16080,10 +16080,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J326" t="n">
-        <v>24.87995286615659</v>
+        <v>25.0046999994482</v>
       </c>
       <c r="K326" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -16128,10 +16128,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J327" t="n">
-        <v>35.32338987254285</v>
+        <v>35.50050000005984</v>
       </c>
       <c r="K327" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -16176,10 +16176,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J328" t="n">
-        <v>45.45966696564204</v>
+        <v>45.68759999931225</v>
       </c>
       <c r="K328" t="n">
-        <v>-78.27180879191273</v>
+        <v>-78.27141229302032</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -16224,10 +16224,10 @@
         <v>6.109054</v>
       </c>
       <c r="J329" t="n">
-        <v>-14.12935594977338</v>
+        <v>-14.20020000078396</v>
       </c>
       <c r="K329" t="n">
-        <v>-88.46103834330346</v>
+        <v>-88.46059022917059</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -16272,10 +16272,10 @@
         <v>6.109054</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.30023876775148</v>
+        <v>-4.321800000669896</v>
       </c>
       <c r="K330" t="n">
-        <v>-89.07856741126034</v>
+        <v>-89.07811616893106</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -16320,10 +16320,10 @@
         <v>6.109054</v>
       </c>
       <c r="J331" t="n">
-        <v>5.836038326428049</v>
+        <v>5.865299999668281</v>
       </c>
       <c r="K331" t="n">
-        <v>-88.769802876887</v>
+        <v>-88.76935319865592</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -16368,10 +16368,10 @@
         <v>6.109054</v>
       </c>
       <c r="J332" t="n">
-        <v>15.97231542065668</v>
+        <v>16.05240000005581</v>
       </c>
       <c r="K332" t="n">
-        <v>-89.07856741126034</v>
+        <v>-89.07811616893106</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -16416,10 +16416,10 @@
         <v>6.109054</v>
       </c>
       <c r="J333" t="n">
-        <v>25.49427269052095</v>
+        <v>25.62209999994577</v>
       </c>
       <c r="K333" t="n">
-        <v>-88.769802876887</v>
+        <v>-88.76935319865592</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -16464,10 +16464,10 @@
         <v>6.109054</v>
       </c>
       <c r="J334" t="n">
-        <v>35.01622996033612</v>
+        <v>35.19179999978638</v>
       </c>
       <c r="K334" t="n">
-        <v>-88.769802876887</v>
+        <v>-88.76935319865592</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -16512,10 +16512,10 @@
         <v>6.109054</v>
       </c>
       <c r="J335" t="n">
-        <v>45.45966696564204</v>
+        <v>45.68759999931225</v>
       </c>
       <c r="K335" t="n">
-        <v>-88.46103834330346</v>
+        <v>-88.46059022917059</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -16560,10 +16560,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J336" t="n">
-        <v>-3.993078855593851</v>
+        <v>-4.013100000445787</v>
       </c>
       <c r="K336" t="n">
-        <v>-7.255966504461676</v>
+        <v>-7.255929748154049</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -16608,10 +16608,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J337" t="n">
-        <v>3.071599119022754</v>
+        <v>3.086999999674756</v>
       </c>
       <c r="K337" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -16656,10 +16656,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J338" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K338" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -16704,10 +16704,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J339" t="n">
-        <v>23.65131321850821</v>
+        <v>23.76989999953881</v>
       </c>
       <c r="K339" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -16752,10 +16752,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J340" t="n">
-        <v>31.02315110533155</v>
+        <v>31.17869999993282</v>
       </c>
       <c r="K340" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -16800,10 +16800,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J341" t="n">
-        <v>38.70214890318307</v>
+        <v>38.89619999941583</v>
       </c>
       <c r="K341" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -16848,10 +16848,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J342" t="n">
-        <v>-4.30023876775148</v>
+        <v>-4.321800000669896</v>
       </c>
       <c r="K342" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -16896,10 +16896,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J343" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K343" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -16944,10 +16944,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J344" t="n">
-        <v>10.44343700584609</v>
+        <v>10.49580000006876</v>
       </c>
       <c r="K344" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -16992,10 +16992,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J345" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K345" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -17040,10 +17040,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J346" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K346" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -17088,10 +17088,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J347" t="n">
-        <v>38.70214890318307</v>
+        <v>38.89619999941583</v>
       </c>
       <c r="K347" t="n">
-        <v>28.56071918508938</v>
+        <v>28.56057450600634</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -17136,10 +17136,10 @@
         <v>1.09964</v>
       </c>
       <c r="J348" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K348" t="n">
-        <v>-60.67223048743409</v>
+        <v>-60.67192314213877</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -17184,10 +17184,10 @@
         <v>1.09964</v>
       </c>
       <c r="J349" t="n">
-        <v>2.457279294658391</v>
+        <v>2.469599999177186</v>
       </c>
       <c r="K349" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -17232,10 +17232,10 @@
         <v>1.09964</v>
       </c>
       <c r="J350" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K350" t="n">
-        <v>-60.67223048743409</v>
+        <v>-60.67192314213877</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -17280,10 +17280,10 @@
         <v>1.09964</v>
       </c>
       <c r="J351" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K351" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -17328,10 +17328,10 @@
         <v>1.09964</v>
       </c>
       <c r="J352" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K352" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -17376,10 +17376,10 @@
         <v>1.09964</v>
       </c>
       <c r="J353" t="n">
-        <v>38.39498899102544</v>
+        <v>38.58749999919171</v>
       </c>
       <c r="K353" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -17424,10 +17424,10 @@
         <v>1.09964</v>
       </c>
       <c r="J354" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K354" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -17472,10 +17472,10 @@
         <v>1.09964</v>
       </c>
       <c r="J355" t="n">
-        <v>2.457279294658391</v>
+        <v>2.469599999177186</v>
       </c>
       <c r="K355" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -17520,10 +17520,10 @@
         <v>1.09964</v>
       </c>
       <c r="J356" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K356" t="n">
-        <v>5.403379298221623</v>
+        <v>5.403351926503246</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -17568,10 +17568,10 @@
         <v>1.09964</v>
       </c>
       <c r="J357" t="n">
-        <v>24.57279295394986</v>
+        <v>24.69599999917474</v>
       </c>
       <c r="K357" t="n">
-        <v>5.712143832594965</v>
+        <v>5.71211489677838</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -17616,10 +17616,10 @@
         <v>1.09964</v>
       </c>
       <c r="J358" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K358" t="n">
-        <v>6.329672900551844</v>
+        <v>6.329640836538847</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -17664,10 +17664,10 @@
         <v>1.09964</v>
       </c>
       <c r="J359" t="n">
-        <v>38.39498899102544</v>
+        <v>38.58749999919171</v>
       </c>
       <c r="K359" t="n">
-        <v>6.020908366178501</v>
+        <v>6.020877866263713</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -17712,10 +17712,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J360" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K360" t="n">
-        <v>-14.04878620064999</v>
+        <v>-14.04871503418209</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -17760,10 +17760,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J361" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K361" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -17808,10 +17808,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J362" t="n">
-        <v>10.44343700584609</v>
+        <v>10.49580000006876</v>
       </c>
       <c r="K362" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -17856,10 +17856,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J363" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K363" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -17904,10 +17904,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J364" t="n">
-        <v>31.02315110533155</v>
+        <v>31.17869999993282</v>
       </c>
       <c r="K364" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -17952,10 +17952,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J365" t="n">
-        <v>38.70214890318307</v>
+        <v>38.89619999941583</v>
       </c>
       <c r="K365" t="n">
-        <v>-13.74002166706646</v>
+        <v>-13.73995206469675</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -18000,10 +18000,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J366" t="n">
-        <v>-4.607398678828769</v>
+        <v>-4.630499999808249</v>
       </c>
       <c r="K366" t="n">
-        <v>21.45913495452772</v>
+        <v>21.45902624970317</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J367" t="n">
-        <v>2.764439206865126</v>
+        <v>2.778299999450647</v>
       </c>
       <c r="K367" t="n">
-        <v>21.45913495452772</v>
+        <v>21.45902624970317</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -18096,10 +18096,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J368" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K368" t="n">
-        <v>21.45913495452772</v>
+        <v>21.45902624970317</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -18144,10 +18144,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J369" t="n">
-        <v>23.34415330635058</v>
+        <v>23.46119999931471</v>
       </c>
       <c r="K369" t="n">
-        <v>21.45913495452772</v>
+        <v>21.45902624970317</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -18192,10 +18192,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J370" t="n">
-        <v>30.71599119317392</v>
+        <v>30.86999999970871</v>
       </c>
       <c r="K370" t="n">
-        <v>21.76789948811125</v>
+        <v>21.7677892191885</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -18240,10 +18240,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J371" t="n">
-        <v>38.08782907994815</v>
+        <v>38.27880000005337</v>
       </c>
       <c r="K371" t="n">
-        <v>21.45913495452772</v>
+        <v>21.45902624970317</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -18288,10 +18288,10 @@
         <v>2.6</v>
       </c>
       <c r="J372" t="n">
-        <v>-10.75059691800372</v>
+        <v>-10.80450000029287</v>
       </c>
       <c r="K372" t="n">
-        <v>-120.5725496440686</v>
+        <v>-120.5719388637234</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -18336,10 +18336,10 @@
         <v>2.6</v>
       </c>
       <c r="J373" t="n">
-        <v>17.5081149804627</v>
+        <v>17.5959000001893</v>
       </c>
       <c r="K373" t="n">
-        <v>-120.8813141784419</v>
+        <v>-120.8807018339985</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -18384,10 +18384,10 @@
         <v>1</v>
       </c>
       <c r="J374" t="n">
-        <v>-101.6699308504173</v>
+        <v>-102.1797000000525</v>
       </c>
       <c r="K374" t="n">
-        <v>-115.6323171304261</v>
+        <v>-115.6317313756521</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -18432,10 +18432,10 @@
         <v>1</v>
       </c>
       <c r="J375" t="n">
-        <v>-77.09713789592723</v>
+        <v>-77.48370000033488</v>
       </c>
       <c r="K375" t="n">
-        <v>-115.6323171304261</v>
+        <v>-115.6317313756521</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -18480,10 +18480,10 @@
         <v>1</v>
       </c>
       <c r="J376" t="n">
-        <v>-51.60286520594644</v>
+        <v>-51.86160000093199</v>
       </c>
       <c r="K376" t="n">
-        <v>-115.6323171304261</v>
+        <v>-115.6317313756521</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -18528,10 +18528,10 @@
         <v>1</v>
       </c>
       <c r="J377" t="n">
-        <v>-62.35346212341</v>
+        <v>-62.66610000068198</v>
       </c>
       <c r="K377" t="n">
-        <v>154.8454126617529</v>
+        <v>154.8446282665081</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
@@ -18576,10 +18576,10 @@
         <v>1</v>
       </c>
       <c r="J378" t="n">
-        <v>-44.53818723132984</v>
+        <v>-44.76150000081144</v>
       </c>
       <c r="K378" t="n">
-        <v>154.8454126617529</v>
+        <v>154.8446282665081</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -18624,10 +18624,10 @@
         <v>1.09964</v>
       </c>
       <c r="J379" t="n">
-        <v>-99.51981146737633</v>
+        <v>-100.0188000005565</v>
       </c>
       <c r="K379" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L379" t="inlineStr">
         <is>
@@ -18672,10 +18672,10 @@
         <v>1.09964</v>
       </c>
       <c r="J380" t="n">
-        <v>-94.91241278800739</v>
+        <v>-95.38830000020542</v>
       </c>
       <c r="K380" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -18720,10 +18720,10 @@
         <v>1.09964</v>
       </c>
       <c r="J381" t="n">
-        <v>-90.30501410858935</v>
+        <v>-90.75779999980493</v>
       </c>
       <c r="K381" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -18768,10 +18768,10 @@
         <v>1.09964</v>
       </c>
       <c r="J382" t="n">
-        <v>-81.39737666308943</v>
+        <v>-81.80550000041254</v>
       </c>
       <c r="K382" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L382" t="inlineStr">
         <is>
@@ -18816,10 +18816,10 @@
         <v>1.09964</v>
       </c>
       <c r="J383" t="n">
-        <v>-71.56825948106753</v>
+        <v>-71.92710000029848</v>
       </c>
       <c r="K383" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -18864,10 +18864,10 @@
         <v>1.09964</v>
       </c>
       <c r="J384" t="n">
-        <v>-66.9608608016986</v>
+        <v>-67.29659999994735</v>
       </c>
       <c r="K384" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -18912,10 +18912,10 @@
         <v>1.09964</v>
       </c>
       <c r="J385" t="n">
-        <v>-62.04630221125237</v>
+        <v>-62.35740000045787</v>
       </c>
       <c r="K385" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -18960,10 +18960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J386" t="n">
-        <v>-53.13866476462302</v>
+        <v>-53.40509999993037</v>
       </c>
       <c r="K386" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -19008,10 +19008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J387" t="n">
-        <v>-43.61670749480785</v>
+        <v>-43.83540000008976</v>
       </c>
       <c r="K387" t="n">
-        <v>-48.63041375349748</v>
+        <v>-48.63016740803174</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -19056,10 +19056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J388" t="n">
-        <v>-94.60525287580066</v>
+        <v>-95.07959999993196</v>
       </c>
       <c r="K388" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -19104,10 +19104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J389" t="n">
-        <v>-90.30501410858935</v>
+        <v>-90.75779999980493</v>
       </c>
       <c r="K389" t="n">
-        <v>64.37740486358315</v>
+        <v>64.37707874910951</v>
       </c>
       <c r="L389" t="inlineStr">
         <is>
@@ -19152,10 +19152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J390" t="n">
-        <v>-86.31193525358476</v>
+        <v>-86.74469999995138</v>
       </c>
       <c r="K390" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -19200,10 +19200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J391" t="n">
-        <v>-81.70453657529617</v>
+        <v>-82.114200000686</v>
       </c>
       <c r="K391" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -19248,10 +19248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J392" t="n">
-        <v>-76.78997798372049</v>
+        <v>-77.17500000006142</v>
       </c>
       <c r="K392" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -19296,10 +19296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J393" t="n">
-        <v>-72.18257930435156</v>
+        <v>-72.5444999997103</v>
       </c>
       <c r="K393" t="n">
-        <v>64.37740486358315</v>
+        <v>64.37707874910951</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -19344,10 +19344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J394" t="n">
-        <v>-67.57518062606296</v>
+        <v>-67.91400000044491</v>
       </c>
       <c r="K394" t="n">
-        <v>64.06864032920981</v>
+        <v>64.06831577883437</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -19392,10 +19392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J395" t="n">
-        <v>-62.66062203448728</v>
+        <v>-62.97479999982033</v>
       </c>
       <c r="K395" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -19440,10 +19440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J396" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K396" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
@@ -19488,10 +19488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J397" t="n">
-        <v>-53.44582467682975</v>
+        <v>-53.71380000020383</v>
       </c>
       <c r="K397" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -19536,10 +19536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J398" t="n">
-        <v>-48.8384259974117</v>
+        <v>-49.08329999980335</v>
       </c>
       <c r="K398" t="n">
-        <v>65.30369845485609</v>
+        <v>65.30336764808789</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
@@ -19584,10 +19584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J399" t="n">
-        <v>-44.23102731912311</v>
+        <v>-44.45280000053798</v>
       </c>
       <c r="K399" t="n">
-        <v>64.68616939795649</v>
+        <v>64.68584171938464</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -19632,10 +19632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J400" t="n">
-        <v>-95.21957270016502</v>
+        <v>-95.69700000042953</v>
       </c>
       <c r="K400" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -19680,10 +19680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J401" t="n">
-        <v>-89.99785419751205</v>
+        <v>-90.44910000066658</v>
       </c>
       <c r="K401" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
@@ -19728,10 +19728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J402" t="n">
-        <v>-86.00477534250747</v>
+        <v>-86.43600000081302</v>
       </c>
       <c r="K402" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
@@ -19776,10 +19776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J403" t="n">
-        <v>-81.39737666308943</v>
+        <v>-81.80550000041254</v>
       </c>
       <c r="K403" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
@@ -19824,10 +19824,10 @@
         <v>1.09964</v>
       </c>
       <c r="J404" t="n">
-        <v>-71.56825948106753</v>
+        <v>-71.92710000029848</v>
       </c>
       <c r="K404" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -19872,10 +19872,10 @@
         <v>1.09964</v>
       </c>
       <c r="J405" t="n">
-        <v>-66.9608608016986</v>
+        <v>-67.29659999994735</v>
       </c>
       <c r="K405" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
@@ -19920,10 +19920,10 @@
         <v>1.09964</v>
       </c>
       <c r="J406" t="n">
-        <v>-62.04630221125237</v>
+        <v>-62.35740000045787</v>
       </c>
       <c r="K406" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
@@ -19968,10 +19968,10 @@
         <v>1.09964</v>
       </c>
       <c r="J407" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K407" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
@@ -20016,10 +20016,10 @@
         <v>1.09964</v>
       </c>
       <c r="J408" t="n">
-        <v>-53.44582467682975</v>
+        <v>-53.71380000020383</v>
       </c>
       <c r="K408" t="n">
-        <v>-39.98500686291619</v>
+        <v>-39.98480431219993</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
@@ -20064,10 +20064,10 @@
         <v>1.09964</v>
       </c>
       <c r="J409" t="n">
-        <v>-43.61670749480785</v>
+        <v>-43.83540000008976</v>
       </c>
       <c r="K409" t="n">
-        <v>-40.29377139649973</v>
+        <v>-40.29356728168526</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
@@ -20112,10 +20112,10 @@
         <v>1.09964</v>
       </c>
       <c r="J410" t="n">
-        <v>-94.91241278800739</v>
+        <v>-95.38830000020542</v>
       </c>
       <c r="K410" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
@@ -20160,10 +20160,10 @@
         <v>1.09964</v>
       </c>
       <c r="J411" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K411" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -20208,10 +20208,10 @@
         <v>1.09964</v>
       </c>
       <c r="J412" t="n">
-        <v>-81.39737666308943</v>
+        <v>-81.80550000041254</v>
       </c>
       <c r="K412" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -20256,10 +20256,10 @@
         <v>1.09964</v>
       </c>
       <c r="J413" t="n">
-        <v>-76.48281807156286</v>
+        <v>-76.86629999983731</v>
       </c>
       <c r="K413" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -20304,10 +20304,10 @@
         <v>1.09964</v>
       </c>
       <c r="J414" t="n">
-        <v>-71.56825948106753</v>
+        <v>-71.92710000029848</v>
       </c>
       <c r="K414" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -20352,10 +20352,10 @@
         <v>1.09964</v>
       </c>
       <c r="J415" t="n">
-        <v>-66.9608608016986</v>
+        <v>-67.29659999994735</v>
       </c>
       <c r="K415" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -20400,10 +20400,10 @@
         <v>1.09964</v>
       </c>
       <c r="J416" t="n">
-        <v>-62.04630221125237</v>
+        <v>-62.35740000045787</v>
       </c>
       <c r="K416" t="n">
-        <v>-31.3395999715451</v>
+        <v>-31.3394412155783</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -20448,10 +20448,10 @@
         <v>1.09964</v>
       </c>
       <c r="J417" t="n">
-        <v>-57.74606344404106</v>
+        <v>-58.03560000033085</v>
       </c>
       <c r="K417" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -20496,10 +20496,10 @@
         <v>1.09964</v>
       </c>
       <c r="J418" t="n">
-        <v>-53.13866476462302</v>
+        <v>-53.40509999993037</v>
       </c>
       <c r="K418" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -20544,10 +20544,10 @@
         <v>1.09964</v>
       </c>
       <c r="J419" t="n">
-        <v>-48.53126608633441</v>
+        <v>-48.774600000665</v>
       </c>
       <c r="K419" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -20592,10 +20592,10 @@
         <v>1.09964</v>
       </c>
       <c r="J420" t="n">
-        <v>-43.92386740696548</v>
+        <v>-44.14410000031387</v>
       </c>
       <c r="K420" t="n">
-        <v>-31.64836450591844</v>
+        <v>-31.64820418585344</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -20640,10 +20640,10 @@
         <v>1.09964</v>
       </c>
       <c r="J421" t="n">
-        <v>-90.61217402079608</v>
+        <v>-91.06650000007839</v>
       </c>
       <c r="K421" t="n">
-        <v>73.02281175416444</v>
+        <v>73.02244184494133</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
@@ -20688,10 +20688,10 @@
         <v>1.09964</v>
       </c>
       <c r="J422" t="n">
-        <v>-86.31193525358476</v>
+        <v>-86.74469999995138</v>
       </c>
       <c r="K422" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
@@ -20736,10 +20736,10 @@
         <v>1.09964</v>
       </c>
       <c r="J423" t="n">
-        <v>-81.70453657529617</v>
+        <v>-82.114200000686</v>
       </c>
       <c r="K423" t="n">
-        <v>73.02281175416444</v>
+        <v>73.02244184494133</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
@@ -20784,10 +20784,10 @@
         <v>1.09964</v>
       </c>
       <c r="J424" t="n">
-        <v>-77.09713789592723</v>
+        <v>-77.48370000033488</v>
       </c>
       <c r="K424" t="n">
-        <v>73.02281175416444</v>
+        <v>73.02244184494133</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
@@ -20832,10 +20832,10 @@
         <v>1.09964</v>
       </c>
       <c r="J425" t="n">
-        <v>-72.18257930435156</v>
+        <v>-72.5444999997103</v>
       </c>
       <c r="K425" t="n">
-        <v>73.02281175416444</v>
+        <v>73.02244184494133</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -20880,10 +20880,10 @@
         <v>1.09964</v>
       </c>
       <c r="J426" t="n">
-        <v>-62.35346212341</v>
+        <v>-62.66610000068198</v>
       </c>
       <c r="K426" t="n">
-        <v>72.71404722058091</v>
+        <v>72.713678875456</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -20928,10 +20928,10 @@
         <v>1.09964</v>
       </c>
       <c r="J427" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K427" t="n">
-        <v>72.40528268620756</v>
+        <v>72.40491590518086</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -20976,10 +20976,10 @@
         <v>1.09964</v>
       </c>
       <c r="J428" t="n">
-        <v>-53.75298458898737</v>
+        <v>-54.02250000042794</v>
       </c>
       <c r="K428" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -21024,10 +21024,10 @@
         <v>1.09964</v>
       </c>
       <c r="J429" t="n">
-        <v>-49.14558590961844</v>
+        <v>-49.39200000007681</v>
       </c>
       <c r="K429" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -21072,10 +21072,10 @@
         <v>1.09964</v>
       </c>
       <c r="J430" t="n">
-        <v>-44.23102731912311</v>
+        <v>-44.45280000053798</v>
       </c>
       <c r="K430" t="n">
-        <v>73.33157628853778</v>
+        <v>73.33120481521647</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -21120,10 +21120,10 @@
         <v>1.09964</v>
       </c>
       <c r="J431" t="n">
-        <v>-81.70453657529617</v>
+        <v>-82.114200000686</v>
       </c>
       <c r="K431" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -21168,10 +21168,10 @@
         <v>1.09964</v>
       </c>
       <c r="J432" t="n">
-        <v>-77.09713789592723</v>
+        <v>-77.48370000033488</v>
       </c>
       <c r="K432" t="n">
-        <v>81.9769831688516</v>
+        <v>81.97656790078086</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -21216,10 +21216,10 @@
         <v>1.09964</v>
       </c>
       <c r="J433" t="n">
-        <v>-72.18257930435156</v>
+        <v>-72.5444999997103</v>
       </c>
       <c r="K433" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -21264,10 +21264,10 @@
         <v>1.09964</v>
       </c>
       <c r="J434" t="n">
-        <v>-62.96778194664491</v>
+        <v>-63.28350000004444</v>
       </c>
       <c r="K434" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
@@ -21312,10 +21312,10 @@
         <v>1.09964</v>
       </c>
       <c r="J435" t="n">
-        <v>-53.13866476462302</v>
+        <v>-53.40509999993037</v>
       </c>
       <c r="K435" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
@@ -21360,10 +21360,10 @@
         <v>1.09964</v>
       </c>
       <c r="J436" t="n">
-        <v>-49.45274582177607</v>
+        <v>-49.70070000030093</v>
       </c>
       <c r="K436" t="n">
-        <v>81.05068957678886</v>
+        <v>81.05027900101268</v>
       </c>
       <c r="L436" t="inlineStr">
         <is>
@@ -21408,10 +21408,10 @@
         <v>1.09964</v>
       </c>
       <c r="J437" t="n">
-        <v>-44.23102731912311</v>
+        <v>-44.45280000053798</v>
       </c>
       <c r="K437" t="n">
-        <v>81.66821864553553</v>
+        <v>81.66780494156295</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
@@ -21456,10 +21456,10 @@
         <v>1</v>
       </c>
       <c r="J438" t="n">
-        <v>-42.38806784715946</v>
+        <v>-42.60060000018038</v>
       </c>
       <c r="K438" t="n">
-        <v>-105.7518521134088</v>
+        <v>-105.751316409777</v>
       </c>
       <c r="L438" t="inlineStr">
         <is>
@@ -21504,10 +21504,10 @@
         <v>1</v>
       </c>
       <c r="J439" t="n">
-        <v>-103.2057304102233</v>
+        <v>-103.723200000186</v>
       </c>
       <c r="K439" t="n">
-        <v>-94.63632898259218</v>
+        <v>-94.63584958649538</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -21552,10 +21552,10 @@
         <v>1</v>
       </c>
       <c r="J440" t="n">
-        <v>-68.49666036150461</v>
+        <v>-68.84010000008084</v>
       </c>
       <c r="K440" t="n">
-        <v>-94.32756444821884</v>
+        <v>-94.32708661622024</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
@@ -21600,10 +21600,10 @@
         <v>1</v>
       </c>
       <c r="J441" t="n">
-        <v>-43.30954758260111</v>
+        <v>-43.5266999998163</v>
       </c>
       <c r="K441" t="n">
-        <v>-97.41520976825809</v>
+        <v>-97.41471629527754</v>
       </c>
       <c r="L441" t="inlineStr">
         <is>
@@ -21648,10 +21648,10 @@
         <v>1</v>
       </c>
       <c r="J442" t="n">
-        <v>-54.98162423663576</v>
+        <v>-55.25730000033732</v>
       </c>
       <c r="K442" t="n">
-        <v>-83.21204130634497</v>
+        <v>-83.2116197818814</v>
       </c>
       <c r="L442" t="inlineStr">
         <is>
@@ -21696,10 +21696,10 @@
         <v>1</v>
       </c>
       <c r="J443" t="n">
-        <v>-68.49666036150461</v>
+        <v>-68.84010000008084</v>
       </c>
       <c r="K443" t="n">
-        <v>-72.71404722137071</v>
+        <v>-72.71367887624579</v>
       </c>
       <c r="L443" t="inlineStr">
         <is>
@@ -21744,10 +21744,10 @@
         <v>1</v>
       </c>
       <c r="J444" t="n">
-        <v>-68.49666036150461</v>
+        <v>-68.84010000008084</v>
       </c>
       <c r="K444" t="n">
-        <v>-64.6861693987463</v>
+        <v>-64.68584172017445</v>
       </c>
       <c r="L444" t="inlineStr">
         <is>
@@ -21792,10 +21792,10 @@
         <v>1</v>
       </c>
       <c r="J445" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K445" t="n">
-        <v>-62.52481768103726</v>
+        <v>-62.52450095115275</v>
       </c>
       <c r="L445" t="inlineStr">
         <is>
@@ -21840,10 +21840,10 @@
         <v>1</v>
       </c>
       <c r="J446" t="n">
-        <v>-55.28878414879339</v>
+        <v>-55.56600000056143</v>
       </c>
       <c r="K446" t="n">
-        <v>-62.21605314745372</v>
+        <v>-62.21573798166742</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -21888,10 +21888,10 @@
         <v>1</v>
       </c>
       <c r="J447" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K447" t="n">
-        <v>-58.81964329304112</v>
+        <v>-58.81934533233499</v>
       </c>
       <c r="L447" t="inlineStr">
         <is>
@@ -21936,10 +21936,10 @@
         <v>1</v>
       </c>
       <c r="J448" t="n">
-        <v>-83.54749604617948</v>
+        <v>-83.96639999995784</v>
       </c>
       <c r="K448" t="n">
-        <v>-37.82365513414988</v>
+        <v>-37.82346353212101</v>
       </c>
       <c r="L448" t="inlineStr">
         <is>
@@ -21984,10 +21984,10 @@
         <v>1</v>
       </c>
       <c r="J449" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K449" t="n">
-        <v>-37.82365513414988</v>
+        <v>-37.82346353212101</v>
       </c>
       <c r="L449" t="inlineStr">
         <is>
@@ -22032,10 +22032,10 @@
         <v>1</v>
       </c>
       <c r="J450" t="n">
-        <v>-68.80382027366224</v>
+        <v>-69.14880000030495</v>
       </c>
       <c r="K450" t="n">
-        <v>-23.9292512066101</v>
+        <v>-23.929129989</v>
       </c>
       <c r="L450" t="inlineStr">
         <is>
@@ -22080,10 +22080,10 @@
         <v>1</v>
       </c>
       <c r="J451" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K451" t="n">
-        <v>-14.6663152583394</v>
+        <v>-14.66624096367513</v>
       </c>
       <c r="L451" t="inlineStr">
         <is>
@@ -22128,10 +22128,10 @@
         <v>1</v>
       </c>
       <c r="J452" t="n">
-        <v>-55.28878414879339</v>
+        <v>-55.56600000056143</v>
       </c>
       <c r="K452" t="n">
-        <v>-14.6663152583394</v>
+        <v>-14.66624096367513</v>
       </c>
       <c r="L452" t="inlineStr">
         <is>
@@ -22176,10 +22176,10 @@
         <v>1</v>
       </c>
       <c r="J453" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K453" t="n">
-        <v>-10.96114088140054</v>
+        <v>-10.96108535591459</v>
       </c>
       <c r="L453" t="inlineStr">
         <is>
@@ -22224,10 +22224,10 @@
         <v>1</v>
       </c>
       <c r="J454" t="n">
-        <v>-68.80382027366224</v>
+        <v>-69.14880000030495</v>
       </c>
       <c r="K454" t="n">
-        <v>-11.57866993830014</v>
+        <v>-11.57861128461784</v>
       </c>
       <c r="L454" t="inlineStr">
         <is>
@@ -22272,10 +22272,10 @@
         <v>1</v>
       </c>
       <c r="J455" t="n">
-        <v>-55.28878414879339</v>
+        <v>-55.56600000056143</v>
       </c>
       <c r="K455" t="n">
-        <v>-10.6523763470272</v>
+        <v>-10.65232238563946</v>
       </c>
       <c r="L455" t="inlineStr">
         <is>
@@ -22320,10 +22320,10 @@
         <v>1</v>
       </c>
       <c r="J456" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K456" t="n">
-        <v>7.255966491824789</v>
+        <v>7.255929735517227</v>
       </c>
       <c r="L456" t="inlineStr">
         <is>
@@ -22368,10 +22368,10 @@
         <v>1</v>
       </c>
       <c r="J457" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K457" t="n">
-        <v>7.564731026198131</v>
+        <v>7.564692705792361</v>
       </c>
       <c r="L457" t="inlineStr">
         <is>
@@ -22416,10 +22416,10 @@
         <v>1</v>
       </c>
       <c r="J458" t="n">
-        <v>-68.80382027366224</v>
+        <v>-69.14880000030495</v>
       </c>
       <c r="K458" t="n">
-        <v>10.03484727749071</v>
+        <v>10.03479644429939</v>
       </c>
       <c r="L458" t="inlineStr">
         <is>
@@ -22464,10 +22464,10 @@
         <v>1</v>
       </c>
       <c r="J459" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K459" t="n">
-        <v>20.53284135140769</v>
+        <v>20.53273733887777</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -22512,10 +22512,10 @@
         <v>1</v>
       </c>
       <c r="J460" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K460" t="n">
-        <v>20.84160588578103</v>
+        <v>20.8415003091529</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -22560,10 +22560,10 @@
         <v>1</v>
       </c>
       <c r="J461" t="n">
-        <v>-83.24033613510218</v>
+        <v>-83.6577000008195</v>
       </c>
       <c r="K461" t="n">
-        <v>24.23801574019364</v>
+        <v>24.23789295848533</v>
       </c>
       <c r="L461" t="inlineStr">
         <is>
@@ -22608,10 +22608,10 @@
         <v>1</v>
       </c>
       <c r="J462" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K462" t="n">
-        <v>24.23801574019364</v>
+        <v>24.23789295848533</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -22656,10 +22656,10 @@
         <v>1</v>
       </c>
       <c r="J463" t="n">
-        <v>-91.53365375623773</v>
+        <v>-91.99259999971432</v>
       </c>
       <c r="K463" t="n">
-        <v>37.2061260654032</v>
+        <v>37.20593759157074</v>
       </c>
       <c r="L463" t="inlineStr">
         <is>
@@ -22704,10 +22704,10 @@
         <v>1</v>
       </c>
       <c r="J464" t="n">
-        <v>-84.16181587054383</v>
+        <v>-84.58380000045543</v>
       </c>
       <c r="K464" t="n">
-        <v>37.2061260654032</v>
+        <v>37.20593759157074</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -22752,10 +22752,10 @@
         <v>1</v>
       </c>
       <c r="J465" t="n">
-        <v>-82.93317622289545</v>
+        <v>-83.34900000054604</v>
       </c>
       <c r="K465" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -22800,10 +22800,10 @@
         <v>1</v>
       </c>
       <c r="J466" t="n">
-        <v>-76.48281807156286</v>
+        <v>-76.86629999983731</v>
       </c>
       <c r="K466" t="n">
-        <v>37.2061260654032</v>
+        <v>37.20593759157074</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>
@@ -22848,10 +22848,10 @@
         <v>1</v>
       </c>
       <c r="J467" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K467" t="n">
-        <v>43.38141670469191</v>
+        <v>43.38119694889553</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -22896,10 +22896,10 @@
         <v>1</v>
       </c>
       <c r="J468" t="n">
-        <v>-77.09713789592723</v>
+        <v>-77.48370000033488</v>
       </c>
       <c r="K468" t="n">
-        <v>48.01288468396099</v>
+        <v>48.01264146669168</v>
       </c>
       <c r="L468" t="inlineStr">
         <is>
@@ -22944,10 +22944,10 @@
         <v>1</v>
       </c>
       <c r="J469" t="n">
-        <v>-69.11098018586897</v>
+        <v>-69.45750000057841</v>
       </c>
       <c r="K469" t="n">
-        <v>50.17423640167003</v>
+        <v>50.17398223571337</v>
       </c>
       <c r="L469" t="inlineStr">
         <is>
@@ -22992,10 +22992,10 @@
         <v>1</v>
       </c>
       <c r="J470" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K470" t="n">
-        <v>46.7778265583147</v>
+        <v>46.77758959743816</v>
       </c>
       <c r="L470" t="inlineStr">
         <is>
@@ -23040,10 +23040,10 @@
         <v>1</v>
       </c>
       <c r="J471" t="n">
-        <v>-93.37661322820138</v>
+        <v>-93.84480000007191</v>
       </c>
       <c r="K471" t="n">
-        <v>64.99493392048275</v>
+        <v>64.99460467781276</v>
       </c>
       <c r="L471" t="inlineStr">
         <is>
@@ -23088,10 +23088,10 @@
         <v>1</v>
       </c>
       <c r="J472" t="n">
-        <v>-56.21026388423504</v>
+        <v>-56.49210000019735</v>
       </c>
       <c r="K472" t="n">
-        <v>71.47898909493462</v>
+        <v>71.47862700620249</v>
       </c>
       <c r="L472" t="inlineStr">
         <is>
@@ -23136,10 +23136,10 @@
         <v>1</v>
       </c>
       <c r="J473" t="n">
-        <v>-84.16181587054383</v>
+        <v>-84.58380000045543</v>
       </c>
       <c r="K473" t="n">
-        <v>73.64034081185385</v>
+        <v>73.63996777443438</v>
       </c>
       <c r="L473" t="inlineStr">
         <is>
@@ -23184,10 +23184,10 @@
         <v>1</v>
       </c>
       <c r="J474" t="n">
-        <v>-83.54749604617948</v>
+        <v>-83.96639999995784</v>
       </c>
       <c r="K474" t="n">
-        <v>72.40528268620756</v>
+        <v>72.40491590518086</v>
       </c>
       <c r="L474" t="inlineStr">
         <is>
@@ -23232,10 +23232,10 @@
         <v>1</v>
       </c>
       <c r="J475" t="n">
-        <v>-69.11098018586897</v>
+        <v>-69.45750000057841</v>
       </c>
       <c r="K475" t="n">
-        <v>75.18416347187348</v>
+        <v>75.18378261396302</v>
       </c>
       <c r="L475" t="inlineStr">
         <is>
@@ -23280,10 +23280,10 @@
         <v>1</v>
       </c>
       <c r="J476" t="n">
-        <v>-100.1341312906112</v>
+        <v>-100.636199999919</v>
       </c>
       <c r="K476" t="n">
-        <v>89.07856739941326</v>
+        <v>89.07811615708404</v>
       </c>
       <c r="L476" t="inlineStr">
         <is>
@@ -23328,10 +23328,10 @@
         <v>1</v>
       </c>
       <c r="J477" t="n">
-        <v>-76.17565816048558</v>
+        <v>-76.55760000069895</v>
       </c>
       <c r="K477" t="n">
-        <v>89.07856739941326</v>
+        <v>89.07811615708404</v>
       </c>
       <c r="L477" t="inlineStr">
         <is>
@@ -23376,10 +23376,10 @@
         <v>1</v>
       </c>
       <c r="J478" t="n">
-        <v>-83.54749604617948</v>
+        <v>-83.96639999995784</v>
       </c>
       <c r="K478" t="n">
-        <v>92.78374177635212</v>
+        <v>92.78327176484457</v>
       </c>
       <c r="L478" t="inlineStr">
         <is>
@@ -23424,10 +23424,10 @@
         <v>1</v>
       </c>
       <c r="J479" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K479" t="n">
-        <v>91.85744818507918</v>
+        <v>91.8569828658662</v>
       </c>
       <c r="L479" t="inlineStr">
         <is>
@@ -23472,10 +23472,10 @@
         <v>1</v>
       </c>
       <c r="J480" t="n">
-        <v>-83.54749604617948</v>
+        <v>-83.96639999995784</v>
       </c>
       <c r="K480" t="n">
-        <v>94.32756443637174</v>
+        <v>94.32708660437322</v>
       </c>
       <c r="L480" t="inlineStr">
         <is>
@@ -23520,10 +23520,10 @@
         <v>1</v>
       </c>
       <c r="J481" t="n">
-        <v>-55.90310397202831</v>
+        <v>-56.18339999992389</v>
       </c>
       <c r="K481" t="n">
-        <v>95.56262257307532</v>
+        <v>95.56213848468396</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -23568,10 +23568,10 @@
         <v>1</v>
       </c>
       <c r="J482" t="n">
-        <v>-69.4181400980266</v>
+        <v>-69.76620000080251</v>
       </c>
       <c r="K482" t="n">
-        <v>105.4430875900927</v>
+        <v>105.4425534505591</v>
       </c>
       <c r="L482" t="inlineStr">
         <is>
@@ -23616,10 +23616,10 @@
         <v>1</v>
       </c>
       <c r="J483" t="n">
-        <v>-49.14558590961844</v>
+        <v>-49.39200000007681</v>
       </c>
       <c r="K483" t="n">
-        <v>104.2080294533891</v>
+        <v>104.2075015702484</v>
       </c>
       <c r="L483" t="inlineStr">
         <is>
@@ -23664,10 +23664,10 @@
         <v>1</v>
       </c>
       <c r="J484" t="n">
-        <v>-44.23102731912311</v>
+        <v>-44.45280000053798</v>
       </c>
       <c r="K484" t="n">
-        <v>100.8116196100338</v>
+        <v>100.8111089319732</v>
       </c>
       <c r="L484" t="inlineStr">
         <is>
@@ -23712,10 +23712,10 @@
         <v>1</v>
       </c>
       <c r="J485" t="n">
-        <v>-42.38806784715946</v>
+        <v>-42.60060000018038</v>
       </c>
       <c r="K485" t="n">
-        <v>100.8116196100338</v>
+        <v>100.8111089319732</v>
       </c>
       <c r="L485" t="inlineStr">
         <is>
@@ -23760,10 +23760,10 @@
         <v>1</v>
       </c>
       <c r="J486" t="n">
-        <v>-34.70907004930794</v>
+        <v>-34.88310000069738</v>
       </c>
       <c r="K486" t="n">
-        <v>104.5167939869727</v>
+        <v>104.5162645397337</v>
       </c>
       <c r="L486" t="inlineStr">
         <is>
@@ -23808,10 +23808,10 @@
         <v>1</v>
       </c>
       <c r="J487" t="n">
-        <v>-55.90310397202831</v>
+        <v>-56.18339999992389</v>
       </c>
       <c r="K487" t="n">
-        <v>116.2498461975932</v>
+        <v>116.2492573146228</v>
       </c>
       <c r="L487" t="inlineStr">
         <is>
@@ -23856,10 +23856,10 @@
         <v>1</v>
       </c>
       <c r="J488" t="n">
-        <v>-69.4181400980266</v>
+        <v>-69.76620000080251</v>
       </c>
       <c r="K488" t="n">
-        <v>128.9091920002765</v>
+        <v>128.9085389892801</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -23904,10 +23904,10 @@
         <v>1</v>
       </c>
       <c r="J489" t="n">
-        <v>-74.0255387763152</v>
+        <v>-74.3967000000679</v>
       </c>
       <c r="K489" t="n">
-        <v>143.729889519879</v>
+        <v>143.7291614321693</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -23952,10 +23952,10 @@
         <v>1</v>
       </c>
       <c r="J490" t="n">
-        <v>-74.0255387763152</v>
+        <v>-74.3967000000679</v>
       </c>
       <c r="K490" t="n">
-        <v>151.140238284814</v>
+        <v>151.1394726587476</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
@@ -24000,10 +24000,10 @@
         <v>1</v>
       </c>
       <c r="J491" t="n">
-        <v>-69.4181400980266</v>
+        <v>-69.76620000080251</v>
       </c>
       <c r="K491" t="n">
-        <v>152.6840609448337</v>
+        <v>152.6832874982762</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
@@ -24048,10 +24048,10 @@
         <v>1</v>
       </c>
       <c r="J492" t="n">
-        <v>-61.12482247581072</v>
+        <v>-61.43130000082195</v>
       </c>
       <c r="K492" t="n">
-        <v>168.1222875213358</v>
+        <v>168.1214358698687</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -24096,10 +24096,10 @@
         <v>1</v>
       </c>
       <c r="J493" t="n">
-        <v>-69.4181400980266</v>
+        <v>-69.76620000080251</v>
       </c>
       <c r="K493" t="n">
-        <v>177.3852234806638</v>
+        <v>177.3843249062508</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -24144,10 +24144,10 @@
         <v>1</v>
       </c>
       <c r="J494" t="n">
-        <v>-35.63054978474959</v>
+        <v>-35.8092000003333</v>
       </c>
       <c r="K494" t="n">
-        <v>-124.2777240210074</v>
+        <v>-124.277094471484</v>
       </c>
       <c r="L494" t="inlineStr">
         <is>
@@ -24192,10 +24192,10 @@
         <v>1</v>
       </c>
       <c r="J495" t="n">
-        <v>-31.33031101753828</v>
+        <v>-31.48740000020628</v>
       </c>
       <c r="K495" t="n">
-        <v>-125.2040176241275</v>
+        <v>-125.2033833823094</v>
       </c>
       <c r="L495" t="inlineStr">
         <is>
@@ -24240,10 +24240,10 @@
         <v>1</v>
       </c>
       <c r="J496" t="n">
-        <v>-35.63054978474959</v>
+        <v>-35.8092000003333</v>
       </c>
       <c r="K496" t="n">
-        <v>-112.2359072878606</v>
+        <v>-112.2353387381667</v>
       </c>
       <c r="L496" t="inlineStr">
         <is>
@@ -24288,10 +24288,10 @@
         <v>1</v>
       </c>
       <c r="J497" t="n">
-        <v>-31.02315110533155</v>
+        <v>-31.17869999993282</v>
       </c>
       <c r="K497" t="n">
-        <v>-97.72397429157415</v>
+        <v>-97.72347925449546</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -24336,10 +24336,10 @@
         <v>1</v>
       </c>
       <c r="J498" t="n">
-        <v>-30.71599119317392</v>
+        <v>-30.86999999970871</v>
       </c>
       <c r="K498" t="n">
-        <v>-94.63632898259218</v>
+        <v>-94.63584958649538</v>
       </c>
       <c r="L498" t="inlineStr">
         <is>
@@ -24384,10 +24384,10 @@
         <v>1</v>
       </c>
       <c r="J499" t="n">
-        <v>-35.93770969690722</v>
+        <v>-36.11790000055741</v>
       </c>
       <c r="K499" t="n">
-        <v>-88.15227380893012</v>
+        <v>-88.15182725889545</v>
       </c>
       <c r="L499" t="inlineStr">
         <is>
@@ -24432,10 +24432,10 @@
         <v>1</v>
       </c>
       <c r="J500" t="n">
-        <v>-32.55895066513756</v>
+        <v>-32.72220000006631</v>
       </c>
       <c r="K500" t="n">
-        <v>-79.81563145193236</v>
+        <v>-79.81522713254897</v>
       </c>
       <c r="L500" t="inlineStr">
         <is>
@@ -24480,10 +24480,10 @@
         <v>1</v>
       </c>
       <c r="J501" t="n">
-        <v>-35.63054978474959</v>
+        <v>-35.8092000003333</v>
       </c>
       <c r="K501" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L501" t="inlineStr">
         <is>
@@ -24528,10 +24528,10 @@
         <v>1</v>
       </c>
       <c r="J502" t="n">
-        <v>-35.93770969690722</v>
+        <v>-36.11790000055741</v>
       </c>
       <c r="K502" t="n">
-        <v>-31.03083543717176</v>
+        <v>-31.03067824530317</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -24576,10 +24576,10 @@
         <v>1</v>
       </c>
       <c r="J503" t="n">
-        <v>-41.46658811171781</v>
+        <v>-41.67450000054446</v>
       </c>
       <c r="K503" t="n">
-        <v>-9.417318221380908</v>
+        <v>-9.417270516385944</v>
       </c>
       <c r="L503" t="inlineStr">
         <is>
@@ -24624,10 +24624,10 @@
         <v>1</v>
       </c>
       <c r="J504" t="n">
-        <v>-35.93770969690722</v>
+        <v>-36.11790000055741</v>
       </c>
       <c r="K504" t="n">
-        <v>-0.7719113300098148</v>
+        <v>-0.771907419764324</v>
       </c>
       <c r="L504" t="inlineStr">
         <is>
@@ -24672,10 +24672,10 @@
         <v>1</v>
       </c>
       <c r="J505" t="n">
-        <v>-41.15942819956018</v>
+        <v>-41.36580000032035</v>
       </c>
       <c r="K505" t="n">
-        <v>12.19619899519974</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L505" t="inlineStr">
         <is>
@@ -24720,10 +24720,10 @@
         <v>1</v>
       </c>
       <c r="J506" t="n">
-        <v>-36.24486960911396</v>
+        <v>-36.42660000083087</v>
       </c>
       <c r="K506" t="n">
-        <v>29.17824824277879</v>
+        <v>29.17810043549939</v>
       </c>
       <c r="L506" t="inlineStr">
         <is>
@@ -24768,10 +24768,10 @@
         <v>1</v>
       </c>
       <c r="J507" t="n">
-        <v>-42.08090793500183</v>
+        <v>-42.29189999995627</v>
       </c>
       <c r="K507" t="n">
-        <v>39.3674777933797</v>
+        <v>39.36727837085986</v>
       </c>
       <c r="L507" t="inlineStr">
         <is>
@@ -24816,10 +24816,10 @@
         <v>1</v>
       </c>
       <c r="J508" t="n">
-        <v>-36.24486960911396</v>
+        <v>-36.42660000083087</v>
       </c>
       <c r="K508" t="n">
-        <v>59.12840782662466</v>
+        <v>59.12810830182032</v>
       </c>
       <c r="L508" t="inlineStr">
         <is>
@@ -24864,10 +24864,10 @@
         <v>1</v>
       </c>
       <c r="J509" t="n">
-        <v>-41.77374802392454</v>
+        <v>-41.98320000081792</v>
       </c>
       <c r="K509" t="n">
-        <v>70.24393096849852</v>
+        <v>70.24357513615917</v>
       </c>
       <c r="L509" t="inlineStr">
         <is>
@@ -24912,10 +24912,10 @@
         <v>1</v>
       </c>
       <c r="J510" t="n">
-        <v>-36.55202952014213</v>
+        <v>-36.73529999991987</v>
       </c>
       <c r="K510" t="n">
-        <v>89.07856739941326</v>
+        <v>89.07811615708404</v>
       </c>
       <c r="L510" t="inlineStr">
         <is>
@@ -24960,10 +24960,10 @@
         <v>6.8</v>
       </c>
       <c r="J511" t="n">
-        <v>-99.51981146737633</v>
+        <v>-100.0188000005565</v>
       </c>
       <c r="K511" t="n">
-        <v>-84.44709943199126</v>
+        <v>-84.44667165113491</v>
       </c>
       <c r="L511" t="inlineStr">
         <is>
@@ -25008,10 +25008,10 @@
         <v>6.8</v>
       </c>
       <c r="J512" t="n">
-        <v>-43.61670749480785</v>
+        <v>-43.83540000008976</v>
       </c>
       <c r="K512" t="n">
-        <v>-84.75586396557479</v>
+        <v>-84.75543462062025</v>
       </c>
       <c r="L512" t="inlineStr">
         <is>
@@ -25056,10 +25056,10 @@
         <v>6.8</v>
       </c>
       <c r="J513" t="n">
-        <v>-40.23794846411853</v>
+        <v>-40.43970000068443</v>
       </c>
       <c r="K513" t="n">
-        <v>117.7936688576128</v>
+        <v>117.7930721541514</v>
       </c>
       <c r="L513" t="inlineStr">
         <is>
@@ -25104,10 +25104,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J514" t="n">
-        <v>-93.06945331712409</v>
+        <v>-93.53610000093357</v>
       </c>
       <c r="K514" t="n">
-        <v>-21.76789948890106</v>
+        <v>-21.7677892199783</v>
       </c>
       <c r="L514" t="inlineStr">
         <is>
@@ -25152,10 +25152,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J515" t="n">
-        <v>-86.00477534250747</v>
+        <v>-86.43600000081302</v>
       </c>
       <c r="K515" t="n">
-        <v>-21.76789948890106</v>
+        <v>-21.7677892199783</v>
       </c>
       <c r="L515" t="inlineStr">
         <is>
@@ -25200,10 +25200,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J516" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K516" t="n">
-        <v>-21.76789948890106</v>
+        <v>-21.7677892199783</v>
       </c>
       <c r="L516" t="inlineStr">
         <is>
@@ -25248,10 +25248,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J517" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K517" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L517" t="inlineStr">
         <is>
@@ -25296,10 +25296,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J518" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K518" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L518" t="inlineStr">
         <is>
@@ -25344,10 +25344,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J519" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K519" t="n">
-        <v>-21.45913495531752</v>
+        <v>-21.45902625049297</v>
       </c>
       <c r="L519" t="inlineStr">
         <is>
@@ -25392,10 +25392,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J520" t="n">
-        <v>-94.29809296364303</v>
+        <v>-94.77089999970784</v>
       </c>
       <c r="K520" t="n">
-        <v>11.88743447188368</v>
+        <v>11.88737425410317</v>
       </c>
       <c r="L520" t="inlineStr">
         <is>
@@ -25440,10 +25440,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J521" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K521" t="n">
-        <v>11.88743447188368</v>
+        <v>11.88737425410317</v>
       </c>
       <c r="L521" t="inlineStr">
         <is>
@@ -25488,10 +25488,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J522" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K522" t="n">
-        <v>12.50496352878328</v>
+        <v>12.50490018280642</v>
       </c>
       <c r="L522" t="inlineStr">
         <is>
@@ -25536,10 +25536,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J523" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K523" t="n">
-        <v>12.81372806315662</v>
+        <v>12.81366315308155</v>
       </c>
       <c r="L523" t="inlineStr">
         <is>
@@ -25584,10 +25584,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J524" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K524" t="n">
-        <v>12.19619899519974</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L524" t="inlineStr">
         <is>
@@ -25632,10 +25632,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J525" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K525" t="n">
-        <v>12.81372806315662</v>
+        <v>12.81366315308155</v>
       </c>
       <c r="L525" t="inlineStr">
         <is>
@@ -25680,10 +25680,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J526" t="n">
-        <v>-65.73222115409932</v>
+        <v>-66.06180000008732</v>
       </c>
       <c r="K526" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L526" t="inlineStr">
         <is>
@@ -25728,10 +25728,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J527" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K527" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L527" t="inlineStr">
         <is>
@@ -25776,10 +25776,10 @@
         <v>1.4765778</v>
       </c>
       <c r="J528" t="n">
-        <v>-50.68138546942446</v>
+        <v>-50.93550000021031</v>
       </c>
       <c r="K528" t="n">
-        <v>54.80570438093911</v>
+        <v>54.80542675350951</v>
       </c>
       <c r="L528" t="inlineStr">
         <is>
@@ -25824,10 +25824,10 @@
         <v>2.6</v>
       </c>
       <c r="J529" t="n">
-        <v>-72.48973921650918</v>
+        <v>-72.8531999999344</v>
       </c>
       <c r="K529" t="n">
-        <v>160.4031742330847</v>
+        <v>160.4023616840724</v>
       </c>
       <c r="L529" t="inlineStr">
         <is>
@@ -25872,10 +25872,10 @@
         <v>2.6</v>
       </c>
       <c r="J530" t="n">
-        <v>-44.53818723132984</v>
+        <v>-44.76150000081144</v>
       </c>
       <c r="K530" t="n">
-        <v>160.4031742330847</v>
+        <v>160.4023616840724</v>
       </c>
       <c r="L530" t="inlineStr">
         <is>
@@ -25920,10 +25920,10 @@
         <v>2.6</v>
       </c>
       <c r="J531" t="n">
-        <v>-99.51981146737633</v>
+        <v>-100.0188000005565</v>
       </c>
       <c r="K531" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L531" t="inlineStr">
         <is>
@@ -25968,10 +25968,10 @@
         <v>2.6</v>
       </c>
       <c r="J532" t="n">
-        <v>-71.56825948106753</v>
+        <v>-71.92710000029848</v>
       </c>
       <c r="K532" t="n">
-        <v>-60.67223048743409</v>
+        <v>-60.67192314213877</v>
       </c>
       <c r="L532" t="inlineStr">
         <is>
@@ -26016,10 +26016,10 @@
         <v>2.6</v>
       </c>
       <c r="J533" t="n">
-        <v>-43.61670749480785</v>
+        <v>-43.83540000008976</v>
       </c>
       <c r="K533" t="n">
-        <v>-60.36346595306075</v>
+        <v>-60.36316017186363</v>
       </c>
       <c r="L533" t="inlineStr">
         <is>
@@ -26064,10 +26064,10 @@
         <v>2.6</v>
       </c>
       <c r="J534" t="n">
-        <v>-99.82697137958306</v>
+        <v>-100.32750000083</v>
       </c>
       <c r="K534" t="n">
-        <v>4.785850240532214</v>
+        <v>4.785825997010199</v>
       </c>
       <c r="L534" t="inlineStr">
         <is>
@@ -26112,10 +26112,10 @@
         <v>2.6</v>
       </c>
       <c r="J535" t="n">
-        <v>-72.18257930435156</v>
+        <v>-72.5444999997103</v>
       </c>
       <c r="K535" t="n">
-        <v>5.403379298221623</v>
+        <v>5.403351926503246</v>
       </c>
       <c r="L535" t="inlineStr">
         <is>
@@ -26160,10 +26160,10 @@
         <v>2.6</v>
       </c>
       <c r="J536" t="n">
-        <v>-43.92386740696548</v>
+        <v>-44.14410000031387</v>
       </c>
       <c r="K536" t="n">
-        <v>5.403379298221623</v>
+        <v>5.403351926503246</v>
       </c>
       <c r="L536" t="inlineStr">
         <is>
@@ -26208,10 +26208,10 @@
         <v>2.6</v>
       </c>
       <c r="J537" t="n">
-        <v>-100.1341312906112</v>
+        <v>-100.636199999919</v>
       </c>
       <c r="K537" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L537" t="inlineStr">
         <is>
@@ -26256,10 +26256,10 @@
         <v>2.6</v>
       </c>
       <c r="J538" t="n">
-        <v>-72.18257930435156</v>
+        <v>-72.5444999997103</v>
       </c>
       <c r="K538" t="n">
-        <v>93.71003537947215</v>
+        <v>93.70956067566998</v>
       </c>
       <c r="L538" t="inlineStr">
         <is>
@@ -26304,10 +26304,10 @@
         <v>2.6</v>
       </c>
       <c r="J539" t="n">
-        <v>-44.53818723132984</v>
+        <v>-44.76150000081144</v>
       </c>
       <c r="K539" t="n">
-        <v>94.01879991305569</v>
+        <v>94.01832364515531</v>
       </c>
       <c r="L539" t="inlineStr">
         <is>
@@ -26352,10 +26352,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J540" t="n">
-        <v>-93.06945331712409</v>
+        <v>-93.53610000093357</v>
       </c>
       <c r="K540" t="n">
-        <v>-85.68215755763754</v>
+        <v>-85.68172352038843</v>
       </c>
       <c r="L540" t="inlineStr">
         <is>
@@ -26400,10 +26400,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J541" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K541" t="n">
-        <v>-85.68215755763754</v>
+        <v>-85.68172352038843</v>
       </c>
       <c r="L541" t="inlineStr">
         <is>
@@ -26448,10 +26448,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J542" t="n">
-        <v>-78.01861763131977</v>
+        <v>-78.40979999992145</v>
       </c>
       <c r="K542" t="n">
-        <v>-85.68215755763754</v>
+        <v>-85.68172352038843</v>
       </c>
       <c r="L542" t="inlineStr">
         <is>
@@ -26496,10 +26496,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J543" t="n">
-        <v>-65.11790133081529</v>
+        <v>-65.4444000006755</v>
       </c>
       <c r="K543" t="n">
-        <v>-85.68215755763754</v>
+        <v>-85.68172352038843</v>
       </c>
       <c r="L543" t="inlineStr">
         <is>
@@ -26544,10 +26544,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J544" t="n">
-        <v>-57.43890353183432</v>
+        <v>-57.72690000005739</v>
       </c>
       <c r="K544" t="n">
-        <v>-85.68215755763754</v>
+        <v>-85.68172352038843</v>
       </c>
       <c r="L544" t="inlineStr">
         <is>
@@ -26592,10 +26592,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J545" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K545" t="n">
-        <v>-85.3733930232642</v>
+        <v>-85.37296055011329</v>
       </c>
       <c r="L545" t="inlineStr">
         <is>
@@ -26640,10 +26640,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J546" t="n">
-        <v>-93.99093305256574</v>
+        <v>-94.46220000056948</v>
       </c>
       <c r="K546" t="n">
-        <v>-66.53875659234947</v>
+        <v>-66.53841952918843</v>
       </c>
       <c r="L546" t="inlineStr">
         <is>
@@ -26688,10 +26688,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J547" t="n">
-        <v>-85.08329560598548</v>
+        <v>-85.50990000009135</v>
       </c>
       <c r="K547" t="n">
-        <v>-66.84752112672281</v>
+        <v>-66.84718249946356</v>
       </c>
       <c r="L547" t="inlineStr">
         <is>
@@ -26736,10 +26736,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J548" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K548" t="n">
-        <v>-66.53875659234947</v>
+        <v>-66.53841952918843</v>
       </c>
       <c r="L548" t="inlineStr">
         <is>
@@ -26784,10 +26784,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J549" t="n">
-        <v>-65.11790133081529</v>
+        <v>-65.4444000006755</v>
       </c>
       <c r="K549" t="n">
-        <v>-66.53875659234947</v>
+        <v>-66.53841952918843</v>
       </c>
       <c r="L549" t="inlineStr">
         <is>
@@ -26832,10 +26832,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J550" t="n">
-        <v>-57.74606344404106</v>
+        <v>-58.03560000033085</v>
       </c>
       <c r="K550" t="n">
-        <v>-66.53875659234947</v>
+        <v>-66.53841952918843</v>
       </c>
       <c r="L550" t="inlineStr">
         <is>
@@ -26880,10 +26880,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J551" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K551" t="n">
-        <v>-66.53875659234947</v>
+        <v>-66.53841952918843</v>
       </c>
       <c r="L551" t="inlineStr">
         <is>
@@ -26928,10 +26928,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J552" t="n">
-        <v>-65.73222115409932</v>
+        <v>-66.06180000008732</v>
       </c>
       <c r="K552" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L552" t="inlineStr">
         <is>
@@ -26976,10 +26976,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J553" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K553" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L553" t="inlineStr">
         <is>
@@ -27024,10 +27024,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J554" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K554" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L554" t="inlineStr">
         <is>
@@ -27072,10 +27072,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J555" t="n">
-        <v>-66.03938106625694</v>
+        <v>-66.37050000031142</v>
       </c>
       <c r="K555" t="n">
-        <v>118.7199624496756</v>
+        <v>118.7193610539196</v>
       </c>
       <c r="L555" t="inlineStr">
         <is>
@@ -27120,10 +27120,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J556" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K556" t="n">
-        <v>118.7199624496756</v>
+        <v>118.7193610539196</v>
       </c>
       <c r="L556" t="inlineStr">
         <is>
@@ -27168,10 +27168,10 @@
         <v>1.0470428</v>
       </c>
       <c r="J557" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K557" t="n">
-        <v>118.7199624496756</v>
+        <v>118.7193610539196</v>
       </c>
       <c r="L557" t="inlineStr">
         <is>
@@ -27216,10 +27216,10 @@
         <v>1</v>
       </c>
       <c r="J558" t="n">
-        <v>-111.4990480324392</v>
+        <v>-112.0581000001666</v>
       </c>
       <c r="K558" t="n">
-        <v>-104.5167939988198</v>
+        <v>-104.5162645515807</v>
       </c>
       <c r="L558" t="inlineStr">
         <is>
@@ -27264,10 +27264,10 @@
         <v>1</v>
       </c>
       <c r="J559" t="n">
-        <v>-111.8062079446459</v>
+        <v>-112.36680000044</v>
       </c>
       <c r="K559" t="n">
-        <v>-100.8116196108236</v>
+        <v>-100.8111089327629</v>
       </c>
       <c r="L559" t="inlineStr">
         <is>
@@ -27312,10 +27312,10 @@
         <v>1</v>
       </c>
       <c r="J560" t="n">
-        <v>-113.6491674155292</v>
+        <v>-114.2189999997119</v>
       </c>
       <c r="K560" t="n">
-        <v>-98.95903242827772</v>
+        <v>-98.95853113480619</v>
       </c>
       <c r="L560" t="inlineStr">
         <is>
@@ -27360,10 +27360,10 @@
         <v>1</v>
       </c>
       <c r="J561" t="n">
-        <v>-91.22649384516043</v>
+        <v>-91.68390000057596</v>
       </c>
       <c r="K561" t="n">
-        <v>-95.25385803949177</v>
+        <v>-95.25337551519863</v>
       </c>
       <c r="L561" t="inlineStr">
         <is>
@@ -27408,10 +27408,10 @@
         <v>1</v>
       </c>
       <c r="J562" t="n">
-        <v>-71.56825948106753</v>
+        <v>-71.92710000029848</v>
       </c>
       <c r="K562" t="n">
-        <v>-95.56262257386511</v>
+        <v>-95.56213848547375</v>
       </c>
       <c r="L562" t="inlineStr">
         <is>
@@ -27456,10 +27456,10 @@
         <v>1</v>
       </c>
       <c r="J563" t="n">
-        <v>-61.73914229904563</v>
+        <v>-62.04870000018441</v>
       </c>
       <c r="K563" t="n">
-        <v>-95.25385803949177</v>
+        <v>-95.25337551519863</v>
       </c>
       <c r="L563" t="inlineStr">
         <is>
@@ -27504,10 +27504,10 @@
         <v>1</v>
       </c>
       <c r="J564" t="n">
-        <v>-40.54510837519582</v>
+        <v>-40.74839999982278</v>
       </c>
       <c r="K564" t="n">
-        <v>-97.72397429157415</v>
+        <v>-97.72347925449546</v>
       </c>
       <c r="L564" t="inlineStr">
         <is>
@@ -27552,10 +27552,10 @@
         <v>1</v>
       </c>
       <c r="J565" t="n">
-        <v>-43.30954758260111</v>
+        <v>-43.5266999998163</v>
       </c>
       <c r="K565" t="n">
-        <v>-92.47497725461567</v>
+        <v>-92.47450880720626</v>
       </c>
       <c r="L565" t="inlineStr">
         <is>
@@ -27600,10 +27600,10 @@
         <v>1</v>
       </c>
       <c r="J566" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K566" t="n">
-        <v>46.16029749035783</v>
+        <v>46.16006365767769</v>
       </c>
       <c r="L566" t="inlineStr">
         <is>
@@ -27648,10 +27648,10 @@
         <v>1</v>
       </c>
       <c r="J567" t="n">
-        <v>-85.08329560598548</v>
+        <v>-85.50990000009135</v>
       </c>
       <c r="K567" t="n">
-        <v>45.85153295598448</v>
+        <v>45.85130068740256</v>
       </c>
       <c r="L567" t="inlineStr">
         <is>
@@ -27696,10 +27696,10 @@
         <v>1</v>
       </c>
       <c r="J568" t="n">
-        <v>-79.24725727896816</v>
+        <v>-79.64459999983083</v>
       </c>
       <c r="K568" t="n">
-        <v>46.16029749035783</v>
+        <v>46.16006365767769</v>
       </c>
       <c r="L568" t="inlineStr">
         <is>
@@ -27744,10 +27744,10 @@
         <v>1</v>
       </c>
       <c r="J569" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K569" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L569" t="inlineStr">
         <is>
@@ -27792,10 +27792,10 @@
         <v>1</v>
       </c>
       <c r="J570" t="n">
-        <v>-86.31193525358476</v>
+        <v>-86.74469999995138</v>
       </c>
       <c r="K570" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L570" t="inlineStr">
         <is>
@@ -27840,10 +27840,10 @@
         <v>1</v>
       </c>
       <c r="J571" t="n">
-        <v>-78.63293745568414</v>
+        <v>-79.02720000041901</v>
       </c>
       <c r="K571" t="n">
-        <v>54.80570438093911</v>
+        <v>54.80542675350951</v>
       </c>
       <c r="L571" t="inlineStr">
         <is>
@@ -27888,10 +27888,10 @@
         <v>1</v>
       </c>
       <c r="J572" t="n">
-        <v>-99.82697137958306</v>
+        <v>-100.32750000083</v>
       </c>
       <c r="K572" t="n">
-        <v>54.49693984656577</v>
+        <v>54.49666378323437</v>
       </c>
       <c r="L572" t="inlineStr">
         <is>
@@ -27936,10 +27936,10 @@
         <v>1</v>
       </c>
       <c r="J573" t="n">
-        <v>-100.441291202818</v>
+        <v>-100.9449000001925</v>
       </c>
       <c r="K573" t="n">
-        <v>64.37740486358315</v>
+        <v>64.37707874910951</v>
       </c>
       <c r="L573" t="inlineStr">
         <is>
@@ -27984,10 +27984,10 @@
         <v>1</v>
       </c>
       <c r="J574" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K574" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L574" t="inlineStr">
         <is>
@@ -28032,10 +28032,10 @@
         <v>1</v>
       </c>
       <c r="J575" t="n">
-        <v>-86.61909516574239</v>
+        <v>-87.05340000017549</v>
       </c>
       <c r="K575" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L575" t="inlineStr">
         <is>
@@ -28080,10 +28080,10 @@
         <v>1</v>
       </c>
       <c r="J576" t="n">
-        <v>-78.94009736789087</v>
+        <v>-79.33590000069248</v>
       </c>
       <c r="K576" t="n">
-        <v>99.57656148438751</v>
+        <v>99.57605706271963</v>
       </c>
       <c r="L576" t="inlineStr">
         <is>
@@ -28128,10 +28128,10 @@
         <v>1</v>
       </c>
       <c r="J577" t="n">
-        <v>-93.99093305256574</v>
+        <v>-94.46220000056948</v>
       </c>
       <c r="K577" t="n">
-        <v>106.3693811813656</v>
+        <v>106.3688423495375</v>
       </c>
       <c r="L577" t="inlineStr">
         <is>
@@ -28176,10 +28176,10 @@
         <v>1</v>
       </c>
       <c r="J578" t="n">
-        <v>-86.31193525358476</v>
+        <v>-86.74469999995138</v>
       </c>
       <c r="K578" t="n">
-        <v>106.3693811813656</v>
+        <v>106.3688423495375</v>
       </c>
       <c r="L578" t="inlineStr">
         <is>
@@ -28224,10 +28224,10 @@
         <v>1</v>
       </c>
       <c r="J579" t="n">
-        <v>-78.94009736789087</v>
+        <v>-79.33590000069248</v>
       </c>
       <c r="K579" t="n">
-        <v>106.3693811813656</v>
+        <v>106.3688423495375</v>
       </c>
       <c r="L579" t="inlineStr">
         <is>
@@ -28272,10 +28272,10 @@
         <v>1</v>
       </c>
       <c r="J580" t="n">
-        <v>-93.99093305256574</v>
+        <v>-94.46220000056948</v>
       </c>
       <c r="K580" t="n">
-        <v>112.2359072752237</v>
+        <v>112.2353387255299</v>
       </c>
       <c r="L580" t="inlineStr">
         <is>
@@ -28320,10 +28320,10 @@
         <v>1</v>
       </c>
       <c r="J581" t="n">
-        <v>-86.31193525358476</v>
+        <v>-86.74469999995138</v>
       </c>
       <c r="K581" t="n">
-        <v>112.5446718095971</v>
+        <v>112.544101695805</v>
       </c>
       <c r="L581" t="inlineStr">
         <is>
@@ -28368,10 +28368,10 @@
         <v>1</v>
       </c>
       <c r="J582" t="n">
-        <v>-78.94009736789087</v>
+        <v>-79.33590000069248</v>
       </c>
       <c r="K582" t="n">
-        <v>112.2359072752237</v>
+        <v>112.2353387255299</v>
       </c>
       <c r="L582" t="inlineStr">
         <is>
@@ -28416,10 +28416,10 @@
         <v>1</v>
       </c>
       <c r="J583" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K583" t="n">
-        <v>127.6741338635729</v>
+        <v>127.6734871089694</v>
       </c>
       <c r="L583" t="inlineStr">
         <is>
@@ -28464,10 +28464,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J584" t="n">
-        <v>-92.45513349275971</v>
+        <v>-92.91870000043599</v>
       </c>
       <c r="K584" t="n">
-        <v>39.3674777933797</v>
+        <v>39.36727837085986</v>
       </c>
       <c r="L584" t="inlineStr">
         <is>
@@ -28512,10 +28512,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J585" t="n">
-        <v>-85.08329560598548</v>
+        <v>-85.50990000009135</v>
       </c>
       <c r="K585" t="n">
-        <v>39.3674777933797</v>
+        <v>39.36727837085986</v>
       </c>
       <c r="L585" t="inlineStr">
         <is>
@@ -28560,10 +28560,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J586" t="n">
-        <v>-78.94009736789087</v>
+        <v>-79.33590000069248</v>
       </c>
       <c r="K586" t="n">
-        <v>39.05871325900636</v>
+        <v>39.05851540058472</v>
       </c>
       <c r="L586" t="inlineStr">
         <is>
@@ -28608,10 +28608,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J587" t="n">
-        <v>-106.5844894419929</v>
+        <v>-107.1189000006771</v>
       </c>
       <c r="K587" t="n">
-        <v>-92.78374178819921</v>
+        <v>-92.78327177669159</v>
       </c>
       <c r="L587" t="inlineStr">
         <is>
@@ -28656,10 +28656,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J588" t="n">
-        <v>-96.4482123477643</v>
+        <v>-96.93180000028956</v>
       </c>
       <c r="K588" t="n">
-        <v>-92.78374178819921</v>
+        <v>-92.78327177669159</v>
       </c>
       <c r="L588" t="inlineStr">
         <is>
@@ -28704,10 +28704,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J589" t="n">
-        <v>-86.61909516574239</v>
+        <v>-87.05340000017549</v>
       </c>
       <c r="K589" t="n">
-        <v>-92.78374178819921</v>
+        <v>-92.78327177669159</v>
       </c>
       <c r="L589" t="inlineStr">
         <is>
@@ -28752,10 +28752,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J590" t="n">
-        <v>-76.48281807156286</v>
+        <v>-76.86629999983731</v>
       </c>
       <c r="K590" t="n">
-        <v>-92.78374178819921</v>
+        <v>-92.78327177669159</v>
       </c>
       <c r="L590" t="inlineStr">
         <is>
@@ -28800,10 +28800,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J591" t="n">
-        <v>-66.65370089062131</v>
+        <v>-66.98790000080899</v>
       </c>
       <c r="K591" t="n">
-        <v>-92.78374178819921</v>
+        <v>-92.78327177669159</v>
       </c>
       <c r="L591" t="inlineStr">
         <is>
@@ -28848,10 +28848,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J592" t="n">
-        <v>-56.51742379639267</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K592" t="n">
-        <v>-92.47497725461567</v>
+        <v>-92.47450880720626</v>
       </c>
       <c r="L592" t="inlineStr">
         <is>
@@ -28896,10 +28896,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J593" t="n">
-        <v>-46.68830661437077</v>
+        <v>-46.9224000003074</v>
       </c>
       <c r="K593" t="n">
-        <v>-92.47497725461567</v>
+        <v>-92.47450880720626</v>
       </c>
       <c r="L593" t="inlineStr">
         <is>
@@ -28944,10 +28944,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J594" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K594" t="n">
-        <v>126.7478402715102</v>
+        <v>126.7471982092012</v>
       </c>
       <c r="L594" t="inlineStr">
         <is>
@@ -28992,10 +28992,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J595" t="n">
-        <v>-55.59594406095102</v>
+        <v>-55.87470000078554</v>
       </c>
       <c r="K595" t="n">
-        <v>126.7478402715102</v>
+        <v>126.7471982092012</v>
       </c>
       <c r="L595" t="inlineStr">
         <is>
@@ -29040,10 +29040,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J596" t="n">
-        <v>-40.85226828735345</v>
+        <v>-41.05710000004689</v>
       </c>
       <c r="K596" t="n">
-        <v>126.7478402715102</v>
+        <v>126.7471982092012</v>
       </c>
       <c r="L596" t="inlineStr">
         <is>
@@ -29088,10 +29088,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J597" t="n">
-        <v>-35.63054978474959</v>
+        <v>-35.8092000003333</v>
       </c>
       <c r="K597" t="n">
-        <v>126.7478402715102</v>
+        <v>126.7471982092012</v>
       </c>
       <c r="L597" t="inlineStr">
         <is>
@@ -29136,10 +29136,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J598" t="n">
-        <v>-66.34654097846368</v>
+        <v>-66.67920000058488</v>
       </c>
       <c r="K598" t="n">
-        <v>174.6063426949979</v>
+        <v>174.6054581974686</v>
       </c>
       <c r="L598" t="inlineStr">
         <is>
@@ -29184,10 +29184,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J599" t="n">
-        <v>-58.66754317948271</v>
+        <v>-58.96169999996678</v>
       </c>
       <c r="K599" t="n">
-        <v>174.6063426949979</v>
+        <v>174.6054581974686</v>
       </c>
       <c r="L599" t="inlineStr">
         <is>
@@ -29232,10 +29232,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J600" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K600" t="n">
-        <v>174.6063426949979</v>
+        <v>174.6054581974686</v>
       </c>
       <c r="L600" t="inlineStr">
         <is>
@@ -29280,10 +29280,10 @@
         <v>6.109054</v>
       </c>
       <c r="J601" t="n">
-        <v>-105.6630097054709</v>
+        <v>-106.1927999999554</v>
       </c>
       <c r="K601" t="n">
-        <v>-102.9729713395899</v>
+        <v>-102.9724497128419</v>
       </c>
       <c r="L601" t="inlineStr">
         <is>
@@ -29328,10 +29328,10 @@
         <v>6.109054</v>
       </c>
       <c r="J602" t="n">
-        <v>-95.83389252344904</v>
+        <v>-96.31439999984133</v>
       </c>
       <c r="K602" t="n">
-        <v>-103.2817358621162</v>
+        <v>-103.28121267127</v>
       </c>
       <c r="L602" t="inlineStr">
         <is>
@@ -29376,10 +29376,10 @@
         <v>6.109054</v>
       </c>
       <c r="J603" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K603" t="n">
-        <v>-102.9729713395899</v>
+        <v>-102.9724497128419</v>
       </c>
       <c r="L603" t="inlineStr">
         <is>
@@ -29424,10 +29424,10 @@
         <v>6.109054</v>
       </c>
       <c r="J604" t="n">
-        <v>-75.86849824827884</v>
+        <v>-76.24890000042549</v>
       </c>
       <c r="K604" t="n">
-        <v>-102.9729713395899</v>
+        <v>-102.9724497128419</v>
       </c>
       <c r="L604" t="inlineStr">
         <is>
@@ -29472,10 +29472,10 @@
         <v>6.109054</v>
       </c>
       <c r="J605" t="n">
-        <v>-65.73222115409932</v>
+        <v>-66.06180000008732</v>
       </c>
       <c r="K605" t="n">
-        <v>-102.9729713395899</v>
+        <v>-102.9724497128419</v>
       </c>
       <c r="L605" t="inlineStr">
         <is>
@@ -29520,10 +29520,10 @@
         <v>6.109054</v>
       </c>
       <c r="J606" t="n">
-        <v>-55.90310397202831</v>
+        <v>-56.18339999992389</v>
       </c>
       <c r="K606" t="n">
-        <v>-103.2817358621162</v>
+        <v>-103.28121267127</v>
       </c>
       <c r="L606" t="inlineStr">
         <is>
@@ -29568,10 +29568,10 @@
         <v>6.109054</v>
       </c>
       <c r="J607" t="n">
-        <v>-45.76682687892912</v>
+        <v>-45.99630000067148</v>
       </c>
       <c r="K607" t="n">
-        <v>-102.9729713395899</v>
+        <v>-102.9724497128419</v>
       </c>
       <c r="L607" t="inlineStr">
         <is>
@@ -29616,10 +29616,10 @@
         <v>6.109054</v>
       </c>
       <c r="J608" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K608" t="n">
-        <v>136.3195407541542</v>
+        <v>136.3188502048012</v>
       </c>
       <c r="L608" t="inlineStr">
         <is>
@@ -29664,10 +29664,10 @@
         <v>6.109054</v>
       </c>
       <c r="J609" t="n">
-        <v>-55.28878414879339</v>
+        <v>-55.56600000056143</v>
       </c>
       <c r="K609" t="n">
-        <v>136.6283052885276</v>
+        <v>136.6276131750763</v>
       </c>
       <c r="L609" t="inlineStr">
         <is>
@@ -29712,10 +29712,10 @@
         <v>6.109054</v>
       </c>
       <c r="J610" t="n">
-        <v>-45.15250705456476</v>
+        <v>-45.37890000017391</v>
       </c>
       <c r="K610" t="n">
-        <v>136.6283052885276</v>
+        <v>136.6276131750763</v>
       </c>
       <c r="L610" t="inlineStr">
         <is>
@@ -29760,10 +29760,10 @@
         <v>6.109054</v>
       </c>
       <c r="J611" t="n">
-        <v>-35.32338987254285</v>
+        <v>-35.50050000005984</v>
       </c>
       <c r="K611" t="n">
-        <v>136.6283052885276</v>
+        <v>136.6276131750763</v>
       </c>
       <c r="L611" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J612" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K612" t="n">
-        <v>-78.88933786065942</v>
+        <v>-78.88893823357058</v>
       </c>
       <c r="L612" t="inlineStr">
         <is>
@@ -29856,10 +29856,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J613" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K613" t="n">
-        <v>-78.88933786065942</v>
+        <v>-78.88893823357058</v>
       </c>
       <c r="L613" t="inlineStr">
         <is>
@@ -29904,10 +29904,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J614" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K614" t="n">
-        <v>-78.58057332628609</v>
+        <v>-78.58017526329546</v>
       </c>
       <c r="L614" t="inlineStr">
         <is>
@@ -29952,10 +29952,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J615" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K615" t="n">
-        <v>-78.58057332628609</v>
+        <v>-78.58017526329546</v>
       </c>
       <c r="L615" t="inlineStr">
         <is>
@@ -30000,10 +30000,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J616" t="n">
-        <v>-58.66754317948271</v>
+        <v>-58.96169999996678</v>
       </c>
       <c r="K616" t="n">
-        <v>-78.58057332628609</v>
+        <v>-78.58017526329546</v>
       </c>
       <c r="L616" t="inlineStr">
         <is>
@@ -30048,10 +30048,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J617" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K617" t="n">
-        <v>-78.58057332628609</v>
+        <v>-78.58017526329546</v>
       </c>
       <c r="L617" t="inlineStr">
         <is>
@@ -30096,10 +30096,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J618" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K618" t="n">
-        <v>-7.255966504461676</v>
+        <v>-7.255929748154049</v>
       </c>
       <c r="L618" t="inlineStr">
         <is>
@@ -30144,10 +30144,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J619" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K619" t="n">
-        <v>-7.255966504461676</v>
+        <v>-7.255929748154049</v>
       </c>
       <c r="L619" t="inlineStr">
         <is>
@@ -30192,10 +30192,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J620" t="n">
-        <v>-78.63293745568414</v>
+        <v>-79.02720000041901</v>
       </c>
       <c r="K620" t="n">
-        <v>-7.564731026987936</v>
+        <v>-7.564692706582162</v>
       </c>
       <c r="L620" t="inlineStr">
         <is>
@@ -30240,10 +30240,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J621" t="n">
-        <v>-65.73222115409932</v>
+        <v>-66.06180000008732</v>
       </c>
       <c r="K621" t="n">
-        <v>-7.255966504461676</v>
+        <v>-7.255929748154049</v>
       </c>
       <c r="L621" t="inlineStr">
         <is>
@@ -30288,10 +30288,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J622" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K622" t="n">
-        <v>-6.947201970088334</v>
+        <v>-6.947166777878915</v>
       </c>
       <c r="L622" t="inlineStr">
         <is>
@@ -30336,10 +30336,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J623" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K623" t="n">
-        <v>-7.255966504461676</v>
+        <v>-7.255929748154049</v>
       </c>
       <c r="L623" t="inlineStr">
         <is>
@@ -30384,10 +30384,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J624" t="n">
-        <v>-93.68377314035899</v>
+        <v>-94.15350000029602</v>
       </c>
       <c r="K624" t="n">
-        <v>27.63442558275915</v>
+        <v>27.63428559597074</v>
       </c>
       <c r="L624" t="inlineStr">
         <is>
@@ -30432,10 +30432,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J625" t="n">
-        <v>-86.00477534250747</v>
+        <v>-86.43600000081302</v>
       </c>
       <c r="K625" t="n">
-        <v>27.9431901171325</v>
+        <v>27.94304856624587</v>
       </c>
       <c r="L625" t="inlineStr">
         <is>
@@ -30480,10 +30480,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J626" t="n">
-        <v>-78.94009736789087</v>
+        <v>-79.33590000069248</v>
       </c>
       <c r="K626" t="n">
-        <v>28.25195465071603</v>
+        <v>28.25181153573121</v>
       </c>
       <c r="L626" t="inlineStr">
         <is>
@@ -30528,10 +30528,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J627" t="n">
-        <v>-65.73222115409932</v>
+        <v>-66.06180000008732</v>
       </c>
       <c r="K627" t="n">
-        <v>27.9431901171325</v>
+        <v>27.94304856624587</v>
       </c>
       <c r="L627" t="inlineStr">
         <is>
@@ -30576,10 +30576,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J628" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K628" t="n">
-        <v>27.9431901171325</v>
+        <v>27.94304856624587</v>
       </c>
       <c r="L628" t="inlineStr">
         <is>
@@ -30624,10 +30624,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J629" t="n">
-        <v>-50.68138546942446</v>
+        <v>-50.93550000021031</v>
       </c>
       <c r="K629" t="n">
-        <v>27.9431901171325</v>
+        <v>27.94304856624587</v>
       </c>
       <c r="L629" t="inlineStr">
         <is>
@@ -30672,10 +30672,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J630" t="n">
-        <v>-66.03938106625694</v>
+        <v>-66.37050000031142</v>
       </c>
       <c r="K630" t="n">
-        <v>39.3674777933797</v>
+        <v>39.36727837085986</v>
       </c>
       <c r="L630" t="inlineStr">
         <is>
@@ -30720,10 +30720,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J631" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K631" t="n">
-        <v>39.67624232775304</v>
+        <v>39.67604134113499</v>
       </c>
       <c r="L631" t="inlineStr">
         <is>
@@ -30768,10 +30768,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J632" t="n">
-        <v>-50.68138546942446</v>
+        <v>-50.93550000021031</v>
       </c>
       <c r="K632" t="n">
-        <v>39.3674777933797</v>
+        <v>39.36727837085986</v>
       </c>
       <c r="L632" t="inlineStr">
         <is>
@@ -30816,10 +30816,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J633" t="n">
-        <v>-66.03938106625694</v>
+        <v>-66.37050000031142</v>
       </c>
       <c r="K633" t="n">
-        <v>112.2359072752237</v>
+        <v>112.2353387255299</v>
       </c>
       <c r="L633" t="inlineStr">
         <is>
@@ -30864,10 +30864,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J634" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K634" t="n">
-        <v>112.2359072752237</v>
+        <v>112.2353387255299</v>
       </c>
       <c r="L634" t="inlineStr">
         <is>
@@ -30912,10 +30912,10 @@
         <v>1.0604858</v>
       </c>
       <c r="J635" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K635" t="n">
-        <v>111.9271427526975</v>
+        <v>111.9265757671018</v>
       </c>
       <c r="L635" t="inlineStr">
         <is>
@@ -30960,10 +30960,10 @@
         <v>1.09964</v>
       </c>
       <c r="J636" t="n">
-        <v>-93.37661322820138</v>
+        <v>-93.84480000007191</v>
       </c>
       <c r="K636" t="n">
-        <v>-61.28975955539097</v>
+        <v>-61.28944908189924</v>
       </c>
       <c r="L636" t="inlineStr">
         <is>
@@ -31008,10 +31008,10 @@
         <v>1.09964</v>
       </c>
       <c r="J637" t="n">
-        <v>-85.39045551814311</v>
+        <v>-85.81860000031546</v>
       </c>
       <c r="K637" t="n">
-        <v>-61.28975955539097</v>
+        <v>-61.28944908189924</v>
       </c>
       <c r="L637" t="inlineStr">
         <is>
@@ -31056,10 +31056,10 @@
         <v>1.09964</v>
       </c>
       <c r="J638" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K638" t="n">
-        <v>-61.28975955539097</v>
+        <v>-61.28944908189924</v>
       </c>
       <c r="L638" t="inlineStr">
         <is>
@@ -31104,10 +31104,10 @@
         <v>1.09964</v>
       </c>
       <c r="J639" t="n">
-        <v>-65.11790133081529</v>
+        <v>-65.4444000006755</v>
       </c>
       <c r="K639" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L639" t="inlineStr">
         <is>
@@ -31152,10 +31152,10 @@
         <v>1.09964</v>
       </c>
       <c r="J640" t="n">
-        <v>-57.74606344404106</v>
+        <v>-58.03560000033085</v>
       </c>
       <c r="K640" t="n">
-        <v>-60.98099502180744</v>
+        <v>-60.98068611241391</v>
       </c>
       <c r="L640" t="inlineStr">
         <is>
@@ -31200,10 +31200,10 @@
         <v>1.09964</v>
       </c>
       <c r="J641" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K641" t="n">
-        <v>-60.67223048743409</v>
+        <v>-60.67192314213877</v>
       </c>
       <c r="L641" t="inlineStr">
         <is>
@@ -31248,10 +31248,10 @@
         <v>1.09964</v>
       </c>
       <c r="J642" t="n">
-        <v>-93.37661322820138</v>
+        <v>-93.84480000007191</v>
       </c>
       <c r="K642" t="n">
-        <v>4.785850240532214</v>
+        <v>4.785825997010199</v>
       </c>
       <c r="L642" t="inlineStr">
         <is>
@@ -31296,10 +31296,10 @@
         <v>1.09964</v>
       </c>
       <c r="J643" t="n">
-        <v>-86.00477534250747</v>
+        <v>-86.43600000081302</v>
       </c>
       <c r="K643" t="n">
-        <v>5.094614774905557</v>
+        <v>5.094588967285333</v>
       </c>
       <c r="L643" t="inlineStr">
         <is>
@@ -31344,10 +31344,10 @@
         <v>1.09964</v>
       </c>
       <c r="J644" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K644" t="n">
-        <v>5.094614774905557</v>
+        <v>5.094588967285333</v>
       </c>
       <c r="L644" t="inlineStr">
         <is>
@@ -31392,10 +31392,10 @@
         <v>1.09964</v>
       </c>
       <c r="J645" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K645" t="n">
-        <v>5.094614774905557</v>
+        <v>5.094588967285333</v>
       </c>
       <c r="L645" t="inlineStr">
         <is>
@@ -31440,10 +31440,10 @@
         <v>1.09964</v>
       </c>
       <c r="J646" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K646" t="n">
-        <v>5.094614774905557</v>
+        <v>5.094588967285333</v>
       </c>
       <c r="L646" t="inlineStr">
         <is>
@@ -31488,10 +31488,10 @@
         <v>1.09964</v>
       </c>
       <c r="J647" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K647" t="n">
-        <v>5.094614774905557</v>
+        <v>5.094588967285333</v>
       </c>
       <c r="L647" t="inlineStr">
         <is>
@@ -31536,10 +31536,10 @@
         <v>1.09964</v>
       </c>
       <c r="J648" t="n">
-        <v>-94.91241278800739</v>
+        <v>-95.38830000020542</v>
       </c>
       <c r="K648" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L648" t="inlineStr">
         <is>
@@ -31584,10 +31584,10 @@
         <v>1.09964</v>
       </c>
       <c r="J649" t="n">
-        <v>-87.23341499010675</v>
+        <v>-87.67080000067305</v>
       </c>
       <c r="K649" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L649" t="inlineStr">
         <is>
@@ -31632,10 +31632,10 @@
         <v>1.09964</v>
       </c>
       <c r="J650" t="n">
-        <v>-79.86157710333252</v>
+        <v>-80.2620000003284</v>
       </c>
       <c r="K650" t="n">
-        <v>93.09250631072547</v>
+        <v>93.09203473511971</v>
       </c>
       <c r="L650" t="inlineStr">
         <is>
@@ -31680,10 +31680,10 @@
         <v>1.09964</v>
       </c>
       <c r="J651" t="n">
-        <v>-66.03938106625694</v>
+        <v>-66.37050000031142</v>
       </c>
       <c r="K651" t="n">
-        <v>93.71003537947215</v>
+        <v>93.70956067566998</v>
       </c>
       <c r="L651" t="inlineStr">
         <is>
@@ -31728,10 +31728,10 @@
         <v>1.09964</v>
       </c>
       <c r="J652" t="n">
-        <v>-58.36038326840542</v>
+        <v>-58.65300000082842</v>
       </c>
       <c r="K652" t="n">
-        <v>93.40127084509881</v>
+        <v>93.40079770539484</v>
       </c>
       <c r="L652" t="inlineStr">
         <is>
@@ -31776,10 +31776,10 @@
         <v>1.09964</v>
       </c>
       <c r="J653" t="n">
-        <v>-50.98854538158208</v>
+        <v>-51.24420000043442</v>
       </c>
       <c r="K653" t="n">
-        <v>93.71003537947215</v>
+        <v>93.70956067566998</v>
       </c>
       <c r="L653" t="inlineStr">
         <is>
@@ -31824,10 +31824,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J654" t="n">
-        <v>-93.37661322820138</v>
+        <v>-93.84480000007191</v>
       </c>
       <c r="K654" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L654" t="inlineStr">
         <is>
@@ -31872,10 +31872,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J655" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K655" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L655" t="inlineStr">
         <is>
@@ -31920,10 +31920,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J656" t="n">
-        <v>-78.32577754352651</v>
+        <v>-78.71850000019491</v>
       </c>
       <c r="K656" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L656" t="inlineStr">
         <is>
@@ -31968,10 +31968,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J657" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K657" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L657" t="inlineStr">
         <is>
@@ -32016,10 +32016,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J658" t="n">
-        <v>-57.74606344404106</v>
+        <v>-58.03560000033085</v>
       </c>
       <c r="K658" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L658" t="inlineStr">
         <is>
@@ -32064,10 +32064,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J659" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K659" t="n">
-        <v>-14.35755072396606</v>
+        <v>-14.3574779934</v>
       </c>
       <c r="L659" t="inlineStr">
         <is>
@@ -32112,10 +32112,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J660" t="n">
-        <v>-93.37661322820138</v>
+        <v>-93.84480000007191</v>
       </c>
       <c r="K660" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L660" t="inlineStr">
         <is>
@@ -32160,10 +32160,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J661" t="n">
-        <v>-85.69761543030074</v>
+        <v>-86.12730000053956</v>
       </c>
       <c r="K661" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L661" t="inlineStr">
         <is>
@@ -32208,10 +32208,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J662" t="n">
-        <v>-78.63293745568414</v>
+        <v>-79.02720000041901</v>
       </c>
       <c r="K662" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L662" t="inlineStr">
         <is>
@@ -32256,10 +32256,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J663" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K663" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L663" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J664" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K664" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L664" t="inlineStr">
         <is>
@@ -32352,10 +32352,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J665" t="n">
-        <v>-50.68138546942446</v>
+        <v>-50.93550000021031</v>
       </c>
       <c r="K665" t="n">
-        <v>21.15037042015437</v>
+        <v>21.15026327942804</v>
       </c>
       <c r="L665" t="inlineStr">
         <is>
@@ -32400,10 +32400,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J666" t="n">
-        <v>-65.42506124189258</v>
+        <v>-65.75309999981386</v>
       </c>
       <c r="K666" t="n">
-        <v>46.16029749035783</v>
+        <v>46.16006365767769</v>
       </c>
       <c r="L666" t="inlineStr">
         <is>
@@ -32448,10 +32448,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J667" t="n">
-        <v>-58.05322335619869</v>
+        <v>-58.34430000055496</v>
       </c>
       <c r="K667" t="n">
-        <v>46.16029749035783</v>
+        <v>46.16006365767769</v>
       </c>
       <c r="L667" t="inlineStr">
         <is>
@@ -32496,10 +32496,10 @@
         <v>1.4084626</v>
       </c>
       <c r="J668" t="n">
-        <v>-50.37422555721772</v>
+        <v>-50.62679999993685</v>
       </c>
       <c r="K668" t="n">
-        <v>46.16029749035783</v>
+        <v>46.16006365767769</v>
       </c>
       <c r="L668" t="inlineStr">
         <is>
@@ -32544,10 +32544,10 @@
         <v>2.6</v>
       </c>
       <c r="J669" t="n">
-        <v>-115.4921268874928</v>
+        <v>-116.0712000000695</v>
       </c>
       <c r="K669" t="n">
-        <v>-109.7657910357782</v>
+        <v>-109.7652349988699</v>
       </c>
       <c r="L669" t="inlineStr">
         <is>
@@ -32592,10 +32592,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J670" t="n">
-        <v>-66.03938106625694</v>
+        <v>-66.37050000031142</v>
       </c>
       <c r="K670" t="n">
-        <v>168.4310520557092</v>
+        <v>168.4301988401438</v>
       </c>
       <c r="L670" t="inlineStr">
         <is>
@@ -32640,10 +32640,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J671" t="n">
-        <v>-58.66754317948271</v>
+        <v>-58.96169999996678</v>
       </c>
       <c r="K671" t="n">
-        <v>168.4310520557092</v>
+        <v>168.4301988401438</v>
       </c>
       <c r="L671" t="inlineStr">
         <is>
@@ -32688,10 +32688,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J672" t="n">
-        <v>-50.68138546942446</v>
+        <v>-50.93550000021031</v>
       </c>
       <c r="K672" t="n">
-        <v>168.7398165892927</v>
+        <v>168.7389618096291</v>
       </c>
       <c r="L672" t="inlineStr">
         <is>
@@ -32736,10 +32736,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J673" t="n">
-        <v>-46.07398679000641</v>
+        <v>-46.30499999980983</v>
       </c>
       <c r="K673" t="n">
-        <v>126.7478402715102</v>
+        <v>126.7471982092012</v>
       </c>
       <c r="L673" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>1</v>
       </c>
       <c r="J674" t="n">
-        <v>-82.93317622289545</v>
+        <v>-83.34900000054604</v>
       </c>
       <c r="K674" t="n">
-        <v>-127.0566048066733</v>
+        <v>-127.0559611802661</v>
       </c>
       <c r="L674" t="inlineStr">
         <is>
@@ -32832,10 +32832,10 @@
         <v>1</v>
       </c>
       <c r="J675" t="n">
-        <v>-68.18950044929788</v>
+        <v>-68.53139999980738</v>
       </c>
       <c r="K675" t="n">
-        <v>-125.5127821466537</v>
+        <v>-125.5121463407375</v>
       </c>
       <c r="L675" t="inlineStr">
         <is>
@@ -32880,10 +32880,10 @@
         <v>1</v>
       </c>
       <c r="J676" t="n">
-        <v>-54.98162423663576</v>
+        <v>-55.25730000033732</v>
       </c>
       <c r="K676" t="n">
-        <v>-127.0566048066733</v>
+        <v>-127.0559611802661</v>
       </c>
       <c r="L676" t="inlineStr">
         <is>
@@ -32928,10 +32928,10 @@
         <v>2.6</v>
       </c>
       <c r="J677" t="n">
-        <v>-99.2126515552187</v>
+        <v>-99.71010000033243</v>
       </c>
       <c r="K677" t="n">
-        <v>-134.1581890380248</v>
+        <v>-134.1575094373591</v>
       </c>
       <c r="L677" t="inlineStr">
         <is>
@@ -32976,10 +32976,10 @@
         <v>2.6</v>
       </c>
       <c r="J678" t="n">
-        <v>-71.2610995689099</v>
+        <v>-71.61840000007436</v>
       </c>
       <c r="K678" t="n">
-        <v>-134.1581890380248</v>
+        <v>-134.1575094373591</v>
       </c>
       <c r="L678" t="inlineStr">
         <is>
@@ -33024,10 +33024,10 @@
         <v>2.6</v>
       </c>
       <c r="J679" t="n">
-        <v>-43.30954758260111</v>
+        <v>-43.5266999998163</v>
       </c>
       <c r="K679" t="n">
-        <v>-134.1581890380248</v>
+        <v>-134.1575094373591</v>
       </c>
       <c r="L679" t="inlineStr">
         <is>
@@ -33072,10 +33072,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J680" t="n">
-        <v>-92.76229340491734</v>
+        <v>-93.22740000066011</v>
       </c>
       <c r="K680" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L680" t="inlineStr">
         <is>
@@ -33120,10 +33120,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J681" t="n">
-        <v>-85.39045551814311</v>
+        <v>-85.81860000031546</v>
       </c>
       <c r="K681" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L681" t="inlineStr">
         <is>
@@ -33168,10 +33168,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J682" t="n">
-        <v>-77.71145772024249</v>
+        <v>-78.10110000078309</v>
       </c>
       <c r="K682" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L682" t="inlineStr">
         <is>
@@ -33216,10 +33216,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J683" t="n">
-        <v>-64.81074141865766</v>
+        <v>-65.13570000045139</v>
       </c>
       <c r="K683" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L683" t="inlineStr">
         <is>
@@ -33264,10 +33264,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J684" t="n">
-        <v>-57.43890353183432</v>
+        <v>-57.72690000005739</v>
       </c>
       <c r="K684" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L684" t="inlineStr">
         <is>
@@ -33312,10 +33312,10 @@
         <v>1.2363128</v>
       </c>
       <c r="J685" t="n">
-        <v>-49.7599057339828</v>
+        <v>-50.00940000057439</v>
       </c>
       <c r="K685" t="n">
-        <v>-148.3613574999379</v>
+        <v>-148.3606059507552</v>
       </c>
       <c r="L685" t="inlineStr">
         <is>
@@ -33360,10 +33360,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J686" t="n">
-        <v>-92.76229340491734</v>
+        <v>-93.22740000066011</v>
       </c>
       <c r="K686" t="n">
-        <v>-142.4948313942328</v>
+        <v>-142.4941095629158</v>
       </c>
       <c r="L686" t="inlineStr">
         <is>
@@ -33408,10 +33408,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J687" t="n">
-        <v>-85.39045551814311</v>
+        <v>-85.81860000031546</v>
       </c>
       <c r="K687" t="n">
-        <v>-142.4948313942328</v>
+        <v>-142.4941095629158</v>
       </c>
       <c r="L687" t="inlineStr">
         <is>
@@ -33456,10 +33456,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J688" t="n">
-        <v>-77.71145772024249</v>
+        <v>-78.10110000078309</v>
       </c>
       <c r="K688" t="n">
-        <v>-142.1860668606492</v>
+        <v>-142.1853465934304</v>
       </c>
       <c r="L688" t="inlineStr">
         <is>
@@ -33504,10 +33504,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J689" t="n">
-        <v>-64.81074141865766</v>
+        <v>-65.13570000045139</v>
       </c>
       <c r="K689" t="n">
-        <v>-142.1860668606492</v>
+        <v>-142.1853465934304</v>
       </c>
       <c r="L689" t="inlineStr">
         <is>
@@ -33552,10 +33552,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J690" t="n">
-        <v>-57.43890353183432</v>
+        <v>-57.72690000005739</v>
       </c>
       <c r="K690" t="n">
-        <v>-142.1860668606492</v>
+        <v>-142.1853465934304</v>
       </c>
       <c r="L690" t="inlineStr">
         <is>
@@ -33600,10 +33600,10 @@
         <v>1.5555572</v>
       </c>
       <c r="J691" t="n">
-        <v>-49.7599057339828</v>
+        <v>-50.00940000057439</v>
       </c>
       <c r="K691" t="n">
-        <v>-142.1860668606492</v>
+        <v>-142.1853465934304</v>
       </c>
       <c r="L691" t="inlineStr">
         <is>
@@ -33648,10 +33648,10 @@
         <v>1</v>
       </c>
       <c r="J692" t="n">
-        <v>77.86503767526551</v>
+        <v>78.25544999983407</v>
       </c>
       <c r="K692" t="n">
-        <v>-17.44519604400532</v>
+        <v>-17.4451076724573</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
@@ -33696,10 +33696,10 @@
         <v>16.0614894048131</v>
       </c>
       <c r="J693" t="n">
-        <v>70.03245992126152</v>
+        <v>70.38360000016499</v>
       </c>
       <c r="K693" t="n">
-        <v>-54.49693985920266</v>
+        <v>-54.4966637958712</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
@@ -33744,10 +33744,10 @@
         <v>17.6058633850347</v>
       </c>
       <c r="J694" t="n">
-        <v>86.77267512184577</v>
+        <v>87.20775000031222</v>
       </c>
       <c r="K694" t="n">
-        <v>-21.76789948890106</v>
+        <v>-21.7677892199783</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
@@ -33792,10 +33792,10 @@
         <v>17.6085645678712</v>
       </c>
       <c r="J695" t="n">
-        <v>86.77267512184577</v>
+        <v>87.20775000031222</v>
       </c>
       <c r="K695" t="n">
-        <v>12.65934579636486</v>
+        <v>12.65928166833888</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
@@ -33840,10 +33840,10 @@
         <v>1</v>
       </c>
       <c r="J696" t="n">
-        <v>70.64677974454554</v>
+        <v>71.00099999957679</v>
       </c>
       <c r="K696" t="n">
-        <v>17.59957829895</v>
+        <v>17.59948914535294</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
@@ -33888,10 +33888,10 @@
         <v>39.2380095193426</v>
       </c>
       <c r="J697" t="n">
-        <v>90.4585940646927</v>
+        <v>90.91214999994166</v>
       </c>
       <c r="K697" t="n">
-        <v>-70.08954871355384</v>
+        <v>-70.08919366326352</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
@@ -33936,10 +33936,10 @@
         <v>1</v>
       </c>
       <c r="J698" t="n">
-        <v>110.4239883398138</v>
+        <v>110.9776499993082</v>
       </c>
       <c r="K698" t="n">
-        <v>-70.86146002697774</v>
+        <v>-70.86110106644202</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
@@ -33984,10 +33984,10 @@
         <v>8.345320482737019</v>
       </c>
       <c r="J699" t="n">
-        <v>75.10059846781111</v>
+        <v>75.47714999979119</v>
       </c>
       <c r="K699" t="n">
-        <v>105.5974698458272</v>
+        <v>105.5969349242445</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
@@ -34032,10 +34032,10 @@
         <v>1</v>
       </c>
       <c r="J700" t="n">
-        <v>115.4921268874928</v>
+        <v>116.0712000000695</v>
       </c>
       <c r="K700" t="n">
-        <v>-70.86146002697774</v>
+        <v>-70.86110106644202</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
@@ -34080,10 +34080,10 @@
         <v>1</v>
       </c>
       <c r="J701" t="n">
-        <v>-23.49773326353428</v>
+        <v>-23.61555000053719</v>
       </c>
       <c r="K701" t="n">
-        <v>-117.4849043248191</v>
+        <v>-117.4843091854559</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
@@ -34128,10 +34128,10 @@
         <v>26.5650228690678</v>
       </c>
       <c r="J702" t="n">
-        <v>-10.13627709363936</v>
+        <v>-10.1870999997953</v>
       </c>
       <c r="K702" t="n">
-        <v>-122.579519094196</v>
+        <v>-122.5788981472126</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
@@ -34176,10 +34176,10 @@
         <v>1</v>
       </c>
       <c r="J703" t="n">
-        <v>-23.49773326353428</v>
+        <v>-23.61555000053719</v>
       </c>
       <c r="K703" t="n">
-        <v>-73.02281175495425</v>
+        <v>-73.02244184573114</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
@@ -34224,10 +34224,10 @@
         <v>75.36545028155891</v>
       </c>
       <c r="J704" t="n">
-        <v>13.82219603648631</v>
+        <v>13.89149999942475</v>
       </c>
       <c r="K704" t="n">
-        <v>-82.28574770322494</v>
+        <v>-82.28533087105599</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
@@ -34272,10 +34272,10 @@
         <v>1</v>
       </c>
       <c r="J705" t="n">
-        <v>-7.678997798440799</v>
+        <v>-7.717500000075235</v>
       </c>
       <c r="K705" t="n">
-        <v>-41.99197632410093</v>
+        <v>-41.99176360674637</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
@@ -34320,10 +34320,10 @@
         <v>85.2500016533164</v>
       </c>
       <c r="J706" t="n">
-        <v>15.66515550849905</v>
+        <v>15.7436999998317</v>
       </c>
       <c r="K706" t="n">
-        <v>-54.96008664931049</v>
+        <v>-54.95980823983178</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -34368,10 +34368,10 @@
         <v>1</v>
       </c>
       <c r="J707" t="n">
-        <v>-7.986157710598427</v>
+        <v>-8.026200000299344</v>
       </c>
       <c r="K707" t="n">
-        <v>-4.631467974530251</v>
+        <v>-4.631444513057334</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>17.9147381814938</v>
       </c>
       <c r="J708" t="n">
-        <v>0.9214797359818215</v>
+        <v>0.9261000001788009</v>
       </c>
       <c r="K708" t="n">
-        <v>-22.0766640232744</v>
+        <v>-22.07655219025344</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
@@ -34464,10 +34464,10 @@
         <v>1</v>
       </c>
       <c r="J709" t="n">
-        <v>-7.986157710598427</v>
+        <v>-8.026200000299344</v>
       </c>
       <c r="K709" t="n">
-        <v>25.62745612157441</v>
+        <v>25.62732630142429</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
@@ -34512,10 +34512,10 @@
         <v>17.9173927965757</v>
       </c>
       <c r="J710" t="n">
-        <v>28.87303172229061</v>
+        <v>29.01780000043686</v>
       </c>
       <c r="K710" t="n">
-        <v>-21.92228175648263</v>
+        <v>-21.92217070551077</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
@@ -34560,10 +34560,10 @@
         <v>1</v>
       </c>
       <c r="J711" t="n">
-        <v>19.811814319607</v>
+        <v>19.91114999982199</v>
       </c>
       <c r="K711" t="n">
-        <v>-3.550792115675732</v>
+        <v>-3.550774128546486</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
@@ -34608,10 +34608,10 @@
         <v>18.2236129780023</v>
       </c>
       <c r="J712" t="n">
-        <v>0.7678997798784543</v>
+        <v>0.7717500000420703</v>
       </c>
       <c r="K712" t="n">
-        <v>12.19619899519974</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
@@ -34656,10 +34656,10 @@
         <v>1</v>
       </c>
       <c r="J713" t="n">
-        <v>19.65823436350363</v>
+        <v>19.75679999968526</v>
       </c>
       <c r="K713" t="n">
-        <v>78.73495558123076</v>
+        <v>78.7345567361911</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
@@ -34704,10 +34704,10 @@
         <v>17.6058633850347</v>
       </c>
       <c r="J714" t="n">
-        <v>28.71945176618724</v>
+        <v>28.86345000030013</v>
       </c>
       <c r="K714" t="n">
-        <v>12.50496352878328</v>
+        <v>12.50490018280642</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
@@ -34752,10 +34752,10 @@
         <v>1</v>
       </c>
       <c r="J715" t="n">
-        <v>12.13281652062603</v>
+        <v>12.19364999920388</v>
       </c>
       <c r="K715" t="n">
-        <v>-156.6979998569357</v>
+        <v>-156.6972060771017</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
@@ -34800,10 +34800,10 @@
         <v>44.7868454542777</v>
       </c>
       <c r="J716" t="n">
-        <v>16.43305528783734</v>
+        <v>16.51544999933089</v>
       </c>
       <c r="K716" t="n">
-        <v>55.73199797300186</v>
+        <v>55.73171565327769</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
@@ -34848,10 +34848,10 @@
         <v>1</v>
       </c>
       <c r="J717" t="n">
-        <v>58.51396322337934</v>
+        <v>58.80734999983004</v>
       </c>
       <c r="K717" t="n">
-        <v>-174.7607249625794</v>
+        <v>-174.7598396830011</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
@@ -34896,10 +34896,10 @@
         <v>46.6400942320942</v>
       </c>
       <c r="J718" t="n">
-        <v>35.47696982751678</v>
+        <v>35.65484999906146</v>
       </c>
       <c r="K718" t="n">
-        <v>-177.3852234814536</v>
+        <v>-177.3843249070406</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
@@ -34944,10 +34944,10 @@
         <v>1</v>
       </c>
       <c r="J719" t="n">
-        <v>11.82565660954874</v>
+        <v>11.88495000006552</v>
       </c>
       <c r="K719" t="n">
-        <v>-126.2846934821922</v>
+        <v>-126.2840537660304</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
@@ -34992,10 +34992,10 @@
         <v>74.13059267213769</v>
       </c>
       <c r="J720" t="n">
-        <v>10.13627709363936</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K720" t="n">
-        <v>98.18712109194946</v>
+        <v>98.18662370872346</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
@@ -35040,10 +35040,10 @@
         <v>78.1459320571828</v>
       </c>
       <c r="J721" t="n">
-        <v>-69.57172005300052</v>
+        <v>-69.92054999980414</v>
       </c>
       <c r="K721" t="n">
-        <v>-96.02576936397296</v>
+        <v>-96.02528292943434</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
@@ -35088,10 +35088,10 @@
         <v>1</v>
       </c>
       <c r="J722" t="n">
-        <v>-46.9954665265775</v>
+        <v>-47.23110000058086</v>
       </c>
       <c r="K722" t="n">
-        <v>37.51489059898673</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
@@ -35136,10 +35136,10 @@
         <v>44.1701726245875</v>
       </c>
       <c r="J723" t="n">
-        <v>-52.67792489636201</v>
+        <v>-52.94204999956953</v>
       </c>
       <c r="K723" t="n">
-        <v>-55.26885118289402</v>
+        <v>-55.26857120931711</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
@@ -35184,10 +35184,10 @@
         <v>1</v>
       </c>
       <c r="J724" t="n">
-        <v>-74.63985860067956</v>
+        <v>-75.01410000056546</v>
       </c>
       <c r="K724" t="n">
-        <v>-42.45512312526604</v>
+        <v>-42.45490806176417</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
@@ -35232,10 +35232,10 @@
         <v>19.1502373674291</v>
       </c>
       <c r="J725" t="n">
-        <v>-84.46897578162113</v>
+        <v>-84.89249999959378</v>
       </c>
       <c r="K725" t="n">
-        <v>-22.38542855764774</v>
+        <v>-22.38531516052857</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
@@ -35280,10 +35280,10 @@
         <v>1</v>
       </c>
       <c r="J726" t="n">
-        <v>-74.79343855565348</v>
+        <v>-75.16844999956709</v>
       </c>
       <c r="K726" t="n">
-        <v>-5.403379299011428</v>
+        <v>-5.403351927293047</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
@@ -35328,10 +35328,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J727" t="n">
-        <v>-56.51742379639267</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K727" t="n">
-        <v>-22.38542855764774</v>
+        <v>-22.38531516052857</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
@@ -35376,10 +35376,10 @@
         <v>1</v>
       </c>
       <c r="J728" t="n">
-        <v>-74.94701851175685</v>
+        <v>-75.32279999970382</v>
       </c>
       <c r="K728" t="n">
-        <v>34.11848075642121</v>
+        <v>34.11830792357066</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
@@ -35424,10 +35424,10 @@
         <v>18.8438866439532</v>
       </c>
       <c r="J729" t="n">
-        <v>-84.31539582551775</v>
+        <v>-84.73814999945705</v>
       </c>
       <c r="K729" t="n">
-        <v>12.04181673867545</v>
+        <v>12.04175573884584</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
@@ -35472,10 +35472,10 @@
         <v>1</v>
       </c>
       <c r="J730" t="n">
-        <v>-75.10059846786022</v>
+        <v>-75.47714999984055</v>
       </c>
       <c r="K730" t="n">
-        <v>79.04372012666138</v>
+        <v>79.04331971752346</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
@@ -35520,10 +35520,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J731" t="n">
-        <v>-56.51742379639267</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K731" t="n">
-        <v>12.19619899519974</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
@@ -35568,10 +35568,10 @@
         <v>18.2236129780023</v>
       </c>
       <c r="J732" t="n">
-        <v>-84.31539582551775</v>
+        <v>-84.73814999945705</v>
       </c>
       <c r="K732" t="n">
-        <v>55.42323343862852</v>
+        <v>55.42295268300256</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
@@ -35616,10 +35616,10 @@
         <v>19.1502373662933</v>
       </c>
       <c r="J733" t="n">
-        <v>-56.51742379639267</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K733" t="n">
-        <v>54.18817531298223</v>
+        <v>54.18790081374905</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
@@ -35664,10 +35664,10 @@
         <v>37.0662586828766</v>
       </c>
       <c r="J734" t="n">
-        <v>-50.06706564506009</v>
+        <v>-50.31809999971274</v>
       </c>
       <c r="K734" t="n">
-        <v>130.2986323927146</v>
+        <v>130.2979723432763</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
@@ -35712,10 +35712,10 @@
         <v>1</v>
       </c>
       <c r="J735" t="n">
-        <v>-39.00930881651925</v>
+        <v>-39.2049000008244</v>
       </c>
       <c r="K735" t="n">
-        <v>-9.417318221380908</v>
+        <v>-9.417270516385944</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
@@ -35760,10 +35760,10 @@
         <v>65.79105449957601</v>
       </c>
       <c r="J736" t="n">
-        <v>-72.64331917261255</v>
+        <v>-73.00755000007113</v>
       </c>
       <c r="K736" t="n">
-        <v>-69.78078416812322</v>
+        <v>-69.78043068193116</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
@@ -35808,10 +35808,10 @@
         <v>1</v>
       </c>
       <c r="J737" t="n">
-        <v>-31.79105088579928</v>
+        <v>-31.95045000056712</v>
       </c>
       <c r="K737" t="n">
-        <v>109.9201732915127</v>
+        <v>109.9196164725553</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
@@ -35856,10 +35856,10 @@
         <v>7.13084897104345</v>
       </c>
       <c r="J738" t="n">
-        <v>-35.47696982864623</v>
+        <v>-35.65485000019657</v>
       </c>
       <c r="K738" t="n">
-        <v>99.57656147333024</v>
+        <v>99.57605705166242</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
@@ -35904,10 +35904,10 @@
         <v>1</v>
       </c>
       <c r="J739" t="n">
-        <v>-26.8764922942236</v>
+        <v>-27.01124999994253</v>
       </c>
       <c r="K739" t="n">
-        <v>109.1482619559743</v>
+        <v>109.1477090472624</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
@@ -35952,10 +35952,10 @@
         <v>1</v>
       </c>
       <c r="J740" t="n">
-        <v>-105.6630097054709</v>
+        <v>-106.1927999999554</v>
       </c>
       <c r="K740" t="n">
-        <v>-71.63337136251619</v>
+        <v>-71.63300849173496</v>
       </c>
       <c r="L740" t="inlineStr">
         <is>

--- a/planilhas/equipment_processado.xlsx
+++ b/planilhas/equipment_processado.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L740"/>
+  <dimension ref="A1:L742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33614,395 +33614,395 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>b_canaleta1deitado</t>
+          <t>ls_diversos</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>-3.12237361111111</v>
+        <v>-3.123187</v>
       </c>
       <c r="C692" t="n">
-        <v>-41.7646361111111</v>
+        <v>-41.765903</v>
       </c>
       <c r="D692" t="n">
         <v>77</v>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>[-41.764636111111145, -3.12237361111111]</t>
+          <t>[-41.765903, -3.123187]</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>[(-3.12237361111111, -41.764636111111145), (-3.12237361111111, -41.764627114699714)]</t>
+          <t>[(-3.123187, -41.765903), (-3.123187, -41.76547117180943)]</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>[(-3.12237361111111, -41.764636111111145), (-3.121481082104531, -41.764636111111145)]</t>
+          <t>[(-3.123187, -41.765903), (-3.1225630035680925, -41.765903)]</t>
         </is>
       </c>
       <c r="H692" t="n">
-        <v>98.6936879523502</v>
+        <v>69</v>
       </c>
       <c r="I692" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="J692" t="n">
-        <v>78.25544999983407</v>
+        <v>-12.13808400033122</v>
       </c>
       <c r="K692" t="n">
-        <v>-17.4451076724573</v>
+        <v>-158.2657219513459</v>
       </c>
       <c r="L692" t="inlineStr">
         <is>
-          <t>b_canaleta1deitado</t>
+          <t>ls_diversos</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>b_canaleta1empe</t>
+          <t>b_svc</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>-3.12244444444444</v>
+        <v>-3.122447</v>
       </c>
       <c r="C693" t="n">
-        <v>-41.7649694444445</v>
+        <v>-41.765774</v>
       </c>
       <c r="D693" t="n">
         <v>77</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>[-41.7649694444445, -3.122444444444445]</t>
+          <t>[-41.765774, -3.122447]</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>[(-3.122444444444445, -41.7649694444445), (-3.122444444444445, -41.764824948547194)]</t>
+          <t>[(-3.122447, -41.765774), (-3.122447, -41.76503179566388)]</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>[(-3.122444444444445, -41.7649694444445), (-3.1224354010091355, -41.7649694444445)]</t>
+          <t>[(-3.122447, -41.765774), (-3.122040949937832, -41.765774)]</t>
         </is>
       </c>
       <c r="H693" t="n">
-        <v>1</v>
+        <v>44.9</v>
       </c>
       <c r="I693" t="n">
-        <v>16.0614894048131</v>
+        <v>82.5</v>
       </c>
       <c r="J693" t="n">
-        <v>70.38360000016499</v>
+        <v>70.09959599966466</v>
       </c>
       <c r="K693" t="n">
-        <v>-54.4966637958712</v>
+        <v>-143.9267697343775</v>
       </c>
       <c r="L693" t="inlineStr">
         <is>
-          <t>b_canaleta1empe</t>
+          <t>b_svc</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>b_canaleta2empe</t>
+          <t>b_canaleta1deitado</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>-3.12229305555555</v>
+        <v>-3.12237361111111</v>
       </c>
       <c r="C694" t="n">
-        <v>-41.764675</v>
+        <v>-41.7646361111111</v>
       </c>
       <c r="D694" t="n">
         <v>77</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>[-41.764675, -3.122293055555555]</t>
+          <t>[-41.764636111111145, -3.12237361111111]</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>[(-3.122293055555555, -41.764675), (-3.122293055555555, -41.7645166102891)]</t>
+          <t>[(-3.12237361111111, -41.764636111111145), (-3.12237361111111, -41.764627114699714)]</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>[(-3.122293055555555, -41.764675), (-3.1222840121182087, -41.764675)]</t>
+          <t>[(-3.12237361111111, -41.764636111111145), (-3.121481082104531, -41.764636111111145)]</t>
         </is>
       </c>
       <c r="H694" t="n">
-        <v>1</v>
+        <v>98.6936879523502</v>
       </c>
       <c r="I694" t="n">
-        <v>17.6058633850347</v>
+        <v>1</v>
       </c>
       <c r="J694" t="n">
-        <v>87.20775000031222</v>
+        <v>78.25544999983407</v>
       </c>
       <c r="K694" t="n">
-        <v>-21.7677892199783</v>
+        <v>-17.4451076724573</v>
       </c>
       <c r="L694" t="inlineStr">
         <is>
-          <t>b_canaleta2empe</t>
+          <t>b_canaleta1deitado</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>b_canaleta3empe</t>
+          <t>b_canaleta1empe</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>-3.12229305555555</v>
+        <v>-3.12244444444444</v>
       </c>
       <c r="C695" t="n">
-        <v>-41.7643652777778</v>
+        <v>-41.7649694444445</v>
       </c>
       <c r="D695" t="n">
         <v>77</v>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>[-41.7643652777778, -3.122293055555555]</t>
+          <t>[-41.7649694444445, -3.122444444444445]</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>[(-3.122293055555555, -41.7643652777778), (-3.122293055555555, -41.76420686376592)]</t>
+          <t>[(-3.122444444444445, -41.7649694444445), (-3.122444444444445, -41.764824948547194)]</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>[(-3.122293055555555, -41.7643652777778), (-3.122284012118205, -41.7643652777778)]</t>
+          <t>[(-3.122444444444445, -41.7649694444445), (-3.1224354010091355, -41.7649694444445)]</t>
         </is>
       </c>
       <c r="H695" t="n">
         <v>1</v>
       </c>
       <c r="I695" t="n">
-        <v>17.6085645678712</v>
+        <v>16.0614894048131</v>
       </c>
       <c r="J695" t="n">
-        <v>87.20775000031222</v>
+        <v>70.38360000016499</v>
       </c>
       <c r="K695" t="n">
-        <v>12.65928166833888</v>
+        <v>-54.4966637958712</v>
       </c>
       <c r="L695" t="inlineStr">
         <is>
-          <t>b_canaleta3empe</t>
+          <t>b_canaleta1empe</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>b_talude1deitado</t>
+          <t>b_canaleta2empe</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>-3.12243888888889</v>
+        <v>-3.12229305555555</v>
       </c>
       <c r="C696" t="n">
-        <v>-41.7643208333334</v>
+        <v>-41.764675</v>
       </c>
       <c r="D696" t="n">
         <v>77</v>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>[-41.76432083333335, -3.1224388888888903]</t>
+          <t>[-41.764675, -3.122293055555555]</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>[(-3.1224388888888903, -41.76432083333335), (-3.1224388888888903, -41.76431183692718)]</t>
+          <t>[(-3.122293055555555, -41.764675), (-3.122293055555555, -41.7645166102891)]</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>[(-3.1224388888888903, -41.76432083333335), (-3.1208630152664005, -41.76432083333335)]</t>
+          <t>[(-3.122293055555555, -41.764675), (-3.1222840121182087, -41.764675)]</t>
         </is>
       </c>
       <c r="H696" t="n">
-        <v>174.256273563526</v>
+        <v>1</v>
       </c>
       <c r="I696" t="n">
-        <v>1</v>
+        <v>17.6058633850347</v>
       </c>
       <c r="J696" t="n">
-        <v>71.00099999957679</v>
+        <v>87.20775000031222</v>
       </c>
       <c r="K696" t="n">
-        <v>17.59948914535294</v>
+        <v>-21.7677892199783</v>
       </c>
       <c r="L696" t="inlineStr">
         <is>
-          <t>b_talude1deitado</t>
+          <t>b_canaleta2empe</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>b_talude1empe</t>
+          <t>b_canaleta3empe</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>-3.12225972222222</v>
+        <v>-3.12229305555555</v>
       </c>
       <c r="C697" t="n">
-        <v>-41.7651097222223</v>
+        <v>-41.7643652777778</v>
       </c>
       <c r="D697" t="n">
         <v>77</v>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>[-41.76510972222225, -3.1222597222222204]</t>
+          <t>[-41.7643652777778, -3.122293055555555]</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>[(-3.1222597222222204, -41.76510972222225), (-3.1222597222222204, -41.76475672068792)]</t>
+          <t>[(-3.122293055555555, -41.7643652777778), (-3.122293055555555, -41.76420686376592)]</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>[(-3.1222597222222204, -41.76510972222225), (-3.122250678737317, -41.76510972222225)]</t>
+          <t>[(-3.122293055555555, -41.7643652777778), (-3.122284012118205, -41.7643652777778)]</t>
         </is>
       </c>
       <c r="H697" t="n">
         <v>1</v>
       </c>
       <c r="I697" t="n">
-        <v>39.2380095193426</v>
+        <v>17.6085645678712</v>
       </c>
       <c r="J697" t="n">
-        <v>90.91214999994166</v>
+        <v>87.20775000031222</v>
       </c>
       <c r="K697" t="n">
-        <v>-70.08919366326352</v>
+        <v>12.65928166833888</v>
       </c>
       <c r="L697" t="inlineStr">
         <is>
-          <t>b_talude1empe</t>
+          <t>b_canaleta3empe</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>b_talude2deitado</t>
+          <t>b_talude1deitado</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>-3.12207916666667</v>
+        <v>-3.12243888888889</v>
       </c>
       <c r="C698" t="n">
-        <v>-41.7651166666666</v>
+        <v>-41.7643208333334</v>
       </c>
       <c r="D698" t="n">
         <v>77</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>[-41.76511666666665, -3.122079166666665]</t>
+          <t>[-41.76432083333335, -3.1224388888888903]</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>[(-3.122079166666665, -41.76511666666665), (-3.122079166666665, -41.76510767025198)]</t>
+          <t>[(-3.1224388888888903, -41.76432083333335), (-3.1224388888888903, -41.76431183692718)]</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>[(-3.122079166666665, -41.76511666666665), (-3.1218614523950214, -41.76511666666665)]</t>
+          <t>[(-3.1224388888888903, -41.76432083333335), (-3.1208630152664005, -41.76432083333335)]</t>
         </is>
       </c>
       <c r="H698" t="n">
-        <v>24.0743149462092</v>
+        <v>174.256273563526</v>
       </c>
       <c r="I698" t="n">
         <v>1</v>
       </c>
       <c r="J698" t="n">
-        <v>110.9776499993082</v>
+        <v>71.00099999957679</v>
       </c>
       <c r="K698" t="n">
-        <v>-70.86110106644202</v>
+        <v>17.59948914535294</v>
       </c>
       <c r="L698" t="inlineStr">
         <is>
-          <t>b_talude2deitado</t>
+          <t>b_talude1deitado</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>b_talude2empe</t>
+          <t>b_talude1empe</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>-3.12239861111111</v>
+        <v>-3.12225972222222</v>
       </c>
       <c r="C699" t="n">
-        <v>-41.7635291666667</v>
+        <v>-41.7651097222223</v>
       </c>
       <c r="D699" t="n">
         <v>77</v>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>[-41.76352916666665, -3.1223986111111097]</t>
+          <t>[-41.76510972222225, -3.1222597222222204]</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>[(-3.1223986111111097, -41.76352916666665), (-3.1223986111111097, -41.763454088665554)]</t>
+          <t>[(-3.1222597222222204, -41.76510972222225), (-3.1222597222222204, -41.76475672068792)]</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>[(-3.1223986111111097, -41.76352916666665), (-3.1223895676830753, -41.76352916666665)]</t>
+          <t>[(-3.1222597222222204, -41.76510972222225), (-3.122250678737317, -41.76510972222225)]</t>
         </is>
       </c>
       <c r="H699" t="n">
         <v>1</v>
       </c>
       <c r="I699" t="n">
-        <v>8.345320482737019</v>
+        <v>39.2380095193426</v>
       </c>
       <c r="J699" t="n">
-        <v>75.47714999979119</v>
+        <v>90.91214999994166</v>
       </c>
       <c r="K699" t="n">
-        <v>105.5969349242445</v>
+        <v>-70.08919366326352</v>
       </c>
       <c r="L699" t="inlineStr">
         <is>
-          <t>b_talude2empe</t>
+          <t>b_talude1empe</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>b_talude3deitado</t>
+          <t>b_talude2deitado</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>-3.12203333333333</v>
+        <v>-3.12207916666667</v>
       </c>
       <c r="C700" t="n">
         <v>-41.7651166666666</v>
@@ -34012,165 +34012,165 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>[-41.76511666666665, -3.12203333333333]</t>
+          <t>[-41.76511666666665, -3.122079166666665]</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>[(-3.12203333333333, -41.76511666666665), (-3.12203333333333, -41.76510767025232)]</t>
+          <t>[(-3.122079166666665, -41.76511666666665), (-3.122079166666665, -41.76510767025198)]</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>[(-3.12203333333333, -41.76511666666665), (-3.1218212850596787, -41.76511666666665)]</t>
+          <t>[(-3.122079166666665, -41.76511666666665), (-3.1218614523950214, -41.76511666666665)]</t>
         </is>
       </c>
       <c r="H700" t="n">
-        <v>23.4477826416907</v>
+        <v>24.0743149462092</v>
       </c>
       <c r="I700" t="n">
         <v>1</v>
       </c>
       <c r="J700" t="n">
-        <v>116.0712000000695</v>
+        <v>110.9776499993082</v>
       </c>
       <c r="K700" t="n">
         <v>-70.86110106644202</v>
       </c>
       <c r="L700" t="inlineStr">
         <is>
-          <t>b_talude3deitado</t>
+          <t>b_talude2deitado</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>cd_canaleta1deitado</t>
+          <t>b_talude2empe</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>-3.12329027777778</v>
+        <v>-3.12239861111111</v>
       </c>
       <c r="C701" t="n">
-        <v>-41.7655361111111</v>
+        <v>-41.7635291666667</v>
       </c>
       <c r="D701" t="n">
         <v>77</v>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>[-41.7655361111111, -3.1232902777777802]</t>
+          <t>[-41.76352916666665, -3.1223986111111097]</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>[(-3.1232902777777802, -41.7655361111111), (-3.1232902777777802, -41.765527114685085)]</t>
+          <t>[(-3.1223986111111097, -41.76352916666665), (-3.1223986111111097, -41.763454088665554)]</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>[(-3.1232902777777802, -41.7655361111111), (-3.1231954059904874, -41.7655361111111)]</t>
+          <t>[(-3.1223986111111097, -41.76352916666665), (-3.1223895676830753, -41.76352916666665)]</t>
         </is>
       </c>
       <c r="H701" t="n">
-        <v>10.4906918800152</v>
+        <v>1</v>
       </c>
       <c r="I701" t="n">
-        <v>1</v>
+        <v>8.345320482737019</v>
       </c>
       <c r="J701" t="n">
-        <v>-23.61555000053719</v>
+        <v>75.47714999979119</v>
       </c>
       <c r="K701" t="n">
-        <v>-117.4843091854559</v>
+        <v>105.5969349242445</v>
       </c>
       <c r="L701" t="inlineStr">
         <is>
-          <t>cd_canaleta1deitado</t>
+          <t>b_talude2empe</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>cd_canaleta1empe</t>
+          <t>b_talude3deitado</t>
         </is>
       </c>
       <c r="B702" t="n">
-        <v>-3.12316944444444</v>
+        <v>-3.12203333333333</v>
       </c>
       <c r="C702" t="n">
-        <v>-41.7655819444444</v>
+        <v>-41.7651166666666</v>
       </c>
       <c r="D702" t="n">
         <v>77</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>[-41.76558194444445, -3.123169444444445]</t>
+          <t>[-41.76511666666665, -3.12203333333333]</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>[(-3.123169444444445, -41.76558194444445), (-3.123169444444445, -41.76534295418944)]</t>
+          <t>[(-3.12203333333333, -41.76511666666665), (-3.12203333333333, -41.76510767025232)]</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>[(-3.123169444444445, -41.76558194444445), (-3.1231604009919396, -41.76558194444445)]</t>
+          <t>[(-3.12203333333333, -41.76511666666665), (-3.1218212850596787, -41.76511666666665)]</t>
         </is>
       </c>
       <c r="H702" t="n">
-        <v>1</v>
+        <v>23.4477826416907</v>
       </c>
       <c r="I702" t="n">
-        <v>26.5650228690678</v>
+        <v>1</v>
       </c>
       <c r="J702" t="n">
-        <v>-10.1870999997953</v>
+        <v>116.0712000000695</v>
       </c>
       <c r="K702" t="n">
-        <v>-122.5788981472126</v>
+        <v>-70.86110106644202</v>
       </c>
       <c r="L702" t="inlineStr">
         <is>
-          <t>cd_canaleta1empe</t>
+          <t>b_talude3deitado</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>cd_canaleta2deitado</t>
+          <t>cd_canaleta1deitado</t>
         </is>
       </c>
       <c r="B703" t="n">
         <v>-3.12329027777778</v>
       </c>
       <c r="C703" t="n">
-        <v>-41.7651361111111</v>
+        <v>-41.7655361111111</v>
       </c>
       <c r="D703" t="n">
         <v>77</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>[-41.765136111111104, -3.1232902777777802]</t>
+          <t>[-41.7655361111111, -3.1232902777777802]</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>[(-3.1232902777777802, -41.765136111111104), (-3.1232902777777802, -41.76512711468703)]</t>
+          <t>[(-3.1232902777777802, -41.7655361111111), (-3.1232902777777802, -41.765527114685085)]</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>[(-3.1232902777777802, -41.765136111111104), (-3.122966725829481, -41.765136111111104)]</t>
+          <t>[(-3.1232902777777802, -41.7655361111111), (-3.1231954059904874, -41.7655361111111)]</t>
         </is>
       </c>
       <c r="H703" t="n">
-        <v>35.7775887565438</v>
+        <v>10.4906918800152</v>
       </c>
       <c r="I703" t="n">
         <v>1</v>
@@ -34179,286 +34179,286 @@
         <v>-23.61555000053719</v>
       </c>
       <c r="K703" t="n">
-        <v>-73.02244184573114</v>
+        <v>-117.4843091854559</v>
       </c>
       <c r="L703" t="inlineStr">
         <is>
-          <t>cd_canaleta2deitado</t>
+          <t>cd_canaleta1deitado</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>cd_canaleta2empe</t>
+          <t>cd_canaleta1empe</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>-3.12295277777778</v>
+        <v>-3.12316944444444</v>
       </c>
       <c r="C704" t="n">
-        <v>-41.7652194444444</v>
+        <v>-41.7655819444444</v>
       </c>
       <c r="D704" t="n">
         <v>77</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>[-41.7652194444444, -3.1229527777777797]</t>
+          <t>[-41.76558194444445, -3.123169444444445]</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>[(-3.1229527777777797, -41.7652194444444), (-3.1229527777777797, -41.764541424908)]</t>
+          <t>[(-3.123169444444445, -41.76558194444445), (-3.123169444444445, -41.76534295418944)]</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>[(-3.1229527777777797, -41.7652194444444), (-3.122943734132839, -41.7652194444444)]</t>
+          <t>[(-3.123169444444445, -41.76558194444445), (-3.1231604009919396, -41.76558194444445)]</t>
         </is>
       </c>
       <c r="H704" t="n">
         <v>1</v>
       </c>
       <c r="I704" t="n">
-        <v>75.36545028155891</v>
+        <v>26.5650228690678</v>
       </c>
       <c r="J704" t="n">
-        <v>13.89149999942475</v>
+        <v>-10.1870999997953</v>
       </c>
       <c r="K704" t="n">
-        <v>-82.28533087105599</v>
+        <v>-122.5788981472126</v>
       </c>
       <c r="L704" t="inlineStr">
         <is>
-          <t>cd_canaleta2empe</t>
+          <t>cd_canaleta1empe</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>cd_canaleta3deitado</t>
+          <t>cd_canaleta2deitado</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>-3.12314722222222</v>
+        <v>-3.12329027777778</v>
       </c>
       <c r="C705" t="n">
-        <v>-41.7648569444445</v>
+        <v>-41.7651361111111</v>
       </c>
       <c r="D705" t="n">
         <v>77</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>[-41.764856944444446, -3.12314722222222]</t>
+          <t>[-41.765136111111104, -3.1232902777777802]</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>[(-3.12314722222222, -41.764856944444446), (-3.12314722222222, -41.76484794802086)]</t>
+          <t>[(-3.1232902777777802, -41.765136111111104), (-3.1232902777777802, -41.76512711468703)]</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>[(-3.12314722222222, -41.764856944444446), (-3.122910145545491, -41.764856944444446)]</t>
+          <t>[(-3.1232902777777802, -41.765136111111104), (-3.122966725829481, -41.765136111111104)]</t>
         </is>
       </c>
       <c r="H705" t="n">
-        <v>26.2153631644481</v>
+        <v>35.7775887565438</v>
       </c>
       <c r="I705" t="n">
         <v>1</v>
       </c>
       <c r="J705" t="n">
-        <v>-7.717500000075235</v>
+        <v>-23.61555000053719</v>
       </c>
       <c r="K705" t="n">
-        <v>-41.99176360674637</v>
+        <v>-73.02244184573114</v>
       </c>
       <c r="L705" t="inlineStr">
         <is>
-          <t>cd_canaleta3deitado</t>
+          <t>cd_canaleta2deitado</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>cd_canaleta3empe</t>
+          <t>cd_canaleta2empe</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>-3.12293611111111</v>
+        <v>-3.12295277777778</v>
       </c>
       <c r="C706" t="n">
-        <v>-41.7649736111111</v>
+        <v>-41.7652194444444</v>
       </c>
       <c r="D706" t="n">
         <v>77</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>[-41.7649736111111, -3.12293611111111]</t>
+          <t>[-41.7652194444444, -3.1229527777777797]</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>[(-3.12293611111111, -41.7649736111111), (-3.12293611111111, -41.76420666597282)]</t>
+          <t>[(-3.1229527777777797, -41.7652194444444), (-3.1229527777777797, -41.764541424908)]</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>[(-3.12293611111111, -41.7649736111111), (-3.12292706740476, -41.7649736111111)]</t>
+          <t>[(-3.1229527777777797, -41.7652194444444), (-3.122943734132839, -41.7652194444444)]</t>
         </is>
       </c>
       <c r="H706" t="n">
         <v>1</v>
       </c>
       <c r="I706" t="n">
-        <v>85.2500016533164</v>
+        <v>75.36545028155891</v>
       </c>
       <c r="J706" t="n">
-        <v>15.7436999998317</v>
+        <v>13.89149999942475</v>
       </c>
       <c r="K706" t="n">
-        <v>-54.95980823983178</v>
+        <v>-82.28533087105599</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
-          <t>cd_canaleta3empe</t>
+          <t>cd_canaleta2empe</t>
         </is>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>cd_canaleta4deitado</t>
+          <t>cd_canaleta3deitado</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>-3.12315</v>
+        <v>-3.12314722222222</v>
       </c>
       <c r="C707" t="n">
-        <v>-41.7645208333333</v>
+        <v>-41.7648569444445</v>
       </c>
       <c r="D707" t="n">
         <v>77</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>[-41.7645208333333, -3.12315]</t>
+          <t>[-41.764856944444446, -3.12314722222222]</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>[(-3.12315, -41.7645208333333), (-3.12315, -41.764511836910685)]</t>
+          <t>[(-3.12314722222222, -41.764856944444446), (-3.12314722222222, -41.76484794802086)]</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>[(-3.12315, -41.7645208333333), (-3.1227957355026765, -41.7645208333333)]</t>
+          <t>[(-3.12314722222222, -41.764856944444446), (-3.122910145545491, -41.764856944444446)]</t>
         </is>
       </c>
       <c r="H707" t="n">
-        <v>39.1737077318761</v>
+        <v>26.2153631644481</v>
       </c>
       <c r="I707" t="n">
         <v>1</v>
       </c>
       <c r="J707" t="n">
-        <v>-8.026200000299344</v>
+        <v>-7.717500000075235</v>
       </c>
       <c r="K707" t="n">
-        <v>-4.631444513057334</v>
+        <v>-41.99176360674637</v>
       </c>
       <c r="L707" t="inlineStr">
         <is>
-          <t>cd_canaleta4deitado</t>
+          <t>cd_canaleta3deitado</t>
         </is>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>cd_canaleta4empe</t>
+          <t>cd_canaleta3empe</t>
         </is>
       </c>
       <c r="B708" t="n">
-        <v>-3.12306944444444</v>
+        <v>-3.12293611111111</v>
       </c>
       <c r="C708" t="n">
-        <v>-41.7646777777778</v>
+        <v>-41.7649736111111</v>
       </c>
       <c r="D708" t="n">
         <v>77</v>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>[-41.7646777777778, -3.123069444444445]</t>
+          <t>[-41.7649736111111, -3.12293611111111]</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>[(-3.123069444444445, -41.7646777777778), (-3.123069444444445, -41.76451660918169)]</t>
+          <t>[(-3.12293611111111, -41.7649736111111), (-3.12293611111111, -41.76420666597282)]</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>[(-3.123069444444445, -41.7646777777778), (-3.1230604010068057, -41.7646777777778)]</t>
+          <t>[(-3.12293611111111, -41.7649736111111), (-3.12292706740476, -41.7649736111111)]</t>
         </is>
       </c>
       <c r="H708" t="n">
         <v>1</v>
       </c>
       <c r="I708" t="n">
-        <v>17.9147381814938</v>
+        <v>85.2500016533164</v>
       </c>
       <c r="J708" t="n">
-        <v>0.9261000001788009</v>
+        <v>15.7436999998317</v>
       </c>
       <c r="K708" t="n">
-        <v>-22.07655219025344</v>
+        <v>-54.95980823983178</v>
       </c>
       <c r="L708" t="inlineStr">
         <is>
-          <t>cd_canaleta4empe</t>
+          <t>cd_canaleta3empe</t>
         </is>
       </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>cd_canaleta5deitado</t>
+          <t>cd_canaleta4deitado</t>
         </is>
       </c>
       <c r="B709" t="n">
         <v>-3.12315</v>
       </c>
       <c r="C709" t="n">
-        <v>-41.7642486111112</v>
+        <v>-41.7645208333333</v>
       </c>
       <c r="D709" t="n">
         <v>77</v>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>[-41.76424861111115, -3.12315]</t>
+          <t>[-41.7645208333333, -3.12315]</t>
         </is>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>[(-3.12315, -41.76424861111115), (-3.12315, -41.76423961468649)]</t>
+          <t>[(-3.12315, -41.7645208333333), (-3.12315, -41.764511836910685)]</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>[(-3.12315, -41.76424861111115), (-3.123035645368097, -41.76424861111115)]</t>
+          <t>[(-3.12315, -41.7645208333333), (-3.1227957355026765, -41.7645208333333)]</t>
         </is>
       </c>
       <c r="H709" t="n">
-        <v>12.6450574952605</v>
+        <v>39.1737077318761</v>
       </c>
       <c r="I709" t="n">
         <v>1</v>
@@ -34467,838 +34467,838 @@
         <v>-8.026200000299344</v>
       </c>
       <c r="K709" t="n">
-        <v>25.62732630142429</v>
+        <v>-4.631444513057334</v>
       </c>
       <c r="L709" t="inlineStr">
         <is>
-          <t>cd_canaleta5deitado</t>
+          <t>cd_canaleta4deitado</t>
         </is>
       </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>cd_canaleta5empe</t>
+          <t>cd_canaleta4empe</t>
         </is>
       </c>
       <c r="B710" t="n">
-        <v>-3.12281666666666</v>
+        <v>-3.12306944444444</v>
       </c>
       <c r="C710" t="n">
-        <v>-41.7646763888889</v>
+        <v>-41.7646777777778</v>
       </c>
       <c r="D710" t="n">
         <v>77</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>[-41.7646763888889, -3.1228166666666652]</t>
+          <t>[-41.7646777777778, -3.123069444444445]</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>[(-3.1228166666666652, -41.7646763888889), (-3.1228166666666652, -41.76451519644929)]</t>
+          <t>[(-3.123069444444445, -41.7646777777778), (-3.123069444444445, -41.76451660918169)]</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>[(-3.1228166666666652, -41.7646763888889), (-3.12280762322898, -41.7646763888889)]</t>
+          <t>[(-3.123069444444445, -41.7646777777778), (-3.1230604010068057, -41.7646777777778)]</t>
         </is>
       </c>
       <c r="H710" t="n">
         <v>1</v>
       </c>
       <c r="I710" t="n">
-        <v>17.9173927965757</v>
+        <v>17.9147381814938</v>
       </c>
       <c r="J710" t="n">
-        <v>29.01780000043686</v>
+        <v>0.9261000001788009</v>
       </c>
       <c r="K710" t="n">
-        <v>-21.92217070551077</v>
+        <v>-22.07655219025344</v>
       </c>
       <c r="L710" t="inlineStr">
         <is>
-          <t>cd_canaleta5empe</t>
+          <t>cd_canaleta4empe</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>cd_canaleta6deitado</t>
+          <t>cd_canaleta5deitado</t>
         </is>
       </c>
       <c r="B711" t="n">
-        <v>-3.12289861111111</v>
+        <v>-3.12315</v>
       </c>
       <c r="C711" t="n">
-        <v>-41.7645111111111</v>
+        <v>-41.7642486111112</v>
       </c>
       <c r="D711" t="n">
         <v>77</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>[-41.7645111111111, -3.1228986111111103]</t>
+          <t>[-41.76424861111115, -3.12315]</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>[(-3.1228986111111103, -41.7645111111111), (-3.1228986111111103, -41.76450211469548)]</t>
+          <t>[(-3.12315, -41.76424861111115), (-3.12315, -41.76423961468649)]</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>[(-3.1228986111111103, -41.7645111111111), (-3.121972613060575, -41.7645111111111)]</t>
+          <t>[(-3.12315, -41.76424861111115), (-3.123035645368097, -41.76424861111115)]</t>
         </is>
       </c>
       <c r="H711" t="n">
-        <v>102.394614467338</v>
+        <v>12.6450574952605</v>
       </c>
       <c r="I711" t="n">
         <v>1</v>
       </c>
       <c r="J711" t="n">
-        <v>19.91114999982199</v>
+        <v>-8.026200000299344</v>
       </c>
       <c r="K711" t="n">
-        <v>-3.550774128546486</v>
+        <v>25.62732630142429</v>
       </c>
       <c r="L711" t="inlineStr">
         <is>
-          <t>cd_canaleta6deitado</t>
+          <t>cd_canaleta5deitado</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>cd_canaleta6empe</t>
+          <t>cd_canaleta5empe</t>
         </is>
       </c>
       <c r="B712" t="n">
-        <v>-3.12307083333333</v>
+        <v>-3.12281666666666</v>
       </c>
       <c r="C712" t="n">
-        <v>-41.7643694444445</v>
+        <v>-41.7646763888889</v>
       </c>
       <c r="D712" t="n">
         <v>77</v>
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>[-41.7643694444445, -3.123070833333335]</t>
+          <t>[-41.7646763888889, -3.1228166666666652]</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>[(-3.123070833333335, -41.7643694444445), (-3.123070833333335, -41.764205497079274)]</t>
+          <t>[(-3.1228166666666652, -41.7646763888889), (-3.1228166666666652, -41.76451519644929)]</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>[(-3.123070833333335, -41.7643694444445), (-3.1230617898952655, -41.7643694444445)]</t>
+          <t>[(-3.1228166666666652, -41.7646763888889), (-3.12280762322898, -41.7646763888889)]</t>
         </is>
       </c>
       <c r="H712" t="n">
         <v>1</v>
       </c>
       <c r="I712" t="n">
-        <v>18.2236129780023</v>
+        <v>17.9173927965757</v>
       </c>
       <c r="J712" t="n">
-        <v>0.7717500000420703</v>
+        <v>29.01780000043686</v>
       </c>
       <c r="K712" t="n">
-        <v>12.19613721332108</v>
+        <v>-21.92217070551077</v>
       </c>
       <c r="L712" t="inlineStr">
         <is>
-          <t>cd_canaleta6empe</t>
+          <t>cd_canaleta5empe</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>cd_canaleta7deitado</t>
+          <t>cd_canaleta6deitado</t>
         </is>
       </c>
       <c r="B713" t="n">
-        <v>-3.1229</v>
+        <v>-3.12289861111111</v>
       </c>
       <c r="C713" t="n">
-        <v>-41.7637708333334</v>
+        <v>-41.7645111111111</v>
       </c>
       <c r="D713" t="n">
         <v>77</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>[-41.76377083333335, -3.1229]</t>
+          <t>[-41.7645111111111, -3.1228986111111103]</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>[(-3.1229, -41.76377083333335), (-3.1229, -41.763761836913815)]</t>
+          <t>[(-3.1228986111111103, -41.7645111111111), (-3.1228986111111103, -41.76450211469548)]</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>[(-3.1229, -41.76377083333335), (-3.122434213945805, -41.76377083333335)]</t>
+          <t>[(-3.1228986111111103, -41.7645111111111), (-3.121972613060575, -41.7645111111111)]</t>
         </is>
       </c>
       <c r="H713" t="n">
-        <v>51.505490345839</v>
+        <v>102.394614467338</v>
       </c>
       <c r="I713" t="n">
         <v>1</v>
       </c>
       <c r="J713" t="n">
-        <v>19.75679999968526</v>
+        <v>19.91114999982199</v>
       </c>
       <c r="K713" t="n">
-        <v>78.7345567361911</v>
+        <v>-3.550774128546486</v>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>cd_canaleta7deitado</t>
+          <t>cd_canaleta6deitado</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>cd_canaleta7empe</t>
+          <t>cd_canaleta6empe</t>
         </is>
       </c>
       <c r="B714" t="n">
-        <v>-3.12281805555555</v>
+        <v>-3.12307083333333</v>
       </c>
       <c r="C714" t="n">
-        <v>-41.7643666666667</v>
+        <v>-41.7643694444445</v>
       </c>
       <c r="D714" t="n">
         <v>77</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>[-41.7643666666667, -3.1228180555555554]</t>
+          <t>[-41.7643694444445, -3.123070833333335]</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>[(-3.1228180555555554, -41.7643666666667), (-3.1228180555555554, -41.764208276877156)]</t>
+          <t>[(-3.123070833333335, -41.7643694444445), (-3.123070833333335, -41.764205497079274)]</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>[(-3.1228180555555554, -41.7643666666667), (-3.122809012118298, -41.7643666666667)]</t>
+          <t>[(-3.123070833333335, -41.7643694444445), (-3.1230617898952655, -41.7643694444445)]</t>
         </is>
       </c>
       <c r="H714" t="n">
         <v>1</v>
       </c>
       <c r="I714" t="n">
-        <v>17.6058633850347</v>
+        <v>18.2236129780023</v>
       </c>
       <c r="J714" t="n">
-        <v>28.86345000030013</v>
+        <v>0.7717500000420703</v>
       </c>
       <c r="K714" t="n">
-        <v>12.50490018280642</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>cd_canaleta7empe</t>
+          <t>cd_canaleta6empe</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>cd_canaleta8deitado</t>
+          <t>cd_canaleta7deitado</t>
         </is>
       </c>
       <c r="B715" t="n">
-        <v>-3.12296805555556</v>
+        <v>-3.1229</v>
       </c>
       <c r="C715" t="n">
-        <v>-41.7658888888889</v>
+        <v>-41.7637708333334</v>
       </c>
       <c r="D715" t="n">
         <v>77</v>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>[-41.7658888888889, -3.1229680555555603]</t>
+          <t>[-41.76377083333335, -3.1229]</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>[(-3.1229680555555603, -41.7658888888889), (-3.1229680555555603, -41.76587989246805)]</t>
+          <t>[(-3.1229, -41.76377083333335), (-3.1229, -41.763761836913815)]</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>[(-3.1229680555555603, -41.7658888888889), (-3.12258872252168, -41.7658888888889)]</t>
+          <t>[(-3.1229, -41.76377083333335), (-3.122434213945805, -41.76377083333335)]</t>
         </is>
       </c>
       <c r="H715" t="n">
-        <v>41.9457254666118</v>
+        <v>51.505490345839</v>
       </c>
       <c r="I715" t="n">
         <v>1</v>
       </c>
       <c r="J715" t="n">
-        <v>12.19364999920388</v>
+        <v>19.75679999968526</v>
       </c>
       <c r="K715" t="n">
-        <v>-156.6972060771017</v>
+        <v>78.7345567361911</v>
       </c>
       <c r="L715" t="inlineStr">
         <is>
-          <t>cd_canaleta8deitado</t>
+          <t>cd_canaleta7deitado</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>cd_canaleta8empe</t>
+          <t>cd_canaleta7empe</t>
         </is>
       </c>
       <c r="B716" t="n">
-        <v>-3.12292916666667</v>
+        <v>-3.12281805555555</v>
       </c>
       <c r="C716" t="n">
-        <v>-41.7639777777778</v>
+        <v>-41.7643666666667</v>
       </c>
       <c r="D716" t="n">
         <v>77</v>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>[-41.7639777777778, -3.12292916666667]</t>
+          <t>[-41.7643666666667, -3.1228180555555554]</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>[(-3.12292916666667, -41.7639777777778), (-3.12292916666667, -41.76357485634099)]</t>
+          <t>[(-3.1228180555555554, -41.7643666666667), (-3.1228180555555554, -41.764208276877156)]</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>[(-3.12292916666667, -41.7639777777778), (-3.1229201231638353, -41.7639777777778)]</t>
+          <t>[(-3.1228180555555554, -41.7643666666667), (-3.122809012118298, -41.7643666666667)]</t>
         </is>
       </c>
       <c r="H716" t="n">
         <v>1</v>
       </c>
       <c r="I716" t="n">
-        <v>44.7868454542777</v>
+        <v>17.6058633850347</v>
       </c>
       <c r="J716" t="n">
-        <v>16.51544999933089</v>
+        <v>28.86345000030013</v>
       </c>
       <c r="K716" t="n">
-        <v>55.73171565327769</v>
+        <v>12.50490018280642</v>
       </c>
       <c r="L716" t="inlineStr">
         <is>
-          <t>cd_canaleta8empe</t>
+          <t>cd_canaleta7empe</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>cd_canaleta9deitado</t>
+          <t>cd_canaleta8deitado</t>
         </is>
       </c>
       <c r="B717" t="n">
-        <v>-3.12254861111111</v>
+        <v>-3.12296805555556</v>
       </c>
       <c r="C717" t="n">
-        <v>-41.7660513888889</v>
+        <v>-41.7658888888889</v>
       </c>
       <c r="D717" t="n">
         <v>77</v>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>[-41.7660513888889, -3.1225486111111103]</t>
+          <t>[-41.7658888888889, -3.1229680555555603]</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>[(-3.1225486111111103, -41.7660513888889), (-3.1225486111111103, -41.76604239246878)]</t>
+          <t>[(-3.1229680555555603, -41.7658888888889), (-3.1229680555555603, -41.76587989246805)]</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>[(-3.1225486111111103, -41.7660513888889), (-3.1225011135419023, -41.7660513888889)]</t>
+          <t>[(-3.1229680555555603, -41.7658888888889), (-3.12258872252168, -41.7658888888889)]</t>
         </is>
       </c>
       <c r="H717" t="n">
-        <v>5.25216579986803</v>
+        <v>41.9457254666118</v>
       </c>
       <c r="I717" t="n">
         <v>1</v>
       </c>
       <c r="J717" t="n">
-        <v>58.80734999983004</v>
+        <v>12.19364999920388</v>
       </c>
       <c r="K717" t="n">
-        <v>-174.7598396830011</v>
+        <v>-156.6972060771017</v>
       </c>
       <c r="L717" t="inlineStr">
         <is>
-          <t>cd_canaleta9deitado</t>
+          <t>cd_canaleta8deitado</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>cd_canaleta9empe</t>
+          <t>cd_canaleta8empe</t>
         </is>
       </c>
       <c r="B718" t="n">
-        <v>-3.12275694444445</v>
+        <v>-3.12292916666667</v>
       </c>
       <c r="C718" t="n">
-        <v>-41.766075</v>
+        <v>-41.7639777777778</v>
       </c>
       <c r="D718" t="n">
         <v>77</v>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>[-41.766075, -3.122756944444445]</t>
+          <t>[-41.7639777777778, -3.12292916666667]</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>[(-3.122756944444445, -41.766075), (-3.122756944444445, -41.76565540602036)]</t>
+          <t>[(-3.12292916666667, -41.7639777777778), (-3.12292916666667, -41.76357485634099)]</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>[(-3.122756944444445, -41.766075), (-3.122747900935032, -41.766075)]</t>
+          <t>[(-3.12292916666667, -41.7639777777778), (-3.1229201231638353, -41.7639777777778)]</t>
         </is>
       </c>
       <c r="H718" t="n">
         <v>1</v>
       </c>
       <c r="I718" t="n">
-        <v>46.6400942320942</v>
+        <v>44.7868454542777</v>
       </c>
       <c r="J718" t="n">
-        <v>35.65484999906146</v>
+        <v>16.51544999933089</v>
       </c>
       <c r="K718" t="n">
-        <v>-177.3843249070406</v>
+        <v>55.73171565327769</v>
       </c>
       <c r="L718" t="inlineStr">
         <is>
-          <t>cd_canaleta9empe</t>
+          <t>cd_canaleta8empe</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>cd_canaleta10deitado</t>
+          <t>cd_canaleta9deitado</t>
         </is>
       </c>
       <c r="B719" t="n">
-        <v>-3.12297083333333</v>
+        <v>-3.12254861111111</v>
       </c>
       <c r="C719" t="n">
-        <v>-41.7656152777778</v>
+        <v>-41.7660513888889</v>
       </c>
       <c r="D719" t="n">
         <v>77</v>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>[-41.7656152777778, -3.1229708333333352]</t>
+          <t>[-41.7660513888889, -3.1225486111111103]</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>[(-3.1229708333333352, -41.7656152777778), (-3.1229708333333352, -41.76560628135429)]</t>
+          <t>[(-3.1225486111111103, -41.7660513888889), (-3.1225486111111103, -41.76604239246878)]</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>[(-3.1229708333333352, -41.7656152777778), (-3.1229010489607996, -41.7656152777778)]</t>
+          <t>[(-3.1225486111111103, -41.7660513888889), (-3.1225011135419023, -41.7660513888889)]</t>
         </is>
       </c>
       <c r="H719" t="n">
-        <v>7.71658642484199</v>
+        <v>5.25216579986803</v>
       </c>
       <c r="I719" t="n">
         <v>1</v>
       </c>
       <c r="J719" t="n">
-        <v>11.88495000006552</v>
+        <v>58.80734999983004</v>
       </c>
       <c r="K719" t="n">
-        <v>-126.2840537660304</v>
+        <v>-174.7598396830011</v>
       </c>
       <c r="L719" t="inlineStr">
         <is>
-          <t>cd_canaleta10deitado</t>
+          <t>cd_canaleta9deitado</t>
         </is>
       </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>cd_talude1empe</t>
+          <t>cd_canaleta9empe</t>
         </is>
       </c>
       <c r="B720" t="n">
-        <v>-3.12298611111111</v>
+        <v>-3.12275694444445</v>
       </c>
       <c r="C720" t="n">
-        <v>-41.7635958333333</v>
+        <v>-41.766075</v>
       </c>
       <c r="D720" t="n">
         <v>77</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>[-41.7635958333333, -3.1229861111111097]</t>
+          <t>[-41.766075, -3.122756944444445]</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>[(-3.1229861111111097, -41.7635958333333), (-3.1229861111111097, -41.762928923078356)]</t>
+          <t>[(-3.122756944444445, -41.766075), (-3.122756944444445, -41.76565540602036)]</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>[(-3.1229861111111097, -41.7635958333333), (-3.1229770674733124, -41.7635958333333)]</t>
+          <t>[(-3.122756944444445, -41.766075), (-3.122747900935032, -41.766075)]</t>
         </is>
       </c>
       <c r="H720" t="n">
         <v>1</v>
       </c>
       <c r="I720" t="n">
-        <v>74.13059267213769</v>
+        <v>46.6400942320942</v>
       </c>
       <c r="J720" t="n">
-        <v>10.1870999997953</v>
+        <v>35.65484999906146</v>
       </c>
       <c r="K720" t="n">
-        <v>98.18662370872346</v>
+        <v>-177.3843249070406</v>
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>cd_talude1empe</t>
+          <t>cd_canaleta9empe</t>
         </is>
       </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>ef_canaleta1empe</t>
+          <t>cd_canaleta10deitado</t>
         </is>
       </c>
       <c r="B721" t="n">
-        <v>-3.12370694444444</v>
+        <v>-3.12297083333333</v>
       </c>
       <c r="C721" t="n">
-        <v>-41.7653430555555</v>
+        <v>-41.7656152777778</v>
       </c>
       <c r="D721" t="n">
         <v>77</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>[-41.76534305555555, -3.1237069444444403]</t>
+          <t>[-41.7656152777778, -3.1229708333333352]</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>[(-3.1237069444444403, -41.76534305555555), (-3.1237069444444403, -41.76464002112494)]</t>
+          <t>[(-3.1229708333333352, -41.7656152777778), (-3.1229708333333352, -41.76560628135429)]</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>[(-3.1237069444444403, -41.76534305555555), (-3.1236979007830614, -41.76534305555555)]</t>
+          <t>[(-3.1229708333333352, -41.7656152777778), (-3.1229010489607996, -41.7656152777778)]</t>
         </is>
       </c>
       <c r="H721" t="n">
-        <v>1</v>
+        <v>7.71658642484199</v>
       </c>
       <c r="I721" t="n">
-        <v>78.1459320571828</v>
+        <v>1</v>
       </c>
       <c r="J721" t="n">
-        <v>-69.92054999980414</v>
+        <v>11.88495000006552</v>
       </c>
       <c r="K721" t="n">
-        <v>-96.02528292943434</v>
+        <v>-126.2840537660304</v>
       </c>
       <c r="L721" t="inlineStr">
         <is>
-          <t>ef_canaleta1empe</t>
+          <t>cd_canaleta10deitado</t>
         </is>
       </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>ef_canaleta2deitado</t>
+          <t>cd_talude1empe</t>
         </is>
       </c>
       <c r="B722" t="n">
-        <v>-3.12350277777778</v>
+        <v>-3.12298611111111</v>
       </c>
       <c r="C722" t="n">
-        <v>-41.7641416666667</v>
+        <v>-41.7635958333333</v>
       </c>
       <c r="D722" t="n">
         <v>77</v>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>[-41.764141666666646, -3.12350277777778]</t>
+          <t>[-41.7635958333333, -3.1229861111111097]</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>[(-3.12350277777778, -41.764141666666646), (-3.12350277777778, -41.76413267025225)]</t>
+          <t>[(-3.1229861111111097, -41.7635958333333), (-3.1229861111111097, -41.762928923078356)]</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>[(-3.12350277777778, -41.764141666666646), (-3.1218292865842563, -41.764141666666646)]</t>
+          <t>[(-3.1229861111111097, -41.7635958333333), (-3.1229770674733124, -41.7635958333333)]</t>
         </is>
       </c>
       <c r="H722" t="n">
-        <v>185.050590800252</v>
+        <v>1</v>
       </c>
       <c r="I722" t="n">
-        <v>1</v>
+        <v>74.13059267213769</v>
       </c>
       <c r="J722" t="n">
-        <v>-47.23110000058086</v>
+        <v>10.1870999997953</v>
       </c>
       <c r="K722" t="n">
-        <v>37.51470056105607</v>
+        <v>98.18662370872346</v>
       </c>
       <c r="L722" t="inlineStr">
         <is>
-          <t>ef_canaleta2deitado</t>
+          <t>cd_talude1empe</t>
         </is>
       </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>ef_canaleta2empe</t>
+          <t>ef_canaleta1empe</t>
         </is>
       </c>
       <c r="B723" t="n">
-        <v>-3.12355416666666</v>
+        <v>-3.12370694444444</v>
       </c>
       <c r="C723" t="n">
-        <v>-41.7649763888889</v>
+        <v>-41.7653430555555</v>
       </c>
       <c r="D723" t="n">
         <v>77</v>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>[-41.7649763888889, -3.123554166666665]</t>
+          <t>[-41.76534305555555, -3.1237069444444403]</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>[(-3.123554166666665, -41.7649763888889), (-3.123554166666665, -41.76457901506719)]</t>
+          <t>[(-3.1237069444444403, -41.76534305555555), (-3.1237069444444403, -41.76464002112494)]</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>[(-3.123554166666665, -41.7649763888889), (-3.1235451231660454, -41.7649763888889)]</t>
+          <t>[(-3.1237069444444403, -41.76534305555555), (-3.1236979007830614, -41.76534305555555)]</t>
         </is>
       </c>
       <c r="H723" t="n">
         <v>1</v>
       </c>
       <c r="I723" t="n">
-        <v>44.1701726245875</v>
+        <v>78.1459320571828</v>
       </c>
       <c r="J723" t="n">
-        <v>-52.94204999956953</v>
+        <v>-69.92054999980414</v>
       </c>
       <c r="K723" t="n">
-        <v>-55.26857120931711</v>
+        <v>-96.02528292943434</v>
       </c>
       <c r="L723" t="inlineStr">
         <is>
-          <t>ef_canaleta2empe</t>
+          <t>ef_canaleta1empe</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>ef_canaleta3deitado</t>
+          <t>ef_canaleta2deitado</t>
         </is>
       </c>
       <c r="B724" t="n">
-        <v>-3.12375277777778</v>
+        <v>-3.12350277777778</v>
       </c>
       <c r="C724" t="n">
-        <v>-41.7648611111112</v>
+        <v>-41.7641416666667</v>
       </c>
       <c r="D724" t="n">
         <v>77</v>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>[-41.76486111111115, -3.12375277777778]</t>
+          <t>[-41.764141666666646, -3.12350277777778]</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>[(-3.12375277777778, -41.76486111111115), (-3.12375277777778, -41.764852114682384)]</t>
+          <t>[(-3.12350277777778, -41.764141666666646), (-3.12350277777778, -41.76413267025225)]</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>[(-3.12375277777778, -41.76486111111115), (-3.1235184903762816, -41.76486111111115)]</t>
+          <t>[(-3.12350277777778, -41.764141666666646), (-3.1218292865842563, -41.764141666666646)]</t>
         </is>
       </c>
       <c r="H724" t="n">
-        <v>25.9069321832122</v>
+        <v>185.050590800252</v>
       </c>
       <c r="I724" t="n">
         <v>1</v>
       </c>
       <c r="J724" t="n">
-        <v>-75.01410000056546</v>
+        <v>-47.23110000058086</v>
       </c>
       <c r="K724" t="n">
-        <v>-42.45490806176417</v>
+        <v>37.51470056105607</v>
       </c>
       <c r="L724" t="inlineStr">
         <is>
-          <t>ef_canaleta3deitado</t>
+          <t>ef_canaleta2deitado</t>
         </is>
       </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>ef_canaleta3empe</t>
+          <t>ef_canaleta2empe</t>
         </is>
       </c>
       <c r="B725" t="n">
-        <v>-3.12384166666666</v>
+        <v>-3.12355416666666</v>
       </c>
       <c r="C725" t="n">
-        <v>-41.7646805555556</v>
+        <v>-41.7649763888889</v>
       </c>
       <c r="D725" t="n">
         <v>77</v>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>[-41.7646805555556, -3.123841666666665]</t>
+          <t>[-41.7649763888889, -3.123554166666665]</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>[(-3.123841666666665, -41.7646805555556), (-3.123841666666665, -41.764508271758025)]</t>
+          <t>[(-3.123554166666665, -41.7649763888889), (-3.123554166666665, -41.76457901506719)]</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
         <is>
-          <t>[(-3.123841666666665, -41.7646805555556), (-3.1238326232273845, -41.7646805555556)]</t>
+          <t>[(-3.123554166666665, -41.7649763888889), (-3.1235451231660454, -41.7649763888889)]</t>
         </is>
       </c>
       <c r="H725" t="n">
         <v>1</v>
       </c>
       <c r="I725" t="n">
-        <v>19.1502373674291</v>
+        <v>44.1701726245875</v>
       </c>
       <c r="J725" t="n">
-        <v>-84.89249999959378</v>
+        <v>-52.94204999956953</v>
       </c>
       <c r="K725" t="n">
-        <v>-22.38531516052857</v>
+        <v>-55.26857120931711</v>
       </c>
       <c r="L725" t="inlineStr">
         <is>
-          <t>ef_canaleta3empe</t>
+          <t>ef_canaleta2empe</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>ef_canaleta4deitado</t>
+          <t>ef_canaleta3deitado</t>
         </is>
       </c>
       <c r="B726" t="n">
-        <v>-3.12375416666666</v>
+        <v>-3.12375277777778</v>
       </c>
       <c r="C726" t="n">
-        <v>-41.7645277777777</v>
+        <v>-41.7648611111112</v>
       </c>
       <c r="D726" t="n">
         <v>77</v>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>[-41.764527777777744, -3.1237541666666653]</t>
+          <t>[-41.76486111111115, -3.12375277777778]</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>[(-3.1237541666666653, -41.764527777777744), (-3.1237541666666653, -41.764518781350105)]</t>
+          <t>[(-3.12375277777778, -41.76486111111115), (-3.12375277777778, -41.764852114682384)]</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
         <is>
-          <t>[(-3.1237541666666653, -41.764527777777744), (-3.1233859901537637, -41.764527777777744)]</t>
+          <t>[(-3.12375277777778, -41.76486111111115), (-3.1235184903762816, -41.76486111111115)]</t>
         </is>
       </c>
       <c r="H726" t="n">
-        <v>40.7120650911164</v>
+        <v>25.9069321832122</v>
       </c>
       <c r="I726" t="n">
         <v>1</v>
       </c>
       <c r="J726" t="n">
-        <v>-75.16844999956709</v>
+        <v>-75.01410000056546</v>
       </c>
       <c r="K726" t="n">
-        <v>-5.403351927293047</v>
+        <v>-42.45490806176417</v>
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>ef_canaleta4deitado</t>
+          <t>ef_canaleta3deitado</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>ef_canaleta4empe</t>
+          <t>ef_canaleta3empe</t>
         </is>
       </c>
       <c r="B727" t="n">
-        <v>-3.12358888888889</v>
+        <v>-3.12384166666666</v>
       </c>
       <c r="C727" t="n">
         <v>-41.7646805555556</v>
@@ -35308,305 +35308,305 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>[-41.7646805555556, -3.1235888888888903]</t>
+          <t>[-41.7646805555556, -3.123841666666665]</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7646805555556), (-3.1235888888888903, -41.764508271799244)]</t>
+          <t>[(-3.123841666666665, -41.7646805555556), (-3.123841666666665, -41.764508271758025)]</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7646805555556), (-3.1235798454495662, -41.7646805555556)]</t>
+          <t>[(-3.123841666666665, -41.7646805555556), (-3.1238326232273845, -41.7646805555556)]</t>
         </is>
       </c>
       <c r="H727" t="n">
         <v>1</v>
       </c>
       <c r="I727" t="n">
-        <v>19.1502373662933</v>
+        <v>19.1502373674291</v>
       </c>
       <c r="J727" t="n">
-        <v>-56.80080000042147</v>
+        <v>-84.89249999959378</v>
       </c>
       <c r="K727" t="n">
         <v>-22.38531516052857</v>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>ef_canaleta4empe</t>
+          <t>ef_canaleta3empe</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>ef_canaleta5deitado</t>
+          <t>ef_canaleta4deitado</t>
         </is>
       </c>
       <c r="B728" t="n">
-        <v>-3.12375555555555</v>
+        <v>-3.12375416666666</v>
       </c>
       <c r="C728" t="n">
-        <v>-41.7641722222222</v>
+        <v>-41.7645277777777</v>
       </c>
       <c r="D728" t="n">
         <v>77</v>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>[-41.7641722222222, -3.12375555555555]</t>
+          <t>[-41.764527777777744, -3.1237541666666653]</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>[(-3.12375555555555, -41.7641722222222), (-3.12375555555555, -41.76416322579374)]</t>
+          <t>[(-3.1237541666666653, -41.764527777777744), (-3.1237541666666653, -41.764518781350105)]</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>[(-3.12375555555555, -41.7641722222222), (-3.1234822202544312, -41.7641722222222)]</t>
+          <t>[(-3.1237541666666653, -41.764527777777744), (-3.1233859901537637, -41.764527777777744)]</t>
         </is>
       </c>
       <c r="H728" t="n">
-        <v>30.2247541350932</v>
+        <v>40.7120650911164</v>
       </c>
       <c r="I728" t="n">
         <v>1</v>
       </c>
       <c r="J728" t="n">
-        <v>-75.32279999970382</v>
+        <v>-75.16844999956709</v>
       </c>
       <c r="K728" t="n">
-        <v>34.11830792357066</v>
+        <v>-5.403351927293047</v>
       </c>
       <c r="L728" t="inlineStr">
         <is>
-          <t>ef_canaleta5deitado</t>
+          <t>ef_canaleta4deitado</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>ef_canaleta5empe</t>
+          <t>ef_canaleta4empe</t>
         </is>
       </c>
       <c r="B729" t="n">
-        <v>-3.12384027777777</v>
+        <v>-3.12358888888889</v>
       </c>
       <c r="C729" t="n">
-        <v>-41.7643708333333</v>
+        <v>-41.7646805555556</v>
       </c>
       <c r="D729" t="n">
         <v>77</v>
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>[-41.764370833333345, -3.123840277777775]</t>
+          <t>[-41.7646805555556, -3.1235888888888903]</t>
         </is>
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>[(-3.123840277777775, -41.764370833333345), (-3.123840277777775, -41.76420130559928)]</t>
+          <t>[(-3.1235888888888903, -41.7646805555556), (-3.1235888888888903, -41.764508271799244)]</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
         <is>
-          <t>[(-3.123840277777775, -41.764370833333345), (-3.1238312343389447, -41.764370833333345)]</t>
+          <t>[(-3.1235888888888903, -41.7646805555556), (-3.1235798454495662, -41.7646805555556)]</t>
         </is>
       </c>
       <c r="H729" t="n">
         <v>1</v>
       </c>
       <c r="I729" t="n">
-        <v>18.8438866439532</v>
+        <v>19.1502373662933</v>
       </c>
       <c r="J729" t="n">
-        <v>-84.73814999945705</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K729" t="n">
-        <v>12.04175573884584</v>
+        <v>-22.38531516052857</v>
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>ef_canaleta5empe</t>
+          <t>ef_canaleta4empe</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>ef_canaleta6deitado</t>
+          <t>ef_canaleta5deitado</t>
         </is>
       </c>
       <c r="B730" t="n">
-        <v>-3.12375694444444</v>
+        <v>-3.12375555555555</v>
       </c>
       <c r="C730" t="n">
-        <v>-41.7637680555555</v>
+        <v>-41.7641722222222</v>
       </c>
       <c r="D730" t="n">
         <v>77</v>
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>[-41.763768055555545, -3.12375694444444]</t>
+          <t>[-41.7641722222222, -3.12375555555555]</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>[(-3.12375694444444, -41.763768055555545), (-3.12375694444444, -41.76375905912862)]</t>
+          <t>[(-3.12375555555555, -41.7641722222222), (-3.12375555555555, -41.76416322579374)]</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
         <is>
-          <t>[(-3.12375694444444, -41.763768055555545), (-3.1233023067400016, -41.763768055555545)]</t>
+          <t>[(-3.12375555555555, -41.7641722222222), (-3.1234822202544312, -41.7641722222222)]</t>
         </is>
       </c>
       <c r="H730" t="n">
-        <v>50.2727337391089</v>
+        <v>30.2247541350932</v>
       </c>
       <c r="I730" t="n">
         <v>1</v>
       </c>
       <c r="J730" t="n">
-        <v>-75.47714999984055</v>
+        <v>-75.32279999970382</v>
       </c>
       <c r="K730" t="n">
-        <v>79.04331971752346</v>
+        <v>34.11830792357066</v>
       </c>
       <c r="L730" t="inlineStr">
         <is>
-          <t>ef_canaleta6deitado</t>
+          <t>ef_canaleta5deitado</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>ef_canaleta6empe</t>
+          <t>ef_canaleta5empe</t>
         </is>
       </c>
       <c r="B731" t="n">
-        <v>-3.12358888888889</v>
+        <v>-3.12384027777777</v>
       </c>
       <c r="C731" t="n">
-        <v>-41.7643694444445</v>
+        <v>-41.7643708333333</v>
       </c>
       <c r="D731" t="n">
         <v>77</v>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>[-41.7643694444445, -3.1235888888888903]</t>
+          <t>[-41.764370833333345, -3.123840277777775]</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7643694444445), (-3.1235888888888903, -41.76419716068814)]</t>
+          <t>[(-3.123840277777775, -41.764370833333345), (-3.123840277777775, -41.76420130559928)]</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7643694444445), (-3.1235798454495662, -41.7643694444445)]</t>
+          <t>[(-3.123840277777775, -41.764370833333345), (-3.1238312343389447, -41.764370833333345)]</t>
         </is>
       </c>
       <c r="H731" t="n">
         <v>1</v>
       </c>
       <c r="I731" t="n">
-        <v>19.1502373662933</v>
+        <v>18.8438866439532</v>
       </c>
       <c r="J731" t="n">
-        <v>-56.80080000042147</v>
+        <v>-84.73814999945705</v>
       </c>
       <c r="K731" t="n">
-        <v>12.19613721332108</v>
+        <v>12.04175573884584</v>
       </c>
       <c r="L731" t="inlineStr">
         <is>
-          <t>ef_canaleta6empe</t>
+          <t>ef_canaleta5empe</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>ef_canaleta7empe</t>
+          <t>ef_canaleta6deitado</t>
         </is>
       </c>
       <c r="B732" t="n">
-        <v>-3.12384027777777</v>
+        <v>-3.12375694444444</v>
       </c>
       <c r="C732" t="n">
-        <v>-41.7639805555556</v>
+        <v>-41.7637680555555</v>
       </c>
       <c r="D732" t="n">
         <v>77</v>
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>[-41.7639805555556, -3.123840277777775]</t>
+          <t>[-41.763768055555545, -3.12375694444444]</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>[(-3.123840277777775, -41.7639805555556), (-3.123840277777775, -41.763816608071025)]</t>
+          <t>[(-3.12375694444444, -41.763768055555545), (-3.12375694444444, -41.76375905912862)]</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>[(-3.123840277777775, -41.7639805555556), (-3.1238312343398342, -41.7639805555556)]</t>
+          <t>[(-3.12375694444444, -41.763768055555545), (-3.1233023067400016, -41.763768055555545)]</t>
         </is>
       </c>
       <c r="H732" t="n">
-        <v>1</v>
+        <v>50.2727337391089</v>
       </c>
       <c r="I732" t="n">
-        <v>18.2236129780023</v>
+        <v>1</v>
       </c>
       <c r="J732" t="n">
-        <v>-84.73814999945705</v>
+        <v>-75.47714999984055</v>
       </c>
       <c r="K732" t="n">
-        <v>55.42295268300256</v>
+        <v>79.04331971752346</v>
       </c>
       <c r="L732" t="inlineStr">
         <is>
-          <t>ef_canaleta7empe</t>
+          <t>ef_canaleta6deitado</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>ef_canaleta8empe</t>
+          <t>ef_canaleta6empe</t>
         </is>
       </c>
       <c r="B733" t="n">
         <v>-3.12358888888889</v>
       </c>
       <c r="C733" t="n">
-        <v>-41.7639916666667</v>
+        <v>-41.7643694444445</v>
       </c>
       <c r="D733" t="n">
         <v>77</v>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>[-41.7639916666667, -3.1235888888888903]</t>
+          <t>[-41.7643694444445, -3.1235888888888903]</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7639916666667), (-3.1235888888888903, -41.76381938291034)]</t>
+          <t>[(-3.1235888888888903, -41.7643694444445), (-3.1235888888888903, -41.76419716068814)]</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>[(-3.1235888888888903, -41.7639916666667), (-3.1235798454495662, -41.7639916666667)]</t>
+          <t>[(-3.1235888888888903, -41.7643694444445), (-3.1235798454495662, -41.7643694444445)]</t>
         </is>
       </c>
       <c r="H733" t="n">
@@ -35619,345 +35619,441 @@
         <v>-56.80080000042147</v>
       </c>
       <c r="K733" t="n">
-        <v>54.18790081374905</v>
+        <v>12.19613721332108</v>
       </c>
       <c r="L733" t="inlineStr">
         <is>
-          <t>ef_canaleta8empe</t>
+          <t>ef_canaleta6empe</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>ef_canaleta9empe</t>
+          <t>ef_canaleta7empe</t>
         </is>
       </c>
       <c r="B734" t="n">
-        <v>-3.12353055555555</v>
+        <v>-3.12384027777777</v>
       </c>
       <c r="C734" t="n">
-        <v>-41.7633069444444</v>
+        <v>-41.7639805555556</v>
       </c>
       <c r="D734" t="n">
         <v>77</v>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>[-41.763306944444395, -3.123530555555555]</t>
+          <t>[-41.7639805555556, -3.123840277777775]</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>[(-3.123530555555555, -41.763306944444395), (-3.123530555555555, -41.762973480487496)]</t>
+          <t>[(-3.123840277777775, -41.7639805555556), (-3.123840277777775, -41.763816608071025)]</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>[(-3.123530555555555, -41.763306944444395), (-3.123521512077257, -41.763306944444395)]</t>
+          <t>[(-3.123840277777775, -41.7639805555556), (-3.1238312343398342, -41.7639805555556)]</t>
         </is>
       </c>
       <c r="H734" t="n">
         <v>1</v>
       </c>
       <c r="I734" t="n">
-        <v>37.0662586828766</v>
+        <v>18.2236129780023</v>
       </c>
       <c r="J734" t="n">
-        <v>-50.31809999971274</v>
+        <v>-84.73814999945705</v>
       </c>
       <c r="K734" t="n">
-        <v>130.2979723432763</v>
+        <v>55.42295268300256</v>
       </c>
       <c r="L734" t="inlineStr">
         <is>
-          <t>ef_canaleta9empe</t>
+          <t>ef_canaleta7empe</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>ef_talude1deitado</t>
+          <t>ef_canaleta8empe</t>
         </is>
       </c>
       <c r="B735" t="n">
-        <v>-3.12343055555556</v>
+        <v>-3.12358888888889</v>
       </c>
       <c r="C735" t="n">
-        <v>-41.7645638888889</v>
+        <v>-41.7639916666667</v>
       </c>
       <c r="D735" t="n">
         <v>77</v>
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>[-41.7645638888889, -3.12343055555556]</t>
+          <t>[-41.7639916666667, -3.1235888888888903]</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>[(-3.12343055555556, -41.7645638888889), (-3.12343055555556, -41.76455489247754)]</t>
+          <t>[(-3.1235888888888903, -41.7639916666667), (-3.1235888888888903, -41.76381938291034)]</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>[(-3.12343055555556, -41.7645638888889), (-3.1214725816264917, -41.7645638888889)]</t>
+          <t>[(-3.1235888888888903, -41.7639916666667), (-3.1235798454495662, -41.7639916666667)]</t>
         </is>
       </c>
       <c r="H735" t="n">
-        <v>216.507999723855</v>
+        <v>1</v>
       </c>
       <c r="I735" t="n">
-        <v>1</v>
+        <v>19.1502373662933</v>
       </c>
       <c r="J735" t="n">
-        <v>-39.2049000008244</v>
+        <v>-56.80080000042147</v>
       </c>
       <c r="K735" t="n">
-        <v>-9.417270516385944</v>
+        <v>54.18790081374905</v>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>ef_talude1deitado</t>
+          <t>ef_canaleta8empe</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>ef_talude1empe</t>
+          <t>ef_canaleta9empe</t>
         </is>
       </c>
       <c r="B736" t="n">
-        <v>-3.12373472222222</v>
+        <v>-3.12353055555555</v>
       </c>
       <c r="C736" t="n">
-        <v>-41.7651069444444</v>
+        <v>-41.7633069444444</v>
       </c>
       <c r="D736" t="n">
         <v>77</v>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>[-41.765106944444454, -3.123734722222225]</t>
+          <t>[-41.763306944444395, -3.123530555555555]</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>[(-3.123734722222225, -41.765106944444454), (-3.123734722222225, -41.76451505979305)]</t>
+          <t>[(-3.123530555555555, -41.763306944444395), (-3.123530555555555, -41.762973480487496)]</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
         <is>
-          <t>[(-3.123734722222225, -41.765106944444454), (-3.1237256786296523, -41.765106944444454)]</t>
+          <t>[(-3.123530555555555, -41.763306944444395), (-3.123521512077257, -41.763306944444395)]</t>
         </is>
       </c>
       <c r="H736" t="n">
         <v>1</v>
       </c>
       <c r="I736" t="n">
-        <v>65.79105449957601</v>
+        <v>37.0662586828766</v>
       </c>
       <c r="J736" t="n">
-        <v>-73.00755000007113</v>
+        <v>-50.31809999971274</v>
       </c>
       <c r="K736" t="n">
-        <v>-69.78043068193116</v>
+        <v>130.2979723432763</v>
       </c>
       <c r="L736" t="inlineStr">
         <is>
-          <t>ef_talude1empe</t>
+          <t>ef_canaleta9empe</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>ef_talude2deitado</t>
+          <t>ef_talude1deitado</t>
         </is>
       </c>
       <c r="B737" t="n">
-        <v>-3.12336527777778</v>
+        <v>-3.12343055555556</v>
       </c>
       <c r="C737" t="n">
-        <v>-41.7634902777778</v>
+        <v>-41.7645638888889</v>
       </c>
       <c r="D737" t="n">
         <v>77</v>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>[-41.7634902777778, -3.12336527777778]</t>
+          <t>[-41.7645638888889, -3.12343055555556]</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>[(-3.12336527777778, -41.7634902777778), (-3.12336527777778, -41.76348128135183)]</t>
+          <t>[(-3.12343055555556, -41.7645638888889), (-3.12343055555556, -41.76455489247754)]</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
         <is>
-          <t>[(-3.12336527777778, -41.7634902777778), (-3.123189539960055, -41.7634902777778)]</t>
+          <t>[(-3.12343055555556, -41.7645638888889), (-3.1214725816264917, -41.7645638888889)]</t>
         </is>
       </c>
       <c r="H737" t="n">
-        <v>19.4326611903087</v>
+        <v>216.507999723855</v>
       </c>
       <c r="I737" t="n">
         <v>1</v>
       </c>
       <c r="J737" t="n">
-        <v>-31.95045000056712</v>
+        <v>-39.2049000008244</v>
       </c>
       <c r="K737" t="n">
-        <v>109.9196164725553</v>
+        <v>-9.417270516385944</v>
       </c>
       <c r="L737" t="inlineStr">
         <is>
-          <t>ef_talude2deitado</t>
+          <t>ef_talude1deitado</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>ef_talude2empe</t>
+          <t>ef_talude1empe</t>
         </is>
       </c>
       <c r="B738" t="n">
-        <v>-3.12339861111111</v>
+        <v>-3.12373472222222</v>
       </c>
       <c r="C738" t="n">
-        <v>-41.7635833333334</v>
+        <v>-41.7651069444444</v>
       </c>
       <c r="D738" t="n">
         <v>77</v>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>[-41.76358333333335, -3.1233986111111154]</t>
+          <t>[-41.765106944444454, -3.123734722222225]</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>[(-3.1233986111111154, -41.76358333333335), (-3.1233986111111154, -41.76351918116635)]</t>
+          <t>[(-3.123734722222225, -41.765106944444454), (-3.123734722222225, -41.76451505979305)]</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
         <is>
-          <t>[(-3.1233986111111154, -41.76358333333335), (-3.123389567683979, -41.76358333333335)]</t>
+          <t>[(-3.123734722222225, -41.765106944444454), (-3.1237256786296523, -41.765106944444454)]</t>
         </is>
       </c>
       <c r="H738" t="n">
         <v>1</v>
       </c>
       <c r="I738" t="n">
-        <v>7.13084897104345</v>
+        <v>65.79105449957601</v>
       </c>
       <c r="J738" t="n">
-        <v>-35.65485000019657</v>
+        <v>-73.00755000007113</v>
       </c>
       <c r="K738" t="n">
-        <v>99.57605705166242</v>
+        <v>-69.78043068193116</v>
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t>ef_talude2empe</t>
+          <t>ef_talude1empe</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>ef_talude3deitado</t>
+          <t>ef_talude2deitado</t>
         </is>
       </c>
       <c r="B739" t="n">
-        <v>-3.12332083333333</v>
+        <v>-3.12336527777778</v>
       </c>
       <c r="C739" t="n">
-        <v>-41.7634972222223</v>
+        <v>-41.7634902777778</v>
       </c>
       <c r="D739" t="n">
         <v>77</v>
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>[-41.76349722222225, -3.12332083333333]</t>
+          <t>[-41.7634902777778, -3.12336527777778]</t>
         </is>
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>[(-3.12332083333333, -41.76349722222225), (-3.12332083333333, -41.76348822579678)]</t>
+          <t>[(-3.12336527777778, -41.7634902777778), (-3.12336527777778, -41.76348128135183)]</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
         <is>
-          <t>[(-3.12332083333333, -41.76349722222225), (-3.1231311514556834, -41.76349722222225)]</t>
+          <t>[(-3.12336527777778, -41.7634902777778), (-3.123189539960055, -41.7634902777778)]</t>
         </is>
       </c>
       <c r="H739" t="n">
-        <v>20.9745614598014</v>
+        <v>19.4326611903087</v>
       </c>
       <c r="I739" t="n">
         <v>1</v>
       </c>
       <c r="J739" t="n">
-        <v>-27.01124999994253</v>
+        <v>-31.95045000056712</v>
       </c>
       <c r="K739" t="n">
-        <v>109.1477090472624</v>
+        <v>109.9196164725553</v>
       </c>
       <c r="L739" t="inlineStr">
         <is>
-          <t>ef_talude3deitado</t>
+          <t>ef_talude2deitado</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
+          <t>ef_talude2empe</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-3.12339861111111</v>
+      </c>
+      <c r="C740" t="n">
+        <v>-41.7635833333334</v>
+      </c>
+      <c r="D740" t="n">
+        <v>77</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>[-41.76358333333335, -3.1233986111111154]</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>[(-3.1233986111111154, -41.76358333333335), (-3.1233986111111154, -41.76351918116635)]</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>[(-3.1233986111111154, -41.76358333333335), (-3.123389567683979, -41.76358333333335)]</t>
+        </is>
+      </c>
+      <c r="H740" t="n">
+        <v>1</v>
+      </c>
+      <c r="I740" t="n">
+        <v>7.13084897104345</v>
+      </c>
+      <c r="J740" t="n">
+        <v>-35.65485000019657</v>
+      </c>
+      <c r="K740" t="n">
+        <v>99.57605705166242</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>ef_talude2empe</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>ef_talude3deitado</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-3.12332083333333</v>
+      </c>
+      <c r="C741" t="n">
+        <v>-41.7634972222223</v>
+      </c>
+      <c r="D741" t="n">
+        <v>77</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>[-41.76349722222225, -3.12332083333333]</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>[(-3.12332083333333, -41.76349722222225), (-3.12332083333333, -41.76348822579678)]</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>[(-3.12332083333333, -41.76349722222225), (-3.1231311514556834, -41.76349722222225)]</t>
+        </is>
+      </c>
+      <c r="H741" t="n">
+        <v>20.9745614598014</v>
+      </c>
+      <c r="I741" t="n">
+        <v>1</v>
+      </c>
+      <c r="J741" t="n">
+        <v>-27.01124999994253</v>
+      </c>
+      <c r="K741" t="n">
+        <v>109.1477090472624</v>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>ef_talude3deitado</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
           <t>ef_talude4deitado</t>
         </is>
       </c>
-      <c r="B740" t="n">
+      <c r="B742" t="n">
         <v>-3.12403333333333</v>
       </c>
-      <c r="C740" t="n">
+      <c r="C742" t="n">
         <v>-41.7651236111111</v>
       </c>
-      <c r="D740" t="n">
-        <v>77</v>
-      </c>
-      <c r="E740" t="inlineStr">
+      <c r="D742" t="n">
+        <v>77</v>
+      </c>
+      <c r="E742" t="inlineStr">
         <is>
           <t>[-41.7651236111111, -3.12403333333333]</t>
         </is>
       </c>
-      <c r="F740" t="inlineStr">
+      <c r="F742" t="inlineStr">
         <is>
           <t>[(-3.12403333333333, -41.7651236111111), (-3.12403333333333, -41.76511461467821)]</t>
         </is>
       </c>
-      <c r="G740" t="inlineStr">
+      <c r="G742" t="inlineStr">
         <is>
           <t>[(-3.12403333333333, -41.7651236111111), (-3.1240026528486196, -41.7651236111111)]</t>
         </is>
       </c>
-      <c r="H740" t="n">
+      <c r="H742" t="n">
         <v>3.39257355102461</v>
       </c>
-      <c r="I740" t="n">
-        <v>1</v>
-      </c>
-      <c r="J740" t="n">
+      <c r="I742" t="n">
+        <v>1</v>
+      </c>
+      <c r="J742" t="n">
         <v>-106.1927999999554</v>
       </c>
-      <c r="K740" t="n">
+      <c r="K742" t="n">
         <v>-71.63300849173496</v>
       </c>
-      <c r="L740" t="inlineStr">
+      <c r="L742" t="inlineStr">
         <is>
           <t>ef_talude4deitado</t>
         </is>
